--- a/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
@@ -1,216 +1,666 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\바탕화면\Project\JewelThief\JewelThief\JsonConverter\ExcelFiles\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F35BDE27-445C-46A5-9498-AED0753ECF37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="528" yWindow="924" windowWidth="28080" windowHeight="14628" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="14592" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="89">
+  <si>
+    <t>미리 로드할 어드레서블 테이블</t>
+  </si>
+  <si>
+    <t>어드레서블 주소</t>
+  </si>
   <si>
     <t>string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>Address</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>어드레서블 주소</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>미리 로드할 어드레서블 테이블</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PreLoadAsset_Stage1_SOTilePreset</t>
+  </si>
+  <si>
+    <t>SOTilePreset</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Stage1_MapGrid</t>
   </si>
   <si>
     <t>MapGrid</t>
   </si>
   <si>
-    <t>SOTilePreset</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <t>PreLoadAsset_Stage1_BoundaryTile</t>
+  </si>
+  <si>
+    <t>BoundaryTile</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Stage1_BackUpTile</t>
+  </si>
+  <si>
+    <t>BackUpTile</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Stage1_TestPresetTile</t>
   </si>
   <si>
     <t>TestPresetTile</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BoundaryTile</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>BackUpTile</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PreLoadAsset_Stage1_Vertical Corridor</t>
   </si>
   <si>
     <t>Vertical Corridor</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PreLoadAsset_Stage1_Room1</t>
   </si>
   <si>
     <t>Room1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PreLoadAsset_Stage1_RightTop Corridor</t>
   </si>
   <si>
     <t>RightTop Corridor</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PreLoadAsset_Stage1_RightDown Corridor</t>
   </si>
   <si>
     <t>RightDown Corridor</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PreLoadAsset_Stage1_LeftTop Corridor</t>
   </si>
   <si>
     <t>LeftTop Corridor</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PreLoadAsset_Stage1_LeftDown Corridor</t>
   </si>
   <si>
     <t>LeftDown Corridor</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PreLoadAsset_Stage1_Horizontal Corridor</t>
   </si>
   <si>
     <t>Horizontal Corridor</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PreLoadAsset_Stage1_Demo Room4</t>
   </si>
   <si>
     <t>Demo Room4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PreLoadAsset_Stage1_Demo Room3</t>
   </si>
   <si>
     <t>Demo Room3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PreLoadAsset_Stage1_Demo Room2</t>
   </si>
   <si>
     <t>Demo Room2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PreLoadAsset_Stage1_Demo Room1</t>
   </si>
   <si>
     <t>Demo Room1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PreLoadAsset_Stage1_All Direction Corridor</t>
   </si>
   <si>
     <t>All Direction Corridor</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PreLoadAsset_Stage1_SOTilePreset</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PreLoadAsset_Stage1_MapGrid</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PreLoadAsset_Stage1_BoundaryTile</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PreLoadAsset_Stage1_BackUpTile</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PreLoadAsset_Stage1_TestPresetTile</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PreLoadAsset_Stage1_Vertical Corridor</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PreLoadAsset_Stage1_Room1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PreLoadAsset_Stage1_RightTop Corridor</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PreLoadAsset_Stage1_RightDown Corridor</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PreLoadAsset_Stage1_LeftTop Corridor</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PreLoadAsset_Stage1_LeftDown Corridor</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PreLoadAsset_Stage1_Horizontal Corridor</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PreLoadAsset_Stage1_Demo Room4</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PreLoadAsset_Stage1_Demo Room3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PreLoadAsset_Stage1_Demo Room2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PreLoadAsset_Stage1_Demo Room1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PreLoadAsset_Stage1_All Direction Corridor</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PreLoadAsset_Player_With_Camera</t>
+  </si>
+  <si>
+    <t>Player</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_BGM_01</t>
+  </si>
+  <si>
+    <t>PlayTheme</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_001</t>
+  </si>
+  <si>
+    <t>AlertUp_01</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_002</t>
+  </si>
+  <si>
+    <t>Click_01</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_003</t>
+  </si>
+  <si>
+    <t>Click_02</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_004</t>
+  </si>
+  <si>
+    <t>Error_01</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_005</t>
+  </si>
+  <si>
+    <t>Error_02</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_006</t>
+  </si>
+  <si>
+    <t>Explosion_01</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_007</t>
+  </si>
+  <si>
+    <t>Explosion_02</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_008</t>
+  </si>
+  <si>
+    <t>Explosion_03</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_009</t>
+  </si>
+  <si>
+    <t>Explosion_04</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_010</t>
+  </si>
+  <si>
+    <t>Explosion_05</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_011</t>
+  </si>
+  <si>
+    <t>Gain_01</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_012</t>
+  </si>
+  <si>
+    <t>GunTrap_01</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_013</t>
+  </si>
+  <si>
+    <t>Lose_01</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_014</t>
+  </si>
+  <si>
+    <t>Lose_02</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_015</t>
+  </si>
+  <si>
+    <t>Notification_01</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_016</t>
+  </si>
+  <si>
+    <t>Notification_02</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_017</t>
+  </si>
+  <si>
+    <t>Open_Box_01</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_018</t>
+  </si>
+  <si>
+    <t>Purchase_01</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_019</t>
+  </si>
+  <si>
+    <t>Purchase_02</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_020</t>
+  </si>
+  <si>
+    <t>TimeUp_01</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_021</t>
+  </si>
+  <si>
+    <t>Win_01</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_022</t>
+  </si>
+  <si>
+    <t>Win_02</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_023</t>
+  </si>
+  <si>
+    <t>Win_03</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -218,24 +668,311 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -284,7 +1021,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
@@ -319,7 +1056,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
@@ -493,187 +1230,382 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:B45"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="39" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.69921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39" customWidth="1"/>
+    <col min="2" max="2" width="19.2037037037037" customWidth="1"/>
+    <col min="3" max="3" width="13.7037037037037" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="B1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
         <v>23</v>
       </c>
-      <c r="B5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
+      <c r="B13" t="s">
         <v>24</v>
       </c>
-      <c r="B6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
         <v>25</v>
       </c>
-      <c r="B7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
+      <c r="B14" t="s">
         <v>26</v>
       </c>
-      <c r="B8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
         <v>27</v>
       </c>
-      <c r="B9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A10" t="s">
+      <c r="B15" t="s">
         <v>28</v>
       </c>
-      <c r="B10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
         <v>29</v>
       </c>
-      <c r="B11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
+      <c r="B16" t="s">
         <v>30</v>
       </c>
-      <c r="B12" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A13" t="s">
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
         <v>31</v>
       </c>
-      <c r="B13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A14" t="s">
+      <c r="B17" t="s">
         <v>32</v>
       </c>
-      <c r="B14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A15" t="s">
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" t="s">
         <v>33</v>
       </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A16" t="s">
+      <c r="B18" t="s">
         <v>34</v>
       </c>
-      <c r="B16" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A17" t="s">
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" t="s">
         <v>35</v>
       </c>
-      <c r="B17" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A18" t="s">
+      <c r="B19" t="s">
         <v>36</v>
       </c>
-      <c r="B18" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A19" t="s">
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
         <v>37</v>
       </c>
-      <c r="B19" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A20" t="s">
+      <c r="B20" t="s">
         <v>38</v>
       </c>
-      <c r="B20" t="s">
-        <v>21</v>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" t="s">
+        <v>47</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" t="s">
+        <v>49</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>57</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>59</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>63</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>67</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>69</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>71</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>73</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>75</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>77</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>79</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>81</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>83</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" t="s">
+        <v>85</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" t="s">
+        <v>87</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="91">
   <si>
     <t>미리 로드할 어드레서블 테이블</t>
   </si>
@@ -144,6 +144,12 @@
   </si>
   <si>
     <t>All Direction Corridor</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Lobby</t>
+  </si>
+  <si>
+    <t>Lobby</t>
   </si>
   <si>
     <t>PreLoadAsset_Player_With_Camera</t>
@@ -1236,7 +1242,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="39" customWidth="1"/>
@@ -1416,7 +1422,7 @@
       <c r="A22" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1602,6 +1608,14 @@
       </c>
       <c r="B45" s="1" t="s">
         <v>88</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s">
+        <v>89</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\바탕화면\Project\JewelThief\JewelThief\JsonConverter\ExcelFiles\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA88FC12-3AD1-4DF3-A9D3-5726EAC8908C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="14592" windowHeight="9000"/>
+    <workbookView xWindow="-30396" yWindow="576" windowWidth="28080" windowHeight="14628" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="125">
   <si>
     <t>미리 로드할 어드레서블 테이블</t>
   </si>
@@ -300,179 +306,183 @@
   </si>
   <si>
     <t>Win_03</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_Black</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Black</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_Yellow</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Yellow</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_KeyMesh[SM_Gen_Prop_Key_01]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AssetType</t>
+  </si>
+  <si>
+    <t>에셋 타입</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mesh</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>M_Gemstone_Ruby</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_M_Gemstone_Diamond,Lit</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>M_Gemstone_Amethyst</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_M_Gemstone_Amethyst</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>M_Gemstone_Aquamarine</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_M_Gemstone_Aquamarine</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>M_Gemstone_Emerald</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_M_Gemstone_Emerald</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_M_Gemstone_Ruby</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>M_Gemstone_Sapphire</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_M_Gemstone_Sapphire</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>M_Gemstone_Topaz</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_M_Gemstone_Topaz</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ToolObject</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>JewelObject</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PreLoadAsset_GameObject_ToolObject</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PreLoadAsset_GameObject_JewelObject</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jewel_Cone[Cone]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_Jewel_Cone[Cone]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PreLoadAsset_FBX_KeyFBX</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>KeyFBX</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>KeyFBX[SM_Gen_Prop_Key_01]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>M_Gemstone_Diamond</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lit</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_Lit</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="21">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -481,192 +491,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -676,309 +506,40 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1236,45 +797,54 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:B46"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C61"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="39" customWidth="1"/>
-    <col min="2" max="2" width="19.2037037037037" customWidth="1"/>
-    <col min="3" max="3" width="13.7037037037037" customWidth="1"/>
+    <col min="1" max="1" width="52.19921875" customWidth="1"/>
+    <col min="2" max="2" width="35.19921875" customWidth="1"/>
+    <col min="3" max="3" width="31.3984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="C1" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
+      <c r="C2" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
+      <c r="C3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -1282,7 +852,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -1290,7 +860,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -1298,7 +868,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1306,7 +876,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>13</v>
       </c>
@@ -1314,7 +884,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -1322,7 +892,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -1330,7 +900,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1338,7 +908,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -1346,7 +916,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>23</v>
       </c>
@@ -1354,7 +924,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -1362,7 +932,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>27</v>
       </c>
@@ -1370,7 +940,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -1378,7 +948,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>31</v>
       </c>
@@ -1386,7 +956,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -1394,7 +964,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>35</v>
       </c>
@@ -1402,7 +972,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>37</v>
       </c>
@@ -1410,7 +980,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>39</v>
       </c>
@@ -1418,7 +988,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>41</v>
       </c>
@@ -1426,7 +996,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>43</v>
       </c>
@@ -1434,7 +1004,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>45</v>
       </c>
@@ -1442,7 +1012,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>47</v>
       </c>
@@ -1450,7 +1020,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>49</v>
       </c>
@@ -1458,7 +1028,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>51</v>
       </c>
@@ -1466,7 +1036,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
         <v>53</v>
       </c>
@@ -1474,7 +1044,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
         <v>55</v>
       </c>
@@ -1482,7 +1052,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
         <v>57</v>
       </c>
@@ -1490,7 +1060,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
         <v>59</v>
       </c>
@@ -1498,7 +1068,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
         <v>61</v>
       </c>
@@ -1506,7 +1076,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
         <v>63</v>
       </c>
@@ -1514,7 +1084,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
         <v>65</v>
       </c>
@@ -1522,7 +1092,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
         <v>67</v>
       </c>
@@ -1530,7 +1100,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
         <v>69</v>
       </c>
@@ -1538,7 +1108,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
         <v>71</v>
       </c>
@@ -1546,7 +1116,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
         <v>73</v>
       </c>
@@ -1554,7 +1124,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
         <v>75</v>
       </c>
@@ -1562,7 +1132,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
         <v>77</v>
       </c>
@@ -1570,7 +1140,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
         <v>79</v>
       </c>
@@ -1578,7 +1148,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
         <v>81</v>
       </c>
@@ -1586,7 +1156,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
         <v>83</v>
       </c>
@@ -1594,7 +1164,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
         <v>85</v>
       </c>
@@ -1602,7 +1172,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
         <v>87</v>
       </c>
@@ -1610,7 +1180,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
         <v>89</v>
       </c>
@@ -1618,8 +1188,134 @@
         <v>90</v>
       </c>
     </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A47" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="A48" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A49" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B49" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A50" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A51" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A52" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A53" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A54" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A55" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A56" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A57" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A58" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A59" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A60" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A61" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B61" t="s">
+        <v>123</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\바탕화면\Project\JewelThief\JewelThief\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA88FC12-3AD1-4DF3-A9D3-5726EAC8908C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD72A944-AC89-41CE-B458-6ADFE4FBAD35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30396" yWindow="576" windowWidth="28080" windowHeight="14628" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1296" yWindow="1548" windowWidth="28080" windowHeight="14628" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -394,14 +394,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>ToolObject</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>JewelObject</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>PreLoadAsset_GameObject_ToolObject</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -438,6 +430,14 @@
   </si>
   <si>
     <t>PreLoadAsset_Material_Lit</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pool_Jewel</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pool_Tool</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.4">
       <c r="A47" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.4">
@@ -1217,7 +1217,7 @@
         <v>95</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>99</v>
@@ -1228,7 +1228,7 @@
         <v>101</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.4">
@@ -1281,26 +1281,26 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A58" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A59" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A60" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>99</v>
@@ -1308,10 +1308,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A61" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B61" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\바탕화면\Project\JewelThief\JewelThief\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\팀과제\JewelThief\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA88FC12-3AD1-4DF3-A9D3-5726EAC8908C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8D04003-F4E1-4C52-9FE0-6C3618EC1FAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30396" yWindow="576" windowWidth="28080" windowHeight="14628" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5232" yWindow="1452" windowWidth="16824" windowHeight="9048" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,8 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -33,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="127">
   <si>
     <t>미리 로드할 어드레서블 테이블</t>
   </si>
@@ -434,10 +432,19 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>PreLoadAsset_Material_Lit</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PreLoadAsset_JewelInventory</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>JewelInventory</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>Lit</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_Material_Lit</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -523,11 +530,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -803,7 +812,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="52.19921875" customWidth="1"/>
@@ -1308,14 +1317,23 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A61" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A62" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="B61" t="s">
-        <v>123</v>
+      <c r="B62" s="5" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
@@ -1,39 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\바탕화면\Project\JewelThief\JewelThief\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hdong\OneDrive\바탕 화면\TeamMiniProject\JewelThief\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD72A944-AC89-41CE-B458-6ADFE4FBAD35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{042846D4-E534-4E86-91AA-8000D042F76E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1296" yWindow="1548" windowWidth="28080" windowHeight="14628" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="127">
   <si>
     <t>미리 로드할 어드레서블 테이블</t>
   </si>
@@ -438,6 +425,14 @@
   </si>
   <si>
     <t>Pool_Tool</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>PreLoadAsset_PoliceThrow_Object</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pool_Throw</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -496,7 +491,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -519,15 +514,44 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -803,7 +827,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C61"/>
+  <dimension ref="A1:C62"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="52.19921875" customWidth="1"/>
@@ -1310,8 +1334,16 @@
       <c r="A61" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="5" t="s">
         <v>121</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A62" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
@@ -1,22 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="enqOkH1Z/tfQ3WIfr7wm+HPEzSLVVhkZawHcM088EJg="/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="144">
   <si>
     <t>미리 로드할 어드레서블 테이블</t>
   </si>
@@ -442,46 +453,201 @@
   </si>
   <si>
     <t>Effect_Normal</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_JewelInventory</t>
+  </si>
+  <si>
+    <t>JewelInventory</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Malgun Gothic"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Malgun Gothic"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
-      <color theme="1"/>
-      <name val="Malgun Gothic"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.0"/>
-      <color theme="1"/>
-      <name val="Malgun Gothic"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.0"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -489,9 +655,201 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
-    <border/>
+  <borders count="10">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -505,39 +863,538 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -727,23 +1584,23 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C1000"/>
+  <sheetFormatPr defaultColWidth="14.4259259259259" defaultRowHeight="15" customHeight="1" outlineLevelCol="2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="52.14"/>
-    <col customWidth="1" min="2" max="2" width="35.14"/>
-    <col customWidth="1" min="3" max="3" width="31.43"/>
-    <col customWidth="1" min="4" max="26" width="9.0"/>
+    <col min="1" max="1" width="52.1388888888889" customWidth="1"/>
+    <col min="2" max="2" width="35.1388888888889" customWidth="1"/>
+    <col min="3" max="3" width="31.4259259259259" customWidth="1"/>
+    <col min="4" max="26" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1">
+    <row r="1" ht="17.25" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -754,7 +1611,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="17.25" customHeight="1">
+    <row r="2" ht="17.25" customHeight="1" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -765,7 +1622,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" ht="17.25" customHeight="1">
+    <row r="3" ht="17.25" customHeight="1" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -776,7 +1633,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" ht="17.25" customHeight="1">
+    <row r="4" ht="17.25" customHeight="1" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -784,7 +1641,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" ht="17.25" customHeight="1">
+    <row r="5" ht="17.25" customHeight="1" spans="1:3">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -792,7 +1649,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" ht="17.25" customHeight="1">
+    <row r="6" ht="17.25" customHeight="1" spans="1:3">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -800,7 +1657,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" ht="17.25" customHeight="1">
+    <row r="7" ht="17.25" customHeight="1" spans="1:3">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -808,7 +1665,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" ht="17.25" customHeight="1">
+    <row r="8" ht="17.25" customHeight="1" spans="1:3">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -816,7 +1673,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" ht="17.25" customHeight="1">
+    <row r="9" ht="17.25" customHeight="1" spans="1:3">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -824,7 +1681,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" ht="17.25" customHeight="1">
+    <row r="10" ht="17.25" customHeight="1" spans="1:3">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -832,7 +1689,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" ht="17.25" customHeight="1">
+    <row r="11" ht="17.25" customHeight="1" spans="1:3">
       <c r="A11" s="1" t="s">
         <v>21</v>
       </c>
@@ -840,7 +1697,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" ht="17.25" customHeight="1">
+    <row r="12" ht="17.25" customHeight="1" spans="1:3">
       <c r="A12" s="1" t="s">
         <v>23</v>
       </c>
@@ -848,7 +1705,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" ht="17.25" customHeight="1">
+    <row r="13" ht="17.25" customHeight="1" spans="1:3">
       <c r="A13" s="1" t="s">
         <v>25</v>
       </c>
@@ -856,7 +1713,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" ht="17.25" customHeight="1">
+    <row r="14" ht="17.25" customHeight="1" spans="1:3">
       <c r="A14" s="1" t="s">
         <v>27</v>
       </c>
@@ -864,7 +1721,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" ht="17.25" customHeight="1">
+    <row r="15" ht="17.25" customHeight="1" spans="1:3">
       <c r="A15" s="1" t="s">
         <v>29</v>
       </c>
@@ -872,7 +1729,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" ht="17.25" customHeight="1">
+    <row r="16" ht="17.25" customHeight="1" spans="1:3">
       <c r="A16" s="1" t="s">
         <v>31</v>
       </c>
@@ -880,7 +1737,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" ht="17.25" customHeight="1">
+    <row r="17" ht="17.25" customHeight="1" spans="1:2">
       <c r="A17" s="1" t="s">
         <v>33</v>
       </c>
@@ -888,7 +1745,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" ht="17.25" customHeight="1">
+    <row r="18" ht="17.25" customHeight="1" spans="1:2">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -896,7 +1753,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" ht="17.25" customHeight="1">
+    <row r="19" ht="17.25" customHeight="1" spans="1:2">
       <c r="A19" s="1" t="s">
         <v>37</v>
       </c>
@@ -904,7 +1761,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" ht="17.25" customHeight="1">
+    <row r="20" ht="17.25" customHeight="1" spans="1:2">
       <c r="A20" s="1" t="s">
         <v>39</v>
       </c>
@@ -912,7 +1769,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" ht="17.25" customHeight="1">
+    <row r="21" ht="17.25" customHeight="1" spans="1:2">
       <c r="A21" s="1" t="s">
         <v>41</v>
       </c>
@@ -920,7 +1777,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" ht="17.25" customHeight="1">
+    <row r="22" ht="17.25" customHeight="1" spans="1:2">
       <c r="A22" s="1" t="s">
         <v>43</v>
       </c>
@@ -928,7 +1785,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" ht="17.25" customHeight="1">
+    <row r="23" ht="17.25" customHeight="1" spans="1:2">
       <c r="A23" s="1" t="s">
         <v>45</v>
       </c>
@@ -936,7 +1793,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" ht="17.25" customHeight="1">
+    <row r="24" ht="17.25" customHeight="1" spans="1:2">
       <c r="A24" s="1" t="s">
         <v>47</v>
       </c>
@@ -944,7 +1801,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" ht="17.25" customHeight="1">
+    <row r="25" ht="17.25" customHeight="1" spans="1:2">
       <c r="A25" s="1" t="s">
         <v>49</v>
       </c>
@@ -952,7 +1809,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" ht="17.25" customHeight="1">
+    <row r="26" ht="17.25" customHeight="1" spans="1:2">
       <c r="A26" s="1" t="s">
         <v>51</v>
       </c>
@@ -960,7 +1817,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" ht="17.25" customHeight="1">
+    <row r="27" ht="17.25" customHeight="1" spans="1:2">
       <c r="A27" s="1" t="s">
         <v>53</v>
       </c>
@@ -968,7 +1825,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" ht="17.25" customHeight="1">
+    <row r="28" ht="17.25" customHeight="1" spans="1:2">
       <c r="A28" s="1" t="s">
         <v>55</v>
       </c>
@@ -976,7 +1833,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" ht="17.25" customHeight="1">
+    <row r="29" ht="17.25" customHeight="1" spans="1:2">
       <c r="A29" s="1" t="s">
         <v>57</v>
       </c>
@@ -984,7 +1841,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" ht="17.25" customHeight="1">
+    <row r="30" ht="17.25" customHeight="1" spans="1:2">
       <c r="A30" s="1" t="s">
         <v>59</v>
       </c>
@@ -992,7 +1849,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" ht="17.25" customHeight="1">
+    <row r="31" ht="17.25" customHeight="1" spans="1:2">
       <c r="A31" s="1" t="s">
         <v>61</v>
       </c>
@@ -1000,7 +1857,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="32" ht="17.25" customHeight="1">
+    <row r="32" ht="17.25" customHeight="1" spans="1:2">
       <c r="A32" s="1" t="s">
         <v>63</v>
       </c>
@@ -1008,7 +1865,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" ht="17.25" customHeight="1">
+    <row r="33" ht="17.25" customHeight="1" spans="1:2">
       <c r="A33" s="1" t="s">
         <v>65</v>
       </c>
@@ -1016,7 +1873,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="34" ht="17.25" customHeight="1">
+    <row r="34" ht="17.25" customHeight="1" spans="1:2">
       <c r="A34" s="1" t="s">
         <v>67</v>
       </c>
@@ -1024,7 +1881,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="35" ht="17.25" customHeight="1">
+    <row r="35" ht="17.25" customHeight="1" spans="1:2">
       <c r="A35" s="1" t="s">
         <v>69</v>
       </c>
@@ -1032,7 +1889,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" ht="17.25" customHeight="1">
+    <row r="36" ht="17.25" customHeight="1" spans="1:2">
       <c r="A36" s="1" t="s">
         <v>71</v>
       </c>
@@ -1040,7 +1897,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="37" ht="17.25" customHeight="1">
+    <row r="37" ht="17.25" customHeight="1" spans="1:2">
       <c r="A37" s="1" t="s">
         <v>73</v>
       </c>
@@ -1048,7 +1905,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" ht="17.25" customHeight="1">
+    <row r="38" ht="17.25" customHeight="1" spans="1:2">
       <c r="A38" s="1" t="s">
         <v>75</v>
       </c>
@@ -1056,7 +1913,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" ht="17.25" customHeight="1">
+    <row r="39" ht="17.25" customHeight="1" spans="1:2">
       <c r="A39" s="1" t="s">
         <v>77</v>
       </c>
@@ -1064,7 +1921,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" ht="17.25" customHeight="1">
+    <row r="40" ht="17.25" customHeight="1" spans="1:2">
       <c r="A40" s="1" t="s">
         <v>79</v>
       </c>
@@ -1072,7 +1929,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41" ht="17.25" customHeight="1">
+    <row r="41" ht="17.25" customHeight="1" spans="1:2">
       <c r="A41" s="1" t="s">
         <v>81</v>
       </c>
@@ -1080,7 +1937,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" ht="17.25" customHeight="1">
+    <row r="42" ht="17.25" customHeight="1" spans="1:2">
       <c r="A42" s="1" t="s">
         <v>83</v>
       </c>
@@ -1088,7 +1945,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" ht="17.25" customHeight="1">
+    <row r="43" ht="17.25" customHeight="1" spans="1:2">
       <c r="A43" s="1" t="s">
         <v>85</v>
       </c>
@@ -1096,7 +1953,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="44" ht="17.25" customHeight="1">
+    <row r="44" ht="17.25" customHeight="1" spans="1:2">
       <c r="A44" s="1" t="s">
         <v>87</v>
       </c>
@@ -1104,7 +1961,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="45" ht="17.25" customHeight="1">
+    <row r="45" ht="17.25" customHeight="1" spans="1:2">
       <c r="A45" s="1" t="s">
         <v>89</v>
       </c>
@@ -1112,7 +1969,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="46" ht="17.25" customHeight="1">
+    <row r="46" ht="17.25" customHeight="1" spans="1:2">
       <c r="A46" s="1" t="s">
         <v>91</v>
       </c>
@@ -1120,7 +1977,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="47" ht="17.25" customHeight="1">
+    <row r="47" ht="17.25" customHeight="1" spans="1:2">
       <c r="A47" s="2" t="s">
         <v>93</v>
       </c>
@@ -1128,7 +1985,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="48" ht="17.25" customHeight="1">
+    <row r="48" ht="17.25" customHeight="1" spans="1:2">
       <c r="A48" s="2" t="s">
         <v>95</v>
       </c>
@@ -1136,7 +1993,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="49" ht="17.25" customHeight="1">
+    <row r="49" ht="17.25" customHeight="1" spans="1:3">
       <c r="A49" s="2" t="s">
         <v>97</v>
       </c>
@@ -1144,7 +2001,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="50" ht="17.25" customHeight="1">
+    <row r="50" ht="17.25" customHeight="1" spans="1:3">
       <c r="A50" s="2" t="s">
         <v>99</v>
       </c>
@@ -1155,7 +2012,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="51" ht="17.25" customHeight="1">
+    <row r="51" ht="17.25" customHeight="1" spans="1:3">
       <c r="A51" s="2" t="s">
         <v>102</v>
       </c>
@@ -1163,7 +2020,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="52" ht="17.25" customHeight="1">
+    <row r="52" ht="17.25" customHeight="1" spans="1:3">
       <c r="A52" s="2" t="s">
         <v>104</v>
       </c>
@@ -1171,7 +2028,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="53" ht="17.25" customHeight="1">
+    <row r="53" ht="17.25" customHeight="1" spans="1:3">
       <c r="A53" s="2" t="s">
         <v>106</v>
       </c>
@@ -1179,7 +2036,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="54" ht="17.25" customHeight="1">
+    <row r="54" ht="17.25" customHeight="1" spans="1:3">
       <c r="A54" s="2" t="s">
         <v>108</v>
       </c>
@@ -1187,7 +2044,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="55" ht="17.25" customHeight="1">
+    <row r="55" ht="17.25" customHeight="1" spans="1:3">
       <c r="A55" s="2" t="s">
         <v>110</v>
       </c>
@@ -1195,7 +2052,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="56" ht="17.25" customHeight="1">
+    <row r="56" ht="17.25" customHeight="1" spans="1:3">
       <c r="A56" s="2" t="s">
         <v>112</v>
       </c>
@@ -1203,7 +2060,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="57" ht="17.25" customHeight="1">
+    <row r="57" ht="17.25" customHeight="1" spans="1:3">
       <c r="A57" s="2" t="s">
         <v>114</v>
       </c>
@@ -1211,7 +2068,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="58" ht="17.25" customHeight="1">
+    <row r="58" ht="17.25" customHeight="1" spans="1:3">
       <c r="A58" s="2" t="s">
         <v>116</v>
       </c>
@@ -1219,7 +2076,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="59" ht="17.25" customHeight="1">
+    <row r="59" ht="17.25" customHeight="1" spans="1:3">
       <c r="A59" s="2" t="s">
         <v>118</v>
       </c>
@@ -1227,7 +2084,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="60" ht="17.25" customHeight="1">
+    <row r="60" ht="17.25" customHeight="1" spans="1:3">
       <c r="A60" s="4" t="s">
         <v>120</v>
       </c>
@@ -1238,7 +2095,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="61" ht="17.25" customHeight="1">
+    <row r="61" ht="17.25" customHeight="1" spans="1:3">
       <c r="A61" s="2" t="s">
         <v>122</v>
       </c>
@@ -1246,79 +2103,86 @@
         <v>123</v>
       </c>
     </row>
-    <row r="62" ht="17.25" customHeight="1">
+    <row r="62" ht="17.25" customHeight="1" spans="1:3">
       <c r="A62" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="B62" s="6" t="s">
+      <c r="B62" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="63" ht="17.25" customHeight="1">
+    <row r="63" ht="17.25" customHeight="1" spans="1:3">
       <c r="A63" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="B63" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="64" ht="17.25" customHeight="1">
+    <row r="64" ht="17.25" customHeight="1" spans="1:3">
       <c r="A64" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="B64" s="6" t="s">
+      <c r="B64" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="65" ht="17.25" customHeight="1">
+    <row r="65" ht="17.25" customHeight="1" spans="1:2">
       <c r="A65" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B65" s="6" t="s">
+      <c r="B65" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="66" ht="17.25" customHeight="1">
+    <row r="66" ht="17.25" customHeight="1" spans="1:2">
       <c r="A66" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="B66" s="6" t="s">
+      <c r="B66" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="67" ht="17.25" customHeight="1">
+    <row r="67" ht="17.25" customHeight="1" spans="1:2">
       <c r="A67" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="B67" s="6" t="s">
+      <c r="B67" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="68" ht="17.25" customHeight="1">
+    <row r="68" ht="17.25" customHeight="1" spans="1:2">
       <c r="A68" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="B68" s="6" t="s">
+      <c r="B68" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="69" ht="17.25" customHeight="1">
+    <row r="69" ht="17.25" customHeight="1" spans="1:2">
       <c r="A69" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="B69" s="6" t="s">
+      <c r="B69" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="70" ht="17.25" customHeight="1">
+    <row r="70" ht="17.25" customHeight="1" spans="1:2">
       <c r="A70" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="B70" s="6" t="s">
+      <c r="B70" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="71" ht="17.25" customHeight="1"/>
+    <row r="71" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A71" t="s">
+        <v>142</v>
+      </c>
+      <c r="B71" t="s">
+        <v>143</v>
+      </c>
+    </row>
     <row r="72" ht="17.25" customHeight="1"/>
     <row r="73" ht="17.25" customHeight="1"/>
     <row r="74" ht="17.25" customHeight="1"/>
@@ -2249,9 +3113,8 @@
     <row r="999" ht="17.25" customHeight="1"/>
     <row r="1000" ht="17.25" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="1" orientation="landscape"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\팀과제\JewelThief\JsonConverter\ExcelFiles\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EDB8936-FC6C-4EED-A460-21DFEB13AAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="5232" yWindow="1452" windowWidth="16824" windowHeight="9048" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="enqOkH1Z/tfQ3WIfr7wm+HPEzSLVVhkZawHcM088EJg="/>
@@ -16,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="144">
   <si>
     <t>미리 로드할 어드레서블 테이블</t>
   </si>
@@ -141,339 +150,366 @@
     <t>All Direction Corridor</t>
   </si>
   <si>
+    <t>Lobby</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Player_With_Camera</t>
+  </si>
+  <si>
+    <t>Player</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_BGM_01</t>
+  </si>
+  <si>
+    <t>PlayTheme</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_001</t>
+  </si>
+  <si>
+    <t>AlertUp_01</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_002</t>
+  </si>
+  <si>
+    <t>Click_01</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_003</t>
+  </si>
+  <si>
+    <t>Click_02</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_004</t>
+  </si>
+  <si>
+    <t>Error_01</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_005</t>
+  </si>
+  <si>
+    <t>Error_02</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_006</t>
+  </si>
+  <si>
+    <t>Explosion_01</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_007</t>
+  </si>
+  <si>
+    <t>Explosion_02</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_008</t>
+  </si>
+  <si>
+    <t>Explosion_03</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_009</t>
+  </si>
+  <si>
+    <t>Explosion_04</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_010</t>
+  </si>
+  <si>
+    <t>Explosion_05</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_011</t>
+  </si>
+  <si>
+    <t>Gain_01</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_012</t>
+  </si>
+  <si>
+    <t>GunTrap_01</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_013</t>
+  </si>
+  <si>
+    <t>Lose_01</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_014</t>
+  </si>
+  <si>
+    <t>Lose_02</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_015</t>
+  </si>
+  <si>
+    <t>Notification_01</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_016</t>
+  </si>
+  <si>
+    <t>Notification_02</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_017</t>
+  </si>
+  <si>
+    <t>Open_Box_01</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_018</t>
+  </si>
+  <si>
+    <t>Purchase_01</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_019</t>
+  </si>
+  <si>
+    <t>Purchase_02</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_020</t>
+  </si>
+  <si>
+    <t>TimeUp_01</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_021</t>
+  </si>
+  <si>
+    <t>Win_01</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_022</t>
+  </si>
+  <si>
+    <t>Win_02</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_023</t>
+  </si>
+  <si>
+    <t>Win_03</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_FBX_KeyFBX</t>
+  </si>
+  <si>
+    <t>KeyFBX</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_Black</t>
+  </si>
+  <si>
+    <t>Black</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_Yellow</t>
+  </si>
+  <si>
+    <t>Yellow</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_KeyMesh[SM_Gen_Prop_Key_01]</t>
+  </si>
+  <si>
+    <t>KeyFBX[SM_Gen_Prop_Key_01]</t>
+  </si>
+  <si>
+    <t>Mesh</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_M_Gemstone_Diamond,Lit</t>
+  </si>
+  <si>
+    <t>M_Gemstone_Diamond</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_M_Gemstone_Amethyst</t>
+  </si>
+  <si>
+    <t>M_Gemstone_Amethyst</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_M_Gemstone_Aquamarine</t>
+  </si>
+  <si>
+    <t>M_Gemstone_Aquamarine</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_M_Gemstone_Emerald</t>
+  </si>
+  <si>
+    <t>M_Gemstone_Emerald</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_M_Gemstone_Ruby</t>
+  </si>
+  <si>
+    <t>M_Gemstone_Ruby</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_M_Gemstone_Sapphire</t>
+  </si>
+  <si>
+    <t>M_Gemstone_Sapphire</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_M_Gemstone_Topaz</t>
+  </si>
+  <si>
+    <t>M_Gemstone_Topaz</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_GameObject_ToolObject</t>
+  </si>
+  <si>
+    <t>Pool_Tool</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_GameObject_JewelObject</t>
+  </si>
+  <si>
+    <t>Pool_Jewel</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_Jewel_Cone[Cone]</t>
+  </si>
+  <si>
+    <t>Jewel_Cone[Cone]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_Lit</t>
+  </si>
+  <si>
+    <t>Lit</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_GameObject_Door</t>
+  </si>
+  <si>
+    <t>Door_Prefab</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_GameObject_InteractableContainer</t>
+  </si>
+  <si>
+    <t>InteractableContainer_Prefab</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_GameObject_MeshDoor</t>
+  </si>
+  <si>
+    <t>Mesh_Door</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_GameObject_MeshCabinet</t>
+  </si>
+  <si>
+    <t>Mesh_Cabinet</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_GameObject_MeshIronBoxPrefab</t>
+  </si>
+  <si>
+    <t>Mesh_IronBox_Prefab</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_GameObject_MeshWoodBoxPrefab</t>
+  </si>
+  <si>
+    <t>Mesh_WoodBox_Prefab</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_GameObject_Effect_High</t>
+  </si>
+  <si>
+    <t>Effect_High</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_GameObject_Effect_Low</t>
+  </si>
+  <si>
+    <t>Effect_Low</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_GameObject_Effect_Normal</t>
+  </si>
+  <si>
+    <t>Effect_Normal</t>
+  </si>
+  <si>
     <t>PreLoadAsset_Lobby</t>
-  </si>
-  <si>
-    <t>Lobby</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_Player_With_Camera</t>
-  </si>
-  <si>
-    <t>Player</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_Sound_BGM_01</t>
-  </si>
-  <si>
-    <t>PlayTheme</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_Sound_SFX_001</t>
-  </si>
-  <si>
-    <t>AlertUp_01</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_Sound_SFX_002</t>
-  </si>
-  <si>
-    <t>Click_01</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_Sound_SFX_003</t>
-  </si>
-  <si>
-    <t>Click_02</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_Sound_SFX_004</t>
-  </si>
-  <si>
-    <t>Error_01</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_Sound_SFX_005</t>
-  </si>
-  <si>
-    <t>Error_02</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_Sound_SFX_006</t>
-  </si>
-  <si>
-    <t>Explosion_01</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_Sound_SFX_007</t>
-  </si>
-  <si>
-    <t>Explosion_02</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_Sound_SFX_008</t>
-  </si>
-  <si>
-    <t>Explosion_03</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_Sound_SFX_009</t>
-  </si>
-  <si>
-    <t>Explosion_04</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_Sound_SFX_010</t>
-  </si>
-  <si>
-    <t>Explosion_05</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_Sound_SFX_011</t>
-  </si>
-  <si>
-    <t>Gain_01</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_Sound_SFX_012</t>
-  </si>
-  <si>
-    <t>GunTrap_01</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_Sound_SFX_013</t>
-  </si>
-  <si>
-    <t>Lose_01</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_Sound_SFX_014</t>
-  </si>
-  <si>
-    <t>Lose_02</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_Sound_SFX_015</t>
-  </si>
-  <si>
-    <t>Notification_01</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_Sound_SFX_016</t>
-  </si>
-  <si>
-    <t>Notification_02</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_Sound_SFX_017</t>
-  </si>
-  <si>
-    <t>Open_Box_01</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_Sound_SFX_018</t>
-  </si>
-  <si>
-    <t>Purchase_01</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_Sound_SFX_019</t>
-  </si>
-  <si>
-    <t>Purchase_02</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_Sound_SFX_020</t>
-  </si>
-  <si>
-    <t>TimeUp_01</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_Sound_SFX_021</t>
-  </si>
-  <si>
-    <t>Win_01</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_Sound_SFX_022</t>
-  </si>
-  <si>
-    <t>Win_02</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_Sound_SFX_023</t>
-  </si>
-  <si>
-    <t>Win_03</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_FBX_KeyFBX</t>
-  </si>
-  <si>
-    <t>KeyFBX</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_Material_Black</t>
-  </si>
-  <si>
-    <t>Black</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_Material_Yellow</t>
-  </si>
-  <si>
-    <t>Yellow</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_Mesh_KeyMesh[SM_Gen_Prop_Key_01]</t>
-  </si>
-  <si>
-    <t>KeyFBX[SM_Gen_Prop_Key_01]</t>
-  </si>
-  <si>
-    <t>Mesh</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_Material_M_Gemstone_Diamond,Lit</t>
-  </si>
-  <si>
-    <t>M_Gemstone_Diamond</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_Material_M_Gemstone_Amethyst</t>
-  </si>
-  <si>
-    <t>M_Gemstone_Amethyst</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_Material_M_Gemstone_Aquamarine</t>
-  </si>
-  <si>
-    <t>M_Gemstone_Aquamarine</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_Material_M_Gemstone_Emerald</t>
-  </si>
-  <si>
-    <t>M_Gemstone_Emerald</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_Material_M_Gemstone_Ruby</t>
-  </si>
-  <si>
-    <t>M_Gemstone_Ruby</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_Material_M_Gemstone_Sapphire</t>
-  </si>
-  <si>
-    <t>M_Gemstone_Sapphire</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_Material_M_Gemstone_Topaz</t>
-  </si>
-  <si>
-    <t>M_Gemstone_Topaz</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_GameObject_ToolObject</t>
-  </si>
-  <si>
-    <t>Pool_Tool</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_GameObject_JewelObject</t>
-  </si>
-  <si>
-    <t>Pool_Jewel</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_Mesh_Jewel_Cone[Cone]</t>
-  </si>
-  <si>
-    <t>Jewel_Cone[Cone]</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_Material_Lit</t>
-  </si>
-  <si>
-    <t>Lit</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_GameObject_Door</t>
-  </si>
-  <si>
-    <t>Door_Prefab</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_GameObject_InteractableContainer</t>
-  </si>
-  <si>
-    <t>InteractableContainer_Prefab</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_GameObject_MeshDoor</t>
-  </si>
-  <si>
-    <t>Mesh_Door</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_GameObject_MeshCabinet</t>
-  </si>
-  <si>
-    <t>Mesh_Cabinet</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_GameObject_MeshIronBoxPrefab</t>
-  </si>
-  <si>
-    <t>Mesh_IronBox_Prefab</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_GameObject_MeshWoodBoxPrefab</t>
-  </si>
-  <si>
-    <t>Mesh_WoodBox_Prefab</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_GameObject_Effect_High</t>
-  </si>
-  <si>
-    <t>Effect_High</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_GameObject_Effect_Low</t>
-  </si>
-  <si>
-    <t>Effect_Low</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_GameObject_Effect_Normal</t>
-  </si>
-  <si>
-    <t>Effect_Normal</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>PreLoadAsset_JewelInventory</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>JewelInventory</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -481,7 +517,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -491,7 +527,13 @@
     </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -505,39 +547,40 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -727,23 +770,23 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C1000"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="52.14"/>
-    <col customWidth="1" min="2" max="2" width="35.14"/>
-    <col customWidth="1" min="3" max="3" width="31.43"/>
-    <col customWidth="1" min="4" max="26" width="9.0"/>
+    <col min="1" max="1" width="52.109375" customWidth="1"/>
+    <col min="2" max="2" width="35.109375" customWidth="1"/>
+    <col min="3" max="3" width="31.44140625" customWidth="1"/>
+    <col min="4" max="26" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1">
+    <row r="1" spans="1:3" ht="17.25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -754,7 +797,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="17.25" customHeight="1">
+    <row r="2" spans="1:3" ht="17.25" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -765,7 +808,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" ht="17.25" customHeight="1">
+    <row r="3" spans="1:3" ht="17.25" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -776,7 +819,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" ht="17.25" customHeight="1">
+    <row r="4" spans="1:3" ht="17.25" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -784,7 +827,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" ht="17.25" customHeight="1">
+    <row r="5" spans="1:3" ht="17.25" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -792,7 +835,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" ht="17.25" customHeight="1">
+    <row r="6" spans="1:3" ht="17.25" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -800,7 +843,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" ht="17.25" customHeight="1">
+    <row r="7" spans="1:3" ht="17.25" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -808,7 +851,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" ht="17.25" customHeight="1">
+    <row r="8" spans="1:3" ht="17.25" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -816,7 +859,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" ht="17.25" customHeight="1">
+    <row r="9" spans="1:3" ht="17.25" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -824,7 +867,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" ht="17.25" customHeight="1">
+    <row r="10" spans="1:3" ht="17.25" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -832,7 +875,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" ht="17.25" customHeight="1">
+    <row r="11" spans="1:3" ht="17.25" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>21</v>
       </c>
@@ -840,7 +883,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" ht="17.25" customHeight="1">
+    <row r="12" spans="1:3" ht="17.25" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>23</v>
       </c>
@@ -848,7 +891,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" ht="17.25" customHeight="1">
+    <row r="13" spans="1:3" ht="17.25" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>25</v>
       </c>
@@ -856,7 +899,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" ht="17.25" customHeight="1">
+    <row r="14" spans="1:3" ht="17.25" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>27</v>
       </c>
@@ -864,7 +907,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" ht="17.25" customHeight="1">
+    <row r="15" spans="1:3" ht="17.25" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>29</v>
       </c>
@@ -872,7 +915,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" ht="17.25" customHeight="1">
+    <row r="16" spans="1:3" ht="17.25" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>31</v>
       </c>
@@ -880,7 +923,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" ht="17.25" customHeight="1">
+    <row r="17" spans="1:2" ht="17.25" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>33</v>
       </c>
@@ -888,7 +931,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" ht="17.25" customHeight="1">
+    <row r="18" spans="1:2" ht="17.25" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -896,7 +939,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" ht="17.25" customHeight="1">
+    <row r="19" spans="1:2" ht="17.25" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>37</v>
       </c>
@@ -904,7 +947,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" ht="17.25" customHeight="1">
+    <row r="20" spans="1:2" ht="17.25" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>39</v>
       </c>
@@ -912,422 +955,429 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" ht="17.25" customHeight="1">
-      <c r="A21" s="1" t="s">
+    <row r="21" spans="1:2" ht="17.25" customHeight="1">
+      <c r="A21" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="1" t="s">
+    </row>
+    <row r="22" spans="1:2" ht="17.25" customHeight="1">
+      <c r="A22" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="22" ht="17.25" customHeight="1">
-      <c r="A22" s="1" t="s">
+      <c r="B22" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="1" t="s">
+    </row>
+    <row r="23" spans="1:2" ht="17.25" customHeight="1">
+      <c r="A23" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="23" ht="17.25" customHeight="1">
-      <c r="A23" s="1" t="s">
+      <c r="B23" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B23" s="3" t="s">
+    </row>
+    <row r="24" spans="1:2" ht="17.25" customHeight="1">
+      <c r="A24" s="1" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="24" ht="17.25" customHeight="1">
-      <c r="A24" s="1" t="s">
+      <c r="B24" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B24" s="3" t="s">
+    </row>
+    <row r="25" spans="1:2" ht="17.25" customHeight="1">
+      <c r="A25" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="25" ht="17.25" customHeight="1">
-      <c r="A25" s="1" t="s">
+      <c r="B25" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B25" s="3" t="s">
+    </row>
+    <row r="26" spans="1:2" ht="17.25" customHeight="1">
+      <c r="A26" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="26" ht="17.25" customHeight="1">
-      <c r="A26" s="1" t="s">
+      <c r="B26" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B26" s="3" t="s">
+    </row>
+    <row r="27" spans="1:2" ht="17.25" customHeight="1">
+      <c r="A27" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="27" ht="17.25" customHeight="1">
-      <c r="A27" s="1" t="s">
+      <c r="B27" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B27" s="3" t="s">
+    </row>
+    <row r="28" spans="1:2" ht="17.25" customHeight="1">
+      <c r="A28" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="28" ht="17.25" customHeight="1">
-      <c r="A28" s="1" t="s">
+      <c r="B28" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B28" s="3" t="s">
+    </row>
+    <row r="29" spans="1:2" ht="17.25" customHeight="1">
+      <c r="A29" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="29" ht="17.25" customHeight="1">
-      <c r="A29" s="1" t="s">
+      <c r="B29" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B29" s="3" t="s">
+    </row>
+    <row r="30" spans="1:2" ht="17.25" customHeight="1">
+      <c r="A30" s="1" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="30" ht="17.25" customHeight="1">
-      <c r="A30" s="1" t="s">
+      <c r="B30" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B30" s="3" t="s">
+    </row>
+    <row r="31" spans="1:2" ht="17.25" customHeight="1">
+      <c r="A31" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="31" ht="17.25" customHeight="1">
-      <c r="A31" s="1" t="s">
+      <c r="B31" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B31" s="3" t="s">
+    </row>
+    <row r="32" spans="1:2" ht="17.25" customHeight="1">
+      <c r="A32" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="32" ht="17.25" customHeight="1">
-      <c r="A32" s="1" t="s">
+      <c r="B32" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B32" s="3" t="s">
+    </row>
+    <row r="33" spans="1:2" ht="17.25" customHeight="1">
+      <c r="A33" s="1" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="33" ht="17.25" customHeight="1">
-      <c r="A33" s="1" t="s">
+      <c r="B33" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B33" s="3" t="s">
+    </row>
+    <row r="34" spans="1:2" ht="17.25" customHeight="1">
+      <c r="A34" s="1" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="34" ht="17.25" customHeight="1">
-      <c r="A34" s="1" t="s">
+      <c r="B34" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B34" s="3" t="s">
+    </row>
+    <row r="35" spans="1:2" ht="17.25" customHeight="1">
+      <c r="A35" s="1" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="35" ht="17.25" customHeight="1">
-      <c r="A35" s="1" t="s">
+      <c r="B35" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B35" s="3" t="s">
+    </row>
+    <row r="36" spans="1:2" ht="17.25" customHeight="1">
+      <c r="A36" s="1" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="36" ht="17.25" customHeight="1">
-      <c r="A36" s="1" t="s">
+      <c r="B36" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B36" s="3" t="s">
+    </row>
+    <row r="37" spans="1:2" ht="17.25" customHeight="1">
+      <c r="A37" s="1" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="37" ht="17.25" customHeight="1">
-      <c r="A37" s="1" t="s">
+      <c r="B37" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B37" s="3" t="s">
+    </row>
+    <row r="38" spans="1:2" ht="17.25" customHeight="1">
+      <c r="A38" s="1" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="38" ht="17.25" customHeight="1">
-      <c r="A38" s="1" t="s">
+      <c r="B38" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B38" s="3" t="s">
+    </row>
+    <row r="39" spans="1:2" ht="17.25" customHeight="1">
+      <c r="A39" s="1" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="39" ht="17.25" customHeight="1">
-      <c r="A39" s="1" t="s">
+      <c r="B39" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B39" s="3" t="s">
+    </row>
+    <row r="40" spans="1:2" ht="17.25" customHeight="1">
+      <c r="A40" s="1" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="40" ht="17.25" customHeight="1">
-      <c r="A40" s="1" t="s">
+      <c r="B40" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B40" s="3" t="s">
+    </row>
+    <row r="41" spans="1:2" ht="17.25" customHeight="1">
+      <c r="A41" s="1" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="41" ht="17.25" customHeight="1">
-      <c r="A41" s="1" t="s">
+      <c r="B41" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B41" s="3" t="s">
+    </row>
+    <row r="42" spans="1:2" ht="17.25" customHeight="1">
+      <c r="A42" s="1" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="42" ht="17.25" customHeight="1">
-      <c r="A42" s="1" t="s">
+      <c r="B42" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="B42" s="3" t="s">
+    </row>
+    <row r="43" spans="1:2" ht="17.25" customHeight="1">
+      <c r="A43" s="1" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="43" ht="17.25" customHeight="1">
-      <c r="A43" s="1" t="s">
+      <c r="B43" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B43" s="3" t="s">
+    </row>
+    <row r="44" spans="1:2" ht="17.25" customHeight="1">
+      <c r="A44" s="1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="44" ht="17.25" customHeight="1">
-      <c r="A44" s="1" t="s">
+      <c r="B44" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B44" s="3" t="s">
+    </row>
+    <row r="45" spans="1:2" ht="17.25" customHeight="1">
+      <c r="A45" s="1" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="45" ht="17.25" customHeight="1">
-      <c r="A45" s="1" t="s">
+      <c r="B45" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B45" s="3" t="s">
+    </row>
+    <row r="46" spans="1:2" ht="17.25" customHeight="1">
+      <c r="A46" s="1" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="46" ht="17.25" customHeight="1">
-      <c r="A46" s="1" t="s">
+      <c r="B46" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B46" s="3" t="s">
+    </row>
+    <row r="47" spans="1:2" ht="17.25" customHeight="1">
+      <c r="A47" s="2" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="47" ht="17.25" customHeight="1">
-      <c r="A47" s="2" t="s">
+      <c r="B47" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B47" s="2" t="s">
+    </row>
+    <row r="48" spans="1:2" ht="17.25" customHeight="1">
+      <c r="A48" s="2" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="48" ht="17.25" customHeight="1">
-      <c r="A48" s="2" t="s">
+      <c r="B48" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B48" s="3" t="s">
+    </row>
+    <row r="49" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A49" s="2" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="49" ht="17.25" customHeight="1">
-      <c r="A49" s="2" t="s">
+      <c r="B49" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B49" s="1" t="s">
+    </row>
+    <row r="50" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A50" s="2" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="50" ht="17.25" customHeight="1">
-      <c r="A50" s="2" t="s">
+      <c r="B50" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="C50" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C50" s="2" t="s">
+    </row>
+    <row r="51" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A51" s="2" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="51" ht="17.25" customHeight="1">
-      <c r="A51" s="2" t="s">
+      <c r="B51" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B51" s="4" t="s">
+    </row>
+    <row r="52" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A52" s="2" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="52" ht="17.25" customHeight="1">
-      <c r="A52" s="2" t="s">
+      <c r="B52" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B52" s="4" t="s">
+    </row>
+    <row r="53" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A53" s="2" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="53" ht="17.25" customHeight="1">
-      <c r="A53" s="2" t="s">
+      <c r="B53" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="B53" s="4" t="s">
+    </row>
+    <row r="54" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A54" s="2" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="54" ht="17.25" customHeight="1">
-      <c r="A54" s="2" t="s">
+      <c r="B54" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B54" s="4" t="s">
+    </row>
+    <row r="55" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A55" s="2" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="55" ht="17.25" customHeight="1">
-      <c r="A55" s="2" t="s">
+      <c r="B55" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B55" s="4" t="s">
+    </row>
+    <row r="56" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A56" s="2" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="56" ht="17.25" customHeight="1">
-      <c r="A56" s="2" t="s">
+      <c r="B56" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="B56" s="4" t="s">
+    </row>
+    <row r="57" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A57" s="2" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="57" ht="17.25" customHeight="1">
-      <c r="A57" s="2" t="s">
+      <c r="B57" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B57" s="4" t="s">
+    </row>
+    <row r="58" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A58" s="2" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="58" ht="17.25" customHeight="1">
-      <c r="A58" s="2" t="s">
+      <c r="B58" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="B58" s="4" t="s">
+    </row>
+    <row r="59" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A59" s="2" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="59" ht="17.25" customHeight="1">
-      <c r="A59" s="2" t="s">
+      <c r="B59" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="B59" s="4" t="s">
+    </row>
+    <row r="60" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A60" s="4" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="60" ht="17.25" customHeight="1">
-      <c r="A60" s="4" t="s">
+      <c r="B60" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="C60" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A61" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C60" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="61" ht="17.25" customHeight="1">
-      <c r="A61" s="2" t="s">
+      <c r="B61" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B61" s="1" t="s">
+    </row>
+    <row r="62" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A62" s="5" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="62" ht="17.25" customHeight="1">
-      <c r="A62" s="5" t="s">
+      <c r="B62" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="B62" s="6" t="s">
+    </row>
+    <row r="63" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A63" s="5" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="63" ht="17.25" customHeight="1">
-      <c r="A63" s="5" t="s">
+      <c r="B63" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="B63" s="6" t="s">
+    </row>
+    <row r="64" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A64" s="5" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="64" ht="17.25" customHeight="1">
-      <c r="A64" s="5" t="s">
+      <c r="B64" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="B64" s="6" t="s">
+    </row>
+    <row r="65" spans="1:2" ht="17.25" customHeight="1">
+      <c r="A65" s="5" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="65" ht="17.25" customHeight="1">
-      <c r="A65" s="5" t="s">
+      <c r="B65" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="B65" s="6" t="s">
+    </row>
+    <row r="66" spans="1:2" ht="17.25" customHeight="1">
+      <c r="A66" s="5" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="66" ht="17.25" customHeight="1">
-      <c r="A66" s="5" t="s">
+      <c r="B66" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="B66" s="6" t="s">
+    </row>
+    <row r="67" spans="1:2" ht="17.25" customHeight="1">
+      <c r="A67" s="5" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="67" ht="17.25" customHeight="1">
-      <c r="A67" s="5" t="s">
+      <c r="B67" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="B67" s="6" t="s">
+    </row>
+    <row r="68" spans="1:2" ht="17.25" customHeight="1">
+      <c r="A68" s="5" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="68" ht="17.25" customHeight="1">
-      <c r="A68" s="5" t="s">
+      <c r="B68" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="B68" s="6" t="s">
+    </row>
+    <row r="69" spans="1:2" ht="17.25" customHeight="1">
+      <c r="A69" s="5" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="69" ht="17.25" customHeight="1">
-      <c r="A69" s="5" t="s">
+      <c r="B69" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="B69" s="6" t="s">
+    </row>
+    <row r="70" spans="1:2" ht="17.25" customHeight="1">
+      <c r="A70" s="5" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="70" ht="17.25" customHeight="1">
-      <c r="A70" s="5" t="s">
+      <c r="B70" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="B70" s="6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="71" ht="17.25" customHeight="1"/>
-    <row r="72" ht="17.25" customHeight="1"/>
-    <row r="73" ht="17.25" customHeight="1"/>
-    <row r="74" ht="17.25" customHeight="1"/>
-    <row r="75" ht="17.25" customHeight="1"/>
-    <row r="76" ht="17.25" customHeight="1"/>
-    <row r="77" ht="17.25" customHeight="1"/>
-    <row r="78" ht="17.25" customHeight="1"/>
-    <row r="79" ht="17.25" customHeight="1"/>
-    <row r="80" ht="17.25" customHeight="1"/>
+    </row>
+    <row r="71" spans="1:2" ht="17.25" customHeight="1">
+      <c r="A71" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="B71" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" ht="17.25" customHeight="1"/>
+    <row r="73" spans="1:2" ht="17.25" customHeight="1"/>
+    <row r="74" spans="1:2" ht="17.25" customHeight="1"/>
+    <row r="75" spans="1:2" ht="17.25" customHeight="1"/>
+    <row r="76" spans="1:2" ht="17.25" customHeight="1"/>
+    <row r="77" spans="1:2" ht="17.25" customHeight="1"/>
+    <row r="78" spans="1:2" ht="17.25" customHeight="1"/>
+    <row r="79" spans="1:2" ht="17.25" customHeight="1"/>
+    <row r="80" spans="1:2" ht="17.25" customHeight="1"/>
     <row r="81" ht="17.25" customHeight="1"/>
     <row r="82" ht="17.25" customHeight="1"/>
     <row r="83" ht="17.25" customHeight="1"/>
@@ -2249,9 +2299,8 @@
     <row r="999" ht="17.25" customHeight="1"/>
     <row r="1000" ht="17.25" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
@@ -1,21 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\팀과제\JewelThief\JsonConverter\ExcelFiles\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EDB8936-FC6C-4EED-A460-21DFEB13AAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="5232" yWindow="1452" windowWidth="16824" windowHeight="9048" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="enqOkH1Z/tfQ3WIfr7wm+HPEzSLVVhkZawHcM088EJg="/>
@@ -25,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="146">
   <si>
     <t>미리 로드할 어드레서블 테이블</t>
   </si>
@@ -150,6 +141,9 @@
     <t>All Direction Corridor</t>
   </si>
   <si>
+    <t>PreLoadAsset_Lobby</t>
+  </si>
+  <si>
     <t>Lobby</t>
   </si>
   <si>
@@ -450,66 +444,48 @@
     <t>Effect_Normal</t>
   </si>
   <si>
-    <t>PreLoadAsset_Lobby</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>PreLoadAsset_JewelInventory</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>JewelInventory</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_PoliceThrow_Object</t>
+  </si>
+  <si>
+    <t>Pool_Throw</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <fonts count="5">
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Malgun Gothic"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color theme="1"/>
       <name val="Malgun Gothic"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -517,7 +493,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -526,14 +502,8 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="3">
+    <border/>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -547,40 +517,52 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+  <cellXfs count="9">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="2" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -770,23 +752,23 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1000"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="52.109375" customWidth="1"/>
-    <col min="2" max="2" width="35.109375" customWidth="1"/>
-    <col min="3" max="3" width="31.44140625" customWidth="1"/>
-    <col min="4" max="26" width="9" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="52.14"/>
+    <col customWidth="1" min="2" max="2" width="35.14"/>
+    <col customWidth="1" min="3" max="3" width="31.43"/>
+    <col customWidth="1" min="4" max="26" width="9.0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="17.25" customHeight="1">
+    <row r="1" ht="17.25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -797,7 +779,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="17.25" customHeight="1">
+    <row r="2" ht="17.25" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -808,7 +790,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="17.25" customHeight="1">
+    <row r="3" ht="17.25" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -819,7 +801,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="17.25" customHeight="1">
+    <row r="4" ht="17.25" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -827,7 +809,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="17.25" customHeight="1">
+    <row r="5" ht="17.25" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -835,7 +817,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="17.25" customHeight="1">
+    <row r="6" ht="17.25" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -843,7 +825,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="17.25" customHeight="1">
+    <row r="7" ht="17.25" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -851,7 +833,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="17.25" customHeight="1">
+    <row r="8" ht="17.25" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -859,7 +841,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="17.25" customHeight="1">
+    <row r="9" ht="17.25" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -867,7 +849,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="17.25" customHeight="1">
+    <row r="10" ht="17.25" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -875,7 +857,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="17.25" customHeight="1">
+    <row r="11" ht="17.25" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>21</v>
       </c>
@@ -883,7 +865,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="17.25" customHeight="1">
+    <row r="12" ht="17.25" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>23</v>
       </c>
@@ -891,7 +873,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="17.25" customHeight="1">
+    <row r="13" ht="17.25" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>25</v>
       </c>
@@ -899,7 +881,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="17.25" customHeight="1">
+    <row r="14" ht="17.25" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>27</v>
       </c>
@@ -907,7 +889,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="17.25" customHeight="1">
+    <row r="15" ht="17.25" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>29</v>
       </c>
@@ -915,7 +897,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="17.25" customHeight="1">
+    <row r="16" ht="17.25" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>31</v>
       </c>
@@ -923,7 +905,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="17.25" customHeight="1">
+    <row r="17" ht="17.25" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>33</v>
       </c>
@@ -931,7 +913,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="17.25" customHeight="1">
+    <row r="18" ht="17.25" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -939,7 +921,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="17.25" customHeight="1">
+    <row r="19" ht="17.25" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>37</v>
       </c>
@@ -947,7 +929,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="17.25" customHeight="1">
+    <row r="20" ht="17.25" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>39</v>
       </c>
@@ -955,429 +937,436 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A21" s="7" t="s">
+    <row r="21" ht="17.25" customHeight="1">
+      <c r="A21" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" ht="17.25" customHeight="1">
+      <c r="A22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" ht="17.25" customHeight="1">
+      <c r="A23" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" ht="17.25" customHeight="1">
+      <c r="A24" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" ht="17.25" customHeight="1">
+      <c r="A25" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" ht="17.25" customHeight="1">
+      <c r="A26" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" ht="17.25" customHeight="1">
+      <c r="A27" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" ht="17.25" customHeight="1">
+      <c r="A28" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" ht="17.25" customHeight="1">
+      <c r="A29" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" ht="17.25" customHeight="1">
+      <c r="A30" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" ht="17.25" customHeight="1">
+      <c r="A31" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="32" ht="17.25" customHeight="1">
+      <c r="A32" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" ht="17.25" customHeight="1">
+      <c r="A33" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="34" ht="17.25" customHeight="1">
+      <c r="A34" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="35" ht="17.25" customHeight="1">
+      <c r="A35" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="36" ht="17.25" customHeight="1">
+      <c r="A36" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" ht="17.25" customHeight="1">
+      <c r="A37" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38" ht="17.25" customHeight="1">
+      <c r="A38" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39" ht="17.25" customHeight="1">
+      <c r="A39" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="40" ht="17.25" customHeight="1">
+      <c r="A40" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41" ht="17.25" customHeight="1">
+      <c r="A41" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="42" ht="17.25" customHeight="1">
+      <c r="A42" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43" ht="17.25" customHeight="1">
+      <c r="A43" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="44" ht="17.25" customHeight="1">
+      <c r="A44" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="45" ht="17.25" customHeight="1">
+      <c r="A45" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="46" ht="17.25" customHeight="1">
+      <c r="A46" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="47" ht="17.25" customHeight="1">
+      <c r="A47" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="48" ht="17.25" customHeight="1">
+      <c r="A48" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="49" ht="17.25" customHeight="1">
+      <c r="A49" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="50" ht="17.25" customHeight="1">
+      <c r="A50" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="51" ht="17.25" customHeight="1">
+      <c r="A51" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="52" ht="17.25" customHeight="1">
+      <c r="A52" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="53" ht="17.25" customHeight="1">
+      <c r="A53" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="54" ht="17.25" customHeight="1">
+      <c r="A54" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="55" ht="17.25" customHeight="1">
+      <c r="A55" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="56" ht="17.25" customHeight="1">
+      <c r="A56" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="57" ht="17.25" customHeight="1">
+      <c r="A57" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="58" ht="17.25" customHeight="1">
+      <c r="A58" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="59" ht="17.25" customHeight="1">
+      <c r="A59" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="60" ht="17.25" customHeight="1">
+      <c r="A60" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="61" ht="17.25" customHeight="1">
+      <c r="A61" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="62" ht="17.25" customHeight="1">
+      <c r="A62" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="63" ht="17.25" customHeight="1">
+      <c r="A63" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="64" ht="17.25" customHeight="1">
+      <c r="A64" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="65" ht="17.25" customHeight="1">
+      <c r="A65" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="66" ht="17.25" customHeight="1">
+      <c r="A66" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="67" ht="17.25" customHeight="1">
+      <c r="A67" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="68" ht="17.25" customHeight="1">
+      <c r="A68" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="69" ht="17.25" customHeight="1">
+      <c r="A69" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="70" ht="17.25" customHeight="1">
+      <c r="A70" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="B70" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A22" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A23" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A24" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A25" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A26" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A27" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A28" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A29" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A30" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A31" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A32" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A33" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A34" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A35" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A36" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A37" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A38" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A39" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A40" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A41" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A42" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A43" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A44" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A45" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A46" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A47" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A48" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A49" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A50" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A51" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A52" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A53" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A54" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A55" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A56" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A57" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A58" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A59" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A60" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A61" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A62" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A63" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A64" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A65" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A66" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A67" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A68" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A69" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A70" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A71" s="5" t="s">
+    </row>
+    <row r="71" ht="17.25" customHeight="1">
+      <c r="A71" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="8" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="72" spans="1:2" ht="17.25" customHeight="1"/>
-    <row r="73" spans="1:2" ht="17.25" customHeight="1"/>
-    <row r="74" spans="1:2" ht="17.25" customHeight="1"/>
-    <row r="75" spans="1:2" ht="17.25" customHeight="1"/>
-    <row r="76" spans="1:2" ht="17.25" customHeight="1"/>
-    <row r="77" spans="1:2" ht="17.25" customHeight="1"/>
-    <row r="78" spans="1:2" ht="17.25" customHeight="1"/>
-    <row r="79" spans="1:2" ht="17.25" customHeight="1"/>
-    <row r="80" spans="1:2" ht="17.25" customHeight="1"/>
+    <row r="72" ht="17.25" customHeight="1">
+      <c r="A72" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="73" ht="17.25" customHeight="1"/>
+    <row r="74" ht="17.25" customHeight="1"/>
+    <row r="75" ht="17.25" customHeight="1"/>
+    <row r="76" ht="17.25" customHeight="1"/>
+    <row r="77" ht="17.25" customHeight="1"/>
+    <row r="78" ht="17.25" customHeight="1"/>
+    <row r="79" ht="17.25" customHeight="1"/>
+    <row r="80" ht="17.25" customHeight="1"/>
     <row r="81" ht="17.25" customHeight="1"/>
     <row r="82" ht="17.25" customHeight="1"/>
     <row r="83" ht="17.25" customHeight="1"/>
@@ -2299,8 +2288,9 @@
     <row r="999" ht="17.25" customHeight="1"/>
     <row r="1000" ht="17.25" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape" r:id="rId1"/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
@@ -1,15 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="enqOkH1Z/tfQ3WIfr7wm+HPEzSLVVhkZawHcM088EJg="/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -459,41 +470,190 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Malgun Gothic"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Malgun Gothic"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
-      <color theme="1"/>
-      <name val="Malgun Gothic"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.0"/>
-      <color theme="1"/>
-      <name val="Malgun Gothic"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.0"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -501,68 +661,736 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
-    <border/>
+  <borders count="9">
     <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color rgb="FFB2B2B2"/>
       </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="2" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -752,23 +1580,23 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C1000"/>
+  <sheetFormatPr defaultColWidth="14.4259259259259" defaultRowHeight="15" customHeight="1" outlineLevelCol="2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="52.14"/>
-    <col customWidth="1" min="2" max="2" width="35.14"/>
-    <col customWidth="1" min="3" max="3" width="31.43"/>
-    <col customWidth="1" min="4" max="26" width="9.0"/>
+    <col min="1" max="1" width="52.1388888888889" customWidth="1"/>
+    <col min="2" max="2" width="35.1388888888889" customWidth="1"/>
+    <col min="3" max="3" width="31.4259259259259" customWidth="1"/>
+    <col min="4" max="26" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1">
+    <row r="1" ht="17.25" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -779,7 +1607,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="17.25" customHeight="1">
+    <row r="2" ht="17.25" customHeight="1" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -790,7 +1618,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" ht="17.25" customHeight="1">
+    <row r="3" ht="17.25" customHeight="1" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -801,7 +1629,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" ht="17.25" customHeight="1">
+    <row r="4" ht="17.25" customHeight="1" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -809,7 +1637,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" ht="17.25" customHeight="1">
+    <row r="5" ht="17.25" customHeight="1" spans="1:3">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -817,7 +1645,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" ht="17.25" customHeight="1">
+    <row r="6" ht="17.25" customHeight="1" spans="1:3">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -825,7 +1653,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" ht="17.25" customHeight="1">
+    <row r="7" ht="17.25" customHeight="1" spans="1:3">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -833,7 +1661,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" ht="17.25" customHeight="1">
+    <row r="8" ht="17.25" customHeight="1" spans="1:3">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -841,7 +1669,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" ht="17.25" customHeight="1">
+    <row r="9" ht="17.25" customHeight="1" spans="1:3">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -849,7 +1677,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" ht="17.25" customHeight="1">
+    <row r="10" ht="17.25" customHeight="1" spans="1:3">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -857,7 +1685,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" ht="17.25" customHeight="1">
+    <row r="11" ht="17.25" customHeight="1" spans="1:3">
       <c r="A11" s="1" t="s">
         <v>21</v>
       </c>
@@ -865,7 +1693,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" ht="17.25" customHeight="1">
+    <row r="12" ht="17.25" customHeight="1" spans="1:3">
       <c r="A12" s="1" t="s">
         <v>23</v>
       </c>
@@ -873,7 +1701,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" ht="17.25" customHeight="1">
+    <row r="13" ht="17.25" customHeight="1" spans="1:3">
       <c r="A13" s="1" t="s">
         <v>25</v>
       </c>
@@ -881,7 +1709,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" ht="17.25" customHeight="1">
+    <row r="14" ht="17.25" customHeight="1" spans="1:3">
       <c r="A14" s="1" t="s">
         <v>27</v>
       </c>
@@ -889,7 +1717,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" ht="17.25" customHeight="1">
+    <row r="15" ht="17.25" customHeight="1" spans="1:3">
       <c r="A15" s="1" t="s">
         <v>29</v>
       </c>
@@ -897,7 +1725,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" ht="17.25" customHeight="1">
+    <row r="16" ht="17.25" customHeight="1" spans="1:3">
       <c r="A16" s="1" t="s">
         <v>31</v>
       </c>
@@ -905,7 +1733,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" ht="17.25" customHeight="1">
+    <row r="17" ht="17.25" customHeight="1" spans="1:2">
       <c r="A17" s="1" t="s">
         <v>33</v>
       </c>
@@ -913,7 +1741,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" ht="17.25" customHeight="1">
+    <row r="18" ht="17.25" customHeight="1" spans="1:2">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -921,7 +1749,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" ht="17.25" customHeight="1">
+    <row r="19" ht="17.25" customHeight="1" spans="1:2">
       <c r="A19" s="1" t="s">
         <v>37</v>
       </c>
@@ -929,7 +1757,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" ht="17.25" customHeight="1">
+    <row r="20" ht="17.25" customHeight="1" spans="1:2">
       <c r="A20" s="1" t="s">
         <v>39</v>
       </c>
@@ -937,7 +1765,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" ht="17.25" customHeight="1">
+    <row r="21" ht="17.25" customHeight="1" spans="1:2">
       <c r="A21" s="1" t="s">
         <v>41</v>
       </c>
@@ -945,7 +1773,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" ht="17.25" customHeight="1">
+    <row r="22" ht="17.25" customHeight="1" spans="1:2">
       <c r="A22" s="1" t="s">
         <v>43</v>
       </c>
@@ -953,7 +1781,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" ht="17.25" customHeight="1">
+    <row r="23" ht="17.25" customHeight="1" spans="1:2">
       <c r="A23" s="1" t="s">
         <v>45</v>
       </c>
@@ -961,7 +1789,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" ht="17.25" customHeight="1">
+    <row r="24" ht="17.25" customHeight="1" spans="1:2">
       <c r="A24" s="1" t="s">
         <v>47</v>
       </c>
@@ -969,7 +1797,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" ht="17.25" customHeight="1">
+    <row r="25" ht="17.25" customHeight="1" spans="1:2">
       <c r="A25" s="1" t="s">
         <v>49</v>
       </c>
@@ -977,7 +1805,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" ht="17.25" customHeight="1">
+    <row r="26" ht="17.25" customHeight="1" spans="1:2">
       <c r="A26" s="1" t="s">
         <v>51</v>
       </c>
@@ -985,7 +1813,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" ht="17.25" customHeight="1">
+    <row r="27" ht="17.25" customHeight="1" spans="1:2">
       <c r="A27" s="1" t="s">
         <v>53</v>
       </c>
@@ -993,7 +1821,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" ht="17.25" customHeight="1">
+    <row r="28" ht="17.25" customHeight="1" spans="1:2">
       <c r="A28" s="1" t="s">
         <v>55</v>
       </c>
@@ -1001,7 +1829,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" ht="17.25" customHeight="1">
+    <row r="29" ht="17.25" customHeight="1" spans="1:2">
       <c r="A29" s="1" t="s">
         <v>57</v>
       </c>
@@ -1009,7 +1837,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" ht="17.25" customHeight="1">
+    <row r="30" ht="17.25" customHeight="1" spans="1:2">
       <c r="A30" s="1" t="s">
         <v>59</v>
       </c>
@@ -1017,7 +1845,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" ht="17.25" customHeight="1">
+    <row r="31" ht="17.25" customHeight="1" spans="1:2">
       <c r="A31" s="1" t="s">
         <v>61</v>
       </c>
@@ -1025,7 +1853,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="32" ht="17.25" customHeight="1">
+    <row r="32" ht="17.25" customHeight="1" spans="1:2">
       <c r="A32" s="1" t="s">
         <v>63</v>
       </c>
@@ -1033,7 +1861,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" ht="17.25" customHeight="1">
+    <row r="33" ht="17.25" customHeight="1" spans="1:2">
       <c r="A33" s="1" t="s">
         <v>65</v>
       </c>
@@ -1041,7 +1869,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="34" ht="17.25" customHeight="1">
+    <row r="34" ht="17.25" customHeight="1" spans="1:2">
       <c r="A34" s="1" t="s">
         <v>67</v>
       </c>
@@ -1049,7 +1877,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="35" ht="17.25" customHeight="1">
+    <row r="35" ht="17.25" customHeight="1" spans="1:2">
       <c r="A35" s="1" t="s">
         <v>69</v>
       </c>
@@ -1057,7 +1885,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" ht="17.25" customHeight="1">
+    <row r="36" ht="17.25" customHeight="1" spans="1:2">
       <c r="A36" s="1" t="s">
         <v>71</v>
       </c>
@@ -1065,7 +1893,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="37" ht="17.25" customHeight="1">
+    <row r="37" ht="17.25" customHeight="1" spans="1:2">
       <c r="A37" s="1" t="s">
         <v>73</v>
       </c>
@@ -1073,7 +1901,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" ht="17.25" customHeight="1">
+    <row r="38" ht="17.25" customHeight="1" spans="1:2">
       <c r="A38" s="1" t="s">
         <v>75</v>
       </c>
@@ -1081,7 +1909,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" ht="17.25" customHeight="1">
+    <row r="39" ht="17.25" customHeight="1" spans="1:2">
       <c r="A39" s="1" t="s">
         <v>77</v>
       </c>
@@ -1089,7 +1917,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" ht="17.25" customHeight="1">
+    <row r="40" ht="17.25" customHeight="1" spans="1:2">
       <c r="A40" s="1" t="s">
         <v>79</v>
       </c>
@@ -1097,7 +1925,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41" ht="17.25" customHeight="1">
+    <row r="41" ht="17.25" customHeight="1" spans="1:2">
       <c r="A41" s="1" t="s">
         <v>81</v>
       </c>
@@ -1105,7 +1933,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" ht="17.25" customHeight="1">
+    <row r="42" ht="17.25" customHeight="1" spans="1:2">
       <c r="A42" s="1" t="s">
         <v>83</v>
       </c>
@@ -1113,7 +1941,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" ht="17.25" customHeight="1">
+    <row r="43" ht="17.25" customHeight="1" spans="1:2">
       <c r="A43" s="1" t="s">
         <v>85</v>
       </c>
@@ -1121,7 +1949,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="44" ht="17.25" customHeight="1">
+    <row r="44" ht="17.25" customHeight="1" spans="1:2">
       <c r="A44" s="1" t="s">
         <v>87</v>
       </c>
@@ -1129,7 +1957,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="45" ht="17.25" customHeight="1">
+    <row r="45" ht="17.25" customHeight="1" spans="1:2">
       <c r="A45" s="1" t="s">
         <v>89</v>
       </c>
@@ -1137,7 +1965,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="46" ht="17.25" customHeight="1">
+    <row r="46" ht="17.25" customHeight="1" spans="1:2">
       <c r="A46" s="1" t="s">
         <v>91</v>
       </c>
@@ -1145,7 +1973,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="47" ht="17.25" customHeight="1">
+    <row r="47" ht="17.25" customHeight="1" spans="1:2">
       <c r="A47" s="2" t="s">
         <v>93</v>
       </c>
@@ -1153,7 +1981,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="48" ht="17.25" customHeight="1">
+    <row r="48" ht="17.25" customHeight="1" spans="1:2">
       <c r="A48" s="2" t="s">
         <v>95</v>
       </c>
@@ -1161,109 +1989,109 @@
         <v>96</v>
       </c>
     </row>
-    <row r="49" ht="17.25" customHeight="1">
-      <c r="A49" s="2" t="s">
+    <row r="49" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A49" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="5" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="50" ht="17.25" customHeight="1">
-      <c r="A50" s="2" t="s">
+    <row r="50" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A50" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="4" t="s">
         <v>100</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="51" ht="17.25" customHeight="1">
-      <c r="A51" s="2" t="s">
+    <row r="51" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A51" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="B51" s="6" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="52" ht="17.25" customHeight="1">
-      <c r="A52" s="2" t="s">
+    <row r="52" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A52" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B52" s="6" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="53" ht="17.25" customHeight="1">
-      <c r="A53" s="2" t="s">
+    <row r="53" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A53" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B53" s="6" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="54" ht="17.25" customHeight="1">
-      <c r="A54" s="2" t="s">
+    <row r="54" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A54" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="6" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="55" ht="17.25" customHeight="1">
-      <c r="A55" s="2" t="s">
+    <row r="55" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A55" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="B55" s="6" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="56" ht="17.25" customHeight="1">
-      <c r="A56" s="2" t="s">
+    <row r="56" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A56" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B56" s="6" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="57" ht="17.25" customHeight="1">
-      <c r="A57" s="2" t="s">
+    <row r="57" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A57" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="B57" s="7" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="58" ht="17.25" customHeight="1">
-      <c r="A58" s="2" t="s">
+    <row r="58" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A58" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="8" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="59" ht="17.25" customHeight="1">
-      <c r="A59" s="2" t="s">
+    <row r="59" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A59" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B59" s="8" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="60" ht="17.25" customHeight="1">
-      <c r="A60" s="6" t="s">
+    <row r="60" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A60" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="B60" s="6" t="s">
+      <c r="B60" s="9" t="s">
         <v>121</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="61" ht="17.25" customHeight="1">
+    <row r="61" ht="17.25" customHeight="1" spans="1:3">
       <c r="A61" s="2" t="s">
         <v>122</v>
       </c>
@@ -1271,91 +2099,91 @@
         <v>123</v>
       </c>
     </row>
-    <row r="62" ht="17.25" customHeight="1">
-      <c r="A62" s="7" t="s">
+    <row r="62" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A62" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="B62" s="8" t="s">
+      <c r="B62" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="63" ht="17.25" customHeight="1">
-      <c r="A63" s="7" t="s">
+    <row r="63" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A63" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="B63" s="8" t="s">
+      <c r="B63" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="64" ht="17.25" customHeight="1">
-      <c r="A64" s="7" t="s">
+    <row r="64" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A64" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="B64" s="8" t="s">
+      <c r="B64" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="65" ht="17.25" customHeight="1">
-      <c r="A65" s="7" t="s">
+    <row r="65" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A65" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="B65" s="8" t="s">
+      <c r="B65" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="66" ht="17.25" customHeight="1">
-      <c r="A66" s="7" t="s">
+    <row r="66" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A66" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="B66" s="8" t="s">
+      <c r="B66" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="67" ht="17.25" customHeight="1">
-      <c r="A67" s="7" t="s">
+    <row r="67" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A67" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="B67" s="8" t="s">
+      <c r="B67" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="68" ht="17.25" customHeight="1">
-      <c r="A68" s="7" t="s">
+    <row r="68" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A68" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="B68" s="8" t="s">
+      <c r="B68" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="69" ht="17.25" customHeight="1">
-      <c r="A69" s="7" t="s">
+    <row r="69" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A69" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="B69" s="8" t="s">
+      <c r="B69" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="70" ht="17.25" customHeight="1">
-      <c r="A70" s="7" t="s">
+    <row r="70" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A70" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="B70" s="8" t="s">
+      <c r="B70" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="71" ht="17.25" customHeight="1">
-      <c r="A71" s="8" t="s">
+    <row r="71" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A71" t="s">
         <v>142</v>
       </c>
-      <c r="B71" s="8" t="s">
+      <c r="B71" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="72" ht="17.25" customHeight="1">
-      <c r="A72" s="8" t="s">
+    <row r="72" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A72" t="s">
         <v>144</v>
       </c>
-      <c r="B72" s="8" t="s">
+      <c r="B72" t="s">
         <v>145</v>
       </c>
     </row>
@@ -2288,9 +3116,8 @@
     <row r="999" ht="17.25" customHeight="1"/>
     <row r="1000" ht="17.25" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="1" orientation="landscape"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
@@ -1,31 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\팀과제\JewelThief\JsonConverter\ExcelFiles\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EDB8936-FC6C-4EED-A460-21DFEB13AAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5232" yWindow="1452" windowWidth="16824" windowHeight="9048" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="enqOkH1Z/tfQ3WIfr7wm+HPEzSLVVhkZawHcM088EJg="/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="174">
   <si>
     <t>미리 로드할 어드레서블 테이블</t>
   </si>
@@ -150,6 +152,9 @@
     <t>All Direction Corridor</t>
   </si>
   <si>
+    <t>PreLoadAsset_Lobby</t>
+  </si>
+  <si>
     <t>Lobby</t>
   </si>
   <si>
@@ -450,69 +455,291 @@
     <t>Effect_Normal</t>
   </si>
   <si>
-    <t>PreLoadAsset_Lobby</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>PreLoadAsset_JewelInventory</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>JewelInventory</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_GameObject_PaintingObject</t>
+  </si>
+  <si>
+    <t>Pool_Painting</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_Painting_1[Painting_1]</t>
+  </si>
+  <si>
+    <t>Painting_1[Painting_1]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_Painting_2[Painting_2]</t>
+  </si>
+  <si>
+    <t>Painting_2[Painting_2]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_Painting_3[Painting_8]</t>
+  </si>
+  <si>
+    <t>Painting_3[Painting_8]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_Painting_4[Painting_4]</t>
+  </si>
+  <si>
+    <t>Painting_4[Painting_4]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_Painting_5[Painting_5]</t>
+  </si>
+  <si>
+    <t>Painting_5[Painting_5]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_Painting_1</t>
+  </si>
+  <si>
+    <t>Painting_1</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_Painting_2</t>
+  </si>
+  <si>
+    <t>Painting_2</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_Painting_3</t>
+  </si>
+  <si>
+    <t>Painting_3</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_Painting_6</t>
+  </si>
+  <si>
+    <t>Painting_6</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_Painting_8</t>
+  </si>
+  <si>
+    <t>Painting_8</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_PaintingFrame_Gold</t>
+  </si>
+  <si>
+    <t>PaintingFrame_Gold</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_PaintingFrame_Black</t>
+  </si>
+  <si>
+    <t>PaintingFrame_Black</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_PaintingFrame_White</t>
+  </si>
+  <si>
+    <t>PaintingFrame_White</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_PaintingFrame_WoodHell</t>
+  </si>
+  <si>
+    <t>PaintingFrame_WoodHell</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Malgun Gothic"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Malgun Gothic"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Malgun Gothic"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Malgun Gothic"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -525,8 +752,194 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -549,31 +962,316 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -771,22 +1469,22 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1000"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C1002"/>
+  <sheetFormatPr defaultColWidth="14.4444444444444" defaultRowHeight="15" customHeight="1" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="52.109375" customWidth="1"/>
-    <col min="2" max="2" width="35.109375" customWidth="1"/>
-    <col min="3" max="3" width="31.44140625" customWidth="1"/>
+    <col min="1" max="1" width="52.1111111111111" customWidth="1"/>
+    <col min="2" max="2" width="35.1111111111111" customWidth="1"/>
+    <col min="3" max="3" width="31.4444444444444" customWidth="1"/>
     <col min="4" max="26" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="17.25" customHeight="1">
+    <row r="1" ht="17.25" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -797,7 +1495,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="17.25" customHeight="1">
+    <row r="2" ht="17.25" customHeight="1" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -808,7 +1506,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="17.25" customHeight="1">
+    <row r="3" ht="17.25" customHeight="1" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -819,7 +1517,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="17.25" customHeight="1">
+    <row r="4" ht="17.25" customHeight="1" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -827,7 +1525,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="17.25" customHeight="1">
+    <row r="5" ht="17.25" customHeight="1" spans="1:3">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -835,7 +1533,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="17.25" customHeight="1">
+    <row r="6" ht="17.25" customHeight="1" spans="1:3">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -843,7 +1541,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="17.25" customHeight="1">
+    <row r="7" ht="17.25" customHeight="1" spans="1:3">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -851,7 +1549,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="17.25" customHeight="1">
+    <row r="8" ht="17.25" customHeight="1" spans="1:3">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -859,7 +1557,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="17.25" customHeight="1">
+    <row r="9" ht="17.25" customHeight="1" spans="1:3">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -867,7 +1565,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="17.25" customHeight="1">
+    <row r="10" ht="17.25" customHeight="1" spans="1:3">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -875,7 +1573,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="17.25" customHeight="1">
+    <row r="11" ht="17.25" customHeight="1" spans="1:3">
       <c r="A11" s="1" t="s">
         <v>21</v>
       </c>
@@ -883,7 +1581,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="17.25" customHeight="1">
+    <row r="12" ht="17.25" customHeight="1" spans="1:3">
       <c r="A12" s="1" t="s">
         <v>23</v>
       </c>
@@ -891,7 +1589,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="17.25" customHeight="1">
+    <row r="13" ht="17.25" customHeight="1" spans="1:3">
       <c r="A13" s="1" t="s">
         <v>25</v>
       </c>
@@ -899,7 +1597,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="17.25" customHeight="1">
+    <row r="14" ht="17.25" customHeight="1" spans="1:3">
       <c r="A14" s="1" t="s">
         <v>27</v>
       </c>
@@ -907,7 +1605,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="17.25" customHeight="1">
+    <row r="15" ht="17.25" customHeight="1" spans="1:3">
       <c r="A15" s="1" t="s">
         <v>29</v>
       </c>
@@ -915,7 +1613,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="17.25" customHeight="1">
+    <row r="16" ht="17.25" customHeight="1" spans="1:3">
       <c r="A16" s="1" t="s">
         <v>31</v>
       </c>
@@ -923,7 +1621,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="17.25" customHeight="1">
+    <row r="17" ht="17.25" customHeight="1" spans="1:2">
       <c r="A17" s="1" t="s">
         <v>33</v>
       </c>
@@ -931,7 +1629,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="17.25" customHeight="1">
+    <row r="18" ht="17.25" customHeight="1" spans="1:2">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -939,7 +1637,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="17.25" customHeight="1">
+    <row r="19" ht="17.25" customHeight="1" spans="1:2">
       <c r="A19" s="1" t="s">
         <v>37</v>
       </c>
@@ -947,7 +1645,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="17.25" customHeight="1">
+    <row r="20" ht="17.25" customHeight="1" spans="1:2">
       <c r="A20" s="1" t="s">
         <v>39</v>
       </c>
@@ -955,441 +1653,555 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A21" s="7" t="s">
+    <row r="21" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A21" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A23" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A24" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A25" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A26" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A27" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A28" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A29" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A30" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A31" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="32" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A32" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A33" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="34" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A34" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="35" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A35" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="36" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A36" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A37" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A38" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A39" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="40" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A40" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A41" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="42" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A42" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A43" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="44" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A44" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="45" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A45" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="46" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A46" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="47" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A47" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="48" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A48" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="49" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A49" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="50" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A50" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="51" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A51" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="52" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A52" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="53" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A53" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="54" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A54" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="55" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A55" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="56" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A56" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="57" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A57" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="58" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A58" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="59" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A59" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="60" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A60" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="61" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A61" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="62" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A62" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B62" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="63" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A63" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B63" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="64" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A64" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B64" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="65" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A65" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B65" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="66" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A66" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B66" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="67" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A67" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B67" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="68" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A68" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B68" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="69" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A69" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B69" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="70" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A70" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="B70" t="s">
         <v>141</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A22" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A23" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A24" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A25" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A26" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A27" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A28" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A29" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A30" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A31" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A32" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A33" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A34" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A35" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A36" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A37" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A38" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A39" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A40" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A41" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A42" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A43" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A44" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A45" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A46" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A47" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A48" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A49" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A50" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A51" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A52" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A53" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A54" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A55" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A56" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A57" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A58" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A59" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A60" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A61" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A62" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A63" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A64" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A65" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A66" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A67" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A68" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A69" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A70" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A71" s="5" t="s">
+    </row>
+    <row r="71" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A71" s="6" t="s">
         <v>142</v>
       </c>
       <c r="B71" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="72" spans="1:2" ht="17.25" customHeight="1"/>
-    <row r="73" spans="1:2" ht="17.25" customHeight="1"/>
-    <row r="74" spans="1:2" ht="17.25" customHeight="1"/>
-    <row r="75" spans="1:2" ht="17.25" customHeight="1"/>
-    <row r="76" spans="1:2" ht="17.25" customHeight="1"/>
-    <row r="77" spans="1:2" ht="17.25" customHeight="1"/>
-    <row r="78" spans="1:2" ht="17.25" customHeight="1"/>
-    <row r="79" spans="1:2" ht="17.25" customHeight="1"/>
-    <row r="80" spans="1:2" ht="17.25" customHeight="1"/>
-    <row r="81" ht="17.25" customHeight="1"/>
-    <row r="82" ht="17.25" customHeight="1"/>
-    <row r="83" ht="17.25" customHeight="1"/>
-    <row r="84" ht="17.25" customHeight="1"/>
-    <row r="85" ht="17.25" customHeight="1"/>
-    <row r="86" ht="17.25" customHeight="1"/>
-    <row r="87" ht="17.25" customHeight="1"/>
-    <row r="88" ht="17.25" customHeight="1"/>
-    <row r="89" ht="17.25" customHeight="1"/>
-    <row r="90" ht="17.25" customHeight="1"/>
-    <row r="91" ht="17.25" customHeight="1"/>
-    <row r="92" ht="17.25" customHeight="1"/>
+    <row r="72" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A72" t="s">
+        <v>144</v>
+      </c>
+      <c r="B72" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="73" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A73" t="s">
+        <v>146</v>
+      </c>
+      <c r="B73" t="s">
+        <v>147</v>
+      </c>
+      <c r="C73" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="74" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A74" t="s">
+        <v>148</v>
+      </c>
+      <c r="B74" t="s">
+        <v>149</v>
+      </c>
+      <c r="C74" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="75" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A75" t="s">
+        <v>150</v>
+      </c>
+      <c r="B75" t="s">
+        <v>151</v>
+      </c>
+      <c r="C75" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="76" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A76" t="s">
+        <v>152</v>
+      </c>
+      <c r="B76" t="s">
+        <v>153</v>
+      </c>
+      <c r="C76" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="77" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A77" t="s">
+        <v>154</v>
+      </c>
+      <c r="B77" t="s">
+        <v>155</v>
+      </c>
+      <c r="C77" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="78" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A78" t="s">
+        <v>156</v>
+      </c>
+      <c r="B78" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="79" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A79" t="s">
+        <v>158</v>
+      </c>
+      <c r="B79" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="80" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A80" t="s">
+        <v>160</v>
+      </c>
+      <c r="B80" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="81" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A81" t="s">
+        <v>162</v>
+      </c>
+      <c r="B81" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="82" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A82" t="s">
+        <v>164</v>
+      </c>
+      <c r="B82" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="83" ht="14.4" spans="1:2">
+      <c r="A83" t="s">
+        <v>166</v>
+      </c>
+      <c r="B83" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="84" ht="14.4" spans="1:2">
+      <c r="A84" t="s">
+        <v>168</v>
+      </c>
+      <c r="B84" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="85" ht="14.4" spans="1:2">
+      <c r="A85" t="s">
+        <v>170</v>
+      </c>
+      <c r="B85" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="86" ht="14.4" spans="1:2">
+      <c r="A86" t="s">
+        <v>172</v>
+      </c>
+      <c r="B86" t="s">
+        <v>173</v>
+      </c>
+    </row>
     <row r="93" ht="17.25" customHeight="1"/>
     <row r="94" ht="17.25" customHeight="1"/>
     <row r="95" ht="17.25" customHeight="1"/>
@@ -2298,9 +3110,11 @@
     <row r="998" ht="17.25" customHeight="1"/>
     <row r="999" ht="17.25" customHeight="1"/>
     <row r="1000" ht="17.25" customHeight="1"/>
+    <row r="1001" ht="17.25" customHeight="1"/>
+    <row r="1002" ht="17.25" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="1" orientation="landscape"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="15636" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -470,31 +470,31 @@
     <t>PreLoadAsset_Mesh_Painting_1[Painting_1]</t>
   </si>
   <si>
-    <t>Painting_1[Painting_1]</t>
+    <t>Painting_1_Mesh[Painting_1]</t>
   </si>
   <si>
     <t>PreLoadAsset_Mesh_Painting_2[Painting_2]</t>
   </si>
   <si>
-    <t>Painting_2[Painting_2]</t>
+    <t>Painting_2_Mesh[Painting_2]</t>
   </si>
   <si>
     <t>PreLoadAsset_Mesh_Painting_3[Painting_8]</t>
   </si>
   <si>
-    <t>Painting_3[Painting_8]</t>
+    <t>Painting_3_Mesh[Painting_8]</t>
   </si>
   <si>
     <t>PreLoadAsset_Mesh_Painting_4[Painting_4]</t>
   </si>
   <si>
-    <t>Painting_4[Painting_4]</t>
+    <t>Painting_4_Mesh[Painting_4]</t>
   </si>
   <si>
     <t>PreLoadAsset_Mesh_Painting_5[Painting_5]</t>
   </si>
   <si>
-    <t>Painting_5[Painting_5]</t>
+    <t>Painting_5_Mesh[Painting_5]</t>
   </si>
   <si>
     <t>PreLoadAsset_Material_Painting_1</t>
@@ -561,7 +561,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -574,13 +574,6 @@
       <color theme="1"/>
       <name val="Malgun Gothic"/>
       <charset val="129"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1078,143 +1071,142 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -1654,7 +1646,7 @@
       </c>
     </row>
     <row r="21" ht="17.25" customHeight="1" spans="1:2">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -1673,7 +1665,7 @@
       <c r="A23" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="3" t="s">
         <v>46</v>
       </c>
     </row>
@@ -1681,7 +1673,7 @@
       <c r="A24" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="3" t="s">
         <v>48</v>
       </c>
     </row>
@@ -1689,7 +1681,7 @@
       <c r="A25" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="3" t="s">
         <v>50</v>
       </c>
     </row>
@@ -1697,7 +1689,7 @@
       <c r="A26" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="3" t="s">
         <v>52</v>
       </c>
     </row>
@@ -1705,7 +1697,7 @@
       <c r="A27" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="3" t="s">
         <v>54</v>
       </c>
     </row>
@@ -1713,7 +1705,7 @@
       <c r="A28" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="3" t="s">
         <v>56</v>
       </c>
     </row>
@@ -1721,7 +1713,7 @@
       <c r="A29" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="3" t="s">
         <v>58</v>
       </c>
     </row>
@@ -1729,7 +1721,7 @@
       <c r="A30" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="3" t="s">
         <v>60</v>
       </c>
     </row>
@@ -1737,7 +1729,7 @@
       <c r="A31" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="3" t="s">
         <v>62</v>
       </c>
     </row>
@@ -1745,7 +1737,7 @@
       <c r="A32" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="3" t="s">
         <v>64</v>
       </c>
     </row>
@@ -1753,7 +1745,7 @@
       <c r="A33" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="3" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1761,7 +1753,7 @@
       <c r="A34" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="3" t="s">
         <v>68</v>
       </c>
     </row>
@@ -1769,7 +1761,7 @@
       <c r="A35" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="3" t="s">
         <v>70</v>
       </c>
     </row>
@@ -1777,7 +1769,7 @@
       <c r="A36" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="3" t="s">
         <v>72</v>
       </c>
     </row>
@@ -1785,7 +1777,7 @@
       <c r="A37" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="3" t="s">
         <v>74</v>
       </c>
     </row>
@@ -1793,7 +1785,7 @@
       <c r="A38" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="3" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1801,7 +1793,7 @@
       <c r="A39" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="3" t="s">
         <v>78</v>
       </c>
     </row>
@@ -1809,7 +1801,7 @@
       <c r="A40" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="3" t="s">
         <v>80</v>
       </c>
     </row>
@@ -1817,7 +1809,7 @@
       <c r="A41" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="3" t="s">
         <v>82</v>
       </c>
     </row>
@@ -1825,7 +1817,7 @@
       <c r="A42" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="3" t="s">
         <v>84</v>
       </c>
     </row>
@@ -1833,7 +1825,7 @@
       <c r="A43" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="3" t="s">
         <v>86</v>
       </c>
     </row>
@@ -1841,7 +1833,7 @@
       <c r="A44" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="3" t="s">
         <v>88</v>
       </c>
     </row>
@@ -1849,7 +1841,7 @@
       <c r="A45" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="3" t="s">
         <v>90</v>
       </c>
     </row>
@@ -1857,7 +1849,7 @@
       <c r="A46" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="3" t="s">
         <v>92</v>
       </c>
     </row>
@@ -1873,7 +1865,7 @@
       <c r="A48" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="3" t="s">
         <v>96</v>
       </c>
     </row>
@@ -1900,7 +1892,7 @@
       <c r="A51" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="B51" s="4" t="s">
         <v>103</v>
       </c>
     </row>
@@ -1908,7 +1900,7 @@
       <c r="A52" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="B52" s="4" t="s">
         <v>105</v>
       </c>
     </row>
@@ -1916,7 +1908,7 @@
       <c r="A53" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B53" s="4" t="s">
         <v>107</v>
       </c>
     </row>
@@ -1924,7 +1916,7 @@
       <c r="A54" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="B54" s="4" t="s">
         <v>109</v>
       </c>
     </row>
@@ -1932,7 +1924,7 @@
       <c r="A55" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="B55" s="4" t="s">
         <v>111</v>
       </c>
     </row>
@@ -1940,7 +1932,7 @@
       <c r="A56" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B56" s="4" t="s">
         <v>113</v>
       </c>
     </row>
@@ -1948,7 +1940,7 @@
       <c r="A57" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="B57" s="4" t="s">
         <v>115</v>
       </c>
     </row>
@@ -1956,7 +1948,7 @@
       <c r="A58" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="B58" s="4" t="s">
         <v>117</v>
       </c>
     </row>
@@ -1964,15 +1956,15 @@
       <c r="A59" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="B59" s="4" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="60" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A60" s="5" t="s">
+      <c r="A60" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="B60" s="4" t="s">
         <v>121</v>
       </c>
       <c r="C60" s="2" t="s">
@@ -1988,7 +1980,7 @@
       </c>
     </row>
     <row r="62" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A62" s="6" t="s">
+      <c r="A62" s="5" t="s">
         <v>124</v>
       </c>
       <c r="B62" t="s">
@@ -1996,7 +1988,7 @@
       </c>
     </row>
     <row r="63" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A63" s="6" t="s">
+      <c r="A63" s="5" t="s">
         <v>126</v>
       </c>
       <c r="B63" t="s">
@@ -2004,7 +1996,7 @@
       </c>
     </row>
     <row r="64" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A64" s="6" t="s">
+      <c r="A64" s="5" t="s">
         <v>128</v>
       </c>
       <c r="B64" t="s">
@@ -2012,7 +2004,7 @@
       </c>
     </row>
     <row r="65" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A65" s="6" t="s">
+      <c r="A65" s="5" t="s">
         <v>130</v>
       </c>
       <c r="B65" t="s">
@@ -2020,7 +2012,7 @@
       </c>
     </row>
     <row r="66" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A66" s="6" t="s">
+      <c r="A66" s="5" t="s">
         <v>132</v>
       </c>
       <c r="B66" t="s">
@@ -2028,7 +2020,7 @@
       </c>
     </row>
     <row r="67" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A67" s="6" t="s">
+      <c r="A67" s="5" t="s">
         <v>134</v>
       </c>
       <c r="B67" t="s">
@@ -2036,7 +2028,7 @@
       </c>
     </row>
     <row r="68" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A68" s="6" t="s">
+      <c r="A68" s="5" t="s">
         <v>136</v>
       </c>
       <c r="B68" t="s">
@@ -2044,7 +2036,7 @@
       </c>
     </row>
     <row r="69" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A69" s="6" t="s">
+      <c r="A69" s="5" t="s">
         <v>138</v>
       </c>
       <c r="B69" t="s">
@@ -2052,7 +2044,7 @@
       </c>
     </row>
     <row r="70" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A70" s="6" t="s">
+      <c r="A70" s="5" t="s">
         <v>140</v>
       </c>
       <c r="B70" t="s">
@@ -2060,7 +2052,7 @@
       </c>
     </row>
     <row r="71" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A71" s="6" t="s">
+      <c r="A71" s="5" t="s">
         <v>142</v>
       </c>
       <c r="B71" t="s">

--- a/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="15636" windowHeight="8400"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="186">
   <si>
     <t>미리 로드할 어드레서블 테이블</t>
   </si>
@@ -467,31 +467,31 @@
     <t>Pool_Painting</t>
   </si>
   <si>
-    <t>PreLoadAsset_Mesh_Painting_1[Painting_1]</t>
+    <t>PreLoadAsset_Mesh_Painting_1</t>
   </si>
   <si>
     <t>Painting_1_Mesh[Painting_1]</t>
   </si>
   <si>
-    <t>PreLoadAsset_Mesh_Painting_2[Painting_2]</t>
+    <t>PreLoadAsset_Mesh_Painting_2</t>
   </si>
   <si>
     <t>Painting_2_Mesh[Painting_2]</t>
   </si>
   <si>
-    <t>PreLoadAsset_Mesh_Painting_3[Painting_8]</t>
+    <t>PreLoadAsset_Mesh_Painting_3</t>
   </si>
   <si>
     <t>Painting_3_Mesh[Painting_8]</t>
   </si>
   <si>
-    <t>PreLoadAsset_Mesh_Painting_4[Painting_4]</t>
+    <t>PreLoadAsset_Mesh_Painting_4</t>
   </si>
   <si>
     <t>Painting_4_Mesh[Painting_4]</t>
   </si>
   <si>
-    <t>PreLoadAsset_Mesh_Painting_5[Painting_5]</t>
+    <t>PreLoadAsset_Mesh_Painting_5</t>
   </si>
   <si>
     <t>Painting_5_Mesh[Painting_5]</t>
@@ -549,6 +549,42 @@
   </si>
   <si>
     <t>PaintingFrame_WoodHell</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_GameObject_StatueObject</t>
+  </si>
+  <si>
+    <t>Pool_Statue</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_SeatedLion</t>
+  </si>
+  <si>
+    <t>SeatedLion[Seated_Lion_LOD0]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_Statue_Stone</t>
+  </si>
+  <si>
+    <t>Statue_Stone</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_Statue_Copper</t>
+  </si>
+  <si>
+    <t>Statue_Copper</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_Statue_Metal</t>
+  </si>
+  <si>
+    <t>Statue_Metal</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_Statue_Marble</t>
+  </si>
+  <si>
+    <t>Statue_Marble</t>
   </si>
 </sst>
 </file>
@@ -942,16 +978,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1201,13 +1237,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1467,7 +1505,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C1002"/>
+  <dimension ref="A1:C1003"/>
   <sheetFormatPr defaultColWidth="14.4444444444444" defaultRowHeight="15" customHeight="1" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="52.1111111111111" customWidth="1"/>
@@ -1516,6 +1554,7 @@
       <c r="B4" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="C4" s="3"/>
     </row>
     <row r="5" ht="17.25" customHeight="1" spans="1:3">
       <c r="A5" s="1" t="s">
@@ -1524,6 +1563,7 @@
       <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="C5" s="3"/>
     </row>
     <row r="6" ht="17.25" customHeight="1" spans="1:3">
       <c r="A6" s="1" t="s">
@@ -1532,6 +1572,7 @@
       <c r="B6" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="C6" s="3"/>
     </row>
     <row r="7" ht="17.25" customHeight="1" spans="1:3">
       <c r="A7" s="1" t="s">
@@ -1540,6 +1581,7 @@
       <c r="B7" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="C7" s="3"/>
     </row>
     <row r="8" ht="17.25" customHeight="1" spans="1:3">
       <c r="A8" s="1" t="s">
@@ -1548,6 +1590,7 @@
       <c r="B8" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="C8" s="3"/>
     </row>
     <row r="9" ht="17.25" customHeight="1" spans="1:3">
       <c r="A9" s="1" t="s">
@@ -1556,6 +1599,7 @@
       <c r="B9" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="C9" s="3"/>
     </row>
     <row r="10" ht="17.25" customHeight="1" spans="1:3">
       <c r="A10" s="1" t="s">
@@ -1564,6 +1608,7 @@
       <c r="B10" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="C10" s="3"/>
     </row>
     <row r="11" ht="17.25" customHeight="1" spans="1:3">
       <c r="A11" s="1" t="s">
@@ -1572,6 +1617,7 @@
       <c r="B11" s="1" t="s">
         <v>22</v>
       </c>
+      <c r="C11" s="3"/>
     </row>
     <row r="12" ht="17.25" customHeight="1" spans="1:3">
       <c r="A12" s="1" t="s">
@@ -1580,6 +1626,7 @@
       <c r="B12" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="C12" s="3"/>
     </row>
     <row r="13" ht="17.25" customHeight="1" spans="1:3">
       <c r="A13" s="1" t="s">
@@ -1588,6 +1635,7 @@
       <c r="B13" s="1" t="s">
         <v>26</v>
       </c>
+      <c r="C13" s="3"/>
     </row>
     <row r="14" ht="17.25" customHeight="1" spans="1:3">
       <c r="A14" s="1" t="s">
@@ -1596,6 +1644,7 @@
       <c r="B14" s="1" t="s">
         <v>28</v>
       </c>
+      <c r="C14" s="3"/>
     </row>
     <row r="15" ht="17.25" customHeight="1" spans="1:3">
       <c r="A15" s="1" t="s">
@@ -1604,6 +1653,7 @@
       <c r="B15" s="1" t="s">
         <v>30</v>
       </c>
+      <c r="C15" s="3"/>
     </row>
     <row r="16" ht="17.25" customHeight="1" spans="1:3">
       <c r="A16" s="1" t="s">
@@ -1612,262 +1662,295 @@
       <c r="B16" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="17" ht="17.25" customHeight="1" spans="1:2">
+      <c r="C16" s="3"/>
+    </row>
+    <row r="17" ht="17.25" customHeight="1" spans="1:3">
       <c r="A17" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="18" ht="17.25" customHeight="1" spans="1:2">
+      <c r="C17" s="3"/>
+    </row>
+    <row r="18" ht="17.25" customHeight="1" spans="1:3">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="19" ht="17.25" customHeight="1" spans="1:2">
+      <c r="C18" s="3"/>
+    </row>
+    <row r="19" ht="17.25" customHeight="1" spans="1:3">
       <c r="A19" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="20" ht="17.25" customHeight="1" spans="1:2">
+      <c r="C19" s="3"/>
+    </row>
+    <row r="20" ht="17.25" customHeight="1" spans="1:3">
       <c r="A20" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="21" ht="17.25" customHeight="1" spans="1:2">
+      <c r="C20" s="3"/>
+    </row>
+    <row r="21" ht="17.25" customHeight="1" spans="1:3">
       <c r="A21" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="22" ht="17.25" customHeight="1" spans="1:2">
+      <c r="C21" s="3"/>
+    </row>
+    <row r="22" ht="17.25" customHeight="1" spans="1:3">
       <c r="A22" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="23" ht="17.25" customHeight="1" spans="1:2">
+      <c r="C22" s="3"/>
+    </row>
+    <row r="23" ht="17.25" customHeight="1" spans="1:3">
       <c r="A23" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="4" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="24" ht="17.25" customHeight="1" spans="1:2">
+      <c r="C23" s="3"/>
+    </row>
+    <row r="24" ht="17.25" customHeight="1" spans="1:3">
       <c r="A24" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="4" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="25" ht="17.25" customHeight="1" spans="1:2">
+      <c r="C24" s="3"/>
+    </row>
+    <row r="25" ht="17.25" customHeight="1" spans="1:3">
       <c r="A25" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="4" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="26" ht="17.25" customHeight="1" spans="1:2">
+      <c r="C25" s="3"/>
+    </row>
+    <row r="26" ht="17.25" customHeight="1" spans="1:3">
       <c r="A26" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="4" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="27" ht="17.25" customHeight="1" spans="1:2">
+      <c r="C26" s="3"/>
+    </row>
+    <row r="27" ht="17.25" customHeight="1" spans="1:3">
       <c r="A27" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="4" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="28" ht="17.25" customHeight="1" spans="1:2">
+      <c r="C27" s="3"/>
+    </row>
+    <row r="28" ht="17.25" customHeight="1" spans="1:3">
       <c r="A28" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="4" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="29" ht="17.25" customHeight="1" spans="1:2">
+      <c r="C28" s="3"/>
+    </row>
+    <row r="29" ht="17.25" customHeight="1" spans="1:3">
       <c r="A29" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="4" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="30" ht="17.25" customHeight="1" spans="1:2">
+      <c r="C29" s="3"/>
+    </row>
+    <row r="30" ht="17.25" customHeight="1" spans="1:3">
       <c r="A30" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="4" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="31" ht="17.25" customHeight="1" spans="1:2">
+      <c r="C30" s="3"/>
+    </row>
+    <row r="31" ht="17.25" customHeight="1" spans="1:3">
       <c r="A31" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="4" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="32" ht="17.25" customHeight="1" spans="1:2">
+      <c r="C31" s="3"/>
+    </row>
+    <row r="32" ht="17.25" customHeight="1" spans="1:3">
       <c r="A32" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="4" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="33" ht="17.25" customHeight="1" spans="1:2">
+      <c r="C32" s="3"/>
+    </row>
+    <row r="33" ht="17.25" customHeight="1" spans="1:3">
       <c r="A33" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="4" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="34" ht="17.25" customHeight="1" spans="1:2">
+      <c r="C33" s="3"/>
+    </row>
+    <row r="34" ht="17.25" customHeight="1" spans="1:3">
       <c r="A34" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="35" ht="17.25" customHeight="1" spans="1:2">
+      <c r="C34" s="3"/>
+    </row>
+    <row r="35" ht="17.25" customHeight="1" spans="1:3">
       <c r="A35" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="4" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="36" ht="17.25" customHeight="1" spans="1:2">
+      <c r="C35" s="3"/>
+    </row>
+    <row r="36" ht="17.25" customHeight="1" spans="1:3">
       <c r="A36" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="4" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="37" ht="17.25" customHeight="1" spans="1:2">
+      <c r="C36" s="3"/>
+    </row>
+    <row r="37" ht="17.25" customHeight="1" spans="1:3">
       <c r="A37" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="4" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="38" ht="17.25" customHeight="1" spans="1:2">
+      <c r="C37" s="3"/>
+    </row>
+    <row r="38" ht="17.25" customHeight="1" spans="1:3">
       <c r="A38" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B38" s="4" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="39" ht="17.25" customHeight="1" spans="1:2">
+      <c r="C38" s="3"/>
+    </row>
+    <row r="39" ht="17.25" customHeight="1" spans="1:3">
       <c r="A39" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B39" s="4" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="40" ht="17.25" customHeight="1" spans="1:2">
+      <c r="C39" s="3"/>
+    </row>
+    <row r="40" ht="17.25" customHeight="1" spans="1:3">
       <c r="A40" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="4" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="41" ht="17.25" customHeight="1" spans="1:2">
+      <c r="C40" s="3"/>
+    </row>
+    <row r="41" ht="17.25" customHeight="1" spans="1:3">
       <c r="A41" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B41" s="3" t="s">
+      <c r="B41" s="4" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="42" ht="17.25" customHeight="1" spans="1:2">
+      <c r="C41" s="3"/>
+    </row>
+    <row r="42" ht="17.25" customHeight="1" spans="1:3">
       <c r="A42" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="4" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="43" ht="17.25" customHeight="1" spans="1:2">
+      <c r="C42" s="3"/>
+    </row>
+    <row r="43" ht="17.25" customHeight="1" spans="1:3">
       <c r="A43" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="B43" s="4" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="44" ht="17.25" customHeight="1" spans="1:2">
+      <c r="C43" s="3"/>
+    </row>
+    <row r="44" ht="17.25" customHeight="1" spans="1:3">
       <c r="A44" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="B44" s="4" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="45" ht="17.25" customHeight="1" spans="1:2">
+      <c r="C44" s="3"/>
+    </row>
+    <row r="45" ht="17.25" customHeight="1" spans="1:3">
       <c r="A45" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="4" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="46" ht="17.25" customHeight="1" spans="1:2">
+      <c r="C45" s="3"/>
+    </row>
+    <row r="46" ht="17.25" customHeight="1" spans="1:3">
       <c r="A46" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="4" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="47" ht="17.25" customHeight="1" spans="1:2">
+      <c r="C46" s="3"/>
+    </row>
+    <row r="47" ht="17.25" customHeight="1" spans="1:3">
       <c r="A47" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="48" ht="17.25" customHeight="1" spans="1:2">
+      <c r="C47" s="3"/>
+    </row>
+    <row r="48" ht="17.25" customHeight="1" spans="1:3">
       <c r="A48" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="4" t="s">
         <v>96</v>
       </c>
+      <c r="C48" s="3"/>
     </row>
     <row r="49" ht="17.25" customHeight="1" spans="1:3">
       <c r="A49" s="2" t="s">
@@ -1876,6 +1959,7 @@
       <c r="B49" s="1" t="s">
         <v>98</v>
       </c>
+      <c r="C49" s="3"/>
     </row>
     <row r="50" ht="17.25" customHeight="1" spans="1:3">
       <c r="A50" s="2" t="s">
@@ -1892,79 +1976,88 @@
       <c r="A51" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="B51" s="5" t="s">
         <v>103</v>
       </c>
+      <c r="C51" s="3"/>
     </row>
     <row r="52" ht="17.25" customHeight="1" spans="1:3">
       <c r="A52" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B52" s="5" t="s">
         <v>105</v>
       </c>
+      <c r="C52" s="3"/>
     </row>
     <row r="53" ht="17.25" customHeight="1" spans="1:3">
       <c r="A53" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B53" s="5" t="s">
         <v>107</v>
       </c>
+      <c r="C53" s="3"/>
     </row>
     <row r="54" ht="17.25" customHeight="1" spans="1:3">
       <c r="A54" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="5" t="s">
         <v>109</v>
       </c>
+      <c r="C54" s="3"/>
     </row>
     <row r="55" ht="17.25" customHeight="1" spans="1:3">
       <c r="A55" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="B55" s="5" t="s">
         <v>111</v>
       </c>
+      <c r="C55" s="3"/>
     </row>
     <row r="56" ht="17.25" customHeight="1" spans="1:3">
       <c r="A56" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B56" s="5" t="s">
         <v>113</v>
       </c>
+      <c r="C56" s="3"/>
     </row>
     <row r="57" ht="17.25" customHeight="1" spans="1:3">
       <c r="A57" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="B57" s="5" t="s">
         <v>115</v>
       </c>
+      <c r="C57" s="3"/>
     </row>
     <row r="58" ht="17.25" customHeight="1" spans="1:3">
       <c r="A58" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B58" s="5" t="s">
         <v>117</v>
       </c>
+      <c r="C58" s="3"/>
     </row>
     <row r="59" ht="17.25" customHeight="1" spans="1:3">
       <c r="A59" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B59" s="5" t="s">
         <v>119</v>
       </c>
+      <c r="C59" s="3"/>
     </row>
     <row r="60" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A60" s="4" t="s">
+      <c r="A60" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B60" s="5" t="s">
         <v>121</v>
       </c>
       <c r="C60" s="2" t="s">
@@ -1978,223 +2071,299 @@
       <c r="B61" s="1" t="s">
         <v>123</v>
       </c>
+      <c r="C61" s="3"/>
     </row>
     <row r="62" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A62" s="5" t="s">
+      <c r="A62" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B62" s="3" t="s">
         <v>125</v>
       </c>
+      <c r="C62" s="3"/>
     </row>
     <row r="63" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A63" s="5" t="s">
+      <c r="A63" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="3" t="s">
         <v>127</v>
       </c>
+      <c r="C63" s="3"/>
     </row>
     <row r="64" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A64" s="5" t="s">
+      <c r="A64" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="3" t="s">
         <v>129</v>
       </c>
+      <c r="C64" s="3"/>
     </row>
     <row r="65" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A65" s="5" t="s">
+      <c r="A65" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="3" t="s">
         <v>131</v>
       </c>
+      <c r="C65" s="3"/>
     </row>
     <row r="66" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A66" s="5" t="s">
+      <c r="A66" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="3" t="s">
         <v>133</v>
       </c>
+      <c r="C66" s="3"/>
     </row>
     <row r="67" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A67" s="5" t="s">
+      <c r="A67" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="3" t="s">
         <v>135</v>
       </c>
+      <c r="C67" s="3"/>
     </row>
     <row r="68" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A68" s="5" t="s">
+      <c r="A68" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B68" s="3" t="s">
         <v>137</v>
       </c>
+      <c r="C68" s="3"/>
     </row>
     <row r="69" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A69" s="5" t="s">
+      <c r="A69" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B69" s="3" t="s">
         <v>139</v>
       </c>
+      <c r="C69" s="3"/>
     </row>
     <row r="70" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A70" s="5" t="s">
+      <c r="A70" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="3" t="s">
         <v>141</v>
       </c>
+      <c r="C70" s="3"/>
     </row>
     <row r="71" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A71" s="5" t="s">
+      <c r="A71" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="3" t="s">
         <v>143</v>
       </c>
+      <c r="C71" s="3"/>
     </row>
     <row r="72" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A72" t="s">
+      <c r="A72" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="3" t="s">
         <v>145</v>
       </c>
+      <c r="C72" s="3"/>
     </row>
     <row r="73" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A73" t="s">
+      <c r="A73" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C73" s="3" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="74" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A74" t="s">
+      <c r="A74" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C74" s="3" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="75" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A75" t="s">
+      <c r="A75" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C75" s="3" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="76" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A76" t="s">
+      <c r="A76" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B76" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C76" s="3" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="77" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A77" t="s">
+      <c r="A77" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B77" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C77" s="3" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="78" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A78" t="s">
+      <c r="A78" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B78" s="3" t="s">
         <v>157</v>
       </c>
+      <c r="C78" s="3"/>
     </row>
     <row r="79" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A79" t="s">
+      <c r="A79" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B79" s="3" t="s">
         <v>159</v>
       </c>
+      <c r="C79" s="3"/>
     </row>
     <row r="80" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A80" t="s">
+      <c r="A80" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B80" s="3" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="81" ht="17.25" customHeight="1" spans="1:2">
-      <c r="A81" t="s">
+      <c r="C80" s="3"/>
+    </row>
+    <row r="81" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A81" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="3" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="82" ht="17.25" customHeight="1" spans="1:2">
-      <c r="A82" t="s">
+      <c r="C81" s="3"/>
+    </row>
+    <row r="82" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A82" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="B82" t="s">
+      <c r="B82" s="3" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="83" ht="14.4" spans="1:2">
-      <c r="A83" t="s">
+      <c r="C82" s="3"/>
+    </row>
+    <row r="83" ht="14.4" spans="1:3">
+      <c r="A83" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B83" s="3" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="84" ht="14.4" spans="1:2">
-      <c r="A84" t="s">
+      <c r="C83" s="3"/>
+    </row>
+    <row r="84" ht="14.4" spans="1:3">
+      <c r="A84" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B84" s="3" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="85" ht="14.4" spans="1:2">
-      <c r="A85" t="s">
+      <c r="C84" s="3"/>
+    </row>
+    <row r="85" ht="14.4" spans="1:3">
+      <c r="A85" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B85" s="3" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="86" ht="14.4" spans="1:2">
-      <c r="A86" t="s">
+      <c r="C85" s="3"/>
+    </row>
+    <row r="86" ht="14.4" spans="1:3">
+      <c r="A86" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B86" s="3" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="93" ht="17.25" customHeight="1"/>
+      <c r="C86" s="3"/>
+    </row>
+    <row r="87" ht="14.4" spans="1:3">
+      <c r="A87" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C87" s="3"/>
+    </row>
+    <row r="88" customHeight="1" spans="1:3">
+      <c r="A88" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B88" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="89" customHeight="1" spans="1:3">
+      <c r="A89" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="C89" s="3"/>
+    </row>
+    <row r="90" customHeight="1" spans="1:3">
+      <c r="A90" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="C90" s="3"/>
+    </row>
+    <row r="91" customHeight="1" spans="1:3">
+      <c r="A91" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C91" s="3"/>
+    </row>
+    <row r="92" customHeight="1" spans="1:3">
+      <c r="A92" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="C92" s="3"/>
+    </row>
     <row r="94" ht="17.25" customHeight="1"/>
     <row r="95" ht="17.25" customHeight="1"/>
     <row r="96" ht="17.25" customHeight="1"/>
@@ -3104,6 +3273,7 @@
     <row r="1000" ht="17.25" customHeight="1"/>
     <row r="1001" ht="17.25" customHeight="1"/>
     <row r="1002" ht="17.25" customHeight="1"/>
+    <row r="1003" ht="17.25" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="1" orientation="landscape"/>

--- a/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="186">
   <si>
     <t>미리 로드할 어드레서블 테이블</t>
   </si>
@@ -454,13 +454,133 @@
   </si>
   <si>
     <t>Pool_Throw</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_GameObject_PaintingObject</t>
+  </si>
+  <si>
+    <t>Pool_Painting</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_Painting_1[Painting_1]</t>
+  </si>
+  <si>
+    <t>Painting_1_Mesh[Painting_1]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_Painting_2[Painting_2]</t>
+  </si>
+  <si>
+    <t>Painting_2_Mesh[Painting_2]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_Painting_3[Painting_8]</t>
+  </si>
+  <si>
+    <t>Painting_3_Mesh[Painting_8]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_Painting_4[Painting_4]</t>
+  </si>
+  <si>
+    <t>Painting_4_Mesh[Painting_4]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_Painting_5[Painting_5]</t>
+  </si>
+  <si>
+    <t>Painting_5_Mesh[Painting_5]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_Painting_1</t>
+  </si>
+  <si>
+    <t>Painting_1</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_Painting_2</t>
+  </si>
+  <si>
+    <t>Painting_2</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_Painting_3</t>
+  </si>
+  <si>
+    <t>Painting_3</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_Painting_6</t>
+  </si>
+  <si>
+    <t>Painting_6</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_Painting_8</t>
+  </si>
+  <si>
+    <t>Painting_8</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_PaintingFrame_Gold</t>
+  </si>
+  <si>
+    <t>PaintingFrame_Gold</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_PaintingFrame_Black</t>
+  </si>
+  <si>
+    <t>PaintingFrame_Black</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_PaintingFrame_White</t>
+  </si>
+  <si>
+    <t>PaintingFrame_White</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_PaintingFrame_WoodHell</t>
+  </si>
+  <si>
+    <t>PaintingFrame_WoodHell</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_PoliceShoot_Object</t>
+  </si>
+  <si>
+    <t>Pool_Bullet</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Police_Normal</t>
+  </si>
+  <si>
+    <t>Police_Normal</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Police_Shoot</t>
+  </si>
+  <si>
+    <t>Police_Shoot</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Police_Throw</t>
+  </si>
+  <si>
+    <t>Police_Throw</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Police_Dog</t>
+  </si>
+  <si>
+    <t>Police_Dog</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -487,6 +607,11 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -502,7 +627,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border/>
     <border>
       <left style="thin">
@@ -518,11 +643,22 @@
         <color rgb="FF000000"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -530,11 +666,19 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="2" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1219,7 +1363,7 @@
       <c r="A57" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="B57" s="5" t="s">
         <v>115</v>
       </c>
     </row>
@@ -1227,7 +1371,7 @@
       <c r="A58" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B58" s="6" t="s">
         <v>117</v>
       </c>
     </row>
@@ -1235,15 +1379,15 @@
       <c r="A59" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B59" s="6" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="60" ht="17.25" customHeight="1">
-      <c r="A60" s="4" t="s">
+      <c r="A60" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B60" s="6" t="s">
         <v>121</v>
       </c>
       <c r="C60" s="2" t="s">
@@ -1259,113 +1403,278 @@
       </c>
     </row>
     <row r="62" ht="17.25" customHeight="1">
-      <c r="A62" s="5" t="s">
+      <c r="A62" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="8" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="63" ht="17.25" customHeight="1">
-      <c r="A63" s="5" t="s">
+      <c r="A63" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="B63" s="8" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="64" ht="17.25" customHeight="1">
-      <c r="A64" s="5" t="s">
+      <c r="A64" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B64" s="6" t="s">
+      <c r="B64" s="8" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="65" ht="17.25" customHeight="1">
-      <c r="A65" s="5" t="s">
+      <c r="A65" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="B65" s="6" t="s">
+      <c r="B65" s="8" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="66" ht="17.25" customHeight="1">
-      <c r="A66" s="5" t="s">
+      <c r="A66" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="8" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="67" ht="17.25" customHeight="1">
-      <c r="A67" s="5" t="s">
+      <c r="A67" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="B67" s="6" t="s">
+      <c r="B67" s="8" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="68" ht="17.25" customHeight="1">
-      <c r="A68" s="5" t="s">
+      <c r="A68" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="B68" s="6" t="s">
+      <c r="B68" s="8" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="69" ht="17.25" customHeight="1">
-      <c r="A69" s="5" t="s">
+      <c r="A69" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="B69" s="6" t="s">
+      <c r="B69" s="8" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="70" ht="17.25" customHeight="1">
-      <c r="A70" s="5" t="s">
+      <c r="A70" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="8" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="71" ht="17.25" customHeight="1">
-      <c r="A71" s="6" t="s">
+      <c r="A71" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="B71" s="6" t="s">
+      <c r="B71" s="8" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="72" ht="17.25" customHeight="1">
-      <c r="A72" s="6" t="s">
+      <c r="A72" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="B72" s="6" t="s">
+      <c r="B72" s="8" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="73" ht="17.25" customHeight="1"/>
-    <row r="74" ht="17.25" customHeight="1"/>
-    <row r="75" ht="17.25" customHeight="1"/>
-    <row r="76" ht="17.25" customHeight="1"/>
-    <row r="77" ht="17.25" customHeight="1"/>
-    <row r="78" ht="17.25" customHeight="1"/>
-    <row r="79" ht="17.25" customHeight="1"/>
-    <row r="80" ht="17.25" customHeight="1"/>
-    <row r="81" ht="17.25" customHeight="1"/>
-    <row r="82" ht="17.25" customHeight="1"/>
-    <row r="83" ht="17.25" customHeight="1"/>
-    <row r="84" ht="17.25" customHeight="1"/>
-    <row r="85" ht="17.25" customHeight="1"/>
-    <row r="86" ht="17.25" customHeight="1"/>
-    <row r="87" ht="17.25" customHeight="1"/>
-    <row r="88" ht="17.25" customHeight="1"/>
-    <row r="89" ht="17.25" customHeight="1"/>
-    <row r="90" ht="17.25" customHeight="1"/>
-    <row r="91" ht="17.25" customHeight="1"/>
-    <row r="92" ht="17.25" customHeight="1"/>
+    <row r="73" ht="17.25" customHeight="1">
+      <c r="A73" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="B73" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="C73" s="10"/>
+    </row>
+    <row r="74" ht="17.25" customHeight="1">
+      <c r="A74" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="B74" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="C74" s="9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="75" ht="17.25" customHeight="1">
+      <c r="A75" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B75" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="C75" s="9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="76" ht="17.25" customHeight="1">
+      <c r="A76" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="B76" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="C76" s="9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="77" ht="17.25" customHeight="1">
+      <c r="A77" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="B77" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="78" ht="17.25" customHeight="1">
+      <c r="A78" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="B78" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="C78" s="9" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="79" ht="17.25" customHeight="1">
+      <c r="A79" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="B79" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C79" s="10"/>
+    </row>
+    <row r="80" ht="17.25" customHeight="1">
+      <c r="A80" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="B80" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="C80" s="10"/>
+    </row>
+    <row r="81" ht="17.25" customHeight="1">
+      <c r="A81" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="B81" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="C81" s="10"/>
+    </row>
+    <row r="82" ht="17.25" customHeight="1">
+      <c r="A82" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="B82" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="C82" s="10"/>
+    </row>
+    <row r="83" ht="17.25" customHeight="1">
+      <c r="A83" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="B83" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="C83" s="10"/>
+    </row>
+    <row r="84" ht="17.25" customHeight="1">
+      <c r="A84" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="B84" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C84" s="10"/>
+    </row>
+    <row r="85" ht="17.25" customHeight="1">
+      <c r="A85" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="B85" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="C85" s="10"/>
+    </row>
+    <row r="86" ht="17.25" customHeight="1">
+      <c r="A86" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="B86" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="C86" s="10"/>
+    </row>
+    <row r="87" ht="17.25" customHeight="1">
+      <c r="A87" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="B87" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="C87" s="10"/>
+    </row>
+    <row r="88" ht="17.25" customHeight="1">
+      <c r="A88" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="B88" s="8" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="89" ht="17.25" customHeight="1">
+      <c r="A89" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="B89" s="8" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="90" ht="17.25" customHeight="1">
+      <c r="A90" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="B90" s="8" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="91" ht="17.25" customHeight="1">
+      <c r="A91" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="B91" s="8" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="92" ht="17.25" customHeight="1">
+      <c r="A92" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="B92" s="8" t="s">
+        <v>185</v>
+      </c>
+    </row>
     <row r="93" ht="17.25" customHeight="1"/>
     <row r="94" ht="17.25" customHeight="1"/>
     <row r="95" ht="17.25" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="enqOkH1Z/tfQ3WIfr7wm+HPEzSLVVhkZawHcM088EJg="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="v4mvBJYERGqiNruBTfijDgsGfB1L8a5WYzdi61pNbdg="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="196">
   <si>
     <t>미리 로드할 어드레서블 테이블</t>
   </si>
@@ -57,12 +57,6 @@
     <t>BoundaryTile</t>
   </si>
   <si>
-    <t>PreLoadAsset_Stage1_BackUpTile</t>
-  </si>
-  <si>
-    <t>BackUpTile</t>
-  </si>
-  <si>
     <t>PreLoadAsset_Stage1_TestPresetTile</t>
   </si>
   <si>
@@ -574,13 +568,49 @@
   </si>
   <si>
     <t>Police_Dog</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_GameObject_StatueObject</t>
+  </si>
+  <si>
+    <t>Pool_Statue</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_SeatedLion</t>
+  </si>
+  <si>
+    <t>SeatedLion[Seated_Lion_LOD0]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_Statue_Stone</t>
+  </si>
+  <si>
+    <t>Statue_Stone</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_Statue_Copper</t>
+  </si>
+  <si>
+    <t>Statue_Copper</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_Statue_Metal</t>
+  </si>
+  <si>
+    <t>Statue_Metal</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_Statue_Marble</t>
+  </si>
+  <si>
+    <t>Statue_Marble</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -611,6 +641,10 @@
       <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="3">
@@ -658,7 +692,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -679,6 +713,9 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1080,7 +1117,7 @@
       <c r="A22" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="3" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1269,10 +1306,10 @@
       </c>
     </row>
     <row r="46" ht="17.25" customHeight="1">
-      <c r="A46" s="1" t="s">
+      <c r="A46" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="2" t="s">
         <v>92</v>
       </c>
     </row>
@@ -1280,7 +1317,7 @@
       <c r="A47" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="3" t="s">
         <v>94</v>
       </c>
     </row>
@@ -1288,7 +1325,7 @@
       <c r="A48" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B48" s="3" t="s">
+      <c r="B48" s="1" t="s">
         <v>96</v>
       </c>
     </row>
@@ -1296,18 +1333,18 @@
       <c r="A49" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="2" t="s">
         <v>98</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="50" ht="17.25" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B50" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="B50" s="4" t="s">
         <v>101</v>
       </c>
     </row>
@@ -1355,7 +1392,7 @@
       <c r="A56" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B56" s="5" t="s">
         <v>113</v>
       </c>
     </row>
@@ -1363,7 +1400,7 @@
       <c r="A57" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="B57" s="6" t="s">
         <v>115</v>
       </c>
     </row>
@@ -1376,29 +1413,29 @@
       </c>
     </row>
     <row r="59" ht="17.25" customHeight="1">
-      <c r="A59" s="2" t="s">
+      <c r="A59" s="6" t="s">
         <v>118</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>119</v>
       </c>
+      <c r="C59" s="2" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="60" ht="17.25" customHeight="1">
-      <c r="A60" s="6" t="s">
+      <c r="A60" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B60" s="6" t="s">
+      <c r="B60" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C60" s="2" t="s">
-        <v>101</v>
-      </c>
     </row>
     <row r="61" ht="17.25" customHeight="1">
-      <c r="A61" s="2" t="s">
+      <c r="A61" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" s="8" t="s">
         <v>123</v>
       </c>
     </row>
@@ -1467,7 +1504,7 @@
       </c>
     </row>
     <row r="70" ht="17.25" customHeight="1">
-      <c r="A70" s="7" t="s">
+      <c r="A70" s="8" t="s">
         <v>140</v>
       </c>
       <c r="B70" s="8" t="s">
@@ -1483,12 +1520,13 @@
       </c>
     </row>
     <row r="72" ht="17.25" customHeight="1">
-      <c r="A72" s="8" t="s">
+      <c r="A72" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="B72" s="8" t="s">
+      <c r="B72" s="9" t="s">
         <v>145</v>
       </c>
+      <c r="C72" s="10"/>
     </row>
     <row r="73" ht="17.25" customHeight="1">
       <c r="A73" s="9" t="s">
@@ -1497,7 +1535,9 @@
       <c r="B73" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="C73" s="10"/>
+      <c r="C73" s="9" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="74" ht="17.25" customHeight="1">
       <c r="A74" s="9" t="s">
@@ -1507,7 +1547,7 @@
         <v>149</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="75" ht="17.25" customHeight="1">
@@ -1518,7 +1558,7 @@
         <v>151</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="76" ht="17.25" customHeight="1">
@@ -1529,7 +1569,7 @@
         <v>153</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="77" ht="17.25" customHeight="1">
@@ -1540,7 +1580,7 @@
         <v>155</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="78" ht="17.25" customHeight="1">
@@ -1550,9 +1590,7 @@
       <c r="B78" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="C78" s="9" t="s">
-        <v>101</v>
-      </c>
+      <c r="C78" s="10"/>
     </row>
     <row r="79" ht="17.25" customHeight="1">
       <c r="A79" s="9" t="s">
@@ -1627,13 +1665,12 @@
       <c r="C86" s="10"/>
     </row>
     <row r="87" ht="17.25" customHeight="1">
-      <c r="A87" s="9" t="s">
+      <c r="A87" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="B87" s="9" t="s">
+      <c r="B87" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="C87" s="10"/>
     </row>
     <row r="88" ht="17.25" customHeight="1">
       <c r="A88" s="8" t="s">
@@ -1668,18 +1705,61 @@
       </c>
     </row>
     <row r="92" ht="17.25" customHeight="1">
-      <c r="A92" s="8" t="s">
+      <c r="A92" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="B92" s="8" t="s">
+      <c r="B92" s="9" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="93" ht="17.25" customHeight="1"/>
-    <row r="94" ht="17.25" customHeight="1"/>
-    <row r="95" ht="17.25" customHeight="1"/>
-    <row r="96" ht="17.25" customHeight="1"/>
-    <row r="97" ht="17.25" customHeight="1"/>
+      <c r="C92" s="10"/>
+    </row>
+    <row r="93" ht="17.25" customHeight="1">
+      <c r="A93" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="B93" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="C93" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="94" ht="17.25" customHeight="1">
+      <c r="A94" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="B94" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="C94" s="10"/>
+    </row>
+    <row r="95" ht="17.25" customHeight="1">
+      <c r="A95" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="B95" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="C95" s="10"/>
+    </row>
+    <row r="96" ht="17.25" customHeight="1">
+      <c r="A96" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="B96" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="C96" s="10"/>
+    </row>
+    <row r="97" ht="17.25" customHeight="1">
+      <c r="A97" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="B97" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C97" s="10"/>
+    </row>
     <row r="98" ht="17.25" customHeight="1"/>
     <row r="99" ht="17.25" customHeight="1"/>
     <row r="100" ht="17.25" customHeight="1"/>
@@ -2582,7 +2662,6 @@
     <row r="997" ht="17.25" customHeight="1"/>
     <row r="998" ht="17.25" customHeight="1"/>
     <row r="999" ht="17.25" customHeight="1"/>
-    <row r="1000" ht="17.25" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>

--- a/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
@@ -1,33 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
-  </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <definedNames/>
+  <calcPr/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext uri="GoogleSheetsCustomDataVersion2">
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="v4mvBJYERGqiNruBTfijDgsGfB1L8a5WYzdi61pNbdg="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="196">
   <si>
     <t>미리 로드할 어드레서블 테이블</t>
   </si>
@@ -68,12 +57,6 @@
     <t>BoundaryTile</t>
   </si>
   <si>
-    <t>PreLoadAsset_Stage1_BackUpTile</t>
-  </si>
-  <si>
-    <t>BackUpTile</t>
-  </si>
-  <si>
     <t>PreLoadAsset_Stage1_TestPresetTile</t>
   </si>
   <si>
@@ -461,37 +444,43 @@
     <t>JewelInventory</t>
   </si>
   <si>
+    <t>PreLoadAsset_PoliceThrow_Object</t>
+  </si>
+  <si>
+    <t>Pool_Throw</t>
+  </si>
+  <si>
     <t>PreLoadAsset_GameObject_PaintingObject</t>
   </si>
   <si>
     <t>Pool_Painting</t>
   </si>
   <si>
-    <t>PreLoadAsset_Mesh_Painting_1</t>
+    <t>PreLoadAsset_Mesh_Painting_1[Painting_1]</t>
   </si>
   <si>
     <t>Painting_1_Mesh[Painting_1]</t>
   </si>
   <si>
-    <t>PreLoadAsset_Mesh_Painting_2</t>
+    <t>PreLoadAsset_Mesh_Painting_2[Painting_2]</t>
   </si>
   <si>
     <t>Painting_2_Mesh[Painting_2]</t>
   </si>
   <si>
-    <t>PreLoadAsset_Mesh_Painting_3</t>
+    <t>PreLoadAsset_Mesh_Painting_3[Painting_8]</t>
   </si>
   <si>
     <t>Painting_3_Mesh[Painting_8]</t>
   </si>
   <si>
-    <t>PreLoadAsset_Mesh_Painting_4</t>
+    <t>PreLoadAsset_Mesh_Painting_4[Painting_4]</t>
   </si>
   <si>
     <t>Painting_4_Mesh[Painting_4]</t>
   </si>
   <si>
-    <t>PreLoadAsset_Mesh_Painting_5</t>
+    <t>PreLoadAsset_Mesh_Painting_5[Painting_5]</t>
   </si>
   <si>
     <t>Painting_5_Mesh[Painting_5]</t>
@@ -549,6 +538,36 @@
   </si>
   <si>
     <t>PaintingFrame_WoodHell</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_PoliceShoot_Object</t>
+  </si>
+  <si>
+    <t>Pool_Bullet</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Police_Normal</t>
+  </si>
+  <si>
+    <t>Police_Normal</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Police_Shoot</t>
+  </si>
+  <si>
+    <t>Police_Shoot</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Police_Throw</t>
+  </si>
+  <si>
+    <t>Police_Throw</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Police_Dog</t>
+  </si>
+  <si>
+    <t>Police_Dog</t>
   </si>
   <si>
     <t>PreLoadAsset_GameObject_StatueObject</t>
@@ -590,190 +609,50 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="23">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <fonts count="7">
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Malgun Gothic"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Malgun Gothic"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Malgun Gothic"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <sz val="10.0"/>
+      <color theme="1"/>
+      <name val="Malgun Gothic"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -781,534 +660,77 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="3">
+    <border/>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+  <cellStyleXfs count="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  </cellStyleXfs>
+  <cellXfs count="12">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="2" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf borderId="0" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-  </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <dxfs count="0"/>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1498,23 +920,23 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:C1003"/>
-  <sheetFormatPr defaultColWidth="14.4444444444444" defaultRowHeight="15" customHeight="1" outlineLevelCol="2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="52.1111111111111" customWidth="1"/>
-    <col min="2" max="2" width="35.1111111111111" customWidth="1"/>
-    <col min="3" max="3" width="31.4444444444444" customWidth="1"/>
-    <col min="4" max="26" width="9" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="52.14"/>
+    <col customWidth="1" min="2" max="2" width="35.14"/>
+    <col customWidth="1" min="3" max="3" width="31.43"/>
+    <col customWidth="1" min="4" max="26" width="9.0"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1" spans="1:3">
+    <row r="1" ht="17.25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1525,7 +947,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="17.25" customHeight="1" spans="1:3">
+    <row r="2" ht="17.25" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1536,7 +958,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" ht="17.25" customHeight="1" spans="1:3">
+    <row r="3" ht="17.25" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1547,827 +969,797 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" ht="17.25" customHeight="1" spans="1:3">
+    <row r="4" ht="17.25" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="3"/>
-    </row>
-    <row r="5" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="5" ht="17.25" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="3"/>
-    </row>
-    <row r="6" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="6" ht="17.25" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="3"/>
-    </row>
-    <row r="7" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="7" ht="17.25" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="3"/>
-    </row>
-    <row r="8" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="8" ht="17.25" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="3"/>
-    </row>
-    <row r="9" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="9" ht="17.25" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="3"/>
-    </row>
-    <row r="10" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="10" ht="17.25" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="3"/>
-    </row>
-    <row r="11" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="11" ht="17.25" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="3"/>
-    </row>
-    <row r="12" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="12" ht="17.25" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C12" s="3"/>
-    </row>
-    <row r="13" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="13" ht="17.25" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="3"/>
-    </row>
-    <row r="14" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="14" ht="17.25" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="3"/>
-    </row>
-    <row r="15" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="15" ht="17.25" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="3"/>
-    </row>
-    <row r="16" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="16" ht="17.25" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="3"/>
-    </row>
-    <row r="17" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="17" ht="17.25" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>33</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="3"/>
-    </row>
-    <row r="18" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="18" ht="17.25" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="3"/>
-    </row>
-    <row r="19" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="19" ht="17.25" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>37</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C19" s="3"/>
-    </row>
-    <row r="20" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="20" ht="17.25" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C20" s="3"/>
-    </row>
-    <row r="21" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="21" ht="17.25" customHeight="1">
       <c r="A21" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="3"/>
-    </row>
-    <row r="22" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="22" ht="17.25" customHeight="1">
       <c r="A22" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="3"/>
-    </row>
-    <row r="23" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="23" ht="17.25" customHeight="1">
       <c r="A23" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="3"/>
-    </row>
-    <row r="24" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="24" ht="17.25" customHeight="1">
       <c r="A24" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C24" s="3"/>
-    </row>
-    <row r="25" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="25" ht="17.25" customHeight="1">
       <c r="A25" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="3"/>
-    </row>
-    <row r="26" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="26" ht="17.25" customHeight="1">
       <c r="A26" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C26" s="3"/>
-    </row>
-    <row r="27" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="27" ht="17.25" customHeight="1">
       <c r="A27" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C27" s="3"/>
-    </row>
-    <row r="28" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="28" ht="17.25" customHeight="1">
       <c r="A28" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C28" s="3"/>
-    </row>
-    <row r="29" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="29" ht="17.25" customHeight="1">
       <c r="A29" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="C29" s="3"/>
-    </row>
-    <row r="30" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="30" ht="17.25" customHeight="1">
       <c r="A30" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C30" s="3"/>
-    </row>
-    <row r="31" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="31" ht="17.25" customHeight="1">
       <c r="A31" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="C31" s="3"/>
-    </row>
-    <row r="32" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="32" ht="17.25" customHeight="1">
       <c r="A32" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C32" s="3"/>
-    </row>
-    <row r="33" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="33" ht="17.25" customHeight="1">
       <c r="A33" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="C33" s="3"/>
-    </row>
-    <row r="34" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="34" ht="17.25" customHeight="1">
       <c r="A34" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C34" s="3"/>
-    </row>
-    <row r="35" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="35" ht="17.25" customHeight="1">
       <c r="A35" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C35" s="3"/>
-    </row>
-    <row r="36" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="36" ht="17.25" customHeight="1">
       <c r="A36" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C36" s="3"/>
-    </row>
-    <row r="37" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="37" ht="17.25" customHeight="1">
       <c r="A37" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C37" s="3"/>
-    </row>
-    <row r="38" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="38" ht="17.25" customHeight="1">
       <c r="A38" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C38" s="3"/>
-    </row>
-    <row r="39" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="39" ht="17.25" customHeight="1">
       <c r="A39" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C39" s="3"/>
-    </row>
-    <row r="40" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="40" ht="17.25" customHeight="1">
       <c r="A40" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C40" s="3"/>
-    </row>
-    <row r="41" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="41" ht="17.25" customHeight="1">
       <c r="A41" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C41" s="3"/>
-    </row>
-    <row r="42" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="42" ht="17.25" customHeight="1">
       <c r="A42" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C42" s="3"/>
-    </row>
-    <row r="43" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="43" ht="17.25" customHeight="1">
       <c r="A43" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C43" s="3"/>
-    </row>
-    <row r="44" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="44" ht="17.25" customHeight="1">
       <c r="A44" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="C44" s="3"/>
-    </row>
-    <row r="45" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="45" ht="17.25" customHeight="1">
       <c r="A45" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C45" s="3"/>
-    </row>
-    <row r="46" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A46" s="1" t="s">
+    </row>
+    <row r="46" ht="17.25" customHeight="1">
+      <c r="A46" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C46" s="3"/>
-    </row>
-    <row r="47" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="47" ht="17.25" customHeight="1">
       <c r="A47" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B47" s="2" t="s">
+      <c r="B47" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C47" s="3"/>
-    </row>
-    <row r="48" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="48" ht="17.25" customHeight="1">
       <c r="A48" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C48" s="3"/>
-    </row>
-    <row r="49" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="49" ht="17.25" customHeight="1">
       <c r="A49" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C49" s="3"/>
-    </row>
-    <row r="50" ht="17.25" customHeight="1" spans="1:3">
+      <c r="C49" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="50" ht="17.25" customHeight="1">
       <c r="A50" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B50" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="B50" s="4" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="51" ht="17.25" customHeight="1" spans="1:3">
+    <row r="51" ht="17.25" customHeight="1">
       <c r="A51" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="B51" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="C51" s="3"/>
-    </row>
-    <row r="52" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="52" ht="17.25" customHeight="1">
       <c r="A52" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="B52" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="C52" s="3"/>
-    </row>
-    <row r="53" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="53" ht="17.25" customHeight="1">
       <c r="A53" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B53" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="C53" s="3"/>
-    </row>
-    <row r="54" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="54" ht="17.25" customHeight="1">
       <c r="A54" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="B54" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="C54" s="3"/>
-    </row>
-    <row r="55" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="55" ht="17.25" customHeight="1">
       <c r="A55" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="B55" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="C55" s="3"/>
-    </row>
-    <row r="56" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="56" ht="17.25" customHeight="1">
       <c r="A56" s="2" t="s">
         <v>112</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="C56" s="3"/>
-    </row>
-    <row r="57" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="57" ht="17.25" customHeight="1">
       <c r="A57" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="B57" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="C57" s="3"/>
-    </row>
-    <row r="58" ht="17.25" customHeight="1" spans="1:3">
+    </row>
+    <row r="58" ht="17.25" customHeight="1">
       <c r="A58" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="B58" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="C58" s="3"/>
-    </row>
-    <row r="59" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A59" s="2" t="s">
+    </row>
+    <row r="59" ht="17.25" customHeight="1">
+      <c r="A59" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="B59" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="C59" s="3"/>
-    </row>
-    <row r="60" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A60" s="5" t="s">
+      <c r="C59" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="60" ht="17.25" customHeight="1">
+      <c r="A60" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="B60" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C60" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="61" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A61" s="2" t="s">
+    </row>
+    <row r="61" ht="17.25" customHeight="1">
+      <c r="A61" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="C61" s="3"/>
-    </row>
-    <row r="62" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A62" s="6" t="s">
+    </row>
+    <row r="62" ht="17.25" customHeight="1">
+      <c r="A62" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B62" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="C62" s="3"/>
-    </row>
-    <row r="63" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A63" s="6" t="s">
+    </row>
+    <row r="63" ht="17.25" customHeight="1">
+      <c r="A63" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="B63" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="C63" s="3"/>
-    </row>
-    <row r="64" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A64" s="6" t="s">
+    </row>
+    <row r="64" ht="17.25" customHeight="1">
+      <c r="A64" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B64" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="C64" s="3"/>
-    </row>
-    <row r="65" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A65" s="6" t="s">
+    </row>
+    <row r="65" ht="17.25" customHeight="1">
+      <c r="A65" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="B65" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="C65" s="3"/>
-    </row>
-    <row r="66" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A66" s="6" t="s">
+    </row>
+    <row r="66" ht="17.25" customHeight="1">
+      <c r="A66" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="B66" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="C66" s="3"/>
-    </row>
-    <row r="67" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A67" s="6" t="s">
+    </row>
+    <row r="67" ht="17.25" customHeight="1">
+      <c r="A67" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="B67" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="C67" s="3"/>
-    </row>
-    <row r="68" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A68" s="6" t="s">
+    </row>
+    <row r="68" ht="17.25" customHeight="1">
+      <c r="A68" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="B68" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="C68" s="3"/>
-    </row>
-    <row r="69" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A69" s="6" t="s">
+    </row>
+    <row r="69" ht="17.25" customHeight="1">
+      <c r="A69" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="B69" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="C69" s="3"/>
-    </row>
-    <row r="70" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A70" s="6" t="s">
+    </row>
+    <row r="70" ht="17.25" customHeight="1">
+      <c r="A70" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B70" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="C70" s="3"/>
-    </row>
-    <row r="71" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A71" s="6" t="s">
+    </row>
+    <row r="71" ht="17.25" customHeight="1">
+      <c r="A71" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="B71" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="C71" s="3"/>
-    </row>
-    <row r="72" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A72" s="3" t="s">
+    </row>
+    <row r="72" ht="17.25" customHeight="1">
+      <c r="A72" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="B72" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="C72" s="3"/>
-    </row>
-    <row r="73" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A73" s="3" t="s">
+      <c r="C72" s="10"/>
+    </row>
+    <row r="73" ht="17.25" customHeight="1">
+      <c r="A73" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="B73" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="C73" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="74" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A74" s="3" t="s">
+      <c r="C73" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="74" ht="17.25" customHeight="1">
+      <c r="A74" s="9" t="s">
         <v>148</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="B74" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="C74" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="75" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A75" s="3" t="s">
+      <c r="C74" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="75" ht="17.25" customHeight="1">
+      <c r="A75" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="B75" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="C75" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="76" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A76" s="3" t="s">
+      <c r="C75" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="76" ht="17.25" customHeight="1">
+      <c r="A76" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="B76" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="C76" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="77" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A77" s="3" t="s">
+      <c r="C76" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="77" ht="17.25" customHeight="1">
+      <c r="A77" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="B77" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="C77" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="78" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A78" s="3" t="s">
+      <c r="C77" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="78" ht="17.25" customHeight="1">
+      <c r="A78" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="B78" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="C78" s="3"/>
-    </row>
-    <row r="79" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A79" s="3" t="s">
+      <c r="C78" s="10"/>
+    </row>
+    <row r="79" ht="17.25" customHeight="1">
+      <c r="A79" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="B79" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="C79" s="3"/>
-    </row>
-    <row r="80" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A80" s="3" t="s">
+      <c r="C79" s="10"/>
+    </row>
+    <row r="80" ht="17.25" customHeight="1">
+      <c r="A80" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="B80" s="3" t="s">
+      <c r="B80" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="C80" s="3"/>
-    </row>
-    <row r="81" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A81" s="3" t="s">
+      <c r="C80" s="10"/>
+    </row>
+    <row r="81" ht="17.25" customHeight="1">
+      <c r="A81" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="B81" s="3" t="s">
+      <c r="B81" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="C81" s="3"/>
-    </row>
-    <row r="82" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A82" s="3" t="s">
+      <c r="C81" s="10"/>
+    </row>
+    <row r="82" ht="17.25" customHeight="1">
+      <c r="A82" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="B82" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="C82" s="3"/>
-    </row>
-    <row r="83" ht="14.4" spans="1:3">
-      <c r="A83" s="3" t="s">
+      <c r="C82" s="10"/>
+    </row>
+    <row r="83" ht="17.25" customHeight="1">
+      <c r="A83" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="B83" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="C83" s="3"/>
-    </row>
-    <row r="84" ht="14.4" spans="1:3">
-      <c r="A84" s="3" t="s">
+      <c r="C83" s="10"/>
+    </row>
+    <row r="84" ht="17.25" customHeight="1">
+      <c r="A84" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="B84" s="3" t="s">
+      <c r="B84" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="C84" s="3"/>
-    </row>
-    <row r="85" ht="14.4" spans="1:3">
-      <c r="A85" s="3" t="s">
+      <c r="C84" s="10"/>
+    </row>
+    <row r="85" ht="17.25" customHeight="1">
+      <c r="A85" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="B85" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="C85" s="3"/>
-    </row>
-    <row r="86" ht="14.4" spans="1:3">
-      <c r="A86" s="3" t="s">
+      <c r="C85" s="10"/>
+    </row>
+    <row r="86" ht="17.25" customHeight="1">
+      <c r="A86" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="B86" s="3" t="s">
+      <c r="B86" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="C86" s="3"/>
-    </row>
-    <row r="87" ht="14.4" spans="1:3">
-      <c r="A87" s="3" t="s">
+      <c r="C86" s="10"/>
+    </row>
+    <row r="87" ht="17.25" customHeight="1">
+      <c r="A87" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="B87" s="3" t="s">
+      <c r="B87" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="C87" s="3"/>
-    </row>
-    <row r="88" customHeight="1" spans="1:3">
-      <c r="A88" s="3" t="s">
+    </row>
+    <row r="88" ht="17.25" customHeight="1">
+      <c r="A88" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="B88" s="7" t="s">
+      <c r="B88" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="C88" s="3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="89" customHeight="1" spans="1:3">
-      <c r="A89" s="3" t="s">
+    </row>
+    <row r="89" ht="17.25" customHeight="1">
+      <c r="A89" s="8" t="s">
         <v>178</v>
       </c>
-      <c r="B89" s="7" t="s">
+      <c r="B89" s="8" t="s">
         <v>179</v>
       </c>
-      <c r="C89" s="3"/>
-    </row>
-    <row r="90" customHeight="1" spans="1:3">
-      <c r="A90" s="3" t="s">
+    </row>
+    <row r="90" ht="17.25" customHeight="1">
+      <c r="A90" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="B90" s="7" t="s">
+      <c r="B90" s="8" t="s">
         <v>181</v>
       </c>
-      <c r="C90" s="3"/>
-    </row>
-    <row r="91" customHeight="1" spans="1:3">
-      <c r="A91" s="3" t="s">
+    </row>
+    <row r="91" ht="17.25" customHeight="1">
+      <c r="A91" s="8" t="s">
         <v>182</v>
       </c>
-      <c r="B91" s="7" t="s">
+      <c r="B91" s="8" t="s">
         <v>183</v>
       </c>
-      <c r="C91" s="3"/>
-    </row>
-    <row r="92" customHeight="1" spans="1:3">
-      <c r="A92" s="3" t="s">
+    </row>
+    <row r="92" ht="17.25" customHeight="1">
+      <c r="A92" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="B92" s="7" t="s">
+      <c r="B92" s="9" t="s">
         <v>185</v>
       </c>
-      <c r="C92" s="3"/>
-    </row>
-    <row r="94" ht="17.25" customHeight="1"/>
-    <row r="95" ht="17.25" customHeight="1"/>
-    <row r="96" ht="17.25" customHeight="1"/>
-    <row r="97" ht="17.25" customHeight="1"/>
+      <c r="C92" s="10"/>
+    </row>
+    <row r="93" ht="17.25" customHeight="1">
+      <c r="A93" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="B93" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="C93" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="94" ht="17.25" customHeight="1">
+      <c r="A94" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="B94" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="C94" s="10"/>
+    </row>
+    <row r="95" ht="17.25" customHeight="1">
+      <c r="A95" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="B95" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="C95" s="10"/>
+    </row>
+    <row r="96" ht="17.25" customHeight="1">
+      <c r="A96" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="B96" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="C96" s="10"/>
+    </row>
+    <row r="97" ht="17.25" customHeight="1">
+      <c r="A97" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="B97" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C97" s="10"/>
+    </row>
     <row r="98" ht="17.25" customHeight="1"/>
     <row r="99" ht="17.25" customHeight="1"/>
     <row r="100" ht="17.25" customHeight="1"/>
@@ -3270,13 +2662,10 @@
     <row r="997" ht="17.25" customHeight="1"/>
     <row r="998" ht="17.25" customHeight="1"/>
     <row r="999" ht="17.25" customHeight="1"/>
-    <row r="1000" ht="17.25" customHeight="1"/>
-    <row r="1001" ht="17.25" customHeight="1"/>
-    <row r="1002" ht="17.25" customHeight="1"/>
-    <row r="1003" ht="17.25" customHeight="1"/>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="1" orientation="landscape"/>
-  <headerFooter/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
@@ -1,31 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\팀과제\JewelThief\JsonConverter\ExcelFiles\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EDB8936-FC6C-4EED-A460-21DFEB13AAD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="5232" yWindow="1452" windowWidth="16824" windowHeight="9048" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="enqOkH1Z/tfQ3WIfr7wm+HPEzSLVVhkZawHcM088EJg="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="v4mvBJYERGqiNruBTfijDgsGfB1L8a5WYzdi61pNbdg="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="210">
   <si>
     <t>미리 로드할 어드레서블 테이블</t>
   </si>
@@ -66,12 +57,6 @@
     <t>BoundaryTile</t>
   </si>
   <si>
-    <t>PreLoadAsset_Stage1_BackUpTile</t>
-  </si>
-  <si>
-    <t>BackUpTile</t>
-  </si>
-  <si>
     <t>PreLoadAsset_Stage1_TestPresetTile</t>
   </si>
   <si>
@@ -150,6 +135,9 @@
     <t>All Direction Corridor</t>
   </si>
   <si>
+    <t>PreLoadAsset_Lobby</t>
+  </si>
+  <si>
     <t>Lobby</t>
   </si>
   <si>
@@ -450,66 +438,255 @@
     <t>Effect_Normal</t>
   </si>
   <si>
-    <t>PreLoadAsset_Lobby</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>PreLoadAsset_JewelInventory</t>
-    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>JewelInventory</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_PoliceThrow_Object</t>
+  </si>
+  <si>
+    <t>Pool_Throw</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_GameObject_PaintingObject</t>
+  </si>
+  <si>
+    <t>Pool_Painting</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_Painting_1[Painting_1]</t>
+  </si>
+  <si>
+    <t>Painting_1_Mesh[Painting_1]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_Painting_2[Painting_2]</t>
+  </si>
+  <si>
+    <t>Painting_2_Mesh[Painting_2]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_Painting_3[Painting_8]</t>
+  </si>
+  <si>
+    <t>Painting_3_Mesh[Painting_8]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_Painting_4[Painting_4]</t>
+  </si>
+  <si>
+    <t>Painting_4_Mesh[Painting_4]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_Painting_5[Painting_5]</t>
+  </si>
+  <si>
+    <t>Painting_5_Mesh[Painting_5]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_Painting_1</t>
+  </si>
+  <si>
+    <t>Painting_1</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_Painting_2</t>
+  </si>
+  <si>
+    <t>Painting_2</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_Painting_3</t>
+  </si>
+  <si>
+    <t>Painting_3</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_Painting_6</t>
+  </si>
+  <si>
+    <t>Painting_6</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_Painting_8</t>
+  </si>
+  <si>
+    <t>Painting_8</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_PaintingFrame_Gold</t>
+  </si>
+  <si>
+    <t>PaintingFrame_Gold</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_PaintingFrame_Black</t>
+  </si>
+  <si>
+    <t>PaintingFrame_Black</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_PaintingFrame_White</t>
+  </si>
+  <si>
+    <t>PaintingFrame_White</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_PaintingFrame_WoodHell</t>
+  </si>
+  <si>
+    <t>PaintingFrame_WoodHell</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_PoliceShoot_Object</t>
+  </si>
+  <si>
+    <t>Pool_Bullet</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Police_Normal</t>
+  </si>
+  <si>
+    <t>Police_Normal</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Police_Shoot</t>
+  </si>
+  <si>
+    <t>Police_Shoot</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Police_Throw</t>
+  </si>
+  <si>
+    <t>Police_Throw</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Police_Dog</t>
+  </si>
+  <si>
+    <t>Police_Dog</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_GameObject_StatueObject</t>
+  </si>
+  <si>
+    <t>Pool_Statue</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_SeatedLion</t>
+  </si>
+  <si>
+    <t>SeatedLion[Seated_Lion_LOD0]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_Statue_Stone</t>
+  </si>
+  <si>
+    <t>Statue_Stone</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_Statue_Copper</t>
+  </si>
+  <si>
+    <t>Statue_Copper</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_Statue_Metal</t>
+  </si>
+  <si>
+    <t>Statue_Metal</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_Statue_Marble</t>
+  </si>
+  <si>
+    <t>Statue_Marble</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Stage1_TCorridor1</t>
+  </si>
+  <si>
+    <t>T Corridor1</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Stage1_TCorridor2</t>
+  </si>
+  <si>
+    <t>T Corridor2</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Stage1_TCorridor3</t>
+  </si>
+  <si>
+    <t>T Corridor3</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Stage1_TCorridor4</t>
+  </si>
+  <si>
+    <t>T Corridor4</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Stage1_Demo Room5</t>
+  </si>
+  <si>
+    <t>Demo Room5</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Stage1_Demo Room6</t>
+  </si>
+  <si>
+    <t>Demo Room6</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Stage1_Demo Room7</t>
+  </si>
+  <si>
+    <t>Demo Room7</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <fonts count="7">
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Malgun Gothic"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color theme="1"/>
       <name val="Malgun Gothic"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="8"/>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="3">
@@ -517,7 +694,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -526,14 +703,8 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="3">
+    <border/>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -547,40 +718,61 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+  <cellXfs count="12">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="2" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -770,23 +962,23 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1000"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="52.109375" customWidth="1"/>
-    <col min="2" max="2" width="35.109375" customWidth="1"/>
-    <col min="3" max="3" width="31.44140625" customWidth="1"/>
-    <col min="4" max="26" width="9" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="52.14"/>
+    <col customWidth="1" min="2" max="2" width="35.14"/>
+    <col customWidth="1" min="3" max="3" width="31.43"/>
+    <col customWidth="1" min="4" max="26" width="9.0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="17.25" customHeight="1">
+    <row r="1" ht="17.25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -797,7 +989,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="17.25" customHeight="1">
+    <row r="2" ht="17.25" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -808,7 +1000,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="17.25" customHeight="1">
+    <row r="3" ht="17.25" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -819,7 +1011,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="17.25" customHeight="1">
+    <row r="4" ht="17.25" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -827,7 +1019,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="17.25" customHeight="1">
+    <row r="5" ht="17.25" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -835,7 +1027,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="17.25" customHeight="1">
+    <row r="6" ht="17.25" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -843,7 +1035,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="17.25" customHeight="1">
+    <row r="7" ht="17.25" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -851,7 +1043,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="17.25" customHeight="1">
+    <row r="8" ht="17.25" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -859,7 +1051,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="17.25" customHeight="1">
+    <row r="9" ht="17.25" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -867,7 +1059,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="17.25" customHeight="1">
+    <row r="10" ht="17.25" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -875,7 +1067,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="17.25" customHeight="1">
+    <row r="11" ht="17.25" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>21</v>
       </c>
@@ -883,7 +1075,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="17.25" customHeight="1">
+    <row r="12" ht="17.25" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>23</v>
       </c>
@@ -891,7 +1083,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="17.25" customHeight="1">
+    <row r="13" ht="17.25" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>25</v>
       </c>
@@ -899,7 +1091,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="17.25" customHeight="1">
+    <row r="14" ht="17.25" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>27</v>
       </c>
@@ -907,7 +1099,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="17.25" customHeight="1">
+    <row r="15" ht="17.25" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>29</v>
       </c>
@@ -915,7 +1107,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="17.25" customHeight="1">
+    <row r="16" ht="17.25" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>31</v>
       </c>
@@ -923,7 +1115,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="17.25" customHeight="1">
+    <row r="17" ht="17.25" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>33</v>
       </c>
@@ -931,7 +1123,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="17.25" customHeight="1">
+    <row r="18" ht="17.25" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -939,7 +1131,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="17.25" customHeight="1">
+    <row r="19" ht="17.25" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>37</v>
       </c>
@@ -947,7 +1139,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="17.25" customHeight="1">
+    <row r="20" ht="17.25" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>39</v>
       </c>
@@ -955,453 +1147,717 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A21" s="7" t="s">
+    <row r="21" ht="17.25" customHeight="1">
+      <c r="A21" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" ht="17.25" customHeight="1">
+      <c r="A22" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="23" ht="17.25" customHeight="1">
+      <c r="A23" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" ht="17.25" customHeight="1">
+      <c r="A24" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" ht="17.25" customHeight="1">
+      <c r="A25" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" ht="17.25" customHeight="1">
+      <c r="A26" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="27" ht="17.25" customHeight="1">
+      <c r="A27" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="28" ht="17.25" customHeight="1">
+      <c r="A28" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="29" ht="17.25" customHeight="1">
+      <c r="A29" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="30" ht="17.25" customHeight="1">
+      <c r="A30" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" ht="17.25" customHeight="1">
+      <c r="A31" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="32" ht="17.25" customHeight="1">
+      <c r="A32" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" ht="17.25" customHeight="1">
+      <c r="A33" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="34" ht="17.25" customHeight="1">
+      <c r="A34" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="35" ht="17.25" customHeight="1">
+      <c r="A35" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="36" ht="17.25" customHeight="1">
+      <c r="A36" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" ht="17.25" customHeight="1">
+      <c r="A37" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="38" ht="17.25" customHeight="1">
+      <c r="A38" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="39" ht="17.25" customHeight="1">
+      <c r="A39" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="40" ht="17.25" customHeight="1">
+      <c r="A40" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="41" ht="17.25" customHeight="1">
+      <c r="A41" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="42" ht="17.25" customHeight="1">
+      <c r="A42" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43" ht="17.25" customHeight="1">
+      <c r="A43" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="44" ht="17.25" customHeight="1">
+      <c r="A44" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="45" ht="17.25" customHeight="1">
+      <c r="A45" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="46" ht="17.25" customHeight="1">
+      <c r="A46" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="47" ht="17.25" customHeight="1">
+      <c r="A47" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="48" ht="17.25" customHeight="1">
+      <c r="A48" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="49" ht="17.25" customHeight="1">
+      <c r="A49" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="50" ht="17.25" customHeight="1">
+      <c r="A50" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="51" ht="17.25" customHeight="1">
+      <c r="A51" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="52" ht="17.25" customHeight="1">
+      <c r="A52" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="53" ht="17.25" customHeight="1">
+      <c r="A53" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="54" ht="17.25" customHeight="1">
+      <c r="A54" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="55" ht="17.25" customHeight="1">
+      <c r="A55" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="56" ht="17.25" customHeight="1">
+      <c r="A56" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="57" ht="17.25" customHeight="1">
+      <c r="A57" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="58" ht="17.25" customHeight="1">
+      <c r="A58" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="59" ht="17.25" customHeight="1">
+      <c r="A59" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="60" ht="17.25" customHeight="1">
+      <c r="A60" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="61" ht="17.25" customHeight="1">
+      <c r="A61" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="62" ht="17.25" customHeight="1">
+      <c r="A62" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="63" ht="17.25" customHeight="1">
+      <c r="A63" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="64" ht="17.25" customHeight="1">
+      <c r="A64" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="65" ht="17.25" customHeight="1">
+      <c r="A65" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="66" ht="17.25" customHeight="1">
+      <c r="A66" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="67" ht="17.25" customHeight="1">
+      <c r="A67" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="68" ht="17.25" customHeight="1">
+      <c r="A68" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="69" ht="17.25" customHeight="1">
+      <c r="A69" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="70" ht="17.25" customHeight="1">
+      <c r="A70" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="B70" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A22" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A23" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A24" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A25" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A26" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A27" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A28" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A29" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A30" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A31" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A32" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A33" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A34" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A35" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A36" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A37" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A38" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A39" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A40" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A41" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A42" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A43" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A44" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A45" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A46" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A47" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A48" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A49" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A50" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B50" s="2" t="s">
+    </row>
+    <row r="71" ht="17.25" customHeight="1">
+      <c r="A71" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="72" ht="17.25" customHeight="1">
+      <c r="A72" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="B72" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="C72" s="10"/>
+    </row>
+    <row r="73" ht="17.25" customHeight="1">
+      <c r="A73" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="B73" s="9" t="s">
+        <v>147</v>
+      </c>
+      <c r="C73" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="C50" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A51" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A52" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A53" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A54" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A55" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A56" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A57" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A58" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A59" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A60" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A61" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A62" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="63" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A63" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A64" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="B64" s="6" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A65" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="B65" s="6" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A66" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="B66" s="6" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A67" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A68" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A69" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="B69" s="6" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A70" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" ht="17.25" customHeight="1">
-      <c r="A71" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="B71" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" ht="17.25" customHeight="1"/>
-    <row r="73" spans="1:2" ht="17.25" customHeight="1"/>
-    <row r="74" spans="1:2" ht="17.25" customHeight="1"/>
-    <row r="75" spans="1:2" ht="17.25" customHeight="1"/>
-    <row r="76" spans="1:2" ht="17.25" customHeight="1"/>
-    <row r="77" spans="1:2" ht="17.25" customHeight="1"/>
-    <row r="78" spans="1:2" ht="17.25" customHeight="1"/>
-    <row r="79" spans="1:2" ht="17.25" customHeight="1"/>
-    <row r="80" spans="1:2" ht="17.25" customHeight="1"/>
-    <row r="81" ht="17.25" customHeight="1"/>
-    <row r="82" ht="17.25" customHeight="1"/>
-    <row r="83" ht="17.25" customHeight="1"/>
-    <row r="84" ht="17.25" customHeight="1"/>
-    <row r="85" ht="17.25" customHeight="1"/>
-    <row r="86" ht="17.25" customHeight="1"/>
-    <row r="87" ht="17.25" customHeight="1"/>
-    <row r="88" ht="17.25" customHeight="1"/>
-    <row r="89" ht="17.25" customHeight="1"/>
-    <row r="90" ht="17.25" customHeight="1"/>
-    <row r="91" ht="17.25" customHeight="1"/>
-    <row r="92" ht="17.25" customHeight="1"/>
-    <row r="93" ht="17.25" customHeight="1"/>
-    <row r="94" ht="17.25" customHeight="1"/>
-    <row r="95" ht="17.25" customHeight="1"/>
-    <row r="96" ht="17.25" customHeight="1"/>
-    <row r="97" ht="17.25" customHeight="1"/>
-    <row r="98" ht="17.25" customHeight="1"/>
-    <row r="99" ht="17.25" customHeight="1"/>
-    <row r="100" ht="17.25" customHeight="1"/>
-    <row r="101" ht="17.25" customHeight="1"/>
-    <row r="102" ht="17.25" customHeight="1"/>
-    <row r="103" ht="17.25" customHeight="1"/>
-    <row r="104" ht="17.25" customHeight="1"/>
+    </row>
+    <row r="74" ht="17.25" customHeight="1">
+      <c r="A74" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="B74" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="C74" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="75" ht="17.25" customHeight="1">
+      <c r="A75" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B75" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="C75" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="76" ht="17.25" customHeight="1">
+      <c r="A76" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="B76" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="C76" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="77" ht="17.25" customHeight="1">
+      <c r="A77" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="B77" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="78" ht="17.25" customHeight="1">
+      <c r="A78" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="B78" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="C78" s="10"/>
+    </row>
+    <row r="79" ht="17.25" customHeight="1">
+      <c r="A79" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="B79" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C79" s="10"/>
+    </row>
+    <row r="80" ht="17.25" customHeight="1">
+      <c r="A80" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="B80" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="C80" s="10"/>
+    </row>
+    <row r="81" ht="17.25" customHeight="1">
+      <c r="A81" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="B81" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="C81" s="10"/>
+    </row>
+    <row r="82" ht="17.25" customHeight="1">
+      <c r="A82" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="B82" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="C82" s="10"/>
+    </row>
+    <row r="83" ht="17.25" customHeight="1">
+      <c r="A83" s="9" t="s">
+        <v>166</v>
+      </c>
+      <c r="B83" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="C83" s="10"/>
+    </row>
+    <row r="84" ht="17.25" customHeight="1">
+      <c r="A84" s="9" t="s">
+        <v>168</v>
+      </c>
+      <c r="B84" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C84" s="10"/>
+    </row>
+    <row r="85" ht="17.25" customHeight="1">
+      <c r="A85" s="9" t="s">
+        <v>170</v>
+      </c>
+      <c r="B85" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="C85" s="10"/>
+    </row>
+    <row r="86" ht="17.25" customHeight="1">
+      <c r="A86" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="B86" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="C86" s="10"/>
+    </row>
+    <row r="87" ht="17.25" customHeight="1">
+      <c r="A87" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="B87" s="8" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="88" ht="17.25" customHeight="1">
+      <c r="A88" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="B88" s="8" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="89" ht="17.25" customHeight="1">
+      <c r="A89" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="B89" s="8" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="90" ht="17.25" customHeight="1">
+      <c r="A90" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="B90" s="8" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="91" ht="17.25" customHeight="1">
+      <c r="A91" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="B91" s="8" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="92" ht="17.25" customHeight="1">
+      <c r="A92" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="B92" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="C92" s="10"/>
+    </row>
+    <row r="93" ht="17.25" customHeight="1">
+      <c r="A93" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="B93" s="11" t="s">
+        <v>187</v>
+      </c>
+      <c r="C93" s="9" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="94" ht="17.25" customHeight="1">
+      <c r="A94" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="B94" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="C94" s="10"/>
+    </row>
+    <row r="95" ht="17.25" customHeight="1">
+      <c r="A95" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="B95" s="11" t="s">
+        <v>191</v>
+      </c>
+      <c r="C95" s="10"/>
+    </row>
+    <row r="96" ht="17.25" customHeight="1">
+      <c r="A96" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="B96" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="C96" s="10"/>
+    </row>
+    <row r="97" ht="17.25" customHeight="1">
+      <c r="A97" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="B97" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="C97" s="10"/>
+    </row>
+    <row r="98" ht="17.25" customHeight="1">
+      <c r="A98" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="B98" s="8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="99" ht="17.25" customHeight="1">
+      <c r="A99" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="B99" s="8" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="100" ht="17.25" customHeight="1">
+      <c r="A100" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="B100" s="8" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="101" ht="17.25" customHeight="1">
+      <c r="A101" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="B101" s="8" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="102" ht="17.25" customHeight="1">
+      <c r="A102" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="B102" s="8" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="103" ht="17.25" customHeight="1">
+      <c r="A103" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="B103" s="8" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="104" ht="17.25" customHeight="1">
+      <c r="A104" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="B104" s="8" t="s">
+        <v>209</v>
+      </c>
+    </row>
     <row r="105" ht="17.25" customHeight="1"/>
     <row r="106" ht="17.25" customHeight="1"/>
     <row r="107" ht="17.25" customHeight="1"/>
@@ -2297,10 +2753,10 @@
     <row r="997" ht="17.25" customHeight="1"/>
     <row r="998" ht="17.25" customHeight="1"/>
     <row r="999" ht="17.25" customHeight="1"/>
-    <row r="1000" ht="17.25" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape" r:id="rId1"/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="v4mvBJYERGqiNruBTfijDgsGfB1L8a5WYzdi61pNbdg="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="ON79YGRFmG0PvJZg2zw1gtIfJ/OB/TVqK39qUUOl2CE="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="208">
   <si>
     <t>미리 로드할 어드레서블 테이블</t>
   </si>
@@ -55,12 +55,6 @@
   </si>
   <si>
     <t>BoundaryTile</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_Stage1_TestPresetTile</t>
-  </si>
-  <si>
-    <t>TestPresetTile</t>
   </si>
   <si>
     <t>PreLoadAsset_Stage1_Vertical Corridor</t>
@@ -1151,7 +1145,7 @@
       <c r="A21" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1340,10 +1334,10 @@
       </c>
     </row>
     <row r="45" ht="17.25" customHeight="1">
-      <c r="A45" s="1" t="s">
+      <c r="A45" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="2" t="s">
         <v>90</v>
       </c>
     </row>
@@ -1351,7 +1345,7 @@
       <c r="A46" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="3" t="s">
         <v>92</v>
       </c>
     </row>
@@ -1359,7 +1353,7 @@
       <c r="A47" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="1" t="s">
         <v>94</v>
       </c>
     </row>
@@ -1367,18 +1361,18 @@
       <c r="A48" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" s="2" t="s">
         <v>96</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="49" ht="17.25" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B49" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="B49" s="4" t="s">
         <v>99</v>
       </c>
     </row>
@@ -1426,7 +1420,7 @@
       <c r="A55" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="B55" s="5" t="s">
         <v>111</v>
       </c>
     </row>
@@ -1434,7 +1428,7 @@
       <c r="A56" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B56" s="6" t="s">
         <v>113</v>
       </c>
     </row>
@@ -1447,29 +1441,29 @@
       </c>
     </row>
     <row r="58" ht="17.25" customHeight="1">
-      <c r="A58" s="2" t="s">
+      <c r="A58" s="6" t="s">
         <v>116</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>117</v>
       </c>
+      <c r="C58" s="2" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="59" ht="17.25" customHeight="1">
-      <c r="A59" s="6" t="s">
+      <c r="A59" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B59" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C59" s="2" t="s">
-        <v>99</v>
-      </c>
     </row>
     <row r="60" ht="17.25" customHeight="1">
-      <c r="A60" s="2" t="s">
+      <c r="A60" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B60" s="8" t="s">
         <v>121</v>
       </c>
     </row>
@@ -1538,7 +1532,7 @@
       </c>
     </row>
     <row r="69" ht="17.25" customHeight="1">
-      <c r="A69" s="7" t="s">
+      <c r="A69" s="8" t="s">
         <v>138</v>
       </c>
       <c r="B69" s="8" t="s">
@@ -1554,12 +1548,13 @@
       </c>
     </row>
     <row r="71" ht="17.25" customHeight="1">
-      <c r="A71" s="8" t="s">
+      <c r="A71" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="B71" s="8" t="s">
+      <c r="B71" s="9" t="s">
         <v>143</v>
       </c>
+      <c r="C71" s="10"/>
     </row>
     <row r="72" ht="17.25" customHeight="1">
       <c r="A72" s="9" t="s">
@@ -1568,7 +1563,9 @@
       <c r="B72" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="C72" s="10"/>
+      <c r="C72" s="9" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="73" ht="17.25" customHeight="1">
       <c r="A73" s="9" t="s">
@@ -1578,7 +1575,7 @@
         <v>147</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="74" ht="17.25" customHeight="1">
@@ -1589,7 +1586,7 @@
         <v>149</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="75" ht="17.25" customHeight="1">
@@ -1600,7 +1597,7 @@
         <v>151</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="76" ht="17.25" customHeight="1">
@@ -1611,7 +1608,7 @@
         <v>153</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="77" ht="17.25" customHeight="1">
@@ -1621,9 +1618,7 @@
       <c r="B77" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="C77" s="9" t="s">
-        <v>99</v>
-      </c>
+      <c r="C77" s="10"/>
     </row>
     <row r="78" ht="17.25" customHeight="1">
       <c r="A78" s="9" t="s">
@@ -1698,13 +1693,12 @@
       <c r="C85" s="10"/>
     </row>
     <row r="86" ht="17.25" customHeight="1">
-      <c r="A86" s="9" t="s">
+      <c r="A86" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="B86" s="9" t="s">
+      <c r="B86" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="C86" s="10"/>
     </row>
     <row r="87" ht="17.25" customHeight="1">
       <c r="A87" s="8" t="s">
@@ -1739,21 +1733,24 @@
       </c>
     </row>
     <row r="91" ht="17.25" customHeight="1">
-      <c r="A91" s="8" t="s">
+      <c r="A91" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="B91" s="8" t="s">
+      <c r="B91" s="9" t="s">
         <v>183</v>
       </c>
+      <c r="C91" s="10"/>
     </row>
     <row r="92" ht="17.25" customHeight="1">
       <c r="A92" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="B92" s="9" t="s">
+      <c r="B92" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="C92" s="10"/>
+      <c r="C92" s="9" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="93" ht="17.25" customHeight="1">
       <c r="A93" s="9" t="s">
@@ -1762,9 +1759,7 @@
       <c r="B93" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="C93" s="9" t="s">
-        <v>99</v>
-      </c>
+      <c r="C93" s="10"/>
     </row>
     <row r="94" ht="17.25" customHeight="1">
       <c r="A94" s="9" t="s">
@@ -1794,13 +1789,12 @@
       <c r="C96" s="10"/>
     </row>
     <row r="97" ht="17.25" customHeight="1">
-      <c r="A97" s="9" t="s">
+      <c r="A97" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="B97" s="11" t="s">
+      <c r="B97" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C97" s="10"/>
     </row>
     <row r="98" ht="17.25" customHeight="1">
       <c r="A98" s="8" t="s">
@@ -1850,14 +1844,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="104" ht="17.25" customHeight="1">
-      <c r="A104" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="B104" s="8" t="s">
-        <v>209</v>
-      </c>
-    </row>
+    <row r="104" ht="17.25" customHeight="1"/>
     <row r="105" ht="17.25" customHeight="1"/>
     <row r="106" ht="17.25" customHeight="1"/>
     <row r="107" ht="17.25" customHeight="1"/>
@@ -2752,7 +2739,6 @@
     <row r="996" ht="17.25" customHeight="1"/>
     <row r="997" ht="17.25" customHeight="1"/>
     <row r="998" ht="17.25" customHeight="1"/>
-    <row r="999" ht="17.25" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>

--- a/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="v4mvBJYERGqiNruBTfijDgsGfB1L8a5WYzdi61pNbdg="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="ON79YGRFmG0PvJZg2zw1gtIfJ/OB/TVqK39qUUOl2CE="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="208">
   <si>
     <t>미리 로드할 어드레서블 테이블</t>
   </si>
@@ -57,12 +57,6 @@
     <t>BoundaryTile</t>
   </si>
   <si>
-    <t>PreLoadAsset_Stage1_TestPresetTile</t>
-  </si>
-  <si>
-    <t>TestPresetTile</t>
-  </si>
-  <si>
     <t>PreLoadAsset_Stage1_Vertical Corridor</t>
   </si>
   <si>
@@ -604,6 +598,48 @@
   </si>
   <si>
     <t>Statue_Marble</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Stage1_TCorridor1</t>
+  </si>
+  <si>
+    <t>T Corridor1</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Stage1_TCorridor2</t>
+  </si>
+  <si>
+    <t>T Corridor2</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Stage1_TCorridor3</t>
+  </si>
+  <si>
+    <t>T Corridor3</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Stage1_TCorridor4</t>
+  </si>
+  <si>
+    <t>T Corridor4</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Stage1_Demo Room5</t>
+  </si>
+  <si>
+    <t>Demo Room5</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Stage1_Demo Room6</t>
+  </si>
+  <si>
+    <t>Demo Room6</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Stage1_Demo Room7</t>
+  </si>
+  <si>
+    <t>Demo Room7</t>
   </si>
 </sst>
 </file>
@@ -1109,7 +1145,7 @@
       <c r="A21" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="3" t="s">
         <v>42</v>
       </c>
     </row>
@@ -1298,10 +1334,10 @@
       </c>
     </row>
     <row r="45" ht="17.25" customHeight="1">
-      <c r="A45" s="1" t="s">
+      <c r="A45" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B45" s="3" t="s">
+      <c r="B45" s="2" t="s">
         <v>90</v>
       </c>
     </row>
@@ -1309,7 +1345,7 @@
       <c r="A46" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="3" t="s">
         <v>92</v>
       </c>
     </row>
@@ -1317,7 +1353,7 @@
       <c r="A47" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="B47" s="3" t="s">
+      <c r="B47" s="1" t="s">
         <v>94</v>
       </c>
     </row>
@@ -1325,18 +1361,18 @@
       <c r="A48" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" s="2" t="s">
         <v>96</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="49" ht="17.25" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B49" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="B49" s="4" t="s">
         <v>99</v>
       </c>
     </row>
@@ -1384,7 +1420,7 @@
       <c r="A55" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="B55" s="5" t="s">
         <v>111</v>
       </c>
     </row>
@@ -1392,7 +1428,7 @@
       <c r="A56" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B56" s="6" t="s">
         <v>113</v>
       </c>
     </row>
@@ -1405,29 +1441,29 @@
       </c>
     </row>
     <row r="58" ht="17.25" customHeight="1">
-      <c r="A58" s="2" t="s">
+      <c r="A58" s="6" t="s">
         <v>116</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>117</v>
       </c>
+      <c r="C58" s="2" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="59" ht="17.25" customHeight="1">
-      <c r="A59" s="6" t="s">
+      <c r="A59" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B59" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="C59" s="2" t="s">
-        <v>99</v>
-      </c>
     </row>
     <row r="60" ht="17.25" customHeight="1">
-      <c r="A60" s="2" t="s">
+      <c r="A60" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B60" s="8" t="s">
         <v>121</v>
       </c>
     </row>
@@ -1496,7 +1532,7 @@
       </c>
     </row>
     <row r="69" ht="17.25" customHeight="1">
-      <c r="A69" s="7" t="s">
+      <c r="A69" s="8" t="s">
         <v>138</v>
       </c>
       <c r="B69" s="8" t="s">
@@ -1512,12 +1548,13 @@
       </c>
     </row>
     <row r="71" ht="17.25" customHeight="1">
-      <c r="A71" s="8" t="s">
+      <c r="A71" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="B71" s="8" t="s">
+      <c r="B71" s="9" t="s">
         <v>143</v>
       </c>
+      <c r="C71" s="10"/>
     </row>
     <row r="72" ht="17.25" customHeight="1">
       <c r="A72" s="9" t="s">
@@ -1526,7 +1563,9 @@
       <c r="B72" s="9" t="s">
         <v>145</v>
       </c>
-      <c r="C72" s="10"/>
+      <c r="C72" s="9" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="73" ht="17.25" customHeight="1">
       <c r="A73" s="9" t="s">
@@ -1536,7 +1575,7 @@
         <v>147</v>
       </c>
       <c r="C73" s="9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="74" ht="17.25" customHeight="1">
@@ -1547,7 +1586,7 @@
         <v>149</v>
       </c>
       <c r="C74" s="9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="75" ht="17.25" customHeight="1">
@@ -1558,7 +1597,7 @@
         <v>151</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="76" ht="17.25" customHeight="1">
@@ -1569,7 +1608,7 @@
         <v>153</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="77" ht="17.25" customHeight="1">
@@ -1579,9 +1618,7 @@
       <c r="B77" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="C77" s="9" t="s">
-        <v>99</v>
-      </c>
+      <c r="C77" s="10"/>
     </row>
     <row r="78" ht="17.25" customHeight="1">
       <c r="A78" s="9" t="s">
@@ -1656,13 +1693,12 @@
       <c r="C85" s="10"/>
     </row>
     <row r="86" ht="17.25" customHeight="1">
-      <c r="A86" s="9" t="s">
+      <c r="A86" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="B86" s="9" t="s">
+      <c r="B86" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="C86" s="10"/>
     </row>
     <row r="87" ht="17.25" customHeight="1">
       <c r="A87" s="8" t="s">
@@ -1697,21 +1733,24 @@
       </c>
     </row>
     <row r="91" ht="17.25" customHeight="1">
-      <c r="A91" s="8" t="s">
+      <c r="A91" s="9" t="s">
         <v>182</v>
       </c>
-      <c r="B91" s="8" t="s">
+      <c r="B91" s="9" t="s">
         <v>183</v>
       </c>
+      <c r="C91" s="10"/>
     </row>
     <row r="92" ht="17.25" customHeight="1">
       <c r="A92" s="9" t="s">
         <v>184</v>
       </c>
-      <c r="B92" s="9" t="s">
+      <c r="B92" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="C92" s="10"/>
+      <c r="C92" s="9" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="93" ht="17.25" customHeight="1">
       <c r="A93" s="9" t="s">
@@ -1720,9 +1759,7 @@
       <c r="B93" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="C93" s="9" t="s">
-        <v>99</v>
-      </c>
+      <c r="C93" s="10"/>
     </row>
     <row r="94" ht="17.25" customHeight="1">
       <c r="A94" s="9" t="s">
@@ -1752,20 +1789,61 @@
       <c r="C96" s="10"/>
     </row>
     <row r="97" ht="17.25" customHeight="1">
-      <c r="A97" s="9" t="s">
+      <c r="A97" s="8" t="s">
         <v>194</v>
       </c>
-      <c r="B97" s="11" t="s">
+      <c r="B97" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="C97" s="10"/>
-    </row>
-    <row r="98" ht="17.25" customHeight="1"/>
-    <row r="99" ht="17.25" customHeight="1"/>
-    <row r="100" ht="17.25" customHeight="1"/>
-    <row r="101" ht="17.25" customHeight="1"/>
-    <row r="102" ht="17.25" customHeight="1"/>
-    <row r="103" ht="17.25" customHeight="1"/>
+    </row>
+    <row r="98" ht="17.25" customHeight="1">
+      <c r="A98" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="B98" s="8" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="99" ht="17.25" customHeight="1">
+      <c r="A99" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="B99" s="8" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="100" ht="17.25" customHeight="1">
+      <c r="A100" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="B100" s="8" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="101" ht="17.25" customHeight="1">
+      <c r="A101" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="B101" s="8" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="102" ht="17.25" customHeight="1">
+      <c r="A102" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="B102" s="8" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="103" ht="17.25" customHeight="1">
+      <c r="A103" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="B103" s="8" t="s">
+        <v>207</v>
+      </c>
+    </row>
     <row r="104" ht="17.25" customHeight="1"/>
     <row r="105" ht="17.25" customHeight="1"/>
     <row r="106" ht="17.25" customHeight="1"/>
@@ -2661,7 +2739,6 @@
     <row r="996" ht="17.25" customHeight="1"/>
     <row r="997" ht="17.25" customHeight="1"/>
     <row r="998" ht="17.25" customHeight="1"/>
-    <row r="999" ht="17.25" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>

--- a/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="234">
   <si>
     <t>미리 로드할 어드레서블 테이블</t>
   </si>
@@ -357,13 +357,13 @@
     <t>PreLoadAsset_GameObject_ToolObject</t>
   </si>
   <si>
-    <t>Pool_Tool</t>
+    <t>ToolObject</t>
   </si>
   <si>
     <t>PreLoadAsset_GameObject_JewelObject</t>
   </si>
   <si>
-    <t>Pool_Jewel</t>
+    <t>JewelObject</t>
   </si>
   <si>
     <t>PreLoadAsset_Mesh_Jewel_Cone[Cone]</t>
@@ -640,13 +640,91 @@
   </si>
   <si>
     <t>Demo Room7</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_GameObject_JunkObject</t>
+  </si>
+  <si>
+    <t>JunkObject</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_PolygonNightclubs_01_A</t>
+  </si>
+  <si>
+    <t>PolygonNightclubs_01_A</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_Junk_Bottle_Blue</t>
+  </si>
+  <si>
+    <t>Junk_Bottle_Blue[SM_Prop_Bar_Bottle_07]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_Junk_Bottle_Pink_Large</t>
+  </si>
+  <si>
+    <t>Junk_Bottle_Pink_Large[SM_Prop_Bar_Bottle_Lage_01]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_Junk_Can_Navy</t>
+  </si>
+  <si>
+    <t>Junk_Can_Navy[SM_Prop_Can_01]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_Junk_Fish</t>
+  </si>
+  <si>
+    <t>Junk_Fish[SM_Prop_Display_Fish_02]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_Junk_Glasses</t>
+  </si>
+  <si>
+    <t>Junk_Glasses[SM_Prop_Glasses_01]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_Junk_Microphone</t>
+  </si>
+  <si>
+    <t>Junk_Microphone[SM_Prop_Microphone_01]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_Junk_Sculpture</t>
+  </si>
+  <si>
+    <t>Junk_Sculpture[SM_Prop_Sculpture_01]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_PolygonNightclub_Mat_01_A_Metallic</t>
+  </si>
+  <si>
+    <t>PolygonNightclub_Mat_01_A_Metallic</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_MeshCollier_Junk_Bottle_Blue</t>
+  </si>
+  <si>
+    <t>MeshCollider_Junk_Bottle_Blue</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_MeshCollider_Junk_Bottle_Pink_Large</t>
+  </si>
+  <si>
+    <t>MeshCollider_Junk_Bottle_Pink_Large</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_MeshCollier_Junk_Glasses</t>
+  </si>
+  <si>
+    <t>MeshCollider_Junk_Glasses</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -680,6 +758,10 @@
     </font>
     <font>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -728,7 +810,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -737,6 +819,9 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="2" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -752,6 +837,15 @@
     </xf>
     <xf borderId="0" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1441,10 +1535,10 @@
       </c>
     </row>
     <row r="58" ht="17.25" customHeight="1">
-      <c r="A58" s="6" t="s">
+      <c r="A58" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="7" t="s">
         <v>117</v>
       </c>
       <c r="C58" s="2" t="s">
@@ -1460,403 +1554,524 @@
       </c>
     </row>
     <row r="60" ht="17.25" customHeight="1">
-      <c r="A60" s="7" t="s">
+      <c r="A60" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="B60" s="9" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="61" ht="17.25" customHeight="1">
-      <c r="A61" s="7" t="s">
+      <c r="A61" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="B61" s="8" t="s">
+      <c r="B61" s="9" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="62" ht="17.25" customHeight="1">
-      <c r="A62" s="7" t="s">
+      <c r="A62" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="B62" s="8" t="s">
+      <c r="B62" s="9" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="63" ht="17.25" customHeight="1">
-      <c r="A63" s="7" t="s">
+      <c r="A63" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="B63" s="8" t="s">
+      <c r="B63" s="9" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="64" ht="17.25" customHeight="1">
-      <c r="A64" s="7" t="s">
+      <c r="A64" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="B64" s="8" t="s">
+      <c r="B64" s="9" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="65" ht="17.25" customHeight="1">
-      <c r="A65" s="7" t="s">
+      <c r="A65" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B65" s="8" t="s">
+      <c r="B65" s="9" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="66" ht="17.25" customHeight="1">
-      <c r="A66" s="7" t="s">
+      <c r="A66" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="B66" s="8" t="s">
+      <c r="B66" s="9" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="67" ht="17.25" customHeight="1">
-      <c r="A67" s="7" t="s">
+      <c r="A67" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="B67" s="8" t="s">
+      <c r="B67" s="9" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="68" ht="17.25" customHeight="1">
-      <c r="A68" s="7" t="s">
+      <c r="A68" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="B68" s="8" t="s">
+      <c r="B68" s="9" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="69" ht="17.25" customHeight="1">
-      <c r="A69" s="8" t="s">
+      <c r="A69" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="B69" s="8" t="s">
+      <c r="B69" s="9" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="70" ht="17.25" customHeight="1">
-      <c r="A70" s="8" t="s">
+      <c r="A70" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="B70" s="8" t="s">
+      <c r="B70" s="9" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="71" ht="17.25" customHeight="1">
-      <c r="A71" s="9" t="s">
+      <c r="A71" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="B71" s="9" t="s">
+      <c r="B71" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="C71" s="10"/>
+      <c r="C71" s="11"/>
     </row>
     <row r="72" ht="17.25" customHeight="1">
-      <c r="A72" s="9" t="s">
+      <c r="A72" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="B72" s="9" t="s">
+      <c r="B72" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="C72" s="9" t="s">
+      <c r="C72" s="10" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="73" ht="17.25" customHeight="1">
-      <c r="A73" s="9" t="s">
+      <c r="A73" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="B73" s="9" t="s">
+      <c r="B73" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="C73" s="9" t="s">
+      <c r="C73" s="10" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="74" ht="17.25" customHeight="1">
-      <c r="A74" s="9" t="s">
+      <c r="A74" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="B74" s="9" t="s">
+      <c r="B74" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="C74" s="9" t="s">
+      <c r="C74" s="10" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="75" ht="17.25" customHeight="1">
-      <c r="A75" s="9" t="s">
+      <c r="A75" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="B75" s="9" t="s">
+      <c r="B75" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="C75" s="9" t="s">
+      <c r="C75" s="10" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="76" ht="17.25" customHeight="1">
-      <c r="A76" s="9" t="s">
+      <c r="A76" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="B76" s="9" t="s">
+      <c r="B76" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="C76" s="9" t="s">
+      <c r="C76" s="10" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="77" ht="17.25" customHeight="1">
-      <c r="A77" s="9" t="s">
+      <c r="A77" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="B77" s="9" t="s">
+      <c r="B77" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="C77" s="10"/>
+      <c r="C77" s="11"/>
     </row>
     <row r="78" ht="17.25" customHeight="1">
-      <c r="A78" s="9" t="s">
+      <c r="A78" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="B78" s="9" t="s">
+      <c r="B78" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="C78" s="10"/>
+      <c r="C78" s="11"/>
     </row>
     <row r="79" ht="17.25" customHeight="1">
-      <c r="A79" s="9" t="s">
+      <c r="A79" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="B79" s="9" t="s">
+      <c r="B79" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="C79" s="10"/>
+      <c r="C79" s="11"/>
     </row>
     <row r="80" ht="17.25" customHeight="1">
-      <c r="A80" s="9" t="s">
+      <c r="A80" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="B80" s="9" t="s">
+      <c r="B80" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="C80" s="10"/>
+      <c r="C80" s="11"/>
     </row>
     <row r="81" ht="17.25" customHeight="1">
-      <c r="A81" s="9" t="s">
+      <c r="A81" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="B81" s="9" t="s">
+      <c r="B81" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="C81" s="10"/>
+      <c r="C81" s="11"/>
     </row>
     <row r="82" ht="17.25" customHeight="1">
-      <c r="A82" s="9" t="s">
+      <c r="A82" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="B82" s="9" t="s">
+      <c r="B82" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="C82" s="10"/>
+      <c r="C82" s="11"/>
     </row>
     <row r="83" ht="17.25" customHeight="1">
-      <c r="A83" s="9" t="s">
+      <c r="A83" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="B83" s="9" t="s">
+      <c r="B83" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="C83" s="10"/>
+      <c r="C83" s="11"/>
     </row>
     <row r="84" ht="17.25" customHeight="1">
-      <c r="A84" s="9" t="s">
+      <c r="A84" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="B84" s="9" t="s">
+      <c r="B84" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="C84" s="10"/>
+      <c r="C84" s="11"/>
     </row>
     <row r="85" ht="17.25" customHeight="1">
-      <c r="A85" s="9" t="s">
+      <c r="A85" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="B85" s="9" t="s">
+      <c r="B85" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="C85" s="10"/>
+      <c r="C85" s="11"/>
     </row>
     <row r="86" ht="17.25" customHeight="1">
-      <c r="A86" s="8" t="s">
+      <c r="A86" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="B86" s="8" t="s">
+      <c r="B86" s="9" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="87" ht="17.25" customHeight="1">
-      <c r="A87" s="8" t="s">
+      <c r="A87" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="B87" s="8" t="s">
+      <c r="B87" s="9" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="88" ht="17.25" customHeight="1">
-      <c r="A88" s="8" t="s">
+      <c r="A88" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="B88" s="8" t="s">
+      <c r="B88" s="9" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="89" ht="17.25" customHeight="1">
-      <c r="A89" s="8" t="s">
+      <c r="A89" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="B89" s="8" t="s">
+      <c r="B89" s="9" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="90" ht="17.25" customHeight="1">
-      <c r="A90" s="8" t="s">
+      <c r="A90" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="B90" s="8" t="s">
+      <c r="B90" s="9" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="91" ht="17.25" customHeight="1">
-      <c r="A91" s="9" t="s">
+      <c r="A91" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="B91" s="9" t="s">
+      <c r="B91" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="C91" s="10"/>
+      <c r="C91" s="11"/>
     </row>
     <row r="92" ht="17.25" customHeight="1">
-      <c r="A92" s="9" t="s">
+      <c r="A92" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="B92" s="11" t="s">
+      <c r="B92" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="C92" s="9" t="s">
+      <c r="C92" s="10" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="93" ht="17.25" customHeight="1">
-      <c r="A93" s="9" t="s">
+      <c r="A93" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="B93" s="11" t="s">
+      <c r="B93" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="C93" s="10"/>
+      <c r="C93" s="11"/>
     </row>
     <row r="94" ht="17.25" customHeight="1">
-      <c r="A94" s="9" t="s">
+      <c r="A94" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="B94" s="11" t="s">
+      <c r="B94" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="C94" s="10"/>
+      <c r="C94" s="11"/>
     </row>
     <row r="95" ht="17.25" customHeight="1">
-      <c r="A95" s="9" t="s">
+      <c r="A95" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="B95" s="11" t="s">
+      <c r="B95" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="C95" s="10"/>
+      <c r="C95" s="11"/>
     </row>
     <row r="96" ht="17.25" customHeight="1">
-      <c r="A96" s="9" t="s">
+      <c r="A96" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="B96" s="11" t="s">
+      <c r="B96" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="C96" s="10"/>
+      <c r="C96" s="11"/>
     </row>
     <row r="97" ht="17.25" customHeight="1">
-      <c r="A97" s="8" t="s">
+      <c r="A97" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="B97" s="8" t="s">
+      <c r="B97" s="9" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="98" ht="17.25" customHeight="1">
-      <c r="A98" s="8" t="s">
+      <c r="A98" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="B98" s="8" t="s">
+      <c r="B98" s="9" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="99" ht="17.25" customHeight="1">
-      <c r="A99" s="8" t="s">
+      <c r="A99" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="B99" s="8" t="s">
+      <c r="B99" s="9" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="100" ht="17.25" customHeight="1">
-      <c r="A100" s="8" t="s">
+      <c r="A100" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="B100" s="8" t="s">
+      <c r="B100" s="9" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="101" ht="17.25" customHeight="1">
-      <c r="A101" s="8" t="s">
+      <c r="A101" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="B101" s="8" t="s">
+      <c r="B101" s="9" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="102" ht="17.25" customHeight="1">
-      <c r="A102" s="8" t="s">
+      <c r="A102" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="B102" s="8" t="s">
+      <c r="B102" s="9" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="103" ht="17.25" customHeight="1">
-      <c r="A103" s="8" t="s">
+      <c r="A103" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="B103" s="8" t="s">
+      <c r="B103" s="9" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="104" ht="17.25" customHeight="1"/>
-    <row r="105" ht="17.25" customHeight="1"/>
-    <row r="106" ht="17.25" customHeight="1"/>
-    <row r="107" ht="17.25" customHeight="1"/>
-    <row r="108" ht="17.25" customHeight="1"/>
-    <row r="109" ht="17.25" customHeight="1"/>
-    <row r="110" ht="17.25" customHeight="1"/>
-    <row r="111" ht="17.25" customHeight="1"/>
-    <row r="112" ht="17.25" customHeight="1"/>
-    <row r="113" ht="17.25" customHeight="1"/>
-    <row r="114" ht="17.25" customHeight="1"/>
-    <row r="115" ht="17.25" customHeight="1"/>
-    <row r="116" ht="17.25" customHeight="1"/>
+    <row r="104" ht="17.25" customHeight="1">
+      <c r="A104" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="B104" s="9" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="105" ht="17.25" customHeight="1">
+      <c r="A105" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="B105" s="13" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="106" ht="17.25" customHeight="1">
+      <c r="A106" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="B106" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="C106" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="107" ht="17.25" customHeight="1">
+      <c r="A107" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="B107" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="C107" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="108" ht="17.25" customHeight="1">
+      <c r="A108" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="B108" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="C108" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="109" ht="17.25" customHeight="1">
+      <c r="A109" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="B109" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="C109" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="110" ht="17.25" customHeight="1">
+      <c r="A110" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="B110" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="C110" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="111" ht="17.25" customHeight="1">
+      <c r="A111" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="B111" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="C111" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="112" ht="17.25" customHeight="1">
+      <c r="A112" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="B112" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="C112" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="113" ht="17.25" customHeight="1">
+      <c r="A113" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="B113" s="13" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="114" ht="17.25" customHeight="1">
+      <c r="A114" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="B114" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="C114" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="115" ht="17.25" customHeight="1">
+      <c r="A115" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="B115" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="C115" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="116" ht="17.25" customHeight="1">
+      <c r="A116" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="B116" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="C116" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
     <row r="117" ht="17.25" customHeight="1"/>
     <row r="118" ht="17.25" customHeight="1"/>
     <row r="119" ht="17.25" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
@@ -3,20 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="ON79YGRFmG0PvJZg2zw1gtIfJ/OB/TVqK39qUUOl2CE="/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="210">
   <si>
     <t>미리 로드할 어드레서블 테이블</t>
   </si>
@@ -370,6 +365,12 @@
   </si>
   <si>
     <t>Jewel_Cone[Cone]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_Jewel_Cone[Cube.058]</t>
+  </si>
+  <si>
+    <t>Jewel_Stone[Cube.058]</t>
   </si>
   <si>
     <t>PreLoadAsset_Material_Lit</t>
@@ -646,7 +647,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -656,7 +657,6 @@
     <font>
       <color theme="1"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11.0"/>
@@ -672,6 +672,11 @@
       <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11.0"/>
@@ -745,13 +750,13 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+      <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf borderId="0" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -763,6 +768,10 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -969,7 +978,7 @@
     <col customWidth="1" min="1" max="1" width="52.14"/>
     <col customWidth="1" min="2" max="2" width="35.14"/>
     <col customWidth="1" min="3" max="3" width="31.43"/>
-    <col customWidth="1" min="4" max="26" width="9.0"/>
+    <col customWidth="1" min="4" max="6" width="9.0"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.25" customHeight="1">
@@ -1452,317 +1461,319 @@
       </c>
     </row>
     <row r="59" ht="17.25" customHeight="1">
-      <c r="A59" s="2" t="s">
+      <c r="A59" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" s="8" t="s">
         <v>119</v>
       </c>
+      <c r="C59" s="9" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="60" ht="17.25" customHeight="1">
-      <c r="A60" s="7" t="s">
+      <c r="A60" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="B60" s="1" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="61" ht="17.25" customHeight="1">
-      <c r="A61" s="7" t="s">
+      <c r="A61" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B61" s="8" t="s">
+      <c r="B61" s="1" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="62" ht="17.25" customHeight="1">
-      <c r="A62" s="7" t="s">
+      <c r="A62" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B62" s="8" t="s">
+      <c r="B62" s="1" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="63" ht="17.25" customHeight="1">
-      <c r="A63" s="7" t="s">
+      <c r="A63" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B63" s="8" t="s">
+      <c r="B63" s="1" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="64" ht="17.25" customHeight="1">
-      <c r="A64" s="7" t="s">
+      <c r="A64" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B64" s="8" t="s">
+      <c r="B64" s="1" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="65" ht="17.25" customHeight="1">
-      <c r="A65" s="7" t="s">
+      <c r="A65" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B65" s="8" t="s">
+      <c r="B65" s="1" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="66" ht="17.25" customHeight="1">
-      <c r="A66" s="7" t="s">
+      <c r="A66" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B66" s="8" t="s">
+      <c r="B66" s="1" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="67" ht="17.25" customHeight="1">
-      <c r="A67" s="7" t="s">
+      <c r="A67" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B67" s="8" t="s">
+      <c r="B67" s="1" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="68" ht="17.25" customHeight="1">
-      <c r="A68" s="7" t="s">
+      <c r="A68" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B68" s="8" t="s">
+      <c r="B68" s="1" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="69" ht="17.25" customHeight="1">
-      <c r="A69" s="8" t="s">
+      <c r="A69" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B69" s="8" t="s">
+      <c r="B69" s="1" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="70" ht="17.25" customHeight="1">
-      <c r="A70" s="8" t="s">
+      <c r="A70" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B70" s="8" t="s">
+      <c r="B70" s="1" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="71" ht="17.25" customHeight="1">
-      <c r="A71" s="9" t="s">
+      <c r="A71" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="B71" s="9" t="s">
+      <c r="B71" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="C71" s="10"/>
     </row>
     <row r="72" ht="17.25" customHeight="1">
-      <c r="A72" s="9" t="s">
+      <c r="A72" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="B72" s="9" t="s">
+      <c r="B72" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="C72" s="9" t="s">
+      <c r="C72" s="10"/>
+    </row>
+    <row r="73" ht="17.25" customHeight="1">
+      <c r="A73" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="B73" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="C73" s="10" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="73" ht="17.25" customHeight="1">
-      <c r="A73" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="B73" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="C73" s="9" t="s">
+    <row r="74" ht="17.25" customHeight="1">
+      <c r="A74" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="B74" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="C74" s="10" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="74" ht="17.25" customHeight="1">
-      <c r="A74" s="9" t="s">
-        <v>148</v>
-      </c>
-      <c r="B74" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="C74" s="9" t="s">
+    <row r="75" ht="17.25" customHeight="1">
+      <c r="A75" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="B75" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="C75" s="10" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="75" ht="17.25" customHeight="1">
-      <c r="A75" s="9" t="s">
-        <v>150</v>
-      </c>
-      <c r="B75" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="C75" s="9" t="s">
+    <row r="76" ht="17.25" customHeight="1">
+      <c r="A76" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="B76" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="C76" s="10" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="76" ht="17.25" customHeight="1">
-      <c r="A76" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="B76" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="C76" s="9" t="s">
+    <row r="77" ht="17.25" customHeight="1">
+      <c r="A77" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="B77" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="C77" s="10" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="77" ht="17.25" customHeight="1">
-      <c r="A77" s="9" t="s">
-        <v>154</v>
-      </c>
-      <c r="B77" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="C77" s="10"/>
-    </row>
     <row r="78" ht="17.25" customHeight="1">
-      <c r="A78" s="9" t="s">
+      <c r="A78" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="B78" s="9" t="s">
+      <c r="B78" s="10" t="s">
         <v>157</v>
       </c>
       <c r="C78" s="10"/>
     </row>
     <row r="79" ht="17.25" customHeight="1">
-      <c r="A79" s="9" t="s">
+      <c r="A79" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="B79" s="9" t="s">
+      <c r="B79" s="10" t="s">
         <v>159</v>
       </c>
       <c r="C79" s="10"/>
     </row>
     <row r="80" ht="17.25" customHeight="1">
-      <c r="A80" s="9" t="s">
+      <c r="A80" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="B80" s="9" t="s">
+      <c r="B80" s="10" t="s">
         <v>161</v>
       </c>
       <c r="C80" s="10"/>
     </row>
     <row r="81" ht="17.25" customHeight="1">
-      <c r="A81" s="9" t="s">
+      <c r="A81" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="B81" s="9" t="s">
+      <c r="B81" s="10" t="s">
         <v>163</v>
       </c>
       <c r="C81" s="10"/>
     </row>
     <row r="82" ht="17.25" customHeight="1">
-      <c r="A82" s="9" t="s">
+      <c r="A82" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="B82" s="9" t="s">
+      <c r="B82" s="10" t="s">
         <v>165</v>
       </c>
       <c r="C82" s="10"/>
     </row>
     <row r="83" ht="17.25" customHeight="1">
-      <c r="A83" s="9" t="s">
+      <c r="A83" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="B83" s="9" t="s">
+      <c r="B83" s="10" t="s">
         <v>167</v>
       </c>
       <c r="C83" s="10"/>
     </row>
     <row r="84" ht="17.25" customHeight="1">
-      <c r="A84" s="9" t="s">
+      <c r="A84" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="B84" s="9" t="s">
+      <c r="B84" s="10" t="s">
         <v>169</v>
       </c>
       <c r="C84" s="10"/>
     </row>
     <row r="85" ht="17.25" customHeight="1">
-      <c r="A85" s="9" t="s">
+      <c r="A85" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="B85" s="9" t="s">
+      <c r="B85" s="10" t="s">
         <v>171</v>
       </c>
       <c r="C85" s="10"/>
     </row>
     <row r="86" ht="17.25" customHeight="1">
-      <c r="A86" s="8" t="s">
+      <c r="A86" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="B86" s="8" t="s">
+      <c r="B86" s="10" t="s">
         <v>173</v>
       </c>
+      <c r="C86" s="10"/>
     </row>
     <row r="87" ht="17.25" customHeight="1">
-      <c r="A87" s="8" t="s">
+      <c r="A87" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B87" s="8" t="s">
+      <c r="B87" s="1" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="88" ht="17.25" customHeight="1">
-      <c r="A88" s="8" t="s">
+      <c r="A88" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B88" s="8" t="s">
+      <c r="B88" s="1" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="89" ht="17.25" customHeight="1">
-      <c r="A89" s="8" t="s">
+      <c r="A89" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B89" s="8" t="s">
+      <c r="B89" s="1" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="90" ht="17.25" customHeight="1">
-      <c r="A90" s="8" t="s">
+      <c r="A90" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B90" s="8" t="s">
+      <c r="B90" s="1" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="91" ht="17.25" customHeight="1">
-      <c r="A91" s="9" t="s">
+      <c r="A91" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B91" s="9" t="s">
+      <c r="B91" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="C91" s="10"/>
     </row>
     <row r="92" ht="17.25" customHeight="1">
-      <c r="A92" s="9" t="s">
+      <c r="A92" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="B92" s="11" t="s">
+      <c r="B92" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="C92" s="9" t="s">
-        <v>97</v>
-      </c>
+      <c r="C92" s="10"/>
     </row>
     <row r="93" ht="17.25" customHeight="1">
-      <c r="A93" s="9" t="s">
+      <c r="A93" s="10" t="s">
         <v>186</v>
       </c>
       <c r="B93" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="C93" s="10"/>
+      <c r="C93" s="10" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="94" ht="17.25" customHeight="1">
-      <c r="A94" s="9" t="s">
+      <c r="A94" s="10" t="s">
         <v>188</v>
       </c>
       <c r="B94" s="11" t="s">
@@ -1771,7 +1782,7 @@
       <c r="C94" s="10"/>
     </row>
     <row r="95" ht="17.25" customHeight="1">
-      <c r="A95" s="9" t="s">
+      <c r="A95" s="10" t="s">
         <v>190</v>
       </c>
       <c r="B95" s="11" t="s">
@@ -1780,7 +1791,7 @@
       <c r="C95" s="10"/>
     </row>
     <row r="96" ht="17.25" customHeight="1">
-      <c r="A96" s="9" t="s">
+      <c r="A96" s="10" t="s">
         <v>192</v>
       </c>
       <c r="B96" s="11" t="s">
@@ -1789,62 +1800,70 @@
       <c r="C96" s="10"/>
     </row>
     <row r="97" ht="17.25" customHeight="1">
-      <c r="A97" s="8" t="s">
+      <c r="A97" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="B97" s="8" t="s">
+      <c r="B97" s="11" t="s">
         <v>195</v>
       </c>
+      <c r="C97" s="10"/>
     </row>
     <row r="98" ht="17.25" customHeight="1">
-      <c r="A98" s="8" t="s">
+      <c r="A98" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B98" s="8" t="s">
+      <c r="B98" s="1" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="99" ht="17.25" customHeight="1">
-      <c r="A99" s="8" t="s">
+      <c r="A99" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B99" s="8" t="s">
+      <c r="B99" s="1" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="100" ht="17.25" customHeight="1">
-      <c r="A100" s="8" t="s">
+      <c r="A100" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B100" s="8" t="s">
+      <c r="B100" s="1" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="101" ht="17.25" customHeight="1">
-      <c r="A101" s="8" t="s">
+      <c r="A101" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B101" s="8" t="s">
+      <c r="B101" s="1" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="102" ht="17.25" customHeight="1">
-      <c r="A102" s="8" t="s">
+      <c r="A102" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B102" s="8" t="s">
+      <c r="B102" s="1" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="103" ht="17.25" customHeight="1">
-      <c r="A103" s="8" t="s">
+      <c r="A103" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B103" s="8" t="s">
+      <c r="B103" s="1" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="104" ht="17.25" customHeight="1"/>
+    <row r="104" ht="17.25" customHeight="1">
+      <c r="A104" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>209</v>
+      </c>
+    </row>
     <row r="105" ht="17.25" customHeight="1"/>
     <row r="106" ht="17.25" customHeight="1"/>
     <row r="107" ht="17.25" customHeight="1"/>
@@ -2045,700 +2064,703 @@
     <row r="302" ht="17.25" customHeight="1"/>
     <row r="303" ht="17.25" customHeight="1"/>
     <row r="304" ht="17.25" customHeight="1"/>
-    <row r="305" ht="17.25" customHeight="1"/>
-    <row r="306" ht="17.25" customHeight="1"/>
-    <row r="307" ht="17.25" customHeight="1"/>
-    <row r="308" ht="17.25" customHeight="1"/>
-    <row r="309" ht="17.25" customHeight="1"/>
-    <row r="310" ht="17.25" customHeight="1"/>
-    <row r="311" ht="17.25" customHeight="1"/>
-    <row r="312" ht="17.25" customHeight="1"/>
-    <row r="313" ht="17.25" customHeight="1"/>
-    <row r="314" ht="17.25" customHeight="1"/>
-    <row r="315" ht="17.25" customHeight="1"/>
-    <row r="316" ht="17.25" customHeight="1"/>
-    <row r="317" ht="17.25" customHeight="1"/>
-    <row r="318" ht="17.25" customHeight="1"/>
-    <row r="319" ht="17.25" customHeight="1"/>
-    <row r="320" ht="17.25" customHeight="1"/>
-    <row r="321" ht="17.25" customHeight="1"/>
-    <row r="322" ht="17.25" customHeight="1"/>
-    <row r="323" ht="17.25" customHeight="1"/>
-    <row r="324" ht="17.25" customHeight="1"/>
-    <row r="325" ht="17.25" customHeight="1"/>
-    <row r="326" ht="17.25" customHeight="1"/>
-    <row r="327" ht="17.25" customHeight="1"/>
-    <row r="328" ht="17.25" customHeight="1"/>
-    <row r="329" ht="17.25" customHeight="1"/>
-    <row r="330" ht="17.25" customHeight="1"/>
-    <row r="331" ht="17.25" customHeight="1"/>
-    <row r="332" ht="17.25" customHeight="1"/>
-    <row r="333" ht="17.25" customHeight="1"/>
-    <row r="334" ht="17.25" customHeight="1"/>
-    <row r="335" ht="17.25" customHeight="1"/>
-    <row r="336" ht="17.25" customHeight="1"/>
-    <row r="337" ht="17.25" customHeight="1"/>
-    <row r="338" ht="17.25" customHeight="1"/>
-    <row r="339" ht="17.25" customHeight="1"/>
-    <row r="340" ht="17.25" customHeight="1"/>
-    <row r="341" ht="17.25" customHeight="1"/>
-    <row r="342" ht="17.25" customHeight="1"/>
-    <row r="343" ht="17.25" customHeight="1"/>
-    <row r="344" ht="17.25" customHeight="1"/>
-    <row r="345" ht="17.25" customHeight="1"/>
-    <row r="346" ht="17.25" customHeight="1"/>
-    <row r="347" ht="17.25" customHeight="1"/>
-    <row r="348" ht="17.25" customHeight="1"/>
-    <row r="349" ht="17.25" customHeight="1"/>
-    <row r="350" ht="17.25" customHeight="1"/>
-    <row r="351" ht="17.25" customHeight="1"/>
-    <row r="352" ht="17.25" customHeight="1"/>
-    <row r="353" ht="17.25" customHeight="1"/>
-    <row r="354" ht="17.25" customHeight="1"/>
-    <row r="355" ht="17.25" customHeight="1"/>
-    <row r="356" ht="17.25" customHeight="1"/>
-    <row r="357" ht="17.25" customHeight="1"/>
-    <row r="358" ht="17.25" customHeight="1"/>
-    <row r="359" ht="17.25" customHeight="1"/>
-    <row r="360" ht="17.25" customHeight="1"/>
-    <row r="361" ht="17.25" customHeight="1"/>
-    <row r="362" ht="17.25" customHeight="1"/>
-    <row r="363" ht="17.25" customHeight="1"/>
-    <row r="364" ht="17.25" customHeight="1"/>
-    <row r="365" ht="17.25" customHeight="1"/>
-    <row r="366" ht="17.25" customHeight="1"/>
-    <row r="367" ht="17.25" customHeight="1"/>
-    <row r="368" ht="17.25" customHeight="1"/>
-    <row r="369" ht="17.25" customHeight="1"/>
-    <row r="370" ht="17.25" customHeight="1"/>
-    <row r="371" ht="17.25" customHeight="1"/>
-    <row r="372" ht="17.25" customHeight="1"/>
-    <row r="373" ht="17.25" customHeight="1"/>
-    <row r="374" ht="17.25" customHeight="1"/>
-    <row r="375" ht="17.25" customHeight="1"/>
-    <row r="376" ht="17.25" customHeight="1"/>
-    <row r="377" ht="17.25" customHeight="1"/>
-    <row r="378" ht="17.25" customHeight="1"/>
-    <row r="379" ht="17.25" customHeight="1"/>
-    <row r="380" ht="17.25" customHeight="1"/>
-    <row r="381" ht="17.25" customHeight="1"/>
-    <row r="382" ht="17.25" customHeight="1"/>
-    <row r="383" ht="17.25" customHeight="1"/>
-    <row r="384" ht="17.25" customHeight="1"/>
-    <row r="385" ht="17.25" customHeight="1"/>
-    <row r="386" ht="17.25" customHeight="1"/>
-    <row r="387" ht="17.25" customHeight="1"/>
-    <row r="388" ht="17.25" customHeight="1"/>
-    <row r="389" ht="17.25" customHeight="1"/>
-    <row r="390" ht="17.25" customHeight="1"/>
-    <row r="391" ht="17.25" customHeight="1"/>
-    <row r="392" ht="17.25" customHeight="1"/>
-    <row r="393" ht="17.25" customHeight="1"/>
-    <row r="394" ht="17.25" customHeight="1"/>
-    <row r="395" ht="17.25" customHeight="1"/>
-    <row r="396" ht="17.25" customHeight="1"/>
-    <row r="397" ht="17.25" customHeight="1"/>
-    <row r="398" ht="17.25" customHeight="1"/>
-    <row r="399" ht="17.25" customHeight="1"/>
-    <row r="400" ht="17.25" customHeight="1"/>
-    <row r="401" ht="17.25" customHeight="1"/>
-    <row r="402" ht="17.25" customHeight="1"/>
-    <row r="403" ht="17.25" customHeight="1"/>
-    <row r="404" ht="17.25" customHeight="1"/>
-    <row r="405" ht="17.25" customHeight="1"/>
-    <row r="406" ht="17.25" customHeight="1"/>
-    <row r="407" ht="17.25" customHeight="1"/>
-    <row r="408" ht="17.25" customHeight="1"/>
-    <row r="409" ht="17.25" customHeight="1"/>
-    <row r="410" ht="17.25" customHeight="1"/>
-    <row r="411" ht="17.25" customHeight="1"/>
-    <row r="412" ht="17.25" customHeight="1"/>
-    <row r="413" ht="17.25" customHeight="1"/>
-    <row r="414" ht="17.25" customHeight="1"/>
-    <row r="415" ht="17.25" customHeight="1"/>
-    <row r="416" ht="17.25" customHeight="1"/>
-    <row r="417" ht="17.25" customHeight="1"/>
-    <row r="418" ht="17.25" customHeight="1"/>
-    <row r="419" ht="17.25" customHeight="1"/>
-    <row r="420" ht="17.25" customHeight="1"/>
-    <row r="421" ht="17.25" customHeight="1"/>
-    <row r="422" ht="17.25" customHeight="1"/>
-    <row r="423" ht="17.25" customHeight="1"/>
-    <row r="424" ht="17.25" customHeight="1"/>
-    <row r="425" ht="17.25" customHeight="1"/>
-    <row r="426" ht="17.25" customHeight="1"/>
-    <row r="427" ht="17.25" customHeight="1"/>
-    <row r="428" ht="17.25" customHeight="1"/>
-    <row r="429" ht="17.25" customHeight="1"/>
-    <row r="430" ht="17.25" customHeight="1"/>
-    <row r="431" ht="17.25" customHeight="1"/>
-    <row r="432" ht="17.25" customHeight="1"/>
-    <row r="433" ht="17.25" customHeight="1"/>
-    <row r="434" ht="17.25" customHeight="1"/>
-    <row r="435" ht="17.25" customHeight="1"/>
-    <row r="436" ht="17.25" customHeight="1"/>
-    <row r="437" ht="17.25" customHeight="1"/>
-    <row r="438" ht="17.25" customHeight="1"/>
-    <row r="439" ht="17.25" customHeight="1"/>
-    <row r="440" ht="17.25" customHeight="1"/>
-    <row r="441" ht="17.25" customHeight="1"/>
-    <row r="442" ht="17.25" customHeight="1"/>
-    <row r="443" ht="17.25" customHeight="1"/>
-    <row r="444" ht="17.25" customHeight="1"/>
-    <row r="445" ht="17.25" customHeight="1"/>
-    <row r="446" ht="17.25" customHeight="1"/>
-    <row r="447" ht="17.25" customHeight="1"/>
-    <row r="448" ht="17.25" customHeight="1"/>
-    <row r="449" ht="17.25" customHeight="1"/>
-    <row r="450" ht="17.25" customHeight="1"/>
-    <row r="451" ht="17.25" customHeight="1"/>
-    <row r="452" ht="17.25" customHeight="1"/>
-    <row r="453" ht="17.25" customHeight="1"/>
-    <row r="454" ht="17.25" customHeight="1"/>
-    <row r="455" ht="17.25" customHeight="1"/>
-    <row r="456" ht="17.25" customHeight="1"/>
-    <row r="457" ht="17.25" customHeight="1"/>
-    <row r="458" ht="17.25" customHeight="1"/>
-    <row r="459" ht="17.25" customHeight="1"/>
-    <row r="460" ht="17.25" customHeight="1"/>
-    <row r="461" ht="17.25" customHeight="1"/>
-    <row r="462" ht="17.25" customHeight="1"/>
-    <row r="463" ht="17.25" customHeight="1"/>
-    <row r="464" ht="17.25" customHeight="1"/>
-    <row r="465" ht="17.25" customHeight="1"/>
-    <row r="466" ht="17.25" customHeight="1"/>
-    <row r="467" ht="17.25" customHeight="1"/>
-    <row r="468" ht="17.25" customHeight="1"/>
-    <row r="469" ht="17.25" customHeight="1"/>
-    <row r="470" ht="17.25" customHeight="1"/>
-    <row r="471" ht="17.25" customHeight="1"/>
-    <row r="472" ht="17.25" customHeight="1"/>
-    <row r="473" ht="17.25" customHeight="1"/>
-    <row r="474" ht="17.25" customHeight="1"/>
-    <row r="475" ht="17.25" customHeight="1"/>
-    <row r="476" ht="17.25" customHeight="1"/>
-    <row r="477" ht="17.25" customHeight="1"/>
-    <row r="478" ht="17.25" customHeight="1"/>
-    <row r="479" ht="17.25" customHeight="1"/>
-    <row r="480" ht="17.25" customHeight="1"/>
-    <row r="481" ht="17.25" customHeight="1"/>
-    <row r="482" ht="17.25" customHeight="1"/>
-    <row r="483" ht="17.25" customHeight="1"/>
-    <row r="484" ht="17.25" customHeight="1"/>
-    <row r="485" ht="17.25" customHeight="1"/>
-    <row r="486" ht="17.25" customHeight="1"/>
-    <row r="487" ht="17.25" customHeight="1"/>
-    <row r="488" ht="17.25" customHeight="1"/>
-    <row r="489" ht="17.25" customHeight="1"/>
-    <row r="490" ht="17.25" customHeight="1"/>
-    <row r="491" ht="17.25" customHeight="1"/>
-    <row r="492" ht="17.25" customHeight="1"/>
-    <row r="493" ht="17.25" customHeight="1"/>
-    <row r="494" ht="17.25" customHeight="1"/>
-    <row r="495" ht="17.25" customHeight="1"/>
-    <row r="496" ht="17.25" customHeight="1"/>
-    <row r="497" ht="17.25" customHeight="1"/>
-    <row r="498" ht="17.25" customHeight="1"/>
-    <row r="499" ht="17.25" customHeight="1"/>
-    <row r="500" ht="17.25" customHeight="1"/>
-    <row r="501" ht="17.25" customHeight="1"/>
-    <row r="502" ht="17.25" customHeight="1"/>
-    <row r="503" ht="17.25" customHeight="1"/>
-    <row r="504" ht="17.25" customHeight="1"/>
-    <row r="505" ht="17.25" customHeight="1"/>
-    <row r="506" ht="17.25" customHeight="1"/>
-    <row r="507" ht="17.25" customHeight="1"/>
-    <row r="508" ht="17.25" customHeight="1"/>
-    <row r="509" ht="17.25" customHeight="1"/>
-    <row r="510" ht="17.25" customHeight="1"/>
-    <row r="511" ht="17.25" customHeight="1"/>
-    <row r="512" ht="17.25" customHeight="1"/>
-    <row r="513" ht="17.25" customHeight="1"/>
-    <row r="514" ht="17.25" customHeight="1"/>
-    <row r="515" ht="17.25" customHeight="1"/>
-    <row r="516" ht="17.25" customHeight="1"/>
-    <row r="517" ht="17.25" customHeight="1"/>
-    <row r="518" ht="17.25" customHeight="1"/>
-    <row r="519" ht="17.25" customHeight="1"/>
-    <row r="520" ht="17.25" customHeight="1"/>
-    <row r="521" ht="17.25" customHeight="1"/>
-    <row r="522" ht="17.25" customHeight="1"/>
-    <row r="523" ht="17.25" customHeight="1"/>
-    <row r="524" ht="17.25" customHeight="1"/>
-    <row r="525" ht="17.25" customHeight="1"/>
-    <row r="526" ht="17.25" customHeight="1"/>
-    <row r="527" ht="17.25" customHeight="1"/>
-    <row r="528" ht="17.25" customHeight="1"/>
-    <row r="529" ht="17.25" customHeight="1"/>
-    <row r="530" ht="17.25" customHeight="1"/>
-    <row r="531" ht="17.25" customHeight="1"/>
-    <row r="532" ht="17.25" customHeight="1"/>
-    <row r="533" ht="17.25" customHeight="1"/>
-    <row r="534" ht="17.25" customHeight="1"/>
-    <row r="535" ht="17.25" customHeight="1"/>
-    <row r="536" ht="17.25" customHeight="1"/>
-    <row r="537" ht="17.25" customHeight="1"/>
-    <row r="538" ht="17.25" customHeight="1"/>
-    <row r="539" ht="17.25" customHeight="1"/>
-    <row r="540" ht="17.25" customHeight="1"/>
-    <row r="541" ht="17.25" customHeight="1"/>
-    <row r="542" ht="17.25" customHeight="1"/>
-    <row r="543" ht="17.25" customHeight="1"/>
-    <row r="544" ht="17.25" customHeight="1"/>
-    <row r="545" ht="17.25" customHeight="1"/>
-    <row r="546" ht="17.25" customHeight="1"/>
-    <row r="547" ht="17.25" customHeight="1"/>
-    <row r="548" ht="17.25" customHeight="1"/>
-    <row r="549" ht="17.25" customHeight="1"/>
-    <row r="550" ht="17.25" customHeight="1"/>
-    <row r="551" ht="17.25" customHeight="1"/>
-    <row r="552" ht="17.25" customHeight="1"/>
-    <row r="553" ht="17.25" customHeight="1"/>
-    <row r="554" ht="17.25" customHeight="1"/>
-    <row r="555" ht="17.25" customHeight="1"/>
-    <row r="556" ht="17.25" customHeight="1"/>
-    <row r="557" ht="17.25" customHeight="1"/>
-    <row r="558" ht="17.25" customHeight="1"/>
-    <row r="559" ht="17.25" customHeight="1"/>
-    <row r="560" ht="17.25" customHeight="1"/>
-    <row r="561" ht="17.25" customHeight="1"/>
-    <row r="562" ht="17.25" customHeight="1"/>
-    <row r="563" ht="17.25" customHeight="1"/>
-    <row r="564" ht="17.25" customHeight="1"/>
-    <row r="565" ht="17.25" customHeight="1"/>
-    <row r="566" ht="17.25" customHeight="1"/>
-    <row r="567" ht="17.25" customHeight="1"/>
-    <row r="568" ht="17.25" customHeight="1"/>
-    <row r="569" ht="17.25" customHeight="1"/>
-    <row r="570" ht="17.25" customHeight="1"/>
-    <row r="571" ht="17.25" customHeight="1"/>
-    <row r="572" ht="17.25" customHeight="1"/>
-    <row r="573" ht="17.25" customHeight="1"/>
-    <row r="574" ht="17.25" customHeight="1"/>
-    <row r="575" ht="17.25" customHeight="1"/>
-    <row r="576" ht="17.25" customHeight="1"/>
-    <row r="577" ht="17.25" customHeight="1"/>
-    <row r="578" ht="17.25" customHeight="1"/>
-    <row r="579" ht="17.25" customHeight="1"/>
-    <row r="580" ht="17.25" customHeight="1"/>
-    <row r="581" ht="17.25" customHeight="1"/>
-    <row r="582" ht="17.25" customHeight="1"/>
-    <row r="583" ht="17.25" customHeight="1"/>
-    <row r="584" ht="17.25" customHeight="1"/>
-    <row r="585" ht="17.25" customHeight="1"/>
-    <row r="586" ht="17.25" customHeight="1"/>
-    <row r="587" ht="17.25" customHeight="1"/>
-    <row r="588" ht="17.25" customHeight="1"/>
-    <row r="589" ht="17.25" customHeight="1"/>
-    <row r="590" ht="17.25" customHeight="1"/>
-    <row r="591" ht="17.25" customHeight="1"/>
-    <row r="592" ht="17.25" customHeight="1"/>
-    <row r="593" ht="17.25" customHeight="1"/>
-    <row r="594" ht="17.25" customHeight="1"/>
-    <row r="595" ht="17.25" customHeight="1"/>
-    <row r="596" ht="17.25" customHeight="1"/>
-    <row r="597" ht="17.25" customHeight="1"/>
-    <row r="598" ht="17.25" customHeight="1"/>
-    <row r="599" ht="17.25" customHeight="1"/>
-    <row r="600" ht="17.25" customHeight="1"/>
-    <row r="601" ht="17.25" customHeight="1"/>
-    <row r="602" ht="17.25" customHeight="1"/>
-    <row r="603" ht="17.25" customHeight="1"/>
-    <row r="604" ht="17.25" customHeight="1"/>
-    <row r="605" ht="17.25" customHeight="1"/>
-    <row r="606" ht="17.25" customHeight="1"/>
-    <row r="607" ht="17.25" customHeight="1"/>
-    <row r="608" ht="17.25" customHeight="1"/>
-    <row r="609" ht="17.25" customHeight="1"/>
-    <row r="610" ht="17.25" customHeight="1"/>
-    <row r="611" ht="17.25" customHeight="1"/>
-    <row r="612" ht="17.25" customHeight="1"/>
-    <row r="613" ht="17.25" customHeight="1"/>
-    <row r="614" ht="17.25" customHeight="1"/>
-    <row r="615" ht="17.25" customHeight="1"/>
-    <row r="616" ht="17.25" customHeight="1"/>
-    <row r="617" ht="17.25" customHeight="1"/>
-    <row r="618" ht="17.25" customHeight="1"/>
-    <row r="619" ht="17.25" customHeight="1"/>
-    <row r="620" ht="17.25" customHeight="1"/>
-    <row r="621" ht="17.25" customHeight="1"/>
-    <row r="622" ht="17.25" customHeight="1"/>
-    <row r="623" ht="17.25" customHeight="1"/>
-    <row r="624" ht="17.25" customHeight="1"/>
-    <row r="625" ht="17.25" customHeight="1"/>
-    <row r="626" ht="17.25" customHeight="1"/>
-    <row r="627" ht="17.25" customHeight="1"/>
-    <row r="628" ht="17.25" customHeight="1"/>
-    <row r="629" ht="17.25" customHeight="1"/>
-    <row r="630" ht="17.25" customHeight="1"/>
-    <row r="631" ht="17.25" customHeight="1"/>
-    <row r="632" ht="17.25" customHeight="1"/>
-    <row r="633" ht="17.25" customHeight="1"/>
-    <row r="634" ht="17.25" customHeight="1"/>
-    <row r="635" ht="17.25" customHeight="1"/>
-    <row r="636" ht="17.25" customHeight="1"/>
-    <row r="637" ht="17.25" customHeight="1"/>
-    <row r="638" ht="17.25" customHeight="1"/>
-    <row r="639" ht="17.25" customHeight="1"/>
-    <row r="640" ht="17.25" customHeight="1"/>
-    <row r="641" ht="17.25" customHeight="1"/>
-    <row r="642" ht="17.25" customHeight="1"/>
-    <row r="643" ht="17.25" customHeight="1"/>
-    <row r="644" ht="17.25" customHeight="1"/>
-    <row r="645" ht="17.25" customHeight="1"/>
-    <row r="646" ht="17.25" customHeight="1"/>
-    <row r="647" ht="17.25" customHeight="1"/>
-    <row r="648" ht="17.25" customHeight="1"/>
-    <row r="649" ht="17.25" customHeight="1"/>
-    <row r="650" ht="17.25" customHeight="1"/>
-    <row r="651" ht="17.25" customHeight="1"/>
-    <row r="652" ht="17.25" customHeight="1"/>
-    <row r="653" ht="17.25" customHeight="1"/>
-    <row r="654" ht="17.25" customHeight="1"/>
-    <row r="655" ht="17.25" customHeight="1"/>
-    <row r="656" ht="17.25" customHeight="1"/>
-    <row r="657" ht="17.25" customHeight="1"/>
-    <row r="658" ht="17.25" customHeight="1"/>
-    <row r="659" ht="17.25" customHeight="1"/>
-    <row r="660" ht="17.25" customHeight="1"/>
-    <row r="661" ht="17.25" customHeight="1"/>
-    <row r="662" ht="17.25" customHeight="1"/>
-    <row r="663" ht="17.25" customHeight="1"/>
-    <row r="664" ht="17.25" customHeight="1"/>
-    <row r="665" ht="17.25" customHeight="1"/>
-    <row r="666" ht="17.25" customHeight="1"/>
-    <row r="667" ht="17.25" customHeight="1"/>
-    <row r="668" ht="17.25" customHeight="1"/>
-    <row r="669" ht="17.25" customHeight="1"/>
-    <row r="670" ht="17.25" customHeight="1"/>
-    <row r="671" ht="17.25" customHeight="1"/>
-    <row r="672" ht="17.25" customHeight="1"/>
-    <row r="673" ht="17.25" customHeight="1"/>
-    <row r="674" ht="17.25" customHeight="1"/>
-    <row r="675" ht="17.25" customHeight="1"/>
-    <row r="676" ht="17.25" customHeight="1"/>
-    <row r="677" ht="17.25" customHeight="1"/>
-    <row r="678" ht="17.25" customHeight="1"/>
-    <row r="679" ht="17.25" customHeight="1"/>
-    <row r="680" ht="17.25" customHeight="1"/>
-    <row r="681" ht="17.25" customHeight="1"/>
-    <row r="682" ht="17.25" customHeight="1"/>
-    <row r="683" ht="17.25" customHeight="1"/>
-    <row r="684" ht="17.25" customHeight="1"/>
-    <row r="685" ht="17.25" customHeight="1"/>
-    <row r="686" ht="17.25" customHeight="1"/>
-    <row r="687" ht="17.25" customHeight="1"/>
-    <row r="688" ht="17.25" customHeight="1"/>
-    <row r="689" ht="17.25" customHeight="1"/>
-    <row r="690" ht="17.25" customHeight="1"/>
-    <row r="691" ht="17.25" customHeight="1"/>
-    <row r="692" ht="17.25" customHeight="1"/>
-    <row r="693" ht="17.25" customHeight="1"/>
-    <row r="694" ht="17.25" customHeight="1"/>
-    <row r="695" ht="17.25" customHeight="1"/>
-    <row r="696" ht="17.25" customHeight="1"/>
-    <row r="697" ht="17.25" customHeight="1"/>
-    <row r="698" ht="17.25" customHeight="1"/>
-    <row r="699" ht="17.25" customHeight="1"/>
-    <row r="700" ht="17.25" customHeight="1"/>
-    <row r="701" ht="17.25" customHeight="1"/>
-    <row r="702" ht="17.25" customHeight="1"/>
-    <row r="703" ht="17.25" customHeight="1"/>
-    <row r="704" ht="17.25" customHeight="1"/>
-    <row r="705" ht="17.25" customHeight="1"/>
-    <row r="706" ht="17.25" customHeight="1"/>
-    <row r="707" ht="17.25" customHeight="1"/>
-    <row r="708" ht="17.25" customHeight="1"/>
-    <row r="709" ht="17.25" customHeight="1"/>
-    <row r="710" ht="17.25" customHeight="1"/>
-    <row r="711" ht="17.25" customHeight="1"/>
-    <row r="712" ht="17.25" customHeight="1"/>
-    <row r="713" ht="17.25" customHeight="1"/>
-    <row r="714" ht="17.25" customHeight="1"/>
-    <row r="715" ht="17.25" customHeight="1"/>
-    <row r="716" ht="17.25" customHeight="1"/>
-    <row r="717" ht="17.25" customHeight="1"/>
-    <row r="718" ht="17.25" customHeight="1"/>
-    <row r="719" ht="17.25" customHeight="1"/>
-    <row r="720" ht="17.25" customHeight="1"/>
-    <row r="721" ht="17.25" customHeight="1"/>
-    <row r="722" ht="17.25" customHeight="1"/>
-    <row r="723" ht="17.25" customHeight="1"/>
-    <row r="724" ht="17.25" customHeight="1"/>
-    <row r="725" ht="17.25" customHeight="1"/>
-    <row r="726" ht="17.25" customHeight="1"/>
-    <row r="727" ht="17.25" customHeight="1"/>
-    <row r="728" ht="17.25" customHeight="1"/>
-    <row r="729" ht="17.25" customHeight="1"/>
-    <row r="730" ht="17.25" customHeight="1"/>
-    <row r="731" ht="17.25" customHeight="1"/>
-    <row r="732" ht="17.25" customHeight="1"/>
-    <row r="733" ht="17.25" customHeight="1"/>
-    <row r="734" ht="17.25" customHeight="1"/>
-    <row r="735" ht="17.25" customHeight="1"/>
-    <row r="736" ht="17.25" customHeight="1"/>
-    <row r="737" ht="17.25" customHeight="1"/>
-    <row r="738" ht="17.25" customHeight="1"/>
-    <row r="739" ht="17.25" customHeight="1"/>
-    <row r="740" ht="17.25" customHeight="1"/>
-    <row r="741" ht="17.25" customHeight="1"/>
-    <row r="742" ht="17.25" customHeight="1"/>
-    <row r="743" ht="17.25" customHeight="1"/>
-    <row r="744" ht="17.25" customHeight="1"/>
-    <row r="745" ht="17.25" customHeight="1"/>
-    <row r="746" ht="17.25" customHeight="1"/>
-    <row r="747" ht="17.25" customHeight="1"/>
-    <row r="748" ht="17.25" customHeight="1"/>
-    <row r="749" ht="17.25" customHeight="1"/>
-    <row r="750" ht="17.25" customHeight="1"/>
-    <row r="751" ht="17.25" customHeight="1"/>
-    <row r="752" ht="17.25" customHeight="1"/>
-    <row r="753" ht="17.25" customHeight="1"/>
-    <row r="754" ht="17.25" customHeight="1"/>
-    <row r="755" ht="17.25" customHeight="1"/>
-    <row r="756" ht="17.25" customHeight="1"/>
-    <row r="757" ht="17.25" customHeight="1"/>
-    <row r="758" ht="17.25" customHeight="1"/>
-    <row r="759" ht="17.25" customHeight="1"/>
-    <row r="760" ht="17.25" customHeight="1"/>
-    <row r="761" ht="17.25" customHeight="1"/>
-    <row r="762" ht="17.25" customHeight="1"/>
-    <row r="763" ht="17.25" customHeight="1"/>
-    <row r="764" ht="17.25" customHeight="1"/>
-    <row r="765" ht="17.25" customHeight="1"/>
-    <row r="766" ht="17.25" customHeight="1"/>
-    <row r="767" ht="17.25" customHeight="1"/>
-    <row r="768" ht="17.25" customHeight="1"/>
-    <row r="769" ht="17.25" customHeight="1"/>
-    <row r="770" ht="17.25" customHeight="1"/>
-    <row r="771" ht="17.25" customHeight="1"/>
-    <row r="772" ht="17.25" customHeight="1"/>
-    <row r="773" ht="17.25" customHeight="1"/>
-    <row r="774" ht="17.25" customHeight="1"/>
-    <row r="775" ht="17.25" customHeight="1"/>
-    <row r="776" ht="17.25" customHeight="1"/>
-    <row r="777" ht="17.25" customHeight="1"/>
-    <row r="778" ht="17.25" customHeight="1"/>
-    <row r="779" ht="17.25" customHeight="1"/>
-    <row r="780" ht="17.25" customHeight="1"/>
-    <row r="781" ht="17.25" customHeight="1"/>
-    <row r="782" ht="17.25" customHeight="1"/>
-    <row r="783" ht="17.25" customHeight="1"/>
-    <row r="784" ht="17.25" customHeight="1"/>
-    <row r="785" ht="17.25" customHeight="1"/>
-    <row r="786" ht="17.25" customHeight="1"/>
-    <row r="787" ht="17.25" customHeight="1"/>
-    <row r="788" ht="17.25" customHeight="1"/>
-    <row r="789" ht="17.25" customHeight="1"/>
-    <row r="790" ht="17.25" customHeight="1"/>
-    <row r="791" ht="17.25" customHeight="1"/>
-    <row r="792" ht="17.25" customHeight="1"/>
-    <row r="793" ht="17.25" customHeight="1"/>
-    <row r="794" ht="17.25" customHeight="1"/>
-    <row r="795" ht="17.25" customHeight="1"/>
-    <row r="796" ht="17.25" customHeight="1"/>
-    <row r="797" ht="17.25" customHeight="1"/>
-    <row r="798" ht="17.25" customHeight="1"/>
-    <row r="799" ht="17.25" customHeight="1"/>
-    <row r="800" ht="17.25" customHeight="1"/>
-    <row r="801" ht="17.25" customHeight="1"/>
-    <row r="802" ht="17.25" customHeight="1"/>
-    <row r="803" ht="17.25" customHeight="1"/>
-    <row r="804" ht="17.25" customHeight="1"/>
-    <row r="805" ht="17.25" customHeight="1"/>
-    <row r="806" ht="17.25" customHeight="1"/>
-    <row r="807" ht="17.25" customHeight="1"/>
-    <row r="808" ht="17.25" customHeight="1"/>
-    <row r="809" ht="17.25" customHeight="1"/>
-    <row r="810" ht="17.25" customHeight="1"/>
-    <row r="811" ht="17.25" customHeight="1"/>
-    <row r="812" ht="17.25" customHeight="1"/>
-    <row r="813" ht="17.25" customHeight="1"/>
-    <row r="814" ht="17.25" customHeight="1"/>
-    <row r="815" ht="17.25" customHeight="1"/>
-    <row r="816" ht="17.25" customHeight="1"/>
-    <row r="817" ht="17.25" customHeight="1"/>
-    <row r="818" ht="17.25" customHeight="1"/>
-    <row r="819" ht="17.25" customHeight="1"/>
-    <row r="820" ht="17.25" customHeight="1"/>
-    <row r="821" ht="17.25" customHeight="1"/>
-    <row r="822" ht="17.25" customHeight="1"/>
-    <row r="823" ht="17.25" customHeight="1"/>
-    <row r="824" ht="17.25" customHeight="1"/>
-    <row r="825" ht="17.25" customHeight="1"/>
-    <row r="826" ht="17.25" customHeight="1"/>
-    <row r="827" ht="17.25" customHeight="1"/>
-    <row r="828" ht="17.25" customHeight="1"/>
-    <row r="829" ht="17.25" customHeight="1"/>
-    <row r="830" ht="17.25" customHeight="1"/>
-    <row r="831" ht="17.25" customHeight="1"/>
-    <row r="832" ht="17.25" customHeight="1"/>
-    <row r="833" ht="17.25" customHeight="1"/>
-    <row r="834" ht="17.25" customHeight="1"/>
-    <row r="835" ht="17.25" customHeight="1"/>
-    <row r="836" ht="17.25" customHeight="1"/>
-    <row r="837" ht="17.25" customHeight="1"/>
-    <row r="838" ht="17.25" customHeight="1"/>
-    <row r="839" ht="17.25" customHeight="1"/>
-    <row r="840" ht="17.25" customHeight="1"/>
-    <row r="841" ht="17.25" customHeight="1"/>
-    <row r="842" ht="17.25" customHeight="1"/>
-    <row r="843" ht="17.25" customHeight="1"/>
-    <row r="844" ht="17.25" customHeight="1"/>
-    <row r="845" ht="17.25" customHeight="1"/>
-    <row r="846" ht="17.25" customHeight="1"/>
-    <row r="847" ht="17.25" customHeight="1"/>
-    <row r="848" ht="17.25" customHeight="1"/>
-    <row r="849" ht="17.25" customHeight="1"/>
-    <row r="850" ht="17.25" customHeight="1"/>
-    <row r="851" ht="17.25" customHeight="1"/>
-    <row r="852" ht="17.25" customHeight="1"/>
-    <row r="853" ht="17.25" customHeight="1"/>
-    <row r="854" ht="17.25" customHeight="1"/>
-    <row r="855" ht="17.25" customHeight="1"/>
-    <row r="856" ht="17.25" customHeight="1"/>
-    <row r="857" ht="17.25" customHeight="1"/>
-    <row r="858" ht="17.25" customHeight="1"/>
-    <row r="859" ht="17.25" customHeight="1"/>
-    <row r="860" ht="17.25" customHeight="1"/>
-    <row r="861" ht="17.25" customHeight="1"/>
-    <row r="862" ht="17.25" customHeight="1"/>
-    <row r="863" ht="17.25" customHeight="1"/>
-    <row r="864" ht="17.25" customHeight="1"/>
-    <row r="865" ht="17.25" customHeight="1"/>
-    <row r="866" ht="17.25" customHeight="1"/>
-    <row r="867" ht="17.25" customHeight="1"/>
-    <row r="868" ht="17.25" customHeight="1"/>
-    <row r="869" ht="17.25" customHeight="1"/>
-    <row r="870" ht="17.25" customHeight="1"/>
-    <row r="871" ht="17.25" customHeight="1"/>
-    <row r="872" ht="17.25" customHeight="1"/>
-    <row r="873" ht="17.25" customHeight="1"/>
-    <row r="874" ht="17.25" customHeight="1"/>
-    <row r="875" ht="17.25" customHeight="1"/>
-    <row r="876" ht="17.25" customHeight="1"/>
-    <row r="877" ht="17.25" customHeight="1"/>
-    <row r="878" ht="17.25" customHeight="1"/>
-    <row r="879" ht="17.25" customHeight="1"/>
-    <row r="880" ht="17.25" customHeight="1"/>
-    <row r="881" ht="17.25" customHeight="1"/>
-    <row r="882" ht="17.25" customHeight="1"/>
-    <row r="883" ht="17.25" customHeight="1"/>
-    <row r="884" ht="17.25" customHeight="1"/>
-    <row r="885" ht="17.25" customHeight="1"/>
-    <row r="886" ht="17.25" customHeight="1"/>
-    <row r="887" ht="17.25" customHeight="1"/>
-    <row r="888" ht="17.25" customHeight="1"/>
-    <row r="889" ht="17.25" customHeight="1"/>
-    <row r="890" ht="17.25" customHeight="1"/>
-    <row r="891" ht="17.25" customHeight="1"/>
-    <row r="892" ht="17.25" customHeight="1"/>
-    <row r="893" ht="17.25" customHeight="1"/>
-    <row r="894" ht="17.25" customHeight="1"/>
-    <row r="895" ht="17.25" customHeight="1"/>
-    <row r="896" ht="17.25" customHeight="1"/>
-    <row r="897" ht="17.25" customHeight="1"/>
-    <row r="898" ht="17.25" customHeight="1"/>
-    <row r="899" ht="17.25" customHeight="1"/>
-    <row r="900" ht="17.25" customHeight="1"/>
-    <row r="901" ht="17.25" customHeight="1"/>
-    <row r="902" ht="17.25" customHeight="1"/>
-    <row r="903" ht="17.25" customHeight="1"/>
-    <row r="904" ht="17.25" customHeight="1"/>
-    <row r="905" ht="17.25" customHeight="1"/>
-    <row r="906" ht="17.25" customHeight="1"/>
-    <row r="907" ht="17.25" customHeight="1"/>
-    <row r="908" ht="17.25" customHeight="1"/>
-    <row r="909" ht="17.25" customHeight="1"/>
-    <row r="910" ht="17.25" customHeight="1"/>
-    <row r="911" ht="17.25" customHeight="1"/>
-    <row r="912" ht="17.25" customHeight="1"/>
-    <row r="913" ht="17.25" customHeight="1"/>
-    <row r="914" ht="17.25" customHeight="1"/>
-    <row r="915" ht="17.25" customHeight="1"/>
-    <row r="916" ht="17.25" customHeight="1"/>
-    <row r="917" ht="17.25" customHeight="1"/>
-    <row r="918" ht="17.25" customHeight="1"/>
-    <row r="919" ht="17.25" customHeight="1"/>
-    <row r="920" ht="17.25" customHeight="1"/>
-    <row r="921" ht="17.25" customHeight="1"/>
-    <row r="922" ht="17.25" customHeight="1"/>
-    <row r="923" ht="17.25" customHeight="1"/>
-    <row r="924" ht="17.25" customHeight="1"/>
-    <row r="925" ht="17.25" customHeight="1"/>
-    <row r="926" ht="17.25" customHeight="1"/>
-    <row r="927" ht="17.25" customHeight="1"/>
-    <row r="928" ht="17.25" customHeight="1"/>
-    <row r="929" ht="17.25" customHeight="1"/>
-    <row r="930" ht="17.25" customHeight="1"/>
-    <row r="931" ht="17.25" customHeight="1"/>
-    <row r="932" ht="17.25" customHeight="1"/>
-    <row r="933" ht="17.25" customHeight="1"/>
-    <row r="934" ht="17.25" customHeight="1"/>
-    <row r="935" ht="17.25" customHeight="1"/>
-    <row r="936" ht="17.25" customHeight="1"/>
-    <row r="937" ht="17.25" customHeight="1"/>
-    <row r="938" ht="17.25" customHeight="1"/>
-    <row r="939" ht="17.25" customHeight="1"/>
-    <row r="940" ht="17.25" customHeight="1"/>
-    <row r="941" ht="17.25" customHeight="1"/>
-    <row r="942" ht="17.25" customHeight="1"/>
-    <row r="943" ht="17.25" customHeight="1"/>
-    <row r="944" ht="17.25" customHeight="1"/>
-    <row r="945" ht="17.25" customHeight="1"/>
-    <row r="946" ht="17.25" customHeight="1"/>
-    <row r="947" ht="17.25" customHeight="1"/>
-    <row r="948" ht="17.25" customHeight="1"/>
-    <row r="949" ht="17.25" customHeight="1"/>
-    <row r="950" ht="17.25" customHeight="1"/>
-    <row r="951" ht="17.25" customHeight="1"/>
-    <row r="952" ht="17.25" customHeight="1"/>
-    <row r="953" ht="17.25" customHeight="1"/>
-    <row r="954" ht="17.25" customHeight="1"/>
-    <row r="955" ht="17.25" customHeight="1"/>
-    <row r="956" ht="17.25" customHeight="1"/>
-    <row r="957" ht="17.25" customHeight="1"/>
-    <row r="958" ht="17.25" customHeight="1"/>
-    <row r="959" ht="17.25" customHeight="1"/>
-    <row r="960" ht="17.25" customHeight="1"/>
-    <row r="961" ht="17.25" customHeight="1"/>
-    <row r="962" ht="17.25" customHeight="1"/>
-    <row r="963" ht="17.25" customHeight="1"/>
-    <row r="964" ht="17.25" customHeight="1"/>
-    <row r="965" ht="17.25" customHeight="1"/>
-    <row r="966" ht="17.25" customHeight="1"/>
-    <row r="967" ht="17.25" customHeight="1"/>
-    <row r="968" ht="17.25" customHeight="1"/>
-    <row r="969" ht="17.25" customHeight="1"/>
-    <row r="970" ht="17.25" customHeight="1"/>
-    <row r="971" ht="17.25" customHeight="1"/>
-    <row r="972" ht="17.25" customHeight="1"/>
-    <row r="973" ht="17.25" customHeight="1"/>
-    <row r="974" ht="17.25" customHeight="1"/>
-    <row r="975" ht="17.25" customHeight="1"/>
-    <row r="976" ht="17.25" customHeight="1"/>
-    <row r="977" ht="17.25" customHeight="1"/>
-    <row r="978" ht="17.25" customHeight="1"/>
-    <row r="979" ht="17.25" customHeight="1"/>
-    <row r="980" ht="17.25" customHeight="1"/>
-    <row r="981" ht="17.25" customHeight="1"/>
-    <row r="982" ht="17.25" customHeight="1"/>
-    <row r="983" ht="17.25" customHeight="1"/>
-    <row r="984" ht="17.25" customHeight="1"/>
-    <row r="985" ht="17.25" customHeight="1"/>
-    <row r="986" ht="17.25" customHeight="1"/>
-    <row r="987" ht="17.25" customHeight="1"/>
-    <row r="988" ht="17.25" customHeight="1"/>
-    <row r="989" ht="17.25" customHeight="1"/>
-    <row r="990" ht="17.25" customHeight="1"/>
-    <row r="991" ht="17.25" customHeight="1"/>
-    <row r="992" ht="17.25" customHeight="1"/>
-    <row r="993" ht="17.25" customHeight="1"/>
-    <row r="994" ht="17.25" customHeight="1"/>
-    <row r="995" ht="17.25" customHeight="1"/>
-    <row r="996" ht="17.25" customHeight="1"/>
-    <row r="997" ht="17.25" customHeight="1"/>
-    <row r="998" ht="17.25" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>

--- a/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="ON79YGRFmG0PvJZg2zw1gtIfJ/OB/TVqK39qUUOl2CE="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="Zo3y2CT06Z9aRkJvrr1FP2fBKanMGUSvILAo2d4duAE="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="230">
   <si>
     <t>미리 로드할 어드레서블 테이블</t>
   </si>
@@ -360,12 +360,6 @@
     <t>Pool_Tool</t>
   </si>
   <si>
-    <t>PreLoadAsset_GameObject_JewelObject</t>
-  </si>
-  <si>
-    <t>Pool_Jewel</t>
-  </si>
-  <si>
     <t>PreLoadAsset_Mesh_Jewel_Cone[Cone]</t>
   </si>
   <si>
@@ -444,12 +438,6 @@
     <t>Pool_Throw</t>
   </si>
   <si>
-    <t>PreLoadAsset_GameObject_PaintingObject</t>
-  </si>
-  <si>
-    <t>Pool_Painting</t>
-  </si>
-  <si>
     <t>PreLoadAsset_Mesh_Painting_1[Painting_1]</t>
   </si>
   <si>
@@ -640,13 +628,91 @@
   </si>
   <si>
     <t>Demo Room7</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_PolygonNightclubs_01_A</t>
+  </si>
+  <si>
+    <t>PolygonNightclubs_01_A</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_Junk_Bottle_Blue</t>
+  </si>
+  <si>
+    <t>Junk_Bottle_Blue[SM_Prop_Bar_Bottle_07]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_Junk_Bottle_Pink_Large</t>
+  </si>
+  <si>
+    <t>Junk_Bottle_Pink_Large[SM_Prop_Bottle_Large_01]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_Junk_Can_Navy</t>
+  </si>
+  <si>
+    <t>Junk_Can_Navy[SM_Prop_Can_01]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_Junk_Fish</t>
+  </si>
+  <si>
+    <t>Junk_Fish[SM_Prop_Display_Fish_02]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_Junk_Glasses</t>
+  </si>
+  <si>
+    <t>Junk_Glasses[SM_Prop_Glasses_01]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_Junk_Microphone</t>
+  </si>
+  <si>
+    <t>Junk_Microphone[SM_Prop_Microphone_01]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_Junk_Sculpture</t>
+  </si>
+  <si>
+    <t>Junk_Sculpture[SM_Prop_Sculpture_01]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_PolygonNightclub_Mat_01_A_Metallic</t>
+  </si>
+  <si>
+    <t>PolygonNightclub_Mat_01_A_Metallic</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_MeshCollier_Junk_Bottle_Blue</t>
+  </si>
+  <si>
+    <t>MeshCollider_Junk_Bottle_Blue</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_MeshCollider_Junk_Bottle_Pink_Large</t>
+  </si>
+  <si>
+    <t>MeshCollider_Junk_Bottle_Pink_Large</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_MeshCollier_Junk_Glasses</t>
+  </si>
+  <si>
+    <t>MeshCollider_Junk_Glasses</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_GameObject_ItemObject</t>
+  </si>
+  <si>
+    <t>ItemObject</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -680,6 +746,10 @@
     </font>
     <font>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -728,7 +798,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -737,6 +807,9 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="2" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -752,6 +825,15 @@
     </xf>
     <xf borderId="0" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1433,246 +1515,247 @@
       </c>
     </row>
     <row r="57" ht="17.25" customHeight="1">
-      <c r="A57" s="2" t="s">
+      <c r="A57" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B57" s="7" t="s">
         <v>115</v>
       </c>
+      <c r="C57" s="2" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="58" ht="17.25" customHeight="1">
-      <c r="A58" s="6" t="s">
+      <c r="A58" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C58" s="2" t="s">
+    </row>
+    <row r="59" ht="17.25" customHeight="1">
+      <c r="A59" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="60" ht="17.25" customHeight="1">
+      <c r="A60" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="B60" s="9" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="61" ht="17.25" customHeight="1">
+      <c r="A61" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="62" ht="17.25" customHeight="1">
+      <c r="A62" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B62" s="9" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="63" ht="17.25" customHeight="1">
+      <c r="A63" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="64" ht="17.25" customHeight="1">
+      <c r="A64" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B64" s="9" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="65" ht="17.25" customHeight="1">
+      <c r="A65" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="66" ht="17.25" customHeight="1">
+      <c r="A66" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="67" ht="17.25" customHeight="1">
+      <c r="A67" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="B67" s="9" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="68" ht="17.25" customHeight="1">
+      <c r="A68" s="9" t="s">
+        <v>136</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="69" ht="17.25" customHeight="1">
+      <c r="A69" s="9" t="s">
+        <v>138</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="70" ht="17.25" customHeight="1">
+      <c r="A70" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B70" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="C70" s="10" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="59" ht="17.25" customHeight="1">
-      <c r="A59" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="60" ht="17.25" customHeight="1">
-      <c r="A60" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="B60" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="61" ht="17.25" customHeight="1">
-      <c r="A61" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="B61" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="62" ht="17.25" customHeight="1">
-      <c r="A62" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="B62" s="8" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="63" ht="17.25" customHeight="1">
-      <c r="A63" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="B63" s="8" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="64" ht="17.25" customHeight="1">
-      <c r="A64" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="B64" s="8" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="65" ht="17.25" customHeight="1">
-      <c r="A65" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="B65" s="8" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="66" ht="17.25" customHeight="1">
-      <c r="A66" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="B66" s="8" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="67" ht="17.25" customHeight="1">
-      <c r="A67" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="B67" s="8" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="68" ht="17.25" customHeight="1">
-      <c r="A68" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="B68" s="8" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="69" ht="17.25" customHeight="1">
-      <c r="A69" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="B69" s="8" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="70" ht="17.25" customHeight="1">
-      <c r="A70" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="B70" s="8" t="s">
-        <v>141</v>
-      </c>
-    </row>
     <row r="71" ht="17.25" customHeight="1">
-      <c r="A71" s="9" t="s">
+      <c r="A71" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="B71" s="9" t="s">
+      <c r="B71" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="C71" s="10"/>
+      <c r="C71" s="10" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="72" ht="17.25" customHeight="1">
-      <c r="A72" s="9" t="s">
+      <c r="A72" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="B72" s="9" t="s">
+      <c r="B72" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="C72" s="9" t="s">
+      <c r="C72" s="10" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="73" ht="17.25" customHeight="1">
-      <c r="A73" s="9" t="s">
+      <c r="A73" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="B73" s="9" t="s">
+      <c r="B73" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="C73" s="9" t="s">
+      <c r="C73" s="10" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="74" ht="17.25" customHeight="1">
-      <c r="A74" s="9" t="s">
+      <c r="A74" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="B74" s="9" t="s">
+      <c r="B74" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="C74" s="9" t="s">
+      <c r="C74" s="10" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="75" ht="17.25" customHeight="1">
-      <c r="A75" s="9" t="s">
+      <c r="A75" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="B75" s="9" t="s">
+      <c r="B75" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="C75" s="9" t="s">
-        <v>97</v>
-      </c>
+      <c r="C75" s="11"/>
     </row>
     <row r="76" ht="17.25" customHeight="1">
-      <c r="A76" s="9" t="s">
+      <c r="A76" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="B76" s="9" t="s">
+      <c r="B76" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="C76" s="9" t="s">
-        <v>97</v>
-      </c>
+      <c r="C76" s="11"/>
     </row>
     <row r="77" ht="17.25" customHeight="1">
-      <c r="A77" s="9" t="s">
+      <c r="A77" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="B77" s="9" t="s">
+      <c r="B77" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="C77" s="10"/>
+      <c r="C77" s="11"/>
     </row>
     <row r="78" ht="17.25" customHeight="1">
-      <c r="A78" s="9" t="s">
+      <c r="A78" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="B78" s="9" t="s">
+      <c r="B78" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="C78" s="10"/>
+      <c r="C78" s="11"/>
     </row>
     <row r="79" ht="17.25" customHeight="1">
-      <c r="A79" s="9" t="s">
+      <c r="A79" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="B79" s="9" t="s">
+      <c r="B79" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="C79" s="10"/>
+      <c r="C79" s="11"/>
     </row>
     <row r="80" ht="17.25" customHeight="1">
-      <c r="A80" s="9" t="s">
+      <c r="A80" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="B80" s="9" t="s">
+      <c r="B80" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="C80" s="10"/>
+      <c r="C80" s="11"/>
     </row>
     <row r="81" ht="17.25" customHeight="1">
-      <c r="A81" s="9" t="s">
+      <c r="A81" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="B81" s="9" t="s">
+      <c r="B81" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="C81" s="10"/>
+      <c r="C81" s="11"/>
     </row>
     <row r="82" ht="17.25" customHeight="1">
-      <c r="A82" s="9" t="s">
+      <c r="A82" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="B82" s="9" t="s">
+      <c r="B82" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="C82" s="10"/>
+      <c r="C82" s="11"/>
     </row>
     <row r="83" ht="17.25" customHeight="1">
-      <c r="A83" s="9" t="s">
+      <c r="A83" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="B83" s="9" t="s">
+      <c r="B83" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="C83" s="10"/>
+      <c r="C83" s="11"/>
     </row>
     <row r="84" ht="17.25" customHeight="1">
       <c r="A84" s="9" t="s">
@@ -1681,7 +1764,6 @@
       <c r="B84" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="C84" s="10"/>
     </row>
     <row r="85" ht="17.25" customHeight="1">
       <c r="A85" s="9" t="s">
@@ -1690,171 +1772,277 @@
       <c r="B85" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="C85" s="10"/>
     </row>
     <row r="86" ht="17.25" customHeight="1">
-      <c r="A86" s="8" t="s">
+      <c r="A86" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="B86" s="8" t="s">
+      <c r="B86" s="9" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="87" ht="17.25" customHeight="1">
-      <c r="A87" s="8" t="s">
+      <c r="A87" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="B87" s="8" t="s">
+      <c r="B87" s="9" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="88" ht="17.25" customHeight="1">
-      <c r="A88" s="8" t="s">
+      <c r="A88" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="B88" s="8" t="s">
+      <c r="B88" s="9" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="89" ht="17.25" customHeight="1">
-      <c r="A89" s="8" t="s">
+      <c r="A89" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="B89" s="8" t="s">
+      <c r="B89" s="10" t="s">
         <v>179</v>
       </c>
+      <c r="C89" s="11"/>
     </row>
     <row r="90" ht="17.25" customHeight="1">
-      <c r="A90" s="8" t="s">
+      <c r="A90" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="B90" s="8" t="s">
+      <c r="B90" s="12" t="s">
         <v>181</v>
       </c>
+      <c r="C90" s="10" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="91" ht="17.25" customHeight="1">
-      <c r="A91" s="9" t="s">
+      <c r="A91" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="B91" s="9" t="s">
+      <c r="B91" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="C91" s="10"/>
+      <c r="C91" s="11"/>
     </row>
     <row r="92" ht="17.25" customHeight="1">
-      <c r="A92" s="9" t="s">
+      <c r="A92" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="B92" s="11" t="s">
+      <c r="B92" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="C92" s="9" t="s">
-        <v>97</v>
-      </c>
+      <c r="C92" s="11"/>
     </row>
     <row r="93" ht="17.25" customHeight="1">
-      <c r="A93" s="9" t="s">
+      <c r="A93" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="B93" s="11" t="s">
+      <c r="B93" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="C93" s="10"/>
+      <c r="C93" s="11"/>
     </row>
     <row r="94" ht="17.25" customHeight="1">
-      <c r="A94" s="9" t="s">
+      <c r="A94" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="B94" s="11" t="s">
+      <c r="B94" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="C94" s="10"/>
+      <c r="C94" s="11"/>
     </row>
     <row r="95" ht="17.25" customHeight="1">
       <c r="A95" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="B95" s="11" t="s">
+      <c r="B95" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="C95" s="10"/>
     </row>
     <row r="96" ht="17.25" customHeight="1">
       <c r="A96" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="B96" s="11" t="s">
+      <c r="B96" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="C96" s="10"/>
     </row>
     <row r="97" ht="17.25" customHeight="1">
-      <c r="A97" s="8" t="s">
+      <c r="A97" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="B97" s="8" t="s">
+      <c r="B97" s="9" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="98" ht="17.25" customHeight="1">
-      <c r="A98" s="8" t="s">
+      <c r="A98" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="B98" s="8" t="s">
+      <c r="B98" s="9" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="99" ht="17.25" customHeight="1">
-      <c r="A99" s="8" t="s">
+      <c r="A99" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="B99" s="8" t="s">
+      <c r="B99" s="9" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="100" ht="17.25" customHeight="1">
-      <c r="A100" s="8" t="s">
+      <c r="A100" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="B100" s="8" t="s">
+      <c r="B100" s="9" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="101" ht="17.25" customHeight="1">
-      <c r="A101" s="8" t="s">
+      <c r="A101" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="B101" s="8" t="s">
+      <c r="B101" s="9" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="102" ht="17.25" customHeight="1">
-      <c r="A102" s="8" t="s">
+      <c r="A102" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="B102" s="8" t="s">
+      <c r="B102" s="13" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="103" ht="17.25" customHeight="1">
-      <c r="A103" s="8" t="s">
+      <c r="A103" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="B103" s="8" t="s">
+      <c r="B103" s="15" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="104" ht="17.25" customHeight="1"/>
-    <row r="105" ht="17.25" customHeight="1"/>
-    <row r="106" ht="17.25" customHeight="1"/>
-    <row r="107" ht="17.25" customHeight="1"/>
-    <row r="108" ht="17.25" customHeight="1"/>
-    <row r="109" ht="17.25" customHeight="1"/>
-    <row r="110" ht="17.25" customHeight="1"/>
-    <row r="111" ht="17.25" customHeight="1"/>
-    <row r="112" ht="17.25" customHeight="1"/>
-    <row r="113" ht="17.25" customHeight="1"/>
-    <row r="114" ht="17.25" customHeight="1"/>
+      <c r="C103" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="104" ht="17.25" customHeight="1">
+      <c r="A104" s="14" t="s">
+        <v>208</v>
+      </c>
+      <c r="B104" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="C104" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="105" ht="17.25" customHeight="1">
+      <c r="A105" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="B105" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="C105" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="106" ht="17.25" customHeight="1">
+      <c r="A106" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="B106" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="C106" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="107" ht="17.25" customHeight="1">
+      <c r="A107" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="B107" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="C107" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="108" ht="17.25" customHeight="1">
+      <c r="A108" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="B108" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="C108" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="109" ht="17.25" customHeight="1">
+      <c r="A109" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="B109" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="C109" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="110" ht="17.25" customHeight="1">
+      <c r="A110" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="B110" s="13" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="111" ht="17.25" customHeight="1">
+      <c r="A111" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="B111" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="C111" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="112" ht="17.25" customHeight="1">
+      <c r="A112" s="14" t="s">
+        <v>224</v>
+      </c>
+      <c r="B112" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="C112" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="113" ht="17.25" customHeight="1">
+      <c r="A113" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="B113" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="C113" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="114" ht="17.25" customHeight="1">
+      <c r="A114" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="B114" s="9" t="s">
+        <v>229</v>
+      </c>
+    </row>
     <row r="115" ht="17.25" customHeight="1"/>
     <row r="116" ht="17.25" customHeight="1"/>
     <row r="117" ht="17.25" customHeight="1"/>
@@ -2736,9 +2924,6 @@
     <row r="993" ht="17.25" customHeight="1"/>
     <row r="994" ht="17.25" customHeight="1"/>
     <row r="995" ht="17.25" customHeight="1"/>
-    <row r="996" ht="17.25" customHeight="1"/>
-    <row r="997" ht="17.25" customHeight="1"/>
-    <row r="998" ht="17.25" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>

--- a/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="ON79YGRFmG0PvJZg2zw1gtIfJ/OB/TVqK39qUUOl2CE="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="Zo3y2CT06Z9aRkJvrr1FP2fBKanMGUSvILAo2d4duAE="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="230">
   <si>
     <t>미리 로드할 어드레서블 테이블</t>
   </si>
@@ -357,13 +357,7 @@
     <t>PreLoadAsset_GameObject_ToolObject</t>
   </si>
   <si>
-    <t>ToolObject</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_GameObject_JewelObject</t>
-  </si>
-  <si>
-    <t>JewelObject</t>
+    <t>Pool_Tool</t>
   </si>
   <si>
     <t>PreLoadAsset_Mesh_Jewel_Cone[Cone]</t>
@@ -444,12 +438,6 @@
     <t>Pool_Throw</t>
   </si>
   <si>
-    <t>PreLoadAsset_GameObject_PaintingObject</t>
-  </si>
-  <si>
-    <t>Pool_Painting</t>
-  </si>
-  <si>
     <t>PreLoadAsset_Mesh_Painting_1[Painting_1]</t>
   </si>
   <si>
@@ -642,12 +630,6 @@
     <t>Demo Room7</t>
   </si>
   <si>
-    <t>PreLoadAsset_GameObject_JunkObject</t>
-  </si>
-  <si>
-    <t>JunkObject</t>
-  </si>
-  <si>
     <t>PreLoadAsset_Material_PolygonNightclubs_01_A</t>
   </si>
   <si>
@@ -663,7 +645,7 @@
     <t>PreLoadAsset_Mesh_Junk_Bottle_Pink_Large</t>
   </si>
   <si>
-    <t>Junk_Bottle_Pink_Large[SM_Prop_Bar_Bottle_Lage_01]</t>
+    <t>Junk_Bottle_Pink_Large[SM_Prop_Bottle_Large_01]</t>
   </si>
   <si>
     <t>PreLoadAsset_Mesh_Junk_Can_Navy</t>
@@ -718,6 +700,12 @@
   </si>
   <si>
     <t>MeshCollider_Junk_Glasses</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_GameObject_ItemObject</t>
+  </si>
+  <si>
+    <t>ItemObject</t>
   </si>
 </sst>
 </file>
@@ -1527,29 +1515,29 @@
       </c>
     </row>
     <row r="57" ht="17.25" customHeight="1">
-      <c r="A57" s="2" t="s">
+      <c r="A57" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B57" s="7" t="s">
         <v>115</v>
       </c>
+      <c r="C57" s="2" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="58" ht="17.25" customHeight="1">
-      <c r="A58" s="7" t="s">
+      <c r="A58" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B58" s="7" t="s">
+      <c r="B58" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C58" s="2" t="s">
-        <v>97</v>
-      </c>
     </row>
     <row r="59" ht="17.25" customHeight="1">
-      <c r="A59" s="2" t="s">
+      <c r="A59" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" s="9" t="s">
         <v>119</v>
       </c>
     </row>
@@ -1618,7 +1606,7 @@
       </c>
     </row>
     <row r="68" ht="17.25" customHeight="1">
-      <c r="A68" s="8" t="s">
+      <c r="A68" s="9" t="s">
         <v>136</v>
       </c>
       <c r="B68" s="9" t="s">
@@ -1634,11 +1622,14 @@
       </c>
     </row>
     <row r="70" ht="17.25" customHeight="1">
-      <c r="A70" s="9" t="s">
+      <c r="A70" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="B70" s="9" t="s">
+      <c r="B70" s="10" t="s">
         <v>141</v>
+      </c>
+      <c r="C70" s="10" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="71" ht="17.25" customHeight="1">
@@ -1648,7 +1639,9 @@
       <c r="B71" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="C71" s="11"/>
+      <c r="C71" s="10" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="72" ht="17.25" customHeight="1">
       <c r="A72" s="10" t="s">
@@ -1690,9 +1683,7 @@
       <c r="B75" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="C75" s="10" t="s">
-        <v>97</v>
-      </c>
+      <c r="C75" s="11"/>
     </row>
     <row r="76" ht="17.25" customHeight="1">
       <c r="A76" s="10" t="s">
@@ -1701,9 +1692,7 @@
       <c r="B76" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="C76" s="10" t="s">
-        <v>97</v>
-      </c>
+      <c r="C76" s="11"/>
     </row>
     <row r="77" ht="17.25" customHeight="1">
       <c r="A77" s="10" t="s">
@@ -1769,22 +1758,20 @@
       <c r="C83" s="11"/>
     </row>
     <row r="84" ht="17.25" customHeight="1">
-      <c r="A84" s="10" t="s">
+      <c r="A84" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="B84" s="10" t="s">
+      <c r="B84" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="C84" s="11"/>
     </row>
     <row r="85" ht="17.25" customHeight="1">
-      <c r="A85" s="10" t="s">
+      <c r="A85" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="B85" s="10" t="s">
+      <c r="B85" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="C85" s="11"/>
     </row>
     <row r="86" ht="17.25" customHeight="1">
       <c r="A86" s="9" t="s">
@@ -1811,26 +1798,30 @@
       </c>
     </row>
     <row r="89" ht="17.25" customHeight="1">
-      <c r="A89" s="9" t="s">
+      <c r="A89" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="B89" s="9" t="s">
+      <c r="B89" s="10" t="s">
         <v>179</v>
       </c>
+      <c r="C89" s="11"/>
     </row>
     <row r="90" ht="17.25" customHeight="1">
-      <c r="A90" s="9" t="s">
+      <c r="A90" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="B90" s="9" t="s">
+      <c r="B90" s="12" t="s">
         <v>181</v>
+      </c>
+      <c r="C90" s="10" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="91" ht="17.25" customHeight="1">
       <c r="A91" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="B91" s="10" t="s">
+      <c r="B91" s="12" t="s">
         <v>183</v>
       </c>
       <c r="C91" s="11"/>
@@ -1842,9 +1833,7 @@
       <c r="B92" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="C92" s="10" t="s">
-        <v>97</v>
-      </c>
+      <c r="C92" s="11"/>
     </row>
     <row r="93" ht="17.25" customHeight="1">
       <c r="A93" s="10" t="s">
@@ -1865,22 +1854,20 @@
       <c r="C94" s="11"/>
     </row>
     <row r="95" ht="17.25" customHeight="1">
-      <c r="A95" s="10" t="s">
+      <c r="A95" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="B95" s="12" t="s">
+      <c r="B95" s="9" t="s">
         <v>191</v>
       </c>
-      <c r="C95" s="11"/>
     </row>
     <row r="96" ht="17.25" customHeight="1">
-      <c r="A96" s="10" t="s">
+      <c r="A96" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="B96" s="12" t="s">
+      <c r="B96" s="9" t="s">
         <v>193</v>
       </c>
-      <c r="C96" s="11"/>
     </row>
     <row r="97" ht="17.25" customHeight="1">
       <c r="A97" s="9" t="s">
@@ -1926,32 +1913,41 @@
       <c r="A102" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="B102" s="9" t="s">
+      <c r="B102" s="13" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="103" ht="17.25" customHeight="1">
-      <c r="A103" s="9" t="s">
+      <c r="A103" s="14" t="s">
         <v>206</v>
       </c>
-      <c r="B103" s="9" t="s">
+      <c r="B103" s="15" t="s">
         <v>207</v>
       </c>
+      <c r="C103" s="10" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="104" ht="17.25" customHeight="1">
-      <c r="A104" s="8" t="s">
+      <c r="A104" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="B104" s="9" t="s">
+      <c r="B104" s="14" t="s">
         <v>209</v>
       </c>
+      <c r="C104" s="10" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="105" ht="17.25" customHeight="1">
-      <c r="A105" s="9" t="s">
+      <c r="A105" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="B105" s="13" t="s">
+      <c r="B105" s="15" t="s">
         <v>211</v>
+      </c>
+      <c r="C105" s="10" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="106" ht="17.25" customHeight="1">
@@ -1999,14 +1995,11 @@
       </c>
     </row>
     <row r="110" ht="17.25" customHeight="1">
-      <c r="A110" s="14" t="s">
+      <c r="A110" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="B110" s="15" t="s">
+      <c r="B110" s="13" t="s">
         <v>221</v>
-      </c>
-      <c r="C110" s="10" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="111" ht="17.25" customHeight="1">
@@ -2032,46 +2025,26 @@
       </c>
     </row>
     <row r="113" ht="17.25" customHeight="1">
-      <c r="A113" s="9" t="s">
+      <c r="A113" s="14" t="s">
         <v>226</v>
       </c>
       <c r="B113" s="13" t="s">
         <v>227</v>
       </c>
+      <c r="C113" s="10" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="114" ht="17.25" customHeight="1">
-      <c r="A114" s="14" t="s">
+      <c r="A114" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="B114" s="15" t="s">
+      <c r="B114" s="9" t="s">
         <v>229</v>
       </c>
-      <c r="C114" s="10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="115" ht="17.25" customHeight="1">
-      <c r="A115" s="14" t="s">
-        <v>230</v>
-      </c>
-      <c r="B115" s="15" t="s">
-        <v>231</v>
-      </c>
-      <c r="C115" s="10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="116" ht="17.25" customHeight="1">
-      <c r="A116" s="14" t="s">
-        <v>232</v>
-      </c>
-      <c r="B116" s="13" t="s">
-        <v>233</v>
-      </c>
-      <c r="C116" s="10" t="s">
-        <v>97</v>
-      </c>
-    </row>
+    </row>
+    <row r="115" ht="17.25" customHeight="1"/>
+    <row r="116" ht="17.25" customHeight="1"/>
     <row r="117" ht="17.25" customHeight="1"/>
     <row r="118" ht="17.25" customHeight="1"/>
     <row r="119" ht="17.25" customHeight="1"/>
@@ -2951,9 +2924,6 @@
     <row r="993" ht="17.25" customHeight="1"/>
     <row r="994" ht="17.25" customHeight="1"/>
     <row r="995" ht="17.25" customHeight="1"/>
-    <row r="996" ht="17.25" customHeight="1"/>
-    <row r="997" ht="17.25" customHeight="1"/>
-    <row r="998" ht="17.25" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>

--- a/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="ON79YGRFmG0PvJZg2zw1gtIfJ/OB/TVqK39qUUOl2CE="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="PjQ/ZH5dNfpZSLhuzuhQKuy/nAO/JzfJl7JGthYVMbo="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="234">
   <si>
     <t>미리 로드할 어드레서블 테이블</t>
   </si>
@@ -360,12 +360,6 @@
     <t>Pool_Tool</t>
   </si>
   <si>
-    <t>PreLoadAsset_GameObject_JewelObject</t>
-  </si>
-  <si>
-    <t>Pool_Jewel</t>
-  </si>
-  <si>
     <t>PreLoadAsset_Mesh_Jewel_Cone[Cone]</t>
   </si>
   <si>
@@ -408,6 +402,18 @@
     <t>Mesh_IronBox_Prefab</t>
   </si>
   <si>
+    <t>PreLoadAsset_GameObject_MeshBrokenIronBoxPrefab</t>
+  </si>
+  <si>
+    <t>Mesh_BrokenIronBox_Prefab</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_GameObject_MeshSafePrefab</t>
+  </si>
+  <si>
+    <t>Mesh_Safe_Prefab</t>
+  </si>
+  <si>
     <t>PreLoadAsset_GameObject_MeshWoodBoxPrefab</t>
   </si>
   <si>
@@ -444,12 +450,6 @@
     <t>Pool_Throw</t>
   </si>
   <si>
-    <t>PreLoadAsset_GameObject_PaintingObject</t>
-  </si>
-  <si>
-    <t>Pool_Painting</t>
-  </si>
-  <si>
     <t>PreLoadAsset_Mesh_Painting_1[Painting_1]</t>
   </si>
   <si>
@@ -640,13 +640,91 @@
   </si>
   <si>
     <t>Demo Room7</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_PolygonNightclubs_01_A</t>
+  </si>
+  <si>
+    <t>PolygonNightclubs_01_A</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_Junk_Bottle_Blue</t>
+  </si>
+  <si>
+    <t>Junk_Bottle_Blue[SM_Prop_Bar_Bottle_07]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_Junk_Bottle_Pink_Large</t>
+  </si>
+  <si>
+    <t>Junk_Bottle_Pink_Large[SM_Prop_Bottle_Large_01]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_Junk_Can_Navy</t>
+  </si>
+  <si>
+    <t>Junk_Can_Navy[SM_Prop_Can_01]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_Junk_Fish</t>
+  </si>
+  <si>
+    <t>Junk_Fish[SM_Prop_Display_Fish_02]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_Junk_Glasses</t>
+  </si>
+  <si>
+    <t>Junk_Glasses[SM_Prop_Glasses_01]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_Junk_Microphone</t>
+  </si>
+  <si>
+    <t>Junk_Microphone[SM_Prop_Microphone_01]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_Junk_Sculpture</t>
+  </si>
+  <si>
+    <t>Junk_Sculpture[SM_Prop_Sculpture_01]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_PolygonNightclub_Mat_01_A_Metallic</t>
+  </si>
+  <si>
+    <t>PolygonNightclub_Mat_01_A_Metallic</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_MeshCollier_Junk_Bottle_Blue</t>
+  </si>
+  <si>
+    <t>MeshCollider_Junk_Bottle_Blue</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_MeshCollider_Junk_Bottle_Pink_Large</t>
+  </si>
+  <si>
+    <t>MeshCollider_Junk_Bottle_Pink_Large</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_MeshCollier_Junk_Glasses</t>
+  </si>
+  <si>
+    <t>MeshCollider_Junk_Glasses</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_GameObject_ItemObject</t>
+  </si>
+  <si>
+    <t>ItemObject</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -680,6 +758,10 @@
     </font>
     <font>
       <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
   </fonts>
@@ -728,7 +810,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="16">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -737,6 +819,9 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="2" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -752,6 +837,15 @@
     </xf>
     <xf borderId="0" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1433,101 +1527,101 @@
       </c>
     </row>
     <row r="57" ht="17.25" customHeight="1">
-      <c r="A57" s="2" t="s">
+      <c r="A57" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B57" s="7" t="s">
         <v>115</v>
       </c>
+      <c r="C57" s="2" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="58" ht="17.25" customHeight="1">
-      <c r="A58" s="6" t="s">
+      <c r="A58" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C58" s="2" t="s">
-        <v>97</v>
-      </c>
     </row>
     <row r="59" ht="17.25" customHeight="1">
-      <c r="A59" s="2" t="s">
+      <c r="A59" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" s="9" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="60" ht="17.25" customHeight="1">
-      <c r="A60" s="7" t="s">
+      <c r="A60" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="B60" s="9" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="61" ht="17.25" customHeight="1">
-      <c r="A61" s="7" t="s">
+      <c r="A61" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="B61" s="8" t="s">
+      <c r="B61" s="9" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="62" ht="17.25" customHeight="1">
-      <c r="A62" s="7" t="s">
+      <c r="A62" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="B62" s="8" t="s">
+      <c r="B62" s="9" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="63" ht="17.25" customHeight="1">
-      <c r="A63" s="7" t="s">
+      <c r="A63" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="B63" s="8" t="s">
+      <c r="B63" s="9" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="64" ht="17.25" customHeight="1">
-      <c r="A64" s="7" t="s">
+      <c r="A64" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="B64" s="8" t="s">
+      <c r="B64" s="9" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="65" ht="17.25" customHeight="1">
-      <c r="A65" s="7" t="s">
+      <c r="A65" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B65" s="8" t="s">
+      <c r="B65" s="9" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="66" ht="17.25" customHeight="1">
-      <c r="A66" s="7" t="s">
+      <c r="A66" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="B66" s="8" t="s">
+      <c r="B66" s="9" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="67" ht="17.25" customHeight="1">
-      <c r="A67" s="7" t="s">
+      <c r="A67" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="B67" s="8" t="s">
+      <c r="B67" s="9" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="68" ht="17.25" customHeight="1">
-      <c r="A68" s="7" t="s">
+      <c r="A68" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="B68" s="8" t="s">
+      <c r="B68" s="9" t="s">
         <v>137</v>
       </c>
     </row>
@@ -1535,15 +1629,15 @@
       <c r="A69" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="B69" s="8" t="s">
+      <c r="B69" s="9" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="70" ht="17.25" customHeight="1">
-      <c r="A70" s="8" t="s">
+      <c r="A70" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="B70" s="8" t="s">
+      <c r="B70" s="9" t="s">
         <v>141</v>
       </c>
     </row>
@@ -1554,309 +1648,429 @@
       <c r="B71" s="9" t="s">
         <v>143</v>
       </c>
-      <c r="C71" s="10"/>
     </row>
     <row r="72" ht="17.25" customHeight="1">
-      <c r="A72" s="9" t="s">
+      <c r="A72" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="B72" s="9" t="s">
+      <c r="B72" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="C72" s="9" t="s">
+      <c r="C72" s="10" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="73" ht="17.25" customHeight="1">
-      <c r="A73" s="9" t="s">
+      <c r="A73" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="B73" s="9" t="s">
+      <c r="B73" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="C73" s="9" t="s">
+      <c r="C73" s="10" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="74" ht="17.25" customHeight="1">
-      <c r="A74" s="9" t="s">
+      <c r="A74" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="B74" s="9" t="s">
+      <c r="B74" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="C74" s="9" t="s">
+      <c r="C74" s="10" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="75" ht="17.25" customHeight="1">
-      <c r="A75" s="9" t="s">
+      <c r="A75" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="B75" s="9" t="s">
+      <c r="B75" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="C75" s="9" t="s">
+      <c r="C75" s="10" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="76" ht="17.25" customHeight="1">
-      <c r="A76" s="9" t="s">
+      <c r="A76" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="B76" s="9" t="s">
+      <c r="B76" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="C76" s="9" t="s">
+      <c r="C76" s="10" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="77" ht="17.25" customHeight="1">
-      <c r="A77" s="9" t="s">
+      <c r="A77" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="B77" s="9" t="s">
+      <c r="B77" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="C77" s="10"/>
+      <c r="C77" s="11"/>
     </row>
     <row r="78" ht="17.25" customHeight="1">
-      <c r="A78" s="9" t="s">
+      <c r="A78" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="B78" s="9" t="s">
+      <c r="B78" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="C78" s="10"/>
+      <c r="C78" s="11"/>
     </row>
     <row r="79" ht="17.25" customHeight="1">
-      <c r="A79" s="9" t="s">
+      <c r="A79" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="B79" s="9" t="s">
+      <c r="B79" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="C79" s="10"/>
+      <c r="C79" s="11"/>
     </row>
     <row r="80" ht="17.25" customHeight="1">
-      <c r="A80" s="9" t="s">
+      <c r="A80" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="B80" s="9" t="s">
+      <c r="B80" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="C80" s="10"/>
+      <c r="C80" s="11"/>
     </row>
     <row r="81" ht="17.25" customHeight="1">
-      <c r="A81" s="9" t="s">
+      <c r="A81" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="B81" s="9" t="s">
+      <c r="B81" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="C81" s="10"/>
+      <c r="C81" s="11"/>
     </row>
     <row r="82" ht="17.25" customHeight="1">
-      <c r="A82" s="9" t="s">
+      <c r="A82" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="B82" s="9" t="s">
+      <c r="B82" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="C82" s="10"/>
+      <c r="C82" s="11"/>
     </row>
     <row r="83" ht="17.25" customHeight="1">
-      <c r="A83" s="9" t="s">
+      <c r="A83" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="B83" s="9" t="s">
+      <c r="B83" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="C83" s="10"/>
+      <c r="C83" s="11"/>
     </row>
     <row r="84" ht="17.25" customHeight="1">
-      <c r="A84" s="9" t="s">
+      <c r="A84" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="B84" s="9" t="s">
+      <c r="B84" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="C84" s="10"/>
+      <c r="C84" s="11"/>
     </row>
     <row r="85" ht="17.25" customHeight="1">
-      <c r="A85" s="9" t="s">
+      <c r="A85" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="B85" s="9" t="s">
+      <c r="B85" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="C85" s="10"/>
+      <c r="C85" s="11"/>
     </row>
     <row r="86" ht="17.25" customHeight="1">
-      <c r="A86" s="8" t="s">
+      <c r="A86" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="B86" s="8" t="s">
+      <c r="B86" s="9" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="87" ht="17.25" customHeight="1">
-      <c r="A87" s="8" t="s">
+      <c r="A87" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="B87" s="8" t="s">
+      <c r="B87" s="9" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="88" ht="17.25" customHeight="1">
-      <c r="A88" s="8" t="s">
+      <c r="A88" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="B88" s="8" t="s">
+      <c r="B88" s="9" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="89" ht="17.25" customHeight="1">
-      <c r="A89" s="8" t="s">
+      <c r="A89" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="B89" s="8" t="s">
+      <c r="B89" s="9" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="90" ht="17.25" customHeight="1">
-      <c r="A90" s="8" t="s">
+      <c r="A90" s="9" t="s">
         <v>180</v>
       </c>
-      <c r="B90" s="8" t="s">
+      <c r="B90" s="9" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="91" ht="17.25" customHeight="1">
-      <c r="A91" s="9" t="s">
+      <c r="A91" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="B91" s="9" t="s">
+      <c r="B91" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="C91" s="10"/>
+      <c r="C91" s="11"/>
     </row>
     <row r="92" ht="17.25" customHeight="1">
-      <c r="A92" s="9" t="s">
+      <c r="A92" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="B92" s="11" t="s">
+      <c r="B92" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="C92" s="9" t="s">
+      <c r="C92" s="10" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="93" ht="17.25" customHeight="1">
-      <c r="A93" s="9" t="s">
+      <c r="A93" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="B93" s="11" t="s">
+      <c r="B93" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="C93" s="10"/>
+      <c r="C93" s="11"/>
     </row>
     <row r="94" ht="17.25" customHeight="1">
-      <c r="A94" s="9" t="s">
+      <c r="A94" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="B94" s="11" t="s">
+      <c r="B94" s="12" t="s">
         <v>189</v>
       </c>
-      <c r="C94" s="10"/>
+      <c r="C94" s="11"/>
     </row>
     <row r="95" ht="17.25" customHeight="1">
-      <c r="A95" s="9" t="s">
+      <c r="A95" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="B95" s="11" t="s">
+      <c r="B95" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="C95" s="10"/>
+      <c r="C95" s="11"/>
     </row>
     <row r="96" ht="17.25" customHeight="1">
-      <c r="A96" s="9" t="s">
+      <c r="A96" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="B96" s="11" t="s">
+      <c r="B96" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="C96" s="10"/>
+      <c r="C96" s="11"/>
     </row>
     <row r="97" ht="17.25" customHeight="1">
-      <c r="A97" s="8" t="s">
+      <c r="A97" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="B97" s="8" t="s">
+      <c r="B97" s="9" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="98" ht="17.25" customHeight="1">
-      <c r="A98" s="8" t="s">
+      <c r="A98" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="B98" s="8" t="s">
+      <c r="B98" s="9" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="99" ht="17.25" customHeight="1">
-      <c r="A99" s="8" t="s">
+      <c r="A99" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="B99" s="8" t="s">
+      <c r="B99" s="9" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="100" ht="17.25" customHeight="1">
-      <c r="A100" s="8" t="s">
+      <c r="A100" s="9" t="s">
         <v>200</v>
       </c>
-      <c r="B100" s="8" t="s">
+      <c r="B100" s="9" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="101" ht="17.25" customHeight="1">
-      <c r="A101" s="8" t="s">
+      <c r="A101" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="B101" s="8" t="s">
+      <c r="B101" s="9" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="102" ht="17.25" customHeight="1">
-      <c r="A102" s="8" t="s">
+      <c r="A102" s="9" t="s">
         <v>204</v>
       </c>
-      <c r="B102" s="8" t="s">
+      <c r="B102" s="9" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="103" ht="17.25" customHeight="1">
-      <c r="A103" s="8" t="s">
+      <c r="A103" s="9" t="s">
         <v>206</v>
       </c>
-      <c r="B103" s="8" t="s">
+      <c r="B103" s="9" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="104" ht="17.25" customHeight="1"/>
-    <row r="105" ht="17.25" customHeight="1"/>
-    <row r="106" ht="17.25" customHeight="1"/>
-    <row r="107" ht="17.25" customHeight="1"/>
-    <row r="108" ht="17.25" customHeight="1"/>
-    <row r="109" ht="17.25" customHeight="1"/>
-    <row r="110" ht="17.25" customHeight="1"/>
-    <row r="111" ht="17.25" customHeight="1"/>
-    <row r="112" ht="17.25" customHeight="1"/>
-    <row r="113" ht="17.25" customHeight="1"/>
-    <row r="114" ht="17.25" customHeight="1"/>
-    <row r="115" ht="17.25" customHeight="1"/>
-    <row r="116" ht="17.25" customHeight="1"/>
+    <row r="104" ht="17.25" customHeight="1">
+      <c r="A104" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="B104" s="13" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="105" ht="17.25" customHeight="1">
+      <c r="A105" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="B105" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="C105" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="106" ht="17.25" customHeight="1">
+      <c r="A106" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="B106" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="C106" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="107" ht="17.25" customHeight="1">
+      <c r="A107" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="B107" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="C107" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="108" ht="17.25" customHeight="1">
+      <c r="A108" s="14" t="s">
+        <v>216</v>
+      </c>
+      <c r="B108" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="C108" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="109" ht="17.25" customHeight="1">
+      <c r="A109" s="14" t="s">
+        <v>218</v>
+      </c>
+      <c r="B109" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="C109" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="110" ht="17.25" customHeight="1">
+      <c r="A110" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="B110" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="C110" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="111" ht="17.25" customHeight="1">
+      <c r="A111" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="B111" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="C111" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="112" ht="17.25" customHeight="1">
+      <c r="A112" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="B112" s="13" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="113" ht="17.25" customHeight="1">
+      <c r="A113" s="14" t="s">
+        <v>226</v>
+      </c>
+      <c r="B113" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="C113" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="114" ht="17.25" customHeight="1">
+      <c r="A114" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="B114" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="C114" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="115" ht="17.25" customHeight="1">
+      <c r="A115" s="14" t="s">
+        <v>230</v>
+      </c>
+      <c r="B115" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="C115" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="116" ht="17.25" customHeight="1">
+      <c r="A116" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="B116" s="9" t="s">
+        <v>233</v>
+      </c>
+    </row>
     <row r="117" ht="17.25" customHeight="1"/>
     <row r="118" ht="17.25" customHeight="1"/>
     <row r="119" ht="17.25" customHeight="1"/>
@@ -2738,7 +2952,6 @@
     <row r="995" ht="17.25" customHeight="1"/>
     <row r="996" ht="17.25" customHeight="1"/>
     <row r="997" ht="17.25" customHeight="1"/>
-    <row r="998" ht="17.25" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>

--- a/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
@@ -1,22 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="Zo3y2CT06Z9aRkJvrr1FP2fBKanMGUSvILAo2d4duAE="/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="236">
   <si>
     <t>미리 로드할 어드레서블 테이블</t>
   </si>
@@ -283,6 +294,24 @@
   </si>
   <si>
     <t>Win_03</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_024</t>
+  </si>
+  <si>
+    <t>Z_Electricity_01</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_025</t>
+  </si>
+  <si>
+    <t>Z_FootStep_01</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_026</t>
+  </si>
+  <si>
+    <t>Z_FootStep_02</t>
   </si>
   <si>
     <t>PreLoadAsset_FBX_KeyFBX</t>
@@ -711,54 +740,208 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="26">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Malgun Gothic"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Malgun Gothic"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
-      <color theme="1"/>
-      <name val="Malgun Gothic"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.0"/>
-      <color theme="1"/>
-      <name val="Malgun Gothic"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.0"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
-      <color rgb="FF000000"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -766,9 +949,201 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
-    <border/>
+  <borders count="11">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -782,6 +1157,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -793,62 +1169,549 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="2" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
+  <cellXfs count="14">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1038,23 +1901,23 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C998"/>
+  <sheetFormatPr defaultColWidth="14.4259259259259" defaultRowHeight="15" customHeight="1" outlineLevelCol="2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="52.14"/>
-    <col customWidth="1" min="2" max="2" width="35.14"/>
-    <col customWidth="1" min="3" max="3" width="31.43"/>
-    <col customWidth="1" min="4" max="26" width="9.0"/>
+    <col min="1" max="1" width="52.1388888888889" customWidth="1"/>
+    <col min="2" max="2" width="35.1388888888889" customWidth="1"/>
+    <col min="3" max="3" width="31.4259259259259" customWidth="1"/>
+    <col min="4" max="26" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1">
+    <row r="1" ht="17.25" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1065,7 +1928,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="17.25" customHeight="1">
+    <row r="2" ht="17.25" customHeight="1" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1076,7 +1939,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" ht="17.25" customHeight="1">
+    <row r="3" ht="17.25" customHeight="1" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1087,7 +1950,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" ht="17.25" customHeight="1">
+    <row r="4" ht="17.25" customHeight="1" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1095,7 +1958,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" ht="17.25" customHeight="1">
+    <row r="5" ht="17.25" customHeight="1" spans="1:3">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -1103,7 +1966,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" ht="17.25" customHeight="1">
+    <row r="6" ht="17.25" customHeight="1" spans="1:3">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -1111,7 +1974,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" ht="17.25" customHeight="1">
+    <row r="7" ht="17.25" customHeight="1" spans="1:3">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -1119,7 +1982,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" ht="17.25" customHeight="1">
+    <row r="8" ht="17.25" customHeight="1" spans="1:3">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -1127,7 +1990,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" ht="17.25" customHeight="1">
+    <row r="9" ht="17.25" customHeight="1" spans="1:3">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -1135,7 +1998,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" ht="17.25" customHeight="1">
+    <row r="10" ht="17.25" customHeight="1" spans="1:3">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -1143,7 +2006,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" ht="17.25" customHeight="1">
+    <row r="11" ht="17.25" customHeight="1" spans="1:3">
       <c r="A11" s="1" t="s">
         <v>21</v>
       </c>
@@ -1151,7 +2014,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" ht="17.25" customHeight="1">
+    <row r="12" ht="17.25" customHeight="1" spans="1:3">
       <c r="A12" s="1" t="s">
         <v>23</v>
       </c>
@@ -1159,7 +2022,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" ht="17.25" customHeight="1">
+    <row r="13" ht="17.25" customHeight="1" spans="1:3">
       <c r="A13" s="1" t="s">
         <v>25</v>
       </c>
@@ -1167,7 +2030,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" ht="17.25" customHeight="1">
+    <row r="14" ht="17.25" customHeight="1" spans="1:3">
       <c r="A14" s="1" t="s">
         <v>27</v>
       </c>
@@ -1175,7 +2038,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" ht="17.25" customHeight="1">
+    <row r="15" ht="17.25" customHeight="1" spans="1:3">
       <c r="A15" s="1" t="s">
         <v>29</v>
       </c>
@@ -1183,7 +2046,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" ht="17.25" customHeight="1">
+    <row r="16" ht="17.25" customHeight="1" spans="1:3">
       <c r="A16" s="1" t="s">
         <v>31</v>
       </c>
@@ -1191,7 +2054,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" ht="17.25" customHeight="1">
+    <row r="17" ht="17.25" customHeight="1" spans="1:2">
       <c r="A17" s="1" t="s">
         <v>33</v>
       </c>
@@ -1199,7 +2062,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" ht="17.25" customHeight="1">
+    <row r="18" ht="17.25" customHeight="1" spans="1:2">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -1207,7 +2070,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" ht="17.25" customHeight="1">
+    <row r="19" ht="17.25" customHeight="1" spans="1:2">
       <c r="A19" s="1" t="s">
         <v>37</v>
       </c>
@@ -1215,7 +2078,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" ht="17.25" customHeight="1">
+    <row r="20" ht="17.25" customHeight="1" spans="1:2">
       <c r="A20" s="1" t="s">
         <v>39</v>
       </c>
@@ -1223,7 +2086,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" ht="17.25" customHeight="1">
+    <row r="21" ht="17.25" customHeight="1" spans="1:2">
       <c r="A21" s="1" t="s">
         <v>41</v>
       </c>
@@ -1231,7 +2094,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" ht="17.25" customHeight="1">
+    <row r="22" ht="17.25" customHeight="1" spans="1:2">
       <c r="A22" s="1" t="s">
         <v>43</v>
       </c>
@@ -1239,7 +2102,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" ht="17.25" customHeight="1">
+    <row r="23" ht="17.25" customHeight="1" spans="1:2">
       <c r="A23" s="1" t="s">
         <v>45</v>
       </c>
@@ -1247,7 +2110,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" ht="17.25" customHeight="1">
+    <row r="24" ht="17.25" customHeight="1" spans="1:2">
       <c r="A24" s="1" t="s">
         <v>47</v>
       </c>
@@ -1255,7 +2118,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" ht="17.25" customHeight="1">
+    <row r="25" ht="17.25" customHeight="1" spans="1:2">
       <c r="A25" s="1" t="s">
         <v>49</v>
       </c>
@@ -1263,7 +2126,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" ht="17.25" customHeight="1">
+    <row r="26" ht="17.25" customHeight="1" spans="1:2">
       <c r="A26" s="1" t="s">
         <v>51</v>
       </c>
@@ -1271,7 +2134,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" ht="17.25" customHeight="1">
+    <row r="27" ht="17.25" customHeight="1" spans="1:2">
       <c r="A27" s="1" t="s">
         <v>53</v>
       </c>
@@ -1279,7 +2142,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" ht="17.25" customHeight="1">
+    <row r="28" ht="17.25" customHeight="1" spans="1:2">
       <c r="A28" s="1" t="s">
         <v>55</v>
       </c>
@@ -1287,7 +2150,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" ht="17.25" customHeight="1">
+    <row r="29" ht="17.25" customHeight="1" spans="1:2">
       <c r="A29" s="1" t="s">
         <v>57</v>
       </c>
@@ -1295,7 +2158,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" ht="17.25" customHeight="1">
+    <row r="30" ht="17.25" customHeight="1" spans="1:2">
       <c r="A30" s="1" t="s">
         <v>59</v>
       </c>
@@ -1303,7 +2166,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" ht="17.25" customHeight="1">
+    <row r="31" ht="17.25" customHeight="1" spans="1:2">
       <c r="A31" s="1" t="s">
         <v>61</v>
       </c>
@@ -1311,7 +2174,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="32" ht="17.25" customHeight="1">
+    <row r="32" ht="17.25" customHeight="1" spans="1:2">
       <c r="A32" s="1" t="s">
         <v>63</v>
       </c>
@@ -1319,7 +2182,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" ht="17.25" customHeight="1">
+    <row r="33" ht="17.25" customHeight="1" spans="1:2">
       <c r="A33" s="1" t="s">
         <v>65</v>
       </c>
@@ -1327,7 +2190,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="34" ht="17.25" customHeight="1">
+    <row r="34" ht="17.25" customHeight="1" spans="1:2">
       <c r="A34" s="1" t="s">
         <v>67</v>
       </c>
@@ -1335,7 +2198,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="35" ht="17.25" customHeight="1">
+    <row r="35" ht="17.25" customHeight="1" spans="1:2">
       <c r="A35" s="1" t="s">
         <v>69</v>
       </c>
@@ -1343,7 +2206,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" ht="17.25" customHeight="1">
+    <row r="36" ht="17.25" customHeight="1" spans="1:2">
       <c r="A36" s="1" t="s">
         <v>71</v>
       </c>
@@ -1351,7 +2214,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="37" ht="17.25" customHeight="1">
+    <row r="37" ht="17.25" customHeight="1" spans="1:2">
       <c r="A37" s="1" t="s">
         <v>73</v>
       </c>
@@ -1359,7 +2222,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" ht="17.25" customHeight="1">
+    <row r="38" ht="17.25" customHeight="1" spans="1:2">
       <c r="A38" s="1" t="s">
         <v>75</v>
       </c>
@@ -1367,7 +2230,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" ht="17.25" customHeight="1">
+    <row r="39" ht="17.25" customHeight="1" spans="1:2">
       <c r="A39" s="1" t="s">
         <v>77</v>
       </c>
@@ -1375,7 +2238,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" ht="17.25" customHeight="1">
+    <row r="40" ht="17.25" customHeight="1" spans="1:2">
       <c r="A40" s="1" t="s">
         <v>79</v>
       </c>
@@ -1383,7 +2246,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41" ht="17.25" customHeight="1">
+    <row r="41" ht="17.25" customHeight="1" spans="1:2">
       <c r="A41" s="1" t="s">
         <v>81</v>
       </c>
@@ -1391,7 +2254,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" ht="17.25" customHeight="1">
+    <row r="42" ht="17.25" customHeight="1" spans="1:2">
       <c r="A42" s="1" t="s">
         <v>83</v>
       </c>
@@ -1399,7 +2262,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" ht="17.25" customHeight="1">
+    <row r="43" ht="17.25" customHeight="1" spans="1:2">
       <c r="A43" s="1" t="s">
         <v>85</v>
       </c>
@@ -1407,7 +2270,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="44" ht="17.25" customHeight="1">
+    <row r="44" ht="17.25" customHeight="1" spans="1:2">
       <c r="A44" s="1" t="s">
         <v>87</v>
       </c>
@@ -1415,90 +2278,90 @@
         <v>88</v>
       </c>
     </row>
-    <row r="45" ht="17.25" customHeight="1">
-      <c r="A45" s="2" t="s">
+    <row r="45" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A45" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="4" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="46" ht="17.25" customHeight="1">
-      <c r="A46" s="2" t="s">
+    <row r="46" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A46" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="4" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="47" ht="17.25" customHeight="1">
-      <c r="A47" s="2" t="s">
+    <row r="47" ht="17.25" customHeight="1" spans="1:2">
+      <c r="A47" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" s="4" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="48" ht="17.25" customHeight="1">
+    <row r="48" ht="17.25" customHeight="1" spans="1:2">
       <c r="A48" s="2" t="s">
         <v>95</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C48" s="2" t="s">
+    </row>
+    <row r="49" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A49" s="2" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="49" ht="17.25" customHeight="1">
-      <c r="A49" s="2" t="s">
+      <c r="B49" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B49" s="4" t="s">
+    </row>
+    <row r="50" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A50" s="2" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="50" ht="17.25" customHeight="1">
-      <c r="A50" s="2" t="s">
+      <c r="B50" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B50" s="4" t="s">
+    </row>
+    <row r="51" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A51" s="2" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="51" ht="17.25" customHeight="1">
-      <c r="A51" s="2" t="s">
+      <c r="B51" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="C51" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="52" ht="17.25" customHeight="1">
+    <row r="52" ht="17.25" customHeight="1" spans="1:3">
       <c r="A52" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B52" s="5" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="53" ht="17.25" customHeight="1">
+    <row r="53" ht="17.25" customHeight="1" spans="1:3">
       <c r="A53" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B53" s="5" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="54" ht="17.25" customHeight="1">
+    <row r="54" ht="17.25" customHeight="1" spans="1:3">
       <c r="A54" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="5" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="55" ht="17.25" customHeight="1">
+    <row r="55" ht="17.25" customHeight="1" spans="1:3">
       <c r="A55" s="2" t="s">
         <v>110</v>
       </c>
@@ -1506,155 +2369,146 @@
         <v>111</v>
       </c>
     </row>
-    <row r="56" ht="17.25" customHeight="1">
+    <row r="56" ht="17.25" customHeight="1" spans="1:3">
       <c r="A56" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B56" s="5" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="57" ht="17.25" customHeight="1">
-      <c r="A57" s="7" t="s">
+    <row r="57" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A57" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B57" s="7" t="s">
+      <c r="B57" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C57" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="58" ht="17.25" customHeight="1">
+    </row>
+    <row r="58" ht="17.25" customHeight="1" spans="1:3">
       <c r="A58" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B58" s="6" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="59" ht="17.25" customHeight="1">
-      <c r="A59" s="8" t="s">
+    <row r="59" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A59" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B59" s="9" t="s">
+      <c r="B59" s="7" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="60" ht="17.25" customHeight="1">
+    <row r="60" ht="17.25" customHeight="1" spans="1:3">
       <c r="A60" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="B60" s="9" t="s">
+      <c r="B60" s="8" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="61" ht="17.25" customHeight="1">
-      <c r="A61" s="8" t="s">
+      <c r="C60" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="61" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A61" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B61" s="9" t="s">
+      <c r="B61" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="62" ht="17.25" customHeight="1">
-      <c r="A62" s="8" t="s">
+    <row r="62" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A62" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="B62" s="9" t="s">
+      <c r="B62" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="63" ht="17.25" customHeight="1">
-      <c r="A63" s="8" t="s">
+    <row r="63" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A63" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="B63" s="9" t="s">
+      <c r="B63" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="64" ht="17.25" customHeight="1">
-      <c r="A64" s="8" t="s">
+    <row r="64" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A64" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="B64" s="9" t="s">
+      <c r="B64" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="65" ht="17.25" customHeight="1">
-      <c r="A65" s="8" t="s">
+    <row r="65" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A65" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="B65" s="9" t="s">
+      <c r="B65" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="66" ht="17.25" customHeight="1">
-      <c r="A66" s="8" t="s">
+    <row r="66" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A66" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="B66" s="9" t="s">
+      <c r="B66" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="67" ht="17.25" customHeight="1">
-      <c r="A67" s="8" t="s">
+    <row r="67" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A67" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="B67" s="9" t="s">
+      <c r="B67" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="68" ht="17.25" customHeight="1">
+    <row r="68" ht="17.25" customHeight="1" spans="1:3">
       <c r="A68" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="B68" s="9" t="s">
+      <c r="B68" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="69" ht="17.25" customHeight="1">
+    <row r="69" ht="17.25" customHeight="1" spans="1:3">
       <c r="A69" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="B69" s="9" t="s">
+      <c r="B69" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="70" ht="17.25" customHeight="1">
-      <c r="A70" s="10" t="s">
+    <row r="70" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A70" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="B70" s="10" t="s">
+      <c r="B70" t="s">
         <v>141</v>
       </c>
-      <c r="C70" s="10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="71" ht="17.25" customHeight="1">
-      <c r="A71" s="10" t="s">
+    </row>
+    <row r="71" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A71" t="s">
         <v>142</v>
       </c>
-      <c r="B71" s="10" t="s">
+      <c r="B71" t="s">
         <v>143</v>
       </c>
-      <c r="C71" s="10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="72" ht="17.25" customHeight="1">
-      <c r="A72" s="10" t="s">
+    </row>
+    <row r="72" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A72" t="s">
         <v>144</v>
       </c>
-      <c r="B72" s="10" t="s">
+      <c r="B72" t="s">
         <v>145</v>
       </c>
-      <c r="C72" s="10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="73" ht="17.25" customHeight="1">
+    </row>
+    <row r="73" ht="17.25" customHeight="1" spans="1:3">
       <c r="A73" s="10" t="s">
         <v>146</v>
       </c>
@@ -1662,10 +2516,10 @@
         <v>147</v>
       </c>
       <c r="C73" s="10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="74" ht="17.25" customHeight="1">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="74" ht="17.25" customHeight="1" spans="1:3">
       <c r="A74" s="10" t="s">
         <v>148</v>
       </c>
@@ -1673,379 +2527,409 @@
         <v>149</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="75" ht="17.25" customHeight="1">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="75" ht="17.25" customHeight="1" spans="1:3">
       <c r="A75" s="10" t="s">
         <v>150</v>
       </c>
       <c r="B75" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="C75" s="11"/>
-    </row>
-    <row r="76" ht="17.25" customHeight="1">
+      <c r="C75" s="10" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="76" ht="17.25" customHeight="1" spans="1:3">
       <c r="A76" s="10" t="s">
         <v>152</v>
       </c>
       <c r="B76" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="C76" s="11"/>
-    </row>
-    <row r="77" ht="17.25" customHeight="1">
+      <c r="C76" s="10" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="77" ht="17.25" customHeight="1" spans="1:3">
       <c r="A77" s="10" t="s">
         <v>154</v>
       </c>
       <c r="B77" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="C77" s="11"/>
-    </row>
-    <row r="78" ht="17.25" customHeight="1">
+      <c r="C77" s="10" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="78" ht="17.25" customHeight="1" spans="1:3">
       <c r="A78" s="10" t="s">
         <v>156</v>
       </c>
       <c r="B78" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="C78" s="11"/>
-    </row>
-    <row r="79" ht="17.25" customHeight="1">
+      <c r="C78" s="10"/>
+    </row>
+    <row r="79" ht="17.25" customHeight="1" spans="1:3">
       <c r="A79" s="10" t="s">
         <v>158</v>
       </c>
       <c r="B79" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="C79" s="11"/>
-    </row>
-    <row r="80" ht="17.25" customHeight="1">
+      <c r="C79" s="10"/>
+    </row>
+    <row r="80" ht="17.25" customHeight="1" spans="1:3">
       <c r="A80" s="10" t="s">
         <v>160</v>
       </c>
       <c r="B80" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="C80" s="11"/>
-    </row>
-    <row r="81" ht="17.25" customHeight="1">
+      <c r="C80" s="10"/>
+    </row>
+    <row r="81" ht="17.25" customHeight="1" spans="1:3">
       <c r="A81" s="10" t="s">
         <v>162</v>
       </c>
       <c r="B81" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="C81" s="11"/>
-    </row>
-    <row r="82" ht="17.25" customHeight="1">
+      <c r="C81" s="10"/>
+    </row>
+    <row r="82" ht="17.25" customHeight="1" spans="1:3">
       <c r="A82" s="10" t="s">
         <v>164</v>
       </c>
       <c r="B82" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="C82" s="11"/>
-    </row>
-    <row r="83" ht="17.25" customHeight="1">
+      <c r="C82" s="10"/>
+    </row>
+    <row r="83" ht="17.25" customHeight="1" spans="1:3">
       <c r="A83" s="10" t="s">
         <v>166</v>
       </c>
       <c r="B83" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="C83" s="11"/>
-    </row>
-    <row r="84" ht="17.25" customHeight="1">
-      <c r="A84" s="9" t="s">
+      <c r="C83" s="10"/>
+    </row>
+    <row r="84" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A84" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="B84" s="9" t="s">
+      <c r="B84" s="10" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="85" ht="17.25" customHeight="1">
-      <c r="A85" s="9" t="s">
+      <c r="C84" s="10"/>
+    </row>
+    <row r="85" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A85" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="B85" s="9" t="s">
+      <c r="B85" s="10" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="86" ht="17.25" customHeight="1">
-      <c r="A86" s="9" t="s">
+      <c r="C85" s="10"/>
+    </row>
+    <row r="86" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A86" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="B86" s="9" t="s">
+      <c r="B86" s="10" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="87" ht="17.25" customHeight="1">
-      <c r="A87" s="9" t="s">
+      <c r="C86" s="10"/>
+    </row>
+    <row r="87" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A87" t="s">
         <v>174</v>
       </c>
-      <c r="B87" s="9" t="s">
+      <c r="B87" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="88" ht="17.25" customHeight="1">
-      <c r="A88" s="9" t="s">
+    <row r="88" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A88" t="s">
         <v>176</v>
       </c>
-      <c r="B88" s="9" t="s">
+      <c r="B88" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="89" ht="17.25" customHeight="1">
-      <c r="A89" s="10" t="s">
+    <row r="89" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A89" t="s">
         <v>178</v>
       </c>
-      <c r="B89" s="10" t="s">
+      <c r="B89" t="s">
         <v>179</v>
       </c>
-      <c r="C89" s="11"/>
-    </row>
-    <row r="90" ht="17.25" customHeight="1">
-      <c r="A90" s="10" t="s">
+    </row>
+    <row r="90" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A90" t="s">
         <v>180</v>
       </c>
-      <c r="B90" s="12" t="s">
+      <c r="B90" t="s">
         <v>181</v>
       </c>
-      <c r="C90" s="10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="91" ht="17.25" customHeight="1">
-      <c r="A91" s="10" t="s">
+    </row>
+    <row r="91" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A91" t="s">
         <v>182</v>
       </c>
-      <c r="B91" s="12" t="s">
+      <c r="B91" t="s">
         <v>183</v>
       </c>
-      <c r="C91" s="11"/>
-    </row>
-    <row r="92" ht="17.25" customHeight="1">
+    </row>
+    <row r="92" ht="17.25" customHeight="1" spans="1:3">
       <c r="A92" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="B92" s="12" t="s">
+      <c r="B92" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="C92" s="11"/>
-    </row>
-    <row r="93" ht="17.25" customHeight="1">
+      <c r="C92" s="10"/>
+    </row>
+    <row r="93" ht="17.25" customHeight="1" spans="1:3">
       <c r="A93" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="B93" s="12" t="s">
+      <c r="B93" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="C93" s="11"/>
-    </row>
-    <row r="94" ht="17.25" customHeight="1">
+      <c r="C93" s="10" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="94" ht="17.25" customHeight="1" spans="1:3">
       <c r="A94" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="B94" s="12" t="s">
+      <c r="B94" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="C94" s="11"/>
-    </row>
-    <row r="95" ht="17.25" customHeight="1">
-      <c r="A95" s="9" t="s">
+      <c r="C94" s="10"/>
+    </row>
+    <row r="95" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A95" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="B95" s="9" t="s">
+      <c r="B95" s="11" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="96" ht="17.25" customHeight="1">
-      <c r="A96" s="9" t="s">
+      <c r="C95" s="10"/>
+    </row>
+    <row r="96" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A96" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="B96" s="9" t="s">
+      <c r="B96" s="11" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="97" ht="17.25" customHeight="1">
-      <c r="A97" s="9" t="s">
+      <c r="C96" s="10"/>
+    </row>
+    <row r="97" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A97" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="B97" s="9" t="s">
+      <c r="B97" s="11" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="98" ht="17.25" customHeight="1">
-      <c r="A98" s="9" t="s">
+      <c r="C97" s="10"/>
+    </row>
+    <row r="98" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A98" t="s">
         <v>196</v>
       </c>
-      <c r="B98" s="9" t="s">
+      <c r="B98" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="99" ht="17.25" customHeight="1">
-      <c r="A99" s="9" t="s">
+    <row r="99" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A99" t="s">
         <v>198</v>
       </c>
-      <c r="B99" s="9" t="s">
+      <c r="B99" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="100" ht="17.25" customHeight="1">
-      <c r="A100" s="9" t="s">
+    <row r="100" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A100" t="s">
         <v>200</v>
       </c>
-      <c r="B100" s="9" t="s">
+      <c r="B100" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="101" ht="17.25" customHeight="1">
-      <c r="A101" s="9" t="s">
+    <row r="101" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A101" t="s">
         <v>202</v>
       </c>
-      <c r="B101" s="9" t="s">
+      <c r="B101" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="102" ht="17.25" customHeight="1">
-      <c r="A102" s="9" t="s">
+    <row r="102" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A102" t="s">
         <v>204</v>
       </c>
-      <c r="B102" s="13" t="s">
+      <c r="B102" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="103" ht="17.25" customHeight="1">
-      <c r="A103" s="14" t="s">
+    <row r="103" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A103" t="s">
         <v>206</v>
       </c>
-      <c r="B103" s="15" t="s">
+      <c r="B103" t="s">
         <v>207</v>
       </c>
-      <c r="C103" s="10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="104" ht="17.25" customHeight="1">
-      <c r="A104" s="14" t="s">
+    </row>
+    <row r="104" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A104" t="s">
         <v>208</v>
       </c>
-      <c r="B104" s="14" t="s">
+      <c r="B104" t="s">
         <v>209</v>
       </c>
-      <c r="C104" s="10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="105" ht="17.25" customHeight="1">
-      <c r="A105" s="14" t="s">
+    </row>
+    <row r="105" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A105" t="s">
         <v>210</v>
       </c>
-      <c r="B105" s="15" t="s">
+      <c r="B105" s="12" t="s">
         <v>211</v>
       </c>
-      <c r="C105" s="10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="106" ht="17.25" customHeight="1">
-      <c r="A106" s="14" t="s">
+    </row>
+    <row r="106" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A106" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="B106" s="15" t="s">
+      <c r="B106" s="13" t="s">
         <v>213</v>
       </c>
       <c r="C106" s="10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="107" ht="17.25" customHeight="1">
-      <c r="A107" s="14" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="107" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A107" s="13" t="s">
         <v>214</v>
       </c>
-      <c r="B107" s="15" t="s">
+      <c r="B107" s="13" t="s">
         <v>215</v>
       </c>
       <c r="C107" s="10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="108" ht="17.25" customHeight="1">
-      <c r="A108" s="14" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="108" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A108" s="13" t="s">
         <v>216</v>
       </c>
-      <c r="B108" s="15" t="s">
+      <c r="B108" s="13" t="s">
         <v>217</v>
       </c>
       <c r="C108" s="10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="109" ht="17.25" customHeight="1">
-      <c r="A109" s="14" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="109" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A109" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="B109" s="15" t="s">
+      <c r="B109" s="13" t="s">
         <v>219</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="110" ht="17.25" customHeight="1">
-      <c r="A110" s="9" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="110" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A110" s="13" t="s">
         <v>220</v>
       </c>
       <c r="B110" s="13" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="111" ht="17.25" customHeight="1">
-      <c r="A111" s="14" t="s">
+      <c r="C110" s="10" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="111" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A111" s="13" t="s">
         <v>222</v>
       </c>
-      <c r="B111" s="15" t="s">
+      <c r="B111" s="13" t="s">
         <v>223</v>
       </c>
       <c r="C111" s="10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="112" ht="17.25" customHeight="1">
-      <c r="A112" s="14" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="112" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A112" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="B112" s="15" t="s">
+      <c r="B112" s="13" t="s">
         <v>225</v>
       </c>
       <c r="C112" s="10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="113" ht="17.25" customHeight="1">
-      <c r="A113" s="14" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="113" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A113" t="s">
         <v>226</v>
       </c>
-      <c r="B113" s="13" t="s">
+      <c r="B113" s="12" t="s">
         <v>227</v>
       </c>
-      <c r="C113" s="10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="114" ht="17.25" customHeight="1">
-      <c r="A114" s="9" t="s">
+    </row>
+    <row r="114" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A114" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="B114" s="9" t="s">
+      <c r="B114" s="13" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="115" ht="17.25" customHeight="1"/>
-    <row r="116" ht="17.25" customHeight="1"/>
-    <row r="117" ht="17.25" customHeight="1"/>
+      <c r="C114" s="10" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="115" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A115" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="B115" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="C115" s="10" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="116" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A116" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="B116" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="C116" s="10" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="117" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A117" t="s">
+        <v>234</v>
+      </c>
+      <c r="B117" t="s">
+        <v>235</v>
+      </c>
+    </row>
     <row r="118" ht="17.25" customHeight="1"/>
     <row r="119" ht="17.25" customHeight="1"/>
     <row r="120" ht="17.25" customHeight="1"/>
@@ -2924,10 +3808,12 @@
     <row r="993" ht="17.25" customHeight="1"/>
     <row r="994" ht="17.25" customHeight="1"/>
     <row r="995" ht="17.25" customHeight="1"/>
+    <row r="996" ht="17.25" customHeight="1"/>
+    <row r="997" ht="17.25" customHeight="1"/>
+    <row r="998" ht="17.25" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="1" orientation="landscape"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
@@ -1,22 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\JewelThief\JsonConverter\ExcelFiles\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{034D7F31-0760-483C-9E03-7128948E6E68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="31140" yWindow="2340" windowWidth="22485" windowHeight="12495" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="Zo3y2CT06Z9aRkJvrr1FP2fBKanMGUSvILAo2d4duAE="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="PjQ/ZH5dNfpZSLhuzuhQKuy/nAO/JzfJl7JGthYVMbo="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="232">
   <si>
     <t>미리 로드할 어드레서블 테이블</t>
   </si>
@@ -402,6 +411,18 @@
     <t>Mesh_IronBox_Prefab</t>
   </si>
   <si>
+    <t>PreLoadAsset_GameObject_MeshBrokenIronBoxPrefab</t>
+  </si>
+  <si>
+    <t>Mesh_BrokenIronBox_Prefab</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_GameObject_MeshSafePrefab</t>
+  </si>
+  <si>
+    <t>Mesh_Safe_Prefab</t>
+  </si>
+  <si>
     <t>PreLoadAsset_GameObject_MeshWoodBoxPrefab</t>
   </si>
   <si>
@@ -700,57 +721,65 @@
   </si>
   <si>
     <t>MeshCollider_Junk_Glasses</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_GameObject_ItemObject</t>
-  </si>
-  <si>
-    <t>ItemObject</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="8">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="9">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -758,7 +787,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -768,7 +797,13 @@
     </fill>
   </fills>
   <borders count="3">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -782,6 +817,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -793,62 +829,43 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="2" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1038,23 +1055,23 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C996"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="52.14"/>
-    <col customWidth="1" min="2" max="2" width="35.14"/>
-    <col customWidth="1" min="3" max="3" width="31.43"/>
-    <col customWidth="1" min="4" max="26" width="9.0"/>
+    <col min="1" max="1" width="52.140625" customWidth="1"/>
+    <col min="2" max="2" width="35.140625" customWidth="1"/>
+    <col min="3" max="3" width="31.42578125" customWidth="1"/>
+    <col min="4" max="26" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1">
+    <row r="1" spans="1:3" ht="17.25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1065,7 +1082,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="17.25" customHeight="1">
+    <row r="2" spans="1:3" ht="17.25" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1076,7 +1093,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" ht="17.25" customHeight="1">
+    <row r="3" spans="1:3" ht="17.25" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1087,7 +1104,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" ht="17.25" customHeight="1">
+    <row r="4" spans="1:3" ht="17.25" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1095,7 +1112,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" ht="17.25" customHeight="1">
+    <row r="5" spans="1:3" ht="17.25" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -1103,7 +1120,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" ht="17.25" customHeight="1">
+    <row r="6" spans="1:3" ht="17.25" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -1111,7 +1128,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" ht="17.25" customHeight="1">
+    <row r="7" spans="1:3" ht="17.25" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -1119,7 +1136,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" ht="17.25" customHeight="1">
+    <row r="8" spans="1:3" ht="17.25" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -1127,7 +1144,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" ht="17.25" customHeight="1">
+    <row r="9" spans="1:3" ht="17.25" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -1135,7 +1152,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" ht="17.25" customHeight="1">
+    <row r="10" spans="1:3" ht="17.25" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -1143,7 +1160,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" ht="17.25" customHeight="1">
+    <row r="11" spans="1:3" ht="17.25" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>21</v>
       </c>
@@ -1151,7 +1168,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" ht="17.25" customHeight="1">
+    <row r="12" spans="1:3" ht="17.25" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>23</v>
       </c>
@@ -1159,7 +1176,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" ht="17.25" customHeight="1">
+    <row r="13" spans="1:3" ht="17.25" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>25</v>
       </c>
@@ -1167,7 +1184,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" ht="17.25" customHeight="1">
+    <row r="14" spans="1:3" ht="17.25" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>27</v>
       </c>
@@ -1175,7 +1192,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" ht="17.25" customHeight="1">
+    <row r="15" spans="1:3" ht="17.25" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>29</v>
       </c>
@@ -1183,7 +1200,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" ht="17.25" customHeight="1">
+    <row r="16" spans="1:3" ht="17.25" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>31</v>
       </c>
@@ -1191,7 +1208,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" ht="17.25" customHeight="1">
+    <row r="17" spans="1:2" ht="17.25" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>33</v>
       </c>
@@ -1199,7 +1216,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" ht="17.25" customHeight="1">
+    <row r="18" spans="1:2" ht="17.25" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -1207,7 +1224,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" ht="17.25" customHeight="1">
+    <row r="19" spans="1:2" ht="17.25" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>37</v>
       </c>
@@ -1215,7 +1232,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" ht="17.25" customHeight="1">
+    <row r="20" spans="1:2" ht="17.25" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>39</v>
       </c>
@@ -1223,7 +1240,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" ht="17.25" customHeight="1">
+    <row r="21" spans="1:2" ht="17.25" customHeight="1">
       <c r="A21" s="1" t="s">
         <v>41</v>
       </c>
@@ -1231,7 +1248,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" ht="17.25" customHeight="1">
+    <row r="22" spans="1:2" ht="17.25" customHeight="1">
       <c r="A22" s="1" t="s">
         <v>43</v>
       </c>
@@ -1239,7 +1256,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" ht="17.25" customHeight="1">
+    <row r="23" spans="1:2" ht="17.25" customHeight="1">
       <c r="A23" s="1" t="s">
         <v>45</v>
       </c>
@@ -1247,7 +1264,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" ht="17.25" customHeight="1">
+    <row r="24" spans="1:2" ht="17.25" customHeight="1">
       <c r="A24" s="1" t="s">
         <v>47</v>
       </c>
@@ -1255,7 +1272,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" ht="17.25" customHeight="1">
+    <row r="25" spans="1:2" ht="17.25" customHeight="1">
       <c r="A25" s="1" t="s">
         <v>49</v>
       </c>
@@ -1263,7 +1280,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" ht="17.25" customHeight="1">
+    <row r="26" spans="1:2" ht="17.25" customHeight="1">
       <c r="A26" s="1" t="s">
         <v>51</v>
       </c>
@@ -1271,7 +1288,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" ht="17.25" customHeight="1">
+    <row r="27" spans="1:2" ht="17.25" customHeight="1">
       <c r="A27" s="1" t="s">
         <v>53</v>
       </c>
@@ -1279,7 +1296,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" ht="17.25" customHeight="1">
+    <row r="28" spans="1:2" ht="17.25" customHeight="1">
       <c r="A28" s="1" t="s">
         <v>55</v>
       </c>
@@ -1287,7 +1304,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" ht="17.25" customHeight="1">
+    <row r="29" spans="1:2" ht="17.25" customHeight="1">
       <c r="A29" s="1" t="s">
         <v>57</v>
       </c>
@@ -1295,7 +1312,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" ht="17.25" customHeight="1">
+    <row r="30" spans="1:2" ht="17.25" customHeight="1">
       <c r="A30" s="1" t="s">
         <v>59</v>
       </c>
@@ -1303,7 +1320,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" ht="17.25" customHeight="1">
+    <row r="31" spans="1:2" ht="17.25" customHeight="1">
       <c r="A31" s="1" t="s">
         <v>61</v>
       </c>
@@ -1311,7 +1328,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="32" ht="17.25" customHeight="1">
+    <row r="32" spans="1:2" ht="17.25" customHeight="1">
       <c r="A32" s="1" t="s">
         <v>63</v>
       </c>
@@ -1319,7 +1336,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" ht="17.25" customHeight="1">
+    <row r="33" spans="1:3" ht="17.25" customHeight="1">
       <c r="A33" s="1" t="s">
         <v>65</v>
       </c>
@@ -1327,7 +1344,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="34" ht="17.25" customHeight="1">
+    <row r="34" spans="1:3" ht="17.25" customHeight="1">
       <c r="A34" s="1" t="s">
         <v>67</v>
       </c>
@@ -1335,7 +1352,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="35" ht="17.25" customHeight="1">
+    <row r="35" spans="1:3" ht="17.25" customHeight="1">
       <c r="A35" s="1" t="s">
         <v>69</v>
       </c>
@@ -1343,7 +1360,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" ht="17.25" customHeight="1">
+    <row r="36" spans="1:3" ht="17.25" customHeight="1">
       <c r="A36" s="1" t="s">
         <v>71</v>
       </c>
@@ -1351,7 +1368,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="37" ht="17.25" customHeight="1">
+    <row r="37" spans="1:3" ht="17.25" customHeight="1">
       <c r="A37" s="1" t="s">
         <v>73</v>
       </c>
@@ -1359,7 +1376,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" ht="17.25" customHeight="1">
+    <row r="38" spans="1:3" ht="17.25" customHeight="1">
       <c r="A38" s="1" t="s">
         <v>75</v>
       </c>
@@ -1367,7 +1384,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" ht="17.25" customHeight="1">
+    <row r="39" spans="1:3" ht="17.25" customHeight="1">
       <c r="A39" s="1" t="s">
         <v>77</v>
       </c>
@@ -1375,7 +1392,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" ht="17.25" customHeight="1">
+    <row r="40" spans="1:3" ht="17.25" customHeight="1">
       <c r="A40" s="1" t="s">
         <v>79</v>
       </c>
@@ -1383,7 +1400,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41" ht="17.25" customHeight="1">
+    <row r="41" spans="1:3" ht="17.25" customHeight="1">
       <c r="A41" s="1" t="s">
         <v>81</v>
       </c>
@@ -1391,7 +1408,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" ht="17.25" customHeight="1">
+    <row r="42" spans="1:3" ht="17.25" customHeight="1">
       <c r="A42" s="1" t="s">
         <v>83</v>
       </c>
@@ -1399,7 +1416,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" ht="17.25" customHeight="1">
+    <row r="43" spans="1:3" ht="17.25" customHeight="1">
       <c r="A43" s="1" t="s">
         <v>85</v>
       </c>
@@ -1407,7 +1424,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="44" ht="17.25" customHeight="1">
+    <row r="44" spans="1:3" ht="17.25" customHeight="1">
       <c r="A44" s="1" t="s">
         <v>87</v>
       </c>
@@ -1415,7 +1432,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="45" ht="17.25" customHeight="1">
+    <row r="45" spans="1:3" ht="17.25" customHeight="1">
       <c r="A45" s="2" t="s">
         <v>89</v>
       </c>
@@ -1423,7 +1440,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="46" ht="17.25" customHeight="1">
+    <row r="46" spans="1:3" ht="17.25" customHeight="1">
       <c r="A46" s="2" t="s">
         <v>91</v>
       </c>
@@ -1431,7 +1448,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="47" ht="17.25" customHeight="1">
+    <row r="47" spans="1:3" ht="17.25" customHeight="1">
       <c r="A47" s="2" t="s">
         <v>93</v>
       </c>
@@ -1439,7 +1456,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="48" ht="17.25" customHeight="1">
+    <row r="48" spans="1:3" ht="17.25" customHeight="1">
       <c r="A48" s="2" t="s">
         <v>95</v>
       </c>
@@ -1450,7 +1467,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="49" ht="17.25" customHeight="1">
+    <row r="49" spans="1:3" ht="17.25" customHeight="1">
       <c r="A49" s="2" t="s">
         <v>98</v>
       </c>
@@ -1458,7 +1475,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="50" ht="17.25" customHeight="1">
+    <row r="50" spans="1:3" ht="17.25" customHeight="1">
       <c r="A50" s="2" t="s">
         <v>100</v>
       </c>
@@ -1466,7 +1483,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="51" ht="17.25" customHeight="1">
+    <row r="51" spans="1:3" ht="17.25" customHeight="1">
       <c r="A51" s="2" t="s">
         <v>102</v>
       </c>
@@ -1474,7 +1491,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="52" ht="17.25" customHeight="1">
+    <row r="52" spans="1:3" ht="17.25" customHeight="1">
       <c r="A52" s="2" t="s">
         <v>104</v>
       </c>
@@ -1482,7 +1499,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="53" ht="17.25" customHeight="1">
+    <row r="53" spans="1:3" ht="17.25" customHeight="1">
       <c r="A53" s="2" t="s">
         <v>106</v>
       </c>
@@ -1490,7 +1507,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="54" ht="17.25" customHeight="1">
+    <row r="54" spans="1:3" ht="17.25" customHeight="1">
       <c r="A54" s="2" t="s">
         <v>108</v>
       </c>
@@ -1498,7 +1515,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="55" ht="17.25" customHeight="1">
+    <row r="55" spans="1:3" ht="17.25" customHeight="1">
       <c r="A55" s="2" t="s">
         <v>110</v>
       </c>
@@ -1506,7 +1523,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="56" ht="17.25" customHeight="1">
+    <row r="56" spans="1:3" ht="17.25" customHeight="1">
       <c r="A56" s="2" t="s">
         <v>112</v>
       </c>
@@ -1514,18 +1531,18 @@
         <v>113</v>
       </c>
     </row>
-    <row r="57" ht="17.25" customHeight="1">
-      <c r="A57" s="7" t="s">
+    <row r="57" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A57" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="B57" s="7" t="s">
+      <c r="B57" s="6" t="s">
         <v>115</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="58" ht="17.25" customHeight="1">
+    <row r="58" spans="1:3" ht="17.25" customHeight="1">
       <c r="A58" s="2" t="s">
         <v>116</v>
       </c>
@@ -1533,530 +1550,537 @@
         <v>117</v>
       </c>
     </row>
-    <row r="59" ht="17.25" customHeight="1">
-      <c r="A59" s="8" t="s">
+    <row r="59" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A59" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B59" s="9" t="s">
+      <c r="B59" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="60" ht="17.25" customHeight="1">
-      <c r="A60" s="8" t="s">
+    <row r="60" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A60" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B60" s="9" t="s">
+      <c r="B60" s="1" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="61" ht="17.25" customHeight="1">
-      <c r="A61" s="8" t="s">
+    <row r="61" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A61" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B61" s="9" t="s">
+      <c r="B61" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="62" ht="17.25" customHeight="1">
-      <c r="A62" s="8" t="s">
+    <row r="62" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A62" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B62" s="9" t="s">
+      <c r="B62" s="1" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="63" ht="17.25" customHeight="1">
-      <c r="A63" s="8" t="s">
+    <row r="63" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A63" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B63" s="9" t="s">
+      <c r="B63" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="64" ht="17.25" customHeight="1">
-      <c r="A64" s="8" t="s">
+    <row r="64" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A64" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B64" s="9" t="s">
+      <c r="B64" s="1" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="65" ht="17.25" customHeight="1">
-      <c r="A65" s="8" t="s">
+    <row r="65" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A65" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B65" s="9" t="s">
+      <c r="B65" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="66" ht="17.25" customHeight="1">
-      <c r="A66" s="8" t="s">
+    <row r="66" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A66" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B66" s="9" t="s">
+      <c r="B66" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="67" ht="17.25" customHeight="1">
-      <c r="A67" s="8" t="s">
+    <row r="67" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A67" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B67" s="9" t="s">
+      <c r="B67" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="68" ht="17.25" customHeight="1">
-      <c r="A68" s="9" t="s">
+    <row r="68" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A68" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B68" s="9" t="s">
+      <c r="B68" s="1" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="69" ht="17.25" customHeight="1">
-      <c r="A69" s="9" t="s">
+    <row r="69" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A69" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B69" s="9" t="s">
+      <c r="B69" s="1" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="70" ht="17.25" customHeight="1">
-      <c r="A70" s="10" t="s">
+    <row r="70" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A70" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B70" s="10" t="s">
+      <c r="B70" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C70" s="10" t="s">
+    </row>
+    <row r="71" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A71" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A72" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="C72" s="7" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="71" ht="17.25" customHeight="1">
-      <c r="A71" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="B71" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="C71" s="10" t="s">
+    <row r="73" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A73" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C73" s="7" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="72" ht="17.25" customHeight="1">
-      <c r="A72" s="10" t="s">
-        <v>144</v>
-      </c>
-      <c r="B72" s="10" t="s">
-        <v>145</v>
-      </c>
-      <c r="C72" s="10" t="s">
+    <row r="74" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A74" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="C74" s="7" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="73" ht="17.25" customHeight="1">
-      <c r="A73" s="10" t="s">
-        <v>146</v>
-      </c>
-      <c r="B73" s="10" t="s">
-        <v>147</v>
-      </c>
-      <c r="C73" s="10" t="s">
+    <row r="75" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A75" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="C75" s="7" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="74" ht="17.25" customHeight="1">
-      <c r="A74" s="10" t="s">
-        <v>148</v>
-      </c>
-      <c r="B74" s="10" t="s">
-        <v>149</v>
-      </c>
-      <c r="C74" s="10" t="s">
+    <row r="76" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A76" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="C76" s="7" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="75" ht="17.25" customHeight="1">
-      <c r="A75" s="10" t="s">
-        <v>150</v>
-      </c>
-      <c r="B75" s="10" t="s">
-        <v>151</v>
-      </c>
-      <c r="C75" s="11"/>
-    </row>
-    <row r="76" ht="17.25" customHeight="1">
-      <c r="A76" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="B76" s="10" t="s">
-        <v>153</v>
-      </c>
-      <c r="C76" s="11"/>
-    </row>
-    <row r="77" ht="17.25" customHeight="1">
-      <c r="A77" s="10" t="s">
+    <row r="77" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A77" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="B77" s="10" t="s">
+      <c r="B77" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="C77" s="11"/>
-    </row>
-    <row r="78" ht="17.25" customHeight="1">
-      <c r="A78" s="10" t="s">
+      <c r="C77" s="7"/>
+    </row>
+    <row r="78" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A78" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="B78" s="10" t="s">
+      <c r="B78" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="C78" s="11"/>
-    </row>
-    <row r="79" ht="17.25" customHeight="1">
-      <c r="A79" s="10" t="s">
+      <c r="C78" s="7"/>
+    </row>
+    <row r="79" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A79" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="B79" s="10" t="s">
+      <c r="B79" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="C79" s="11"/>
-    </row>
-    <row r="80" ht="17.25" customHeight="1">
-      <c r="A80" s="10" t="s">
+      <c r="C79" s="7"/>
+    </row>
+    <row r="80" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A80" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="B80" s="10" t="s">
+      <c r="B80" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="C80" s="11"/>
-    </row>
-    <row r="81" ht="17.25" customHeight="1">
-      <c r="A81" s="10" t="s">
+      <c r="C80" s="7"/>
+    </row>
+    <row r="81" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A81" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="B81" s="10" t="s">
+      <c r="B81" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="C81" s="11"/>
-    </row>
-    <row r="82" ht="17.25" customHeight="1">
-      <c r="A82" s="10" t="s">
+      <c r="C81" s="7"/>
+    </row>
+    <row r="82" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A82" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="B82" s="10" t="s">
+      <c r="B82" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="C82" s="11"/>
-    </row>
-    <row r="83" ht="17.25" customHeight="1">
-      <c r="A83" s="10" t="s">
+      <c r="C82" s="7"/>
+    </row>
+    <row r="83" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A83" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="B83" s="10" t="s">
+      <c r="B83" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="C83" s="11"/>
-    </row>
-    <row r="84" ht="17.25" customHeight="1">
-      <c r="A84" s="9" t="s">
+      <c r="C83" s="7"/>
+    </row>
+    <row r="84" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A84" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="B84" s="9" t="s">
+      <c r="B84" s="7" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="85" ht="17.25" customHeight="1">
-      <c r="A85" s="9" t="s">
+      <c r="C84" s="7"/>
+    </row>
+    <row r="85" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A85" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="B85" s="9" t="s">
+      <c r="B85" s="7" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="86" ht="17.25" customHeight="1">
-      <c r="A86" s="9" t="s">
+      <c r="C85" s="7"/>
+    </row>
+    <row r="86" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A86" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B86" s="9" t="s">
+      <c r="B86" s="1" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="87" ht="17.25" customHeight="1">
-      <c r="A87" s="9" t="s">
+    <row r="87" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A87" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B87" s="9" t="s">
+      <c r="B87" s="1" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="88" ht="17.25" customHeight="1">
-      <c r="A88" s="9" t="s">
+    <row r="88" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A88" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B88" s="9" t="s">
+      <c r="B88" s="1" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="89" ht="17.25" customHeight="1">
-      <c r="A89" s="10" t="s">
+    <row r="89" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A89" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B89" s="10" t="s">
+      <c r="B89" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="C89" s="11"/>
-    </row>
-    <row r="90" ht="17.25" customHeight="1">
-      <c r="A90" s="10" t="s">
+    </row>
+    <row r="90" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A90" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B90" s="12" t="s">
+      <c r="B90" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="C90" s="10" t="s">
+    </row>
+    <row r="91" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A91" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C91" s="7"/>
+    </row>
+    <row r="92" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A92" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="B92" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="C92" s="7" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="91" ht="17.25" customHeight="1">
-      <c r="A91" s="10" t="s">
-        <v>182</v>
-      </c>
-      <c r="B91" s="12" t="s">
-        <v>183</v>
-      </c>
-      <c r="C91" s="11"/>
-    </row>
-    <row r="92" ht="17.25" customHeight="1">
-      <c r="A92" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="B92" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="C92" s="11"/>
-    </row>
-    <row r="93" ht="17.25" customHeight="1">
-      <c r="A93" s="10" t="s">
+    <row r="93" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A93" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="B93" s="12" t="s">
+      <c r="B93" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="C93" s="11"/>
-    </row>
-    <row r="94" ht="17.25" customHeight="1">
-      <c r="A94" s="10" t="s">
+      <c r="C93" s="7"/>
+    </row>
+    <row r="94" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A94" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="B94" s="12" t="s">
+      <c r="B94" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="C94" s="11"/>
-    </row>
-    <row r="95" ht="17.25" customHeight="1">
-      <c r="A95" s="9" t="s">
+      <c r="C94" s="7"/>
+    </row>
+    <row r="95" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A95" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="B95" s="9" t="s">
+      <c r="B95" s="8" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="96" ht="17.25" customHeight="1">
-      <c r="A96" s="9" t="s">
+      <c r="C95" s="7"/>
+    </row>
+    <row r="96" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A96" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="B96" s="9" t="s">
+      <c r="B96" s="8" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="97" ht="17.25" customHeight="1">
-      <c r="A97" s="9" t="s">
+      <c r="C96" s="7"/>
+    </row>
+    <row r="97" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A97" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="B97" s="9" t="s">
+      <c r="B97" s="1" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="98" ht="17.25" customHeight="1">
-      <c r="A98" s="9" t="s">
+    <row r="98" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A98" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B98" s="9" t="s">
+      <c r="B98" s="1" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="99" ht="17.25" customHeight="1">
-      <c r="A99" s="9" t="s">
+    <row r="99" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A99" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B99" s="9" t="s">
+      <c r="B99" s="1" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="100" ht="17.25" customHeight="1">
-      <c r="A100" s="9" t="s">
+    <row r="100" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A100" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B100" s="9" t="s">
+      <c r="B100" s="1" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="101" ht="17.25" customHeight="1">
-      <c r="A101" s="9" t="s">
+    <row r="101" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A101" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B101" s="9" t="s">
+      <c r="B101" s="1" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="102" ht="17.25" customHeight="1">
-      <c r="A102" s="9" t="s">
+    <row r="102" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A102" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B102" s="13" t="s">
+      <c r="B102" s="1" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="103" ht="17.25" customHeight="1">
-      <c r="A103" s="14" t="s">
+    <row r="103" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A103" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B103" s="15" t="s">
+      <c r="B103" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="C103" s="10" t="s">
+    </row>
+    <row r="104" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A104" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A105" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="B105" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="C105" s="7" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="104" ht="17.25" customHeight="1">
-      <c r="A104" s="14" t="s">
-        <v>208</v>
-      </c>
-      <c r="B104" s="14" t="s">
-        <v>209</v>
-      </c>
-      <c r="C104" s="10" t="s">
+    <row r="106" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A106" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="B106" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="C106" s="7" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="105" ht="17.25" customHeight="1">
-      <c r="A105" s="14" t="s">
-        <v>210</v>
-      </c>
-      <c r="B105" s="15" t="s">
-        <v>211</v>
-      </c>
-      <c r="C105" s="10" t="s">
+    <row r="107" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A107" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="B107" s="9" t="s">
+        <v>215</v>
+      </c>
+      <c r="C107" s="7" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="106" ht="17.25" customHeight="1">
-      <c r="A106" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="B106" s="15" t="s">
-        <v>213</v>
-      </c>
-      <c r="C106" s="10" t="s">
+    <row r="108" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A108" s="9" t="s">
+        <v>216</v>
+      </c>
+      <c r="B108" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="C108" s="7" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="107" ht="17.25" customHeight="1">
-      <c r="A107" s="14" t="s">
-        <v>214</v>
-      </c>
-      <c r="B107" s="15" t="s">
-        <v>215</v>
-      </c>
-      <c r="C107" s="10" t="s">
+    <row r="109" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A109" s="9" t="s">
+        <v>218</v>
+      </c>
+      <c r="B109" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="C109" s="7" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="108" ht="17.25" customHeight="1">
-      <c r="A108" s="14" t="s">
-        <v>216</v>
-      </c>
-      <c r="B108" s="15" t="s">
-        <v>217</v>
-      </c>
-      <c r="C108" s="10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="109" ht="17.25" customHeight="1">
-      <c r="A109" s="14" t="s">
-        <v>218</v>
-      </c>
-      <c r="B109" s="15" t="s">
-        <v>219</v>
-      </c>
-      <c r="C109" s="10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="110" ht="17.25" customHeight="1">
+    <row r="110" spans="1:3" ht="17.25" customHeight="1">
       <c r="A110" s="9" t="s">
         <v>220</v>
       </c>
-      <c r="B110" s="13" t="s">
+      <c r="B110" s="9" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="111" ht="17.25" customHeight="1">
-      <c r="A111" s="14" t="s">
+      <c r="C110" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A111" s="9" t="s">
         <v>222</v>
       </c>
-      <c r="B111" s="15" t="s">
+      <c r="B111" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="C111" s="10" t="s">
+      <c r="C111" s="7" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="112" ht="17.25" customHeight="1">
-      <c r="A112" s="14" t="s">
+    <row r="112" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A112" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B112" s="15" t="s">
+      <c r="B112" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="C112" s="10" t="s">
+    </row>
+    <row r="113" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A113" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="B113" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="C113" s="7" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="113" ht="17.25" customHeight="1">
-      <c r="A113" s="14" t="s">
-        <v>226</v>
-      </c>
-      <c r="B113" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="C113" s="10" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="114" ht="17.25" customHeight="1">
+    <row r="114" spans="1:3" ht="17.25" customHeight="1">
       <c r="A114" s="9" t="s">
         <v>228</v>
       </c>
       <c r="B114" s="9" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="115" ht="17.25" customHeight="1"/>
-    <row r="116" ht="17.25" customHeight="1"/>
-    <row r="117" ht="17.25" customHeight="1"/>
-    <row r="118" ht="17.25" customHeight="1"/>
-    <row r="119" ht="17.25" customHeight="1"/>
-    <row r="120" ht="17.25" customHeight="1"/>
-    <row r="121" ht="17.25" customHeight="1"/>
-    <row r="122" ht="17.25" customHeight="1"/>
-    <row r="123" ht="17.25" customHeight="1"/>
-    <row r="124" ht="17.25" customHeight="1"/>
-    <row r="125" ht="17.25" customHeight="1"/>
-    <row r="126" ht="17.25" customHeight="1"/>
-    <row r="127" ht="17.25" customHeight="1"/>
-    <row r="128" ht="17.25" customHeight="1"/>
+      <c r="C114" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A115" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="B115" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="C115" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" ht="17.25" customHeight="1"/>
+    <row r="117" spans="1:3" ht="17.25" customHeight="1"/>
+    <row r="118" spans="1:3" ht="17.25" customHeight="1"/>
+    <row r="119" spans="1:3" ht="17.25" customHeight="1"/>
+    <row r="120" spans="1:3" ht="17.25" customHeight="1"/>
+    <row r="121" spans="1:3" ht="17.25" customHeight="1"/>
+    <row r="122" spans="1:3" ht="17.25" customHeight="1"/>
+    <row r="123" spans="1:3" ht="17.25" customHeight="1"/>
+    <row r="124" spans="1:3" ht="17.25" customHeight="1"/>
+    <row r="125" spans="1:3" ht="17.25" customHeight="1"/>
+    <row r="126" spans="1:3" ht="17.25" customHeight="1"/>
+    <row r="127" spans="1:3" ht="17.25" customHeight="1"/>
+    <row r="128" spans="1:3" ht="17.25" customHeight="1"/>
     <row r="129" ht="17.25" customHeight="1"/>
     <row r="130" ht="17.25" customHeight="1"/>
     <row r="131" ht="17.25" customHeight="1"/>
@@ -2924,10 +2948,10 @@
     <row r="993" ht="17.25" customHeight="1"/>
     <row r="994" ht="17.25" customHeight="1"/>
     <row r="995" ht="17.25" customHeight="1"/>
+    <row r="996" ht="17.25" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
@@ -3,20 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="Zo3y2CT06Z9aRkJvrr1FP2fBKanMGUSvILAo2d4duAE="/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="232">
   <si>
     <t>미리 로드할 어드레서블 테이블</t>
   </si>
@@ -364,6 +359,12 @@
   </si>
   <si>
     <t>Jewel_Cone[Cone]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_Jewel_Stone[Cube.058]</t>
+  </si>
+  <si>
+    <t>Jewel_Stone[Cube.058]</t>
   </si>
   <si>
     <t>PreLoadAsset_Material_Lit</t>
@@ -712,7 +713,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -722,7 +723,6 @@
     <font>
       <color theme="1"/>
       <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11.0"/>
@@ -738,6 +738,11 @@
       <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11.0"/>
@@ -798,7 +803,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -807,9 +812,6 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="2" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
     <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -818,21 +820,15 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+      <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf borderId="0" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -845,6 +841,10 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1051,7 +1051,7 @@
     <col customWidth="1" min="1" max="1" width="52.14"/>
     <col customWidth="1" min="2" max="2" width="35.14"/>
     <col customWidth="1" min="3" max="3" width="31.43"/>
-    <col customWidth="1" min="4" max="26" width="9.0"/>
+    <col customWidth="1" min="4" max="6" width="9.0"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.25" customHeight="1">
@@ -1515,10 +1515,10 @@
       </c>
     </row>
     <row r="57" ht="17.25" customHeight="1">
-      <c r="A57" s="7" t="s">
+      <c r="A57" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="B57" s="7" t="s">
+      <c r="B57" s="6" t="s">
         <v>115</v>
       </c>
       <c r="C57" s="2" t="s">
@@ -1526,110 +1526,110 @@
       </c>
     </row>
     <row r="58" ht="17.25" customHeight="1">
-      <c r="A58" s="2" t="s">
+      <c r="A58" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B58" s="8" t="s">
         <v>117</v>
       </c>
+      <c r="C58" s="9" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="59" ht="17.25" customHeight="1">
-      <c r="A59" s="8" t="s">
+      <c r="A59" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B59" s="9" t="s">
+      <c r="B59" s="1" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="60" ht="17.25" customHeight="1">
-      <c r="A60" s="8" t="s">
+      <c r="A60" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B60" s="9" t="s">
+      <c r="B60" s="1" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="61" ht="17.25" customHeight="1">
-      <c r="A61" s="8" t="s">
+      <c r="A61" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B61" s="9" t="s">
+      <c r="B61" s="1" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="62" ht="17.25" customHeight="1">
-      <c r="A62" s="8" t="s">
+      <c r="A62" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B62" s="9" t="s">
+      <c r="B62" s="1" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="63" ht="17.25" customHeight="1">
-      <c r="A63" s="8" t="s">
+      <c r="A63" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B63" s="9" t="s">
+      <c r="B63" s="1" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="64" ht="17.25" customHeight="1">
-      <c r="A64" s="8" t="s">
+      <c r="A64" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B64" s="9" t="s">
+      <c r="B64" s="1" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="65" ht="17.25" customHeight="1">
-      <c r="A65" s="8" t="s">
+      <c r="A65" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B65" s="9" t="s">
+      <c r="B65" s="1" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="66" ht="17.25" customHeight="1">
-      <c r="A66" s="8" t="s">
+      <c r="A66" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B66" s="9" t="s">
+      <c r="B66" s="1" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="67" ht="17.25" customHeight="1">
-      <c r="A67" s="8" t="s">
+      <c r="A67" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B67" s="9" t="s">
+      <c r="B67" s="1" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="68" ht="17.25" customHeight="1">
-      <c r="A68" s="9" t="s">
+      <c r="A68" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B68" s="9" t="s">
+      <c r="B68" s="1" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="69" ht="17.25" customHeight="1">
-      <c r="A69" s="9" t="s">
+      <c r="A69" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B69" s="9" t="s">
+      <c r="B69" s="1" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="70" ht="17.25" customHeight="1">
-      <c r="A70" s="10" t="s">
+      <c r="A70" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B70" s="10" t="s">
+      <c r="B70" s="1" t="s">
         <v>141</v>
-      </c>
-      <c r="C70" s="10" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="71" ht="17.25" customHeight="1">
@@ -1683,7 +1683,9 @@
       <c r="B75" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="C75" s="11"/>
+      <c r="C75" s="10" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="76" ht="17.25" customHeight="1">
       <c r="A76" s="10" t="s">
@@ -1692,7 +1694,7 @@
       <c r="B76" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="C76" s="11"/>
+      <c r="C76" s="10"/>
     </row>
     <row r="77" ht="17.25" customHeight="1">
       <c r="A77" s="10" t="s">
@@ -1701,7 +1703,7 @@
       <c r="B77" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="C77" s="11"/>
+      <c r="C77" s="10"/>
     </row>
     <row r="78" ht="17.25" customHeight="1">
       <c r="A78" s="10" t="s">
@@ -1710,7 +1712,7 @@
       <c r="B78" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="C78" s="11"/>
+      <c r="C78" s="10"/>
     </row>
     <row r="79" ht="17.25" customHeight="1">
       <c r="A79" s="10" t="s">
@@ -1719,7 +1721,7 @@
       <c r="B79" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="C79" s="11"/>
+      <c r="C79" s="10"/>
     </row>
     <row r="80" ht="17.25" customHeight="1">
       <c r="A80" s="10" t="s">
@@ -1728,7 +1730,7 @@
       <c r="B80" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="C80" s="11"/>
+      <c r="C80" s="10"/>
     </row>
     <row r="81" ht="17.25" customHeight="1">
       <c r="A81" s="10" t="s">
@@ -1737,7 +1739,7 @@
       <c r="B81" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="C81" s="11"/>
+      <c r="C81" s="10"/>
     </row>
     <row r="82" ht="17.25" customHeight="1">
       <c r="A82" s="10" t="s">
@@ -1746,7 +1748,7 @@
       <c r="B82" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="C82" s="11"/>
+      <c r="C82" s="10"/>
     </row>
     <row r="83" ht="17.25" customHeight="1">
       <c r="A83" s="10" t="s">
@@ -1755,184 +1757,182 @@
       <c r="B83" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="C83" s="11"/>
+      <c r="C83" s="10"/>
     </row>
     <row r="84" ht="17.25" customHeight="1">
-      <c r="A84" s="9" t="s">
+      <c r="A84" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="B84" s="9" t="s">
+      <c r="B84" s="10" t="s">
         <v>169</v>
       </c>
+      <c r="C84" s="10"/>
     </row>
     <row r="85" ht="17.25" customHeight="1">
-      <c r="A85" s="9" t="s">
+      <c r="A85" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="B85" s="9" t="s">
+      <c r="B85" s="1" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="86" ht="17.25" customHeight="1">
-      <c r="A86" s="9" t="s">
+      <c r="A86" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B86" s="9" t="s">
+      <c r="B86" s="1" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="87" ht="17.25" customHeight="1">
-      <c r="A87" s="9" t="s">
+      <c r="A87" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B87" s="9" t="s">
+      <c r="B87" s="1" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="88" ht="17.25" customHeight="1">
-      <c r="A88" s="9" t="s">
+      <c r="A88" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B88" s="9" t="s">
+      <c r="B88" s="1" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="89" ht="17.25" customHeight="1">
-      <c r="A89" s="10" t="s">
+      <c r="A89" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B89" s="10" t="s">
+      <c r="B89" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="C89" s="11"/>
     </row>
     <row r="90" ht="17.25" customHeight="1">
       <c r="A90" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="B90" s="12" t="s">
+      <c r="B90" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="C90" s="10" t="s">
-        <v>97</v>
-      </c>
+      <c r="C90" s="10"/>
     </row>
     <row r="91" ht="17.25" customHeight="1">
       <c r="A91" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="B91" s="12" t="s">
+      <c r="B91" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="C91" s="11"/>
+      <c r="C91" s="10" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="92" ht="17.25" customHeight="1">
       <c r="A92" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="B92" s="12" t="s">
+      <c r="B92" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="C92" s="11"/>
+      <c r="C92" s="10"/>
     </row>
     <row r="93" ht="17.25" customHeight="1">
       <c r="A93" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="B93" s="12" t="s">
+      <c r="B93" s="11" t="s">
         <v>187</v>
       </c>
-      <c r="C93" s="11"/>
+      <c r="C93" s="10"/>
     </row>
     <row r="94" ht="17.25" customHeight="1">
       <c r="A94" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="B94" s="12" t="s">
+      <c r="B94" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="C94" s="11"/>
+      <c r="C94" s="10"/>
     </row>
     <row r="95" ht="17.25" customHeight="1">
-      <c r="A95" s="9" t="s">
+      <c r="A95" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="B95" s="9" t="s">
+      <c r="B95" s="11" t="s">
         <v>191</v>
       </c>
+      <c r="C95" s="10"/>
     </row>
     <row r="96" ht="17.25" customHeight="1">
-      <c r="A96" s="9" t="s">
+      <c r="A96" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="B96" s="9" t="s">
+      <c r="B96" s="1" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="97" ht="17.25" customHeight="1">
-      <c r="A97" s="9" t="s">
+      <c r="A97" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="B97" s="9" t="s">
+      <c r="B97" s="1" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="98" ht="17.25" customHeight="1">
-      <c r="A98" s="9" t="s">
+      <c r="A98" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="B98" s="9" t="s">
+      <c r="B98" s="1" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="99" ht="17.25" customHeight="1">
-      <c r="A99" s="9" t="s">
+      <c r="A99" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="B99" s="9" t="s">
+      <c r="B99" s="1" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="100" ht="17.25" customHeight="1">
-      <c r="A100" s="9" t="s">
+      <c r="A100" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B100" s="9" t="s">
+      <c r="B100" s="1" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="101" ht="17.25" customHeight="1">
-      <c r="A101" s="9" t="s">
+      <c r="A101" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B101" s="9" t="s">
+      <c r="B101" s="1" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="102" ht="17.25" customHeight="1">
-      <c r="A102" s="9" t="s">
+      <c r="A102" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B102" s="13" t="s">
+      <c r="B102" s="1" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="103" ht="17.25" customHeight="1">
-      <c r="A103" s="14" t="s">
+      <c r="A103" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B103" s="15" t="s">
+      <c r="B103" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="C103" s="10" t="s">
-        <v>97</v>
-      </c>
     </row>
     <row r="104" ht="17.25" customHeight="1">
-      <c r="A104" s="14" t="s">
+      <c r="A104" s="12" t="s">
         <v>208</v>
       </c>
-      <c r="B104" s="14" t="s">
+      <c r="B104" s="12" t="s">
         <v>209</v>
       </c>
       <c r="C104" s="10" t="s">
@@ -1940,10 +1940,10 @@
       </c>
     </row>
     <row r="105" ht="17.25" customHeight="1">
-      <c r="A105" s="14" t="s">
+      <c r="A105" s="12" t="s">
         <v>210</v>
       </c>
-      <c r="B105" s="15" t="s">
+      <c r="B105" s="12" t="s">
         <v>211</v>
       </c>
       <c r="C105" s="10" t="s">
@@ -1951,10 +1951,10 @@
       </c>
     </row>
     <row r="106" ht="17.25" customHeight="1">
-      <c r="A106" s="14" t="s">
+      <c r="A106" s="12" t="s">
         <v>212</v>
       </c>
-      <c r="B106" s="15" t="s">
+      <c r="B106" s="12" t="s">
         <v>213</v>
       </c>
       <c r="C106" s="10" t="s">
@@ -1962,10 +1962,10 @@
       </c>
     </row>
     <row r="107" ht="17.25" customHeight="1">
-      <c r="A107" s="14" t="s">
+      <c r="A107" s="12" t="s">
         <v>214</v>
       </c>
-      <c r="B107" s="15" t="s">
+      <c r="B107" s="12" t="s">
         <v>215</v>
       </c>
       <c r="C107" s="10" t="s">
@@ -1973,10 +1973,10 @@
       </c>
     </row>
     <row r="108" ht="17.25" customHeight="1">
-      <c r="A108" s="14" t="s">
+      <c r="A108" s="12" t="s">
         <v>216</v>
       </c>
-      <c r="B108" s="15" t="s">
+      <c r="B108" s="12" t="s">
         <v>217</v>
       </c>
       <c r="C108" s="10" t="s">
@@ -1984,10 +1984,10 @@
       </c>
     </row>
     <row r="109" ht="17.25" customHeight="1">
-      <c r="A109" s="14" t="s">
+      <c r="A109" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="B109" s="15" t="s">
+      <c r="B109" s="12" t="s">
         <v>219</v>
       </c>
       <c r="C109" s="10" t="s">
@@ -1995,29 +1995,29 @@
       </c>
     </row>
     <row r="110" ht="17.25" customHeight="1">
-      <c r="A110" s="9" t="s">
+      <c r="A110" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="B110" s="13" t="s">
+      <c r="B110" s="12" t="s">
         <v>221</v>
       </c>
+      <c r="C110" s="10" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="111" ht="17.25" customHeight="1">
-      <c r="A111" s="14" t="s">
+      <c r="A111" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="B111" s="15" t="s">
+      <c r="B111" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="C111" s="10" t="s">
-        <v>97</v>
-      </c>
     </row>
     <row r="112" ht="17.25" customHeight="1">
-      <c r="A112" s="14" t="s">
+      <c r="A112" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="B112" s="15" t="s">
+      <c r="B112" s="12" t="s">
         <v>225</v>
       </c>
       <c r="C112" s="10" t="s">
@@ -2025,10 +2025,10 @@
       </c>
     </row>
     <row r="113" ht="17.25" customHeight="1">
-      <c r="A113" s="14" t="s">
+      <c r="A113" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="B113" s="13" t="s">
+      <c r="B113" s="12" t="s">
         <v>227</v>
       </c>
       <c r="C113" s="10" t="s">
@@ -2036,14 +2036,24 @@
       </c>
     </row>
     <row r="114" ht="17.25" customHeight="1">
-      <c r="A114" s="9" t="s">
+      <c r="A114" s="12" t="s">
         <v>228</v>
       </c>
-      <c r="B114" s="9" t="s">
+      <c r="B114" s="4" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="115" ht="17.25" customHeight="1"/>
+      <c r="C114" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="115" ht="17.25" customHeight="1">
+      <c r="A115" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>231</v>
+      </c>
+    </row>
     <row r="116" ht="17.25" customHeight="1"/>
     <row r="117" ht="17.25" customHeight="1"/>
     <row r="118" ht="17.25" customHeight="1"/>
@@ -2244,686 +2254,692 @@
     <row r="313" ht="17.25" customHeight="1"/>
     <row r="314" ht="17.25" customHeight="1"/>
     <row r="315" ht="17.25" customHeight="1"/>
-    <row r="316" ht="17.25" customHeight="1"/>
-    <row r="317" ht="17.25" customHeight="1"/>
-    <row r="318" ht="17.25" customHeight="1"/>
-    <row r="319" ht="17.25" customHeight="1"/>
-    <row r="320" ht="17.25" customHeight="1"/>
-    <row r="321" ht="17.25" customHeight="1"/>
-    <row r="322" ht="17.25" customHeight="1"/>
-    <row r="323" ht="17.25" customHeight="1"/>
-    <row r="324" ht="17.25" customHeight="1"/>
-    <row r="325" ht="17.25" customHeight="1"/>
-    <row r="326" ht="17.25" customHeight="1"/>
-    <row r="327" ht="17.25" customHeight="1"/>
-    <row r="328" ht="17.25" customHeight="1"/>
-    <row r="329" ht="17.25" customHeight="1"/>
-    <row r="330" ht="17.25" customHeight="1"/>
-    <row r="331" ht="17.25" customHeight="1"/>
-    <row r="332" ht="17.25" customHeight="1"/>
-    <row r="333" ht="17.25" customHeight="1"/>
-    <row r="334" ht="17.25" customHeight="1"/>
-    <row r="335" ht="17.25" customHeight="1"/>
-    <row r="336" ht="17.25" customHeight="1"/>
-    <row r="337" ht="17.25" customHeight="1"/>
-    <row r="338" ht="17.25" customHeight="1"/>
-    <row r="339" ht="17.25" customHeight="1"/>
-    <row r="340" ht="17.25" customHeight="1"/>
-    <row r="341" ht="17.25" customHeight="1"/>
-    <row r="342" ht="17.25" customHeight="1"/>
-    <row r="343" ht="17.25" customHeight="1"/>
-    <row r="344" ht="17.25" customHeight="1"/>
-    <row r="345" ht="17.25" customHeight="1"/>
-    <row r="346" ht="17.25" customHeight="1"/>
-    <row r="347" ht="17.25" customHeight="1"/>
-    <row r="348" ht="17.25" customHeight="1"/>
-    <row r="349" ht="17.25" customHeight="1"/>
-    <row r="350" ht="17.25" customHeight="1"/>
-    <row r="351" ht="17.25" customHeight="1"/>
-    <row r="352" ht="17.25" customHeight="1"/>
-    <row r="353" ht="17.25" customHeight="1"/>
-    <row r="354" ht="17.25" customHeight="1"/>
-    <row r="355" ht="17.25" customHeight="1"/>
-    <row r="356" ht="17.25" customHeight="1"/>
-    <row r="357" ht="17.25" customHeight="1"/>
-    <row r="358" ht="17.25" customHeight="1"/>
-    <row r="359" ht="17.25" customHeight="1"/>
-    <row r="360" ht="17.25" customHeight="1"/>
-    <row r="361" ht="17.25" customHeight="1"/>
-    <row r="362" ht="17.25" customHeight="1"/>
-    <row r="363" ht="17.25" customHeight="1"/>
-    <row r="364" ht="17.25" customHeight="1"/>
-    <row r="365" ht="17.25" customHeight="1"/>
-    <row r="366" ht="17.25" customHeight="1"/>
-    <row r="367" ht="17.25" customHeight="1"/>
-    <row r="368" ht="17.25" customHeight="1"/>
-    <row r="369" ht="17.25" customHeight="1"/>
-    <row r="370" ht="17.25" customHeight="1"/>
-    <row r="371" ht="17.25" customHeight="1"/>
-    <row r="372" ht="17.25" customHeight="1"/>
-    <row r="373" ht="17.25" customHeight="1"/>
-    <row r="374" ht="17.25" customHeight="1"/>
-    <row r="375" ht="17.25" customHeight="1"/>
-    <row r="376" ht="17.25" customHeight="1"/>
-    <row r="377" ht="17.25" customHeight="1"/>
-    <row r="378" ht="17.25" customHeight="1"/>
-    <row r="379" ht="17.25" customHeight="1"/>
-    <row r="380" ht="17.25" customHeight="1"/>
-    <row r="381" ht="17.25" customHeight="1"/>
-    <row r="382" ht="17.25" customHeight="1"/>
-    <row r="383" ht="17.25" customHeight="1"/>
-    <row r="384" ht="17.25" customHeight="1"/>
-    <row r="385" ht="17.25" customHeight="1"/>
-    <row r="386" ht="17.25" customHeight="1"/>
-    <row r="387" ht="17.25" customHeight="1"/>
-    <row r="388" ht="17.25" customHeight="1"/>
-    <row r="389" ht="17.25" customHeight="1"/>
-    <row r="390" ht="17.25" customHeight="1"/>
-    <row r="391" ht="17.25" customHeight="1"/>
-    <row r="392" ht="17.25" customHeight="1"/>
-    <row r="393" ht="17.25" customHeight="1"/>
-    <row r="394" ht="17.25" customHeight="1"/>
-    <row r="395" ht="17.25" customHeight="1"/>
-    <row r="396" ht="17.25" customHeight="1"/>
-    <row r="397" ht="17.25" customHeight="1"/>
-    <row r="398" ht="17.25" customHeight="1"/>
-    <row r="399" ht="17.25" customHeight="1"/>
-    <row r="400" ht="17.25" customHeight="1"/>
-    <row r="401" ht="17.25" customHeight="1"/>
-    <row r="402" ht="17.25" customHeight="1"/>
-    <row r="403" ht="17.25" customHeight="1"/>
-    <row r="404" ht="17.25" customHeight="1"/>
-    <row r="405" ht="17.25" customHeight="1"/>
-    <row r="406" ht="17.25" customHeight="1"/>
-    <row r="407" ht="17.25" customHeight="1"/>
-    <row r="408" ht="17.25" customHeight="1"/>
-    <row r="409" ht="17.25" customHeight="1"/>
-    <row r="410" ht="17.25" customHeight="1"/>
-    <row r="411" ht="17.25" customHeight="1"/>
-    <row r="412" ht="17.25" customHeight="1"/>
-    <row r="413" ht="17.25" customHeight="1"/>
-    <row r="414" ht="17.25" customHeight="1"/>
-    <row r="415" ht="17.25" customHeight="1"/>
-    <row r="416" ht="17.25" customHeight="1"/>
-    <row r="417" ht="17.25" customHeight="1"/>
-    <row r="418" ht="17.25" customHeight="1"/>
-    <row r="419" ht="17.25" customHeight="1"/>
-    <row r="420" ht="17.25" customHeight="1"/>
-    <row r="421" ht="17.25" customHeight="1"/>
-    <row r="422" ht="17.25" customHeight="1"/>
-    <row r="423" ht="17.25" customHeight="1"/>
-    <row r="424" ht="17.25" customHeight="1"/>
-    <row r="425" ht="17.25" customHeight="1"/>
-    <row r="426" ht="17.25" customHeight="1"/>
-    <row r="427" ht="17.25" customHeight="1"/>
-    <row r="428" ht="17.25" customHeight="1"/>
-    <row r="429" ht="17.25" customHeight="1"/>
-    <row r="430" ht="17.25" customHeight="1"/>
-    <row r="431" ht="17.25" customHeight="1"/>
-    <row r="432" ht="17.25" customHeight="1"/>
-    <row r="433" ht="17.25" customHeight="1"/>
-    <row r="434" ht="17.25" customHeight="1"/>
-    <row r="435" ht="17.25" customHeight="1"/>
-    <row r="436" ht="17.25" customHeight="1"/>
-    <row r="437" ht="17.25" customHeight="1"/>
-    <row r="438" ht="17.25" customHeight="1"/>
-    <row r="439" ht="17.25" customHeight="1"/>
-    <row r="440" ht="17.25" customHeight="1"/>
-    <row r="441" ht="17.25" customHeight="1"/>
-    <row r="442" ht="17.25" customHeight="1"/>
-    <row r="443" ht="17.25" customHeight="1"/>
-    <row r="444" ht="17.25" customHeight="1"/>
-    <row r="445" ht="17.25" customHeight="1"/>
-    <row r="446" ht="17.25" customHeight="1"/>
-    <row r="447" ht="17.25" customHeight="1"/>
-    <row r="448" ht="17.25" customHeight="1"/>
-    <row r="449" ht="17.25" customHeight="1"/>
-    <row r="450" ht="17.25" customHeight="1"/>
-    <row r="451" ht="17.25" customHeight="1"/>
-    <row r="452" ht="17.25" customHeight="1"/>
-    <row r="453" ht="17.25" customHeight="1"/>
-    <row r="454" ht="17.25" customHeight="1"/>
-    <row r="455" ht="17.25" customHeight="1"/>
-    <row r="456" ht="17.25" customHeight="1"/>
-    <row r="457" ht="17.25" customHeight="1"/>
-    <row r="458" ht="17.25" customHeight="1"/>
-    <row r="459" ht="17.25" customHeight="1"/>
-    <row r="460" ht="17.25" customHeight="1"/>
-    <row r="461" ht="17.25" customHeight="1"/>
-    <row r="462" ht="17.25" customHeight="1"/>
-    <row r="463" ht="17.25" customHeight="1"/>
-    <row r="464" ht="17.25" customHeight="1"/>
-    <row r="465" ht="17.25" customHeight="1"/>
-    <row r="466" ht="17.25" customHeight="1"/>
-    <row r="467" ht="17.25" customHeight="1"/>
-    <row r="468" ht="17.25" customHeight="1"/>
-    <row r="469" ht="17.25" customHeight="1"/>
-    <row r="470" ht="17.25" customHeight="1"/>
-    <row r="471" ht="17.25" customHeight="1"/>
-    <row r="472" ht="17.25" customHeight="1"/>
-    <row r="473" ht="17.25" customHeight="1"/>
-    <row r="474" ht="17.25" customHeight="1"/>
-    <row r="475" ht="17.25" customHeight="1"/>
-    <row r="476" ht="17.25" customHeight="1"/>
-    <row r="477" ht="17.25" customHeight="1"/>
-    <row r="478" ht="17.25" customHeight="1"/>
-    <row r="479" ht="17.25" customHeight="1"/>
-    <row r="480" ht="17.25" customHeight="1"/>
-    <row r="481" ht="17.25" customHeight="1"/>
-    <row r="482" ht="17.25" customHeight="1"/>
-    <row r="483" ht="17.25" customHeight="1"/>
-    <row r="484" ht="17.25" customHeight="1"/>
-    <row r="485" ht="17.25" customHeight="1"/>
-    <row r="486" ht="17.25" customHeight="1"/>
-    <row r="487" ht="17.25" customHeight="1"/>
-    <row r="488" ht="17.25" customHeight="1"/>
-    <row r="489" ht="17.25" customHeight="1"/>
-    <row r="490" ht="17.25" customHeight="1"/>
-    <row r="491" ht="17.25" customHeight="1"/>
-    <row r="492" ht="17.25" customHeight="1"/>
-    <row r="493" ht="17.25" customHeight="1"/>
-    <row r="494" ht="17.25" customHeight="1"/>
-    <row r="495" ht="17.25" customHeight="1"/>
-    <row r="496" ht="17.25" customHeight="1"/>
-    <row r="497" ht="17.25" customHeight="1"/>
-    <row r="498" ht="17.25" customHeight="1"/>
-    <row r="499" ht="17.25" customHeight="1"/>
-    <row r="500" ht="17.25" customHeight="1"/>
-    <row r="501" ht="17.25" customHeight="1"/>
-    <row r="502" ht="17.25" customHeight="1"/>
-    <row r="503" ht="17.25" customHeight="1"/>
-    <row r="504" ht="17.25" customHeight="1"/>
-    <row r="505" ht="17.25" customHeight="1"/>
-    <row r="506" ht="17.25" customHeight="1"/>
-    <row r="507" ht="17.25" customHeight="1"/>
-    <row r="508" ht="17.25" customHeight="1"/>
-    <row r="509" ht="17.25" customHeight="1"/>
-    <row r="510" ht="17.25" customHeight="1"/>
-    <row r="511" ht="17.25" customHeight="1"/>
-    <row r="512" ht="17.25" customHeight="1"/>
-    <row r="513" ht="17.25" customHeight="1"/>
-    <row r="514" ht="17.25" customHeight="1"/>
-    <row r="515" ht="17.25" customHeight="1"/>
-    <row r="516" ht="17.25" customHeight="1"/>
-    <row r="517" ht="17.25" customHeight="1"/>
-    <row r="518" ht="17.25" customHeight="1"/>
-    <row r="519" ht="17.25" customHeight="1"/>
-    <row r="520" ht="17.25" customHeight="1"/>
-    <row r="521" ht="17.25" customHeight="1"/>
-    <row r="522" ht="17.25" customHeight="1"/>
-    <row r="523" ht="17.25" customHeight="1"/>
-    <row r="524" ht="17.25" customHeight="1"/>
-    <row r="525" ht="17.25" customHeight="1"/>
-    <row r="526" ht="17.25" customHeight="1"/>
-    <row r="527" ht="17.25" customHeight="1"/>
-    <row r="528" ht="17.25" customHeight="1"/>
-    <row r="529" ht="17.25" customHeight="1"/>
-    <row r="530" ht="17.25" customHeight="1"/>
-    <row r="531" ht="17.25" customHeight="1"/>
-    <row r="532" ht="17.25" customHeight="1"/>
-    <row r="533" ht="17.25" customHeight="1"/>
-    <row r="534" ht="17.25" customHeight="1"/>
-    <row r="535" ht="17.25" customHeight="1"/>
-    <row r="536" ht="17.25" customHeight="1"/>
-    <row r="537" ht="17.25" customHeight="1"/>
-    <row r="538" ht="17.25" customHeight="1"/>
-    <row r="539" ht="17.25" customHeight="1"/>
-    <row r="540" ht="17.25" customHeight="1"/>
-    <row r="541" ht="17.25" customHeight="1"/>
-    <row r="542" ht="17.25" customHeight="1"/>
-    <row r="543" ht="17.25" customHeight="1"/>
-    <row r="544" ht="17.25" customHeight="1"/>
-    <row r="545" ht="17.25" customHeight="1"/>
-    <row r="546" ht="17.25" customHeight="1"/>
-    <row r="547" ht="17.25" customHeight="1"/>
-    <row r="548" ht="17.25" customHeight="1"/>
-    <row r="549" ht="17.25" customHeight="1"/>
-    <row r="550" ht="17.25" customHeight="1"/>
-    <row r="551" ht="17.25" customHeight="1"/>
-    <row r="552" ht="17.25" customHeight="1"/>
-    <row r="553" ht="17.25" customHeight="1"/>
-    <row r="554" ht="17.25" customHeight="1"/>
-    <row r="555" ht="17.25" customHeight="1"/>
-    <row r="556" ht="17.25" customHeight="1"/>
-    <row r="557" ht="17.25" customHeight="1"/>
-    <row r="558" ht="17.25" customHeight="1"/>
-    <row r="559" ht="17.25" customHeight="1"/>
-    <row r="560" ht="17.25" customHeight="1"/>
-    <row r="561" ht="17.25" customHeight="1"/>
-    <row r="562" ht="17.25" customHeight="1"/>
-    <row r="563" ht="17.25" customHeight="1"/>
-    <row r="564" ht="17.25" customHeight="1"/>
-    <row r="565" ht="17.25" customHeight="1"/>
-    <row r="566" ht="17.25" customHeight="1"/>
-    <row r="567" ht="17.25" customHeight="1"/>
-    <row r="568" ht="17.25" customHeight="1"/>
-    <row r="569" ht="17.25" customHeight="1"/>
-    <row r="570" ht="17.25" customHeight="1"/>
-    <row r="571" ht="17.25" customHeight="1"/>
-    <row r="572" ht="17.25" customHeight="1"/>
-    <row r="573" ht="17.25" customHeight="1"/>
-    <row r="574" ht="17.25" customHeight="1"/>
-    <row r="575" ht="17.25" customHeight="1"/>
-    <row r="576" ht="17.25" customHeight="1"/>
-    <row r="577" ht="17.25" customHeight="1"/>
-    <row r="578" ht="17.25" customHeight="1"/>
-    <row r="579" ht="17.25" customHeight="1"/>
-    <row r="580" ht="17.25" customHeight="1"/>
-    <row r="581" ht="17.25" customHeight="1"/>
-    <row r="582" ht="17.25" customHeight="1"/>
-    <row r="583" ht="17.25" customHeight="1"/>
-    <row r="584" ht="17.25" customHeight="1"/>
-    <row r="585" ht="17.25" customHeight="1"/>
-    <row r="586" ht="17.25" customHeight="1"/>
-    <row r="587" ht="17.25" customHeight="1"/>
-    <row r="588" ht="17.25" customHeight="1"/>
-    <row r="589" ht="17.25" customHeight="1"/>
-    <row r="590" ht="17.25" customHeight="1"/>
-    <row r="591" ht="17.25" customHeight="1"/>
-    <row r="592" ht="17.25" customHeight="1"/>
-    <row r="593" ht="17.25" customHeight="1"/>
-    <row r="594" ht="17.25" customHeight="1"/>
-    <row r="595" ht="17.25" customHeight="1"/>
-    <row r="596" ht="17.25" customHeight="1"/>
-    <row r="597" ht="17.25" customHeight="1"/>
-    <row r="598" ht="17.25" customHeight="1"/>
-    <row r="599" ht="17.25" customHeight="1"/>
-    <row r="600" ht="17.25" customHeight="1"/>
-    <row r="601" ht="17.25" customHeight="1"/>
-    <row r="602" ht="17.25" customHeight="1"/>
-    <row r="603" ht="17.25" customHeight="1"/>
-    <row r="604" ht="17.25" customHeight="1"/>
-    <row r="605" ht="17.25" customHeight="1"/>
-    <row r="606" ht="17.25" customHeight="1"/>
-    <row r="607" ht="17.25" customHeight="1"/>
-    <row r="608" ht="17.25" customHeight="1"/>
-    <row r="609" ht="17.25" customHeight="1"/>
-    <row r="610" ht="17.25" customHeight="1"/>
-    <row r="611" ht="17.25" customHeight="1"/>
-    <row r="612" ht="17.25" customHeight="1"/>
-    <row r="613" ht="17.25" customHeight="1"/>
-    <row r="614" ht="17.25" customHeight="1"/>
-    <row r="615" ht="17.25" customHeight="1"/>
-    <row r="616" ht="17.25" customHeight="1"/>
-    <row r="617" ht="17.25" customHeight="1"/>
-    <row r="618" ht="17.25" customHeight="1"/>
-    <row r="619" ht="17.25" customHeight="1"/>
-    <row r="620" ht="17.25" customHeight="1"/>
-    <row r="621" ht="17.25" customHeight="1"/>
-    <row r="622" ht="17.25" customHeight="1"/>
-    <row r="623" ht="17.25" customHeight="1"/>
-    <row r="624" ht="17.25" customHeight="1"/>
-    <row r="625" ht="17.25" customHeight="1"/>
-    <row r="626" ht="17.25" customHeight="1"/>
-    <row r="627" ht="17.25" customHeight="1"/>
-    <row r="628" ht="17.25" customHeight="1"/>
-    <row r="629" ht="17.25" customHeight="1"/>
-    <row r="630" ht="17.25" customHeight="1"/>
-    <row r="631" ht="17.25" customHeight="1"/>
-    <row r="632" ht="17.25" customHeight="1"/>
-    <row r="633" ht="17.25" customHeight="1"/>
-    <row r="634" ht="17.25" customHeight="1"/>
-    <row r="635" ht="17.25" customHeight="1"/>
-    <row r="636" ht="17.25" customHeight="1"/>
-    <row r="637" ht="17.25" customHeight="1"/>
-    <row r="638" ht="17.25" customHeight="1"/>
-    <row r="639" ht="17.25" customHeight="1"/>
-    <row r="640" ht="17.25" customHeight="1"/>
-    <row r="641" ht="17.25" customHeight="1"/>
-    <row r="642" ht="17.25" customHeight="1"/>
-    <row r="643" ht="17.25" customHeight="1"/>
-    <row r="644" ht="17.25" customHeight="1"/>
-    <row r="645" ht="17.25" customHeight="1"/>
-    <row r="646" ht="17.25" customHeight="1"/>
-    <row r="647" ht="17.25" customHeight="1"/>
-    <row r="648" ht="17.25" customHeight="1"/>
-    <row r="649" ht="17.25" customHeight="1"/>
-    <row r="650" ht="17.25" customHeight="1"/>
-    <row r="651" ht="17.25" customHeight="1"/>
-    <row r="652" ht="17.25" customHeight="1"/>
-    <row r="653" ht="17.25" customHeight="1"/>
-    <row r="654" ht="17.25" customHeight="1"/>
-    <row r="655" ht="17.25" customHeight="1"/>
-    <row r="656" ht="17.25" customHeight="1"/>
-    <row r="657" ht="17.25" customHeight="1"/>
-    <row r="658" ht="17.25" customHeight="1"/>
-    <row r="659" ht="17.25" customHeight="1"/>
-    <row r="660" ht="17.25" customHeight="1"/>
-    <row r="661" ht="17.25" customHeight="1"/>
-    <row r="662" ht="17.25" customHeight="1"/>
-    <row r="663" ht="17.25" customHeight="1"/>
-    <row r="664" ht="17.25" customHeight="1"/>
-    <row r="665" ht="17.25" customHeight="1"/>
-    <row r="666" ht="17.25" customHeight="1"/>
-    <row r="667" ht="17.25" customHeight="1"/>
-    <row r="668" ht="17.25" customHeight="1"/>
-    <row r="669" ht="17.25" customHeight="1"/>
-    <row r="670" ht="17.25" customHeight="1"/>
-    <row r="671" ht="17.25" customHeight="1"/>
-    <row r="672" ht="17.25" customHeight="1"/>
-    <row r="673" ht="17.25" customHeight="1"/>
-    <row r="674" ht="17.25" customHeight="1"/>
-    <row r="675" ht="17.25" customHeight="1"/>
-    <row r="676" ht="17.25" customHeight="1"/>
-    <row r="677" ht="17.25" customHeight="1"/>
-    <row r="678" ht="17.25" customHeight="1"/>
-    <row r="679" ht="17.25" customHeight="1"/>
-    <row r="680" ht="17.25" customHeight="1"/>
-    <row r="681" ht="17.25" customHeight="1"/>
-    <row r="682" ht="17.25" customHeight="1"/>
-    <row r="683" ht="17.25" customHeight="1"/>
-    <row r="684" ht="17.25" customHeight="1"/>
-    <row r="685" ht="17.25" customHeight="1"/>
-    <row r="686" ht="17.25" customHeight="1"/>
-    <row r="687" ht="17.25" customHeight="1"/>
-    <row r="688" ht="17.25" customHeight="1"/>
-    <row r="689" ht="17.25" customHeight="1"/>
-    <row r="690" ht="17.25" customHeight="1"/>
-    <row r="691" ht="17.25" customHeight="1"/>
-    <row r="692" ht="17.25" customHeight="1"/>
-    <row r="693" ht="17.25" customHeight="1"/>
-    <row r="694" ht="17.25" customHeight="1"/>
-    <row r="695" ht="17.25" customHeight="1"/>
-    <row r="696" ht="17.25" customHeight="1"/>
-    <row r="697" ht="17.25" customHeight="1"/>
-    <row r="698" ht="17.25" customHeight="1"/>
-    <row r="699" ht="17.25" customHeight="1"/>
-    <row r="700" ht="17.25" customHeight="1"/>
-    <row r="701" ht="17.25" customHeight="1"/>
-    <row r="702" ht="17.25" customHeight="1"/>
-    <row r="703" ht="17.25" customHeight="1"/>
-    <row r="704" ht="17.25" customHeight="1"/>
-    <row r="705" ht="17.25" customHeight="1"/>
-    <row r="706" ht="17.25" customHeight="1"/>
-    <row r="707" ht="17.25" customHeight="1"/>
-    <row r="708" ht="17.25" customHeight="1"/>
-    <row r="709" ht="17.25" customHeight="1"/>
-    <row r="710" ht="17.25" customHeight="1"/>
-    <row r="711" ht="17.25" customHeight="1"/>
-    <row r="712" ht="17.25" customHeight="1"/>
-    <row r="713" ht="17.25" customHeight="1"/>
-    <row r="714" ht="17.25" customHeight="1"/>
-    <row r="715" ht="17.25" customHeight="1"/>
-    <row r="716" ht="17.25" customHeight="1"/>
-    <row r="717" ht="17.25" customHeight="1"/>
-    <row r="718" ht="17.25" customHeight="1"/>
-    <row r="719" ht="17.25" customHeight="1"/>
-    <row r="720" ht="17.25" customHeight="1"/>
-    <row r="721" ht="17.25" customHeight="1"/>
-    <row r="722" ht="17.25" customHeight="1"/>
-    <row r="723" ht="17.25" customHeight="1"/>
-    <row r="724" ht="17.25" customHeight="1"/>
-    <row r="725" ht="17.25" customHeight="1"/>
-    <row r="726" ht="17.25" customHeight="1"/>
-    <row r="727" ht="17.25" customHeight="1"/>
-    <row r="728" ht="17.25" customHeight="1"/>
-    <row r="729" ht="17.25" customHeight="1"/>
-    <row r="730" ht="17.25" customHeight="1"/>
-    <row r="731" ht="17.25" customHeight="1"/>
-    <row r="732" ht="17.25" customHeight="1"/>
-    <row r="733" ht="17.25" customHeight="1"/>
-    <row r="734" ht="17.25" customHeight="1"/>
-    <row r="735" ht="17.25" customHeight="1"/>
-    <row r="736" ht="17.25" customHeight="1"/>
-    <row r="737" ht="17.25" customHeight="1"/>
-    <row r="738" ht="17.25" customHeight="1"/>
-    <row r="739" ht="17.25" customHeight="1"/>
-    <row r="740" ht="17.25" customHeight="1"/>
-    <row r="741" ht="17.25" customHeight="1"/>
-    <row r="742" ht="17.25" customHeight="1"/>
-    <row r="743" ht="17.25" customHeight="1"/>
-    <row r="744" ht="17.25" customHeight="1"/>
-    <row r="745" ht="17.25" customHeight="1"/>
-    <row r="746" ht="17.25" customHeight="1"/>
-    <row r="747" ht="17.25" customHeight="1"/>
-    <row r="748" ht="17.25" customHeight="1"/>
-    <row r="749" ht="17.25" customHeight="1"/>
-    <row r="750" ht="17.25" customHeight="1"/>
-    <row r="751" ht="17.25" customHeight="1"/>
-    <row r="752" ht="17.25" customHeight="1"/>
-    <row r="753" ht="17.25" customHeight="1"/>
-    <row r="754" ht="17.25" customHeight="1"/>
-    <row r="755" ht="17.25" customHeight="1"/>
-    <row r="756" ht="17.25" customHeight="1"/>
-    <row r="757" ht="17.25" customHeight="1"/>
-    <row r="758" ht="17.25" customHeight="1"/>
-    <row r="759" ht="17.25" customHeight="1"/>
-    <row r="760" ht="17.25" customHeight="1"/>
-    <row r="761" ht="17.25" customHeight="1"/>
-    <row r="762" ht="17.25" customHeight="1"/>
-    <row r="763" ht="17.25" customHeight="1"/>
-    <row r="764" ht="17.25" customHeight="1"/>
-    <row r="765" ht="17.25" customHeight="1"/>
-    <row r="766" ht="17.25" customHeight="1"/>
-    <row r="767" ht="17.25" customHeight="1"/>
-    <row r="768" ht="17.25" customHeight="1"/>
-    <row r="769" ht="17.25" customHeight="1"/>
-    <row r="770" ht="17.25" customHeight="1"/>
-    <row r="771" ht="17.25" customHeight="1"/>
-    <row r="772" ht="17.25" customHeight="1"/>
-    <row r="773" ht="17.25" customHeight="1"/>
-    <row r="774" ht="17.25" customHeight="1"/>
-    <row r="775" ht="17.25" customHeight="1"/>
-    <row r="776" ht="17.25" customHeight="1"/>
-    <row r="777" ht="17.25" customHeight="1"/>
-    <row r="778" ht="17.25" customHeight="1"/>
-    <row r="779" ht="17.25" customHeight="1"/>
-    <row r="780" ht="17.25" customHeight="1"/>
-    <row r="781" ht="17.25" customHeight="1"/>
-    <row r="782" ht="17.25" customHeight="1"/>
-    <row r="783" ht="17.25" customHeight="1"/>
-    <row r="784" ht="17.25" customHeight="1"/>
-    <row r="785" ht="17.25" customHeight="1"/>
-    <row r="786" ht="17.25" customHeight="1"/>
-    <row r="787" ht="17.25" customHeight="1"/>
-    <row r="788" ht="17.25" customHeight="1"/>
-    <row r="789" ht="17.25" customHeight="1"/>
-    <row r="790" ht="17.25" customHeight="1"/>
-    <row r="791" ht="17.25" customHeight="1"/>
-    <row r="792" ht="17.25" customHeight="1"/>
-    <row r="793" ht="17.25" customHeight="1"/>
-    <row r="794" ht="17.25" customHeight="1"/>
-    <row r="795" ht="17.25" customHeight="1"/>
-    <row r="796" ht="17.25" customHeight="1"/>
-    <row r="797" ht="17.25" customHeight="1"/>
-    <row r="798" ht="17.25" customHeight="1"/>
-    <row r="799" ht="17.25" customHeight="1"/>
-    <row r="800" ht="17.25" customHeight="1"/>
-    <row r="801" ht="17.25" customHeight="1"/>
-    <row r="802" ht="17.25" customHeight="1"/>
-    <row r="803" ht="17.25" customHeight="1"/>
-    <row r="804" ht="17.25" customHeight="1"/>
-    <row r="805" ht="17.25" customHeight="1"/>
-    <row r="806" ht="17.25" customHeight="1"/>
-    <row r="807" ht="17.25" customHeight="1"/>
-    <row r="808" ht="17.25" customHeight="1"/>
-    <row r="809" ht="17.25" customHeight="1"/>
-    <row r="810" ht="17.25" customHeight="1"/>
-    <row r="811" ht="17.25" customHeight="1"/>
-    <row r="812" ht="17.25" customHeight="1"/>
-    <row r="813" ht="17.25" customHeight="1"/>
-    <row r="814" ht="17.25" customHeight="1"/>
-    <row r="815" ht="17.25" customHeight="1"/>
-    <row r="816" ht="17.25" customHeight="1"/>
-    <row r="817" ht="17.25" customHeight="1"/>
-    <row r="818" ht="17.25" customHeight="1"/>
-    <row r="819" ht="17.25" customHeight="1"/>
-    <row r="820" ht="17.25" customHeight="1"/>
-    <row r="821" ht="17.25" customHeight="1"/>
-    <row r="822" ht="17.25" customHeight="1"/>
-    <row r="823" ht="17.25" customHeight="1"/>
-    <row r="824" ht="17.25" customHeight="1"/>
-    <row r="825" ht="17.25" customHeight="1"/>
-    <row r="826" ht="17.25" customHeight="1"/>
-    <row r="827" ht="17.25" customHeight="1"/>
-    <row r="828" ht="17.25" customHeight="1"/>
-    <row r="829" ht="17.25" customHeight="1"/>
-    <row r="830" ht="17.25" customHeight="1"/>
-    <row r="831" ht="17.25" customHeight="1"/>
-    <row r="832" ht="17.25" customHeight="1"/>
-    <row r="833" ht="17.25" customHeight="1"/>
-    <row r="834" ht="17.25" customHeight="1"/>
-    <row r="835" ht="17.25" customHeight="1"/>
-    <row r="836" ht="17.25" customHeight="1"/>
-    <row r="837" ht="17.25" customHeight="1"/>
-    <row r="838" ht="17.25" customHeight="1"/>
-    <row r="839" ht="17.25" customHeight="1"/>
-    <row r="840" ht="17.25" customHeight="1"/>
-    <row r="841" ht="17.25" customHeight="1"/>
-    <row r="842" ht="17.25" customHeight="1"/>
-    <row r="843" ht="17.25" customHeight="1"/>
-    <row r="844" ht="17.25" customHeight="1"/>
-    <row r="845" ht="17.25" customHeight="1"/>
-    <row r="846" ht="17.25" customHeight="1"/>
-    <row r="847" ht="17.25" customHeight="1"/>
-    <row r="848" ht="17.25" customHeight="1"/>
-    <row r="849" ht="17.25" customHeight="1"/>
-    <row r="850" ht="17.25" customHeight="1"/>
-    <row r="851" ht="17.25" customHeight="1"/>
-    <row r="852" ht="17.25" customHeight="1"/>
-    <row r="853" ht="17.25" customHeight="1"/>
-    <row r="854" ht="17.25" customHeight="1"/>
-    <row r="855" ht="17.25" customHeight="1"/>
-    <row r="856" ht="17.25" customHeight="1"/>
-    <row r="857" ht="17.25" customHeight="1"/>
-    <row r="858" ht="17.25" customHeight="1"/>
-    <row r="859" ht="17.25" customHeight="1"/>
-    <row r="860" ht="17.25" customHeight="1"/>
-    <row r="861" ht="17.25" customHeight="1"/>
-    <row r="862" ht="17.25" customHeight="1"/>
-    <row r="863" ht="17.25" customHeight="1"/>
-    <row r="864" ht="17.25" customHeight="1"/>
-    <row r="865" ht="17.25" customHeight="1"/>
-    <row r="866" ht="17.25" customHeight="1"/>
-    <row r="867" ht="17.25" customHeight="1"/>
-    <row r="868" ht="17.25" customHeight="1"/>
-    <row r="869" ht="17.25" customHeight="1"/>
-    <row r="870" ht="17.25" customHeight="1"/>
-    <row r="871" ht="17.25" customHeight="1"/>
-    <row r="872" ht="17.25" customHeight="1"/>
-    <row r="873" ht="17.25" customHeight="1"/>
-    <row r="874" ht="17.25" customHeight="1"/>
-    <row r="875" ht="17.25" customHeight="1"/>
-    <row r="876" ht="17.25" customHeight="1"/>
-    <row r="877" ht="17.25" customHeight="1"/>
-    <row r="878" ht="17.25" customHeight="1"/>
-    <row r="879" ht="17.25" customHeight="1"/>
-    <row r="880" ht="17.25" customHeight="1"/>
-    <row r="881" ht="17.25" customHeight="1"/>
-    <row r="882" ht="17.25" customHeight="1"/>
-    <row r="883" ht="17.25" customHeight="1"/>
-    <row r="884" ht="17.25" customHeight="1"/>
-    <row r="885" ht="17.25" customHeight="1"/>
-    <row r="886" ht="17.25" customHeight="1"/>
-    <row r="887" ht="17.25" customHeight="1"/>
-    <row r="888" ht="17.25" customHeight="1"/>
-    <row r="889" ht="17.25" customHeight="1"/>
-    <row r="890" ht="17.25" customHeight="1"/>
-    <row r="891" ht="17.25" customHeight="1"/>
-    <row r="892" ht="17.25" customHeight="1"/>
-    <row r="893" ht="17.25" customHeight="1"/>
-    <row r="894" ht="17.25" customHeight="1"/>
-    <row r="895" ht="17.25" customHeight="1"/>
-    <row r="896" ht="17.25" customHeight="1"/>
-    <row r="897" ht="17.25" customHeight="1"/>
-    <row r="898" ht="17.25" customHeight="1"/>
-    <row r="899" ht="17.25" customHeight="1"/>
-    <row r="900" ht="17.25" customHeight="1"/>
-    <row r="901" ht="17.25" customHeight="1"/>
-    <row r="902" ht="17.25" customHeight="1"/>
-    <row r="903" ht="17.25" customHeight="1"/>
-    <row r="904" ht="17.25" customHeight="1"/>
-    <row r="905" ht="17.25" customHeight="1"/>
-    <row r="906" ht="17.25" customHeight="1"/>
-    <row r="907" ht="17.25" customHeight="1"/>
-    <row r="908" ht="17.25" customHeight="1"/>
-    <row r="909" ht="17.25" customHeight="1"/>
-    <row r="910" ht="17.25" customHeight="1"/>
-    <row r="911" ht="17.25" customHeight="1"/>
-    <row r="912" ht="17.25" customHeight="1"/>
-    <row r="913" ht="17.25" customHeight="1"/>
-    <row r="914" ht="17.25" customHeight="1"/>
-    <row r="915" ht="17.25" customHeight="1"/>
-    <row r="916" ht="17.25" customHeight="1"/>
-    <row r="917" ht="17.25" customHeight="1"/>
-    <row r="918" ht="17.25" customHeight="1"/>
-    <row r="919" ht="17.25" customHeight="1"/>
-    <row r="920" ht="17.25" customHeight="1"/>
-    <row r="921" ht="17.25" customHeight="1"/>
-    <row r="922" ht="17.25" customHeight="1"/>
-    <row r="923" ht="17.25" customHeight="1"/>
-    <row r="924" ht="17.25" customHeight="1"/>
-    <row r="925" ht="17.25" customHeight="1"/>
-    <row r="926" ht="17.25" customHeight="1"/>
-    <row r="927" ht="17.25" customHeight="1"/>
-    <row r="928" ht="17.25" customHeight="1"/>
-    <row r="929" ht="17.25" customHeight="1"/>
-    <row r="930" ht="17.25" customHeight="1"/>
-    <row r="931" ht="17.25" customHeight="1"/>
-    <row r="932" ht="17.25" customHeight="1"/>
-    <row r="933" ht="17.25" customHeight="1"/>
-    <row r="934" ht="17.25" customHeight="1"/>
-    <row r="935" ht="17.25" customHeight="1"/>
-    <row r="936" ht="17.25" customHeight="1"/>
-    <row r="937" ht="17.25" customHeight="1"/>
-    <row r="938" ht="17.25" customHeight="1"/>
-    <row r="939" ht="17.25" customHeight="1"/>
-    <row r="940" ht="17.25" customHeight="1"/>
-    <row r="941" ht="17.25" customHeight="1"/>
-    <row r="942" ht="17.25" customHeight="1"/>
-    <row r="943" ht="17.25" customHeight="1"/>
-    <row r="944" ht="17.25" customHeight="1"/>
-    <row r="945" ht="17.25" customHeight="1"/>
-    <row r="946" ht="17.25" customHeight="1"/>
-    <row r="947" ht="17.25" customHeight="1"/>
-    <row r="948" ht="17.25" customHeight="1"/>
-    <row r="949" ht="17.25" customHeight="1"/>
-    <row r="950" ht="17.25" customHeight="1"/>
-    <row r="951" ht="17.25" customHeight="1"/>
-    <row r="952" ht="17.25" customHeight="1"/>
-    <row r="953" ht="17.25" customHeight="1"/>
-    <row r="954" ht="17.25" customHeight="1"/>
-    <row r="955" ht="17.25" customHeight="1"/>
-    <row r="956" ht="17.25" customHeight="1"/>
-    <row r="957" ht="17.25" customHeight="1"/>
-    <row r="958" ht="17.25" customHeight="1"/>
-    <row r="959" ht="17.25" customHeight="1"/>
-    <row r="960" ht="17.25" customHeight="1"/>
-    <row r="961" ht="17.25" customHeight="1"/>
-    <row r="962" ht="17.25" customHeight="1"/>
-    <row r="963" ht="17.25" customHeight="1"/>
-    <row r="964" ht="17.25" customHeight="1"/>
-    <row r="965" ht="17.25" customHeight="1"/>
-    <row r="966" ht="17.25" customHeight="1"/>
-    <row r="967" ht="17.25" customHeight="1"/>
-    <row r="968" ht="17.25" customHeight="1"/>
-    <row r="969" ht="17.25" customHeight="1"/>
-    <row r="970" ht="17.25" customHeight="1"/>
-    <row r="971" ht="17.25" customHeight="1"/>
-    <row r="972" ht="17.25" customHeight="1"/>
-    <row r="973" ht="17.25" customHeight="1"/>
-    <row r="974" ht="17.25" customHeight="1"/>
-    <row r="975" ht="17.25" customHeight="1"/>
-    <row r="976" ht="17.25" customHeight="1"/>
-    <row r="977" ht="17.25" customHeight="1"/>
-    <row r="978" ht="17.25" customHeight="1"/>
-    <row r="979" ht="17.25" customHeight="1"/>
-    <row r="980" ht="17.25" customHeight="1"/>
-    <row r="981" ht="17.25" customHeight="1"/>
-    <row r="982" ht="17.25" customHeight="1"/>
-    <row r="983" ht="17.25" customHeight="1"/>
-    <row r="984" ht="17.25" customHeight="1"/>
-    <row r="985" ht="17.25" customHeight="1"/>
-    <row r="986" ht="17.25" customHeight="1"/>
-    <row r="987" ht="17.25" customHeight="1"/>
-    <row r="988" ht="17.25" customHeight="1"/>
-    <row r="989" ht="17.25" customHeight="1"/>
-    <row r="990" ht="17.25" customHeight="1"/>
-    <row r="991" ht="17.25" customHeight="1"/>
-    <row r="992" ht="17.25" customHeight="1"/>
-    <row r="993" ht="17.25" customHeight="1"/>
-    <row r="994" ht="17.25" customHeight="1"/>
-    <row r="995" ht="17.25" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>

--- a/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OZ_Project\JewelThief\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{034D7F31-0760-483C-9E03-7128948E6E68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25C61224-DBEF-46C6-9A50-A6730EA69A81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31140" yWindow="2340" windowWidth="22485" windowHeight="12495" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29970" yWindow="720" windowWidth="22485" windowHeight="12495" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -708,26 +708,27 @@
     <t>PreLoadAsset_MeshCollier_Junk_Bottle_Blue</t>
   </si>
   <si>
+    <t>PreLoadAsset_MeshCollider_Junk_Bottle_Pink_Large</t>
+  </si>
+  <si>
+    <t>MeshCollider_Junk_Bottle_Pink_Large</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_MeshCollier_Junk_Glasses</t>
+  </si>
+  <si>
+    <t>MeshCollider_Junk_Glasses</t>
+  </si>
+  <si>
     <t>MeshCollider_Junk_Bottle_Blue</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_MeshCollider_Junk_Bottle_Pink_Large</t>
-  </si>
-  <si>
-    <t>MeshCollider_Junk_Bottle_Pink_Large</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_MeshCollier_Junk_Glasses</t>
-  </si>
-  <si>
-    <t>MeshCollider_Junk_Glasses</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -780,6 +781,12 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -836,7 +843,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -847,6 +854,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -2039,8 +2047,8 @@
       <c r="A113" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="B113" s="9" t="s">
-        <v>227</v>
+      <c r="B113" s="10" t="s">
+        <v>231</v>
       </c>
       <c r="C113" s="7" t="s">
         <v>97</v>
@@ -2048,10 +2056,10 @@
     </row>
     <row r="114" spans="1:3" ht="17.25" customHeight="1">
       <c r="A114" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="B114" s="9" t="s">
         <v>228</v>
-      </c>
-      <c r="B114" s="9" t="s">
-        <v>229</v>
       </c>
       <c r="C114" s="7" t="s">
         <v>97</v>
@@ -2059,10 +2067,10 @@
     </row>
     <row r="115" spans="1:3" ht="17.25" customHeight="1">
       <c r="A115" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="B115" s="4" t="s">
         <v>230</v>
-      </c>
-      <c r="B115" s="4" t="s">
-        <v>231</v>
       </c>
       <c r="C115" s="7" t="s">
         <v>97</v>

--- a/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
@@ -3,15 +3,20 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr/>
+  <extLst>
+    <ext uri="GoogleSheetsCustomDataVersion2">
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="PjQ/ZH5dNfpZSLhuzuhQKuy/nAO/JzfJl7JGthYVMbo="/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="234">
   <si>
     <t>미리 로드할 어드레서블 테이블</t>
   </si>
@@ -280,6 +285,24 @@
     <t>Win_03</t>
   </si>
   <si>
+    <t>PreLoadAsset_Sound_SFX_024</t>
+  </si>
+  <si>
+    <t>Z_Electricity_01</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_025</t>
+  </si>
+  <si>
+    <t>Z_FootStep_01</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Sound_SFX_026</t>
+  </si>
+  <si>
+    <t>Z_FootStep_02</t>
+  </si>
+  <si>
     <t>PreLoadAsset_FBX_KeyFBX</t>
   </si>
   <si>
@@ -547,12 +570,6 @@
     <t>Police_Throw</t>
   </si>
   <si>
-    <t>PreLoadAsset_Police_Dog</t>
-  </si>
-  <si>
-    <t>Police_Dog</t>
-  </si>
-  <si>
     <t>PreLoadAsset_GameObject_StatueObject</t>
   </si>
   <si>
@@ -695,12 +712,6 @@
   </si>
   <si>
     <t>MeshCollider_Junk_Bottle_Pink_Large</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_MeshCollier_Junk_Glasses</t>
-  </si>
-  <si>
-    <t>MeshCollider_Junk_Glasses</t>
   </si>
   <si>
     <t>PreLoadAsset_GameObject_ItemObject</t>
@@ -713,7 +724,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -723,6 +734,7 @@
     <font>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11.0"/>
@@ -735,23 +747,18 @@
       <name val="Malgun Gothic"/>
     </font>
     <font>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
     </font>
     <font>
       <color theme="1"/>
@@ -803,32 +810,44 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="2" fillId="2" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="2" fillId="2" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -841,10 +860,6 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1051,7 +1066,7 @@
     <col customWidth="1" min="1" max="1" width="52.14"/>
     <col customWidth="1" min="2" max="2" width="35.14"/>
     <col customWidth="1" min="3" max="3" width="31.43"/>
-    <col customWidth="1" min="4" max="6" width="9.0"/>
+    <col customWidth="1" min="4" max="26" width="9.0"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.25" customHeight="1">
@@ -1416,26 +1431,26 @@
       </c>
     </row>
     <row r="45" ht="17.25" customHeight="1">
-      <c r="A45" s="2" t="s">
+      <c r="A45" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="B45" s="4" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="46" ht="17.25" customHeight="1">
-      <c r="A46" s="2" t="s">
+      <c r="A46" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="4" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="47" ht="17.25" customHeight="1">
-      <c r="A47" s="2" t="s">
+      <c r="A47" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" s="4" t="s">
         <v>94</v>
       </c>
     </row>
@@ -1446,31 +1461,31 @@
       <c r="B48" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C48" s="2" t="s">
-        <v>97</v>
-      </c>
     </row>
     <row r="49" ht="17.25" customHeight="1">
       <c r="A49" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B49" s="3" t="s">
         <v>98</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="50" ht="17.25" customHeight="1">
       <c r="A50" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B50" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="51" ht="17.25" customHeight="1">
       <c r="A51" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="C51" s="2" t="s">
         <v>103</v>
       </c>
     </row>
@@ -1478,7 +1493,7 @@
       <c r="A52" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B52" s="5" t="s">
         <v>105</v>
       </c>
     </row>
@@ -1486,7 +1501,7 @@
       <c r="A53" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B53" s="5" t="s">
         <v>107</v>
       </c>
     </row>
@@ -1494,7 +1509,7 @@
       <c r="A54" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="5" t="s">
         <v>109</v>
       </c>
     </row>
@@ -1510,54 +1525,54 @@
       <c r="A56" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B56" s="5" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="57" ht="17.25" customHeight="1">
-      <c r="A57" s="6" t="s">
+      <c r="A57" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B57" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="C57" s="2" t="s">
-        <v>97</v>
-      </c>
     </row>
     <row r="58" ht="17.25" customHeight="1">
-      <c r="A58" s="7" t="s">
+      <c r="A58" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B58" s="8" t="s">
+      <c r="B58" s="6" t="s">
         <v>117</v>
-      </c>
-      <c r="C58" s="9" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="59" ht="17.25" customHeight="1">
       <c r="A59" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" s="7" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="60" ht="17.25" customHeight="1">
-      <c r="A60" s="2" t="s">
+      <c r="A60" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B60" s="8" t="s">
         <v>121</v>
       </c>
+      <c r="C60" s="2" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="61" ht="17.25" customHeight="1">
-      <c r="A61" s="2" t="s">
+      <c r="A61" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" s="10" t="s">
         <v>123</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="62" ht="17.25" customHeight="1">
@@ -1569,78 +1584,75 @@
       </c>
     </row>
     <row r="63" ht="17.25" customHeight="1">
-      <c r="A63" s="2" t="s">
+      <c r="A63" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B63" s="10" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="64" ht="17.25" customHeight="1">
-      <c r="A64" s="2" t="s">
+      <c r="A64" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B64" s="10" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="65" ht="17.25" customHeight="1">
-      <c r="A65" s="2" t="s">
+      <c r="A65" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B65" s="10" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="66" ht="17.25" customHeight="1">
-      <c r="A66" s="2" t="s">
+      <c r="A66" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B66" s="10" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="67" ht="17.25" customHeight="1">
-      <c r="A67" s="2" t="s">
+      <c r="A67" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" s="10" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="68" ht="17.25" customHeight="1">
-      <c r="A68" s="2" t="s">
+      <c r="A68" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B68" s="10" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="69" ht="17.25" customHeight="1">
-      <c r="A69" s="1" t="s">
+      <c r="A69" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B69" s="10" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="70" ht="17.25" customHeight="1">
-      <c r="A70" s="1" t="s">
+      <c r="A70" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B70" s="10" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="71" ht="17.25" customHeight="1">
-      <c r="A71" s="10" t="s">
+      <c r="A71" s="9" t="s">
         <v>142</v>
       </c>
       <c r="B71" s="10" t="s">
         <v>143</v>
-      </c>
-      <c r="C71" s="10" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="72" ht="17.25" customHeight="1">
@@ -1650,9 +1662,6 @@
       <c r="B72" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="C72" s="10" t="s">
-        <v>97</v>
-      </c>
     </row>
     <row r="73" ht="17.25" customHeight="1">
       <c r="A73" s="10" t="s">
@@ -1661,150 +1670,156 @@
       <c r="B73" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="C73" s="10" t="s">
-        <v>97</v>
-      </c>
     </row>
     <row r="74" ht="17.25" customHeight="1">
-      <c r="A74" s="10" t="s">
+      <c r="A74" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="B74" s="10" t="s">
+      <c r="B74" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="C74" s="10" t="s">
-        <v>97</v>
+      <c r="C74" s="11" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="75" ht="17.25" customHeight="1">
-      <c r="A75" s="10" t="s">
+      <c r="A75" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="B75" s="10" t="s">
+      <c r="B75" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="C75" s="10" t="s">
-        <v>97</v>
+      <c r="C75" s="11" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="76" ht="17.25" customHeight="1">
-      <c r="A76" s="10" t="s">
+      <c r="A76" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="B76" s="10" t="s">
+      <c r="B76" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="C76" s="10"/>
+      <c r="C76" s="11" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="77" ht="17.25" customHeight="1">
-      <c r="A77" s="10" t="s">
+      <c r="A77" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="B77" s="10" t="s">
+      <c r="B77" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="C77" s="10"/>
+      <c r="C77" s="11" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="78" ht="17.25" customHeight="1">
-      <c r="A78" s="10" t="s">
+      <c r="A78" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="B78" s="10" t="s">
+      <c r="B78" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="C78" s="10"/>
+      <c r="C78" s="11" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="79" ht="17.25" customHeight="1">
-      <c r="A79" s="10" t="s">
+      <c r="A79" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="B79" s="10" t="s">
+      <c r="B79" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="C79" s="10"/>
+      <c r="C79" s="12"/>
     </row>
     <row r="80" ht="17.25" customHeight="1">
-      <c r="A80" s="10" t="s">
+      <c r="A80" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="B80" s="10" t="s">
+      <c r="B80" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="C80" s="10"/>
+      <c r="C80" s="12"/>
     </row>
     <row r="81" ht="17.25" customHeight="1">
-      <c r="A81" s="10" t="s">
+      <c r="A81" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="B81" s="10" t="s">
+      <c r="B81" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="C81" s="10"/>
+      <c r="C81" s="12"/>
     </row>
     <row r="82" ht="17.25" customHeight="1">
-      <c r="A82" s="10" t="s">
+      <c r="A82" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="B82" s="10" t="s">
+      <c r="B82" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="C82" s="10"/>
+      <c r="C82" s="12"/>
     </row>
     <row r="83" ht="17.25" customHeight="1">
-      <c r="A83" s="10" t="s">
+      <c r="A83" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="B83" s="10" t="s">
+      <c r="B83" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="C83" s="10"/>
+      <c r="C83" s="12"/>
     </row>
     <row r="84" ht="17.25" customHeight="1">
-      <c r="A84" s="10" t="s">
+      <c r="A84" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="B84" s="10" t="s">
+      <c r="B84" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="C84" s="10"/>
+      <c r="C84" s="12"/>
     </row>
     <row r="85" ht="17.25" customHeight="1">
-      <c r="A85" s="1" t="s">
+      <c r="A85" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="B85" s="11" t="s">
         <v>171</v>
       </c>
+      <c r="C85" s="12"/>
     </row>
     <row r="86" ht="17.25" customHeight="1">
-      <c r="A86" s="1" t="s">
+      <c r="A86" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="B86" s="11" t="s">
         <v>173</v>
       </c>
+      <c r="C86" s="12"/>
     </row>
     <row r="87" ht="17.25" customHeight="1">
-      <c r="A87" s="1" t="s">
+      <c r="A87" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="B87" s="11" t="s">
         <v>175</v>
       </c>
+      <c r="C87" s="12"/>
     </row>
     <row r="88" ht="17.25" customHeight="1">
-      <c r="A88" s="1" t="s">
+      <c r="A88" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="B88" s="10" t="s">
         <v>177</v>
       </c>
     </row>
     <row r="89" ht="17.25" customHeight="1">
-      <c r="A89" s="1" t="s">
+      <c r="A89" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="B89" s="10" t="s">
         <v>179</v>
       </c>
     </row>
@@ -1815,246 +1830,250 @@
       <c r="B90" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="C90" s="10"/>
     </row>
     <row r="91" ht="17.25" customHeight="1">
       <c r="A91" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="B91" s="11" t="s">
+      <c r="B91" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="C91" s="10" t="s">
-        <v>97</v>
-      </c>
     </row>
     <row r="92" ht="17.25" customHeight="1">
-      <c r="A92" s="10" t="s">
+      <c r="A92" s="11" t="s">
         <v>184</v>
       </c>
       <c r="B92" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="C92" s="10"/>
+      <c r="C92" s="12"/>
     </row>
     <row r="93" ht="17.25" customHeight="1">
-      <c r="A93" s="10" t="s">
+      <c r="A93" s="11" t="s">
         <v>186</v>
       </c>
-      <c r="B93" s="11" t="s">
+      <c r="B93" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="C93" s="10"/>
+      <c r="C93" s="11" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="94" ht="17.25" customHeight="1">
-      <c r="A94" s="10" t="s">
+      <c r="A94" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="B94" s="11" t="s">
+      <c r="B94" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="C94" s="10"/>
+      <c r="C94" s="12"/>
     </row>
     <row r="95" ht="17.25" customHeight="1">
-      <c r="A95" s="10" t="s">
+      <c r="A95" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="B95" s="11" t="s">
+      <c r="B95" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="C95" s="10"/>
+      <c r="C95" s="12"/>
     </row>
     <row r="96" ht="17.25" customHeight="1">
-      <c r="A96" s="1" t="s">
+      <c r="A96" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="B96" s="1" t="s">
+      <c r="B96" s="13" t="s">
         <v>193</v>
       </c>
+      <c r="C96" s="12"/>
     </row>
     <row r="97" ht="17.25" customHeight="1">
-      <c r="A97" s="1" t="s">
+      <c r="A97" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="B97" s="1" t="s">
+      <c r="B97" s="13" t="s">
         <v>195</v>
       </c>
+      <c r="C97" s="12"/>
     </row>
     <row r="98" ht="17.25" customHeight="1">
-      <c r="A98" s="1" t="s">
+      <c r="A98" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="B98" s="1" t="s">
+      <c r="B98" s="10" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="99" ht="17.25" customHeight="1">
-      <c r="A99" s="1" t="s">
+      <c r="A99" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="B99" s="10" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="100" ht="17.25" customHeight="1">
-      <c r="A100" s="1" t="s">
+      <c r="A100" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="B100" s="10" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="101" ht="17.25" customHeight="1">
-      <c r="A101" s="1" t="s">
+      <c r="A101" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="B101" s="10" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="102" ht="17.25" customHeight="1">
-      <c r="A102" s="1" t="s">
+      <c r="A102" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="B102" s="10" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="103" ht="17.25" customHeight="1">
-      <c r="A103" s="1" t="s">
+      <c r="A103" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="B103" s="4" t="s">
+      <c r="B103" s="10" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="104" ht="17.25" customHeight="1">
-      <c r="A104" s="12" t="s">
+      <c r="A104" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="B104" s="12" t="s">
+      <c r="B104" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="C104" s="10" t="s">
-        <v>97</v>
-      </c>
     </row>
     <row r="105" ht="17.25" customHeight="1">
-      <c r="A105" s="12" t="s">
+      <c r="A105" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="B105" s="12" t="s">
+      <c r="B105" s="14" t="s">
         <v>211</v>
       </c>
-      <c r="C105" s="10" t="s">
-        <v>97</v>
-      </c>
     </row>
     <row r="106" ht="17.25" customHeight="1">
-      <c r="A106" s="12" t="s">
+      <c r="A106" s="15" t="s">
         <v>212</v>
       </c>
-      <c r="B106" s="12" t="s">
+      <c r="B106" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="C106" s="10" t="s">
-        <v>97</v>
+      <c r="C106" s="11" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="107" ht="17.25" customHeight="1">
-      <c r="A107" s="12" t="s">
+      <c r="A107" s="15" t="s">
         <v>214</v>
       </c>
-      <c r="B107" s="12" t="s">
+      <c r="B107" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="C107" s="10" t="s">
-        <v>97</v>
+      <c r="C107" s="11" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="108" ht="17.25" customHeight="1">
-      <c r="A108" s="12" t="s">
+      <c r="A108" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="B108" s="12" t="s">
+      <c r="B108" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="C108" s="10" t="s">
-        <v>97</v>
+      <c r="C108" s="11" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="109" ht="17.25" customHeight="1">
-      <c r="A109" s="12" t="s">
+      <c r="A109" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="B109" s="12" t="s">
+      <c r="B109" s="16" t="s">
         <v>219</v>
       </c>
-      <c r="C109" s="10" t="s">
-        <v>97</v>
+      <c r="C109" s="11" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="110" ht="17.25" customHeight="1">
-      <c r="A110" s="12" t="s">
+      <c r="A110" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="B110" s="12" t="s">
+      <c r="B110" s="16" t="s">
         <v>221</v>
       </c>
-      <c r="C110" s="10" t="s">
-        <v>97</v>
+      <c r="C110" s="11" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="111" ht="17.25" customHeight="1">
-      <c r="A111" s="1" t="s">
+      <c r="A111" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="B111" s="4" t="s">
+      <c r="B111" s="16" t="s">
         <v>223</v>
       </c>
+      <c r="C111" s="11" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="112" ht="17.25" customHeight="1">
-      <c r="A112" s="12" t="s">
+      <c r="A112" s="15" t="s">
         <v>224</v>
       </c>
-      <c r="B112" s="12" t="s">
+      <c r="B112" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="C112" s="10" t="s">
-        <v>97</v>
+      <c r="C112" s="11" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="113" ht="17.25" customHeight="1">
-      <c r="A113" s="12" t="s">
+      <c r="A113" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="B113" s="12" t="s">
+      <c r="B113" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="C113" s="10" t="s">
-        <v>97</v>
-      </c>
     </row>
     <row r="114" ht="17.25" customHeight="1">
-      <c r="A114" s="12" t="s">
+      <c r="A114" s="15" t="s">
         <v>228</v>
       </c>
-      <c r="B114" s="4" t="s">
+      <c r="B114" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="C114" s="10" t="s">
-        <v>97</v>
+      <c r="C114" s="11" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="115" ht="17.25" customHeight="1">
-      <c r="A115" s="1" t="s">
+      <c r="A115" s="15" t="s">
         <v>230</v>
       </c>
-      <c r="B115" s="1" t="s">
+      <c r="B115" s="16" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="116" ht="17.25" customHeight="1"/>
+      <c r="C115" s="11" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="116" ht="17.25" customHeight="1">
+      <c r="A116" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="B116" s="10" t="s">
+        <v>233</v>
+      </c>
+    </row>
     <row r="117" ht="17.25" customHeight="1"/>
     <row r="118" ht="17.25" customHeight="1"/>
     <row r="119" ht="17.25" customHeight="1"/>
@@ -2254,692 +2273,688 @@
     <row r="313" ht="17.25" customHeight="1"/>
     <row r="314" ht="17.25" customHeight="1"/>
     <row r="315" ht="17.25" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
-    <row r="838" ht="15.75" customHeight="1"/>
-    <row r="839" ht="15.75" customHeight="1"/>
-    <row r="840" ht="15.75" customHeight="1"/>
-    <row r="841" ht="15.75" customHeight="1"/>
-    <row r="842" ht="15.75" customHeight="1"/>
-    <row r="843" ht="15.75" customHeight="1"/>
-    <row r="844" ht="15.75" customHeight="1"/>
-    <row r="845" ht="15.75" customHeight="1"/>
-    <row r="846" ht="15.75" customHeight="1"/>
-    <row r="847" ht="15.75" customHeight="1"/>
-    <row r="848" ht="15.75" customHeight="1"/>
-    <row r="849" ht="15.75" customHeight="1"/>
-    <row r="850" ht="15.75" customHeight="1"/>
-    <row r="851" ht="15.75" customHeight="1"/>
-    <row r="852" ht="15.75" customHeight="1"/>
-    <row r="853" ht="15.75" customHeight="1"/>
-    <row r="854" ht="15.75" customHeight="1"/>
-    <row r="855" ht="15.75" customHeight="1"/>
-    <row r="856" ht="15.75" customHeight="1"/>
-    <row r="857" ht="15.75" customHeight="1"/>
-    <row r="858" ht="15.75" customHeight="1"/>
-    <row r="859" ht="15.75" customHeight="1"/>
-    <row r="860" ht="15.75" customHeight="1"/>
-    <row r="861" ht="15.75" customHeight="1"/>
-    <row r="862" ht="15.75" customHeight="1"/>
-    <row r="863" ht="15.75" customHeight="1"/>
-    <row r="864" ht="15.75" customHeight="1"/>
-    <row r="865" ht="15.75" customHeight="1"/>
-    <row r="866" ht="15.75" customHeight="1"/>
-    <row r="867" ht="15.75" customHeight="1"/>
-    <row r="868" ht="15.75" customHeight="1"/>
-    <row r="869" ht="15.75" customHeight="1"/>
-    <row r="870" ht="15.75" customHeight="1"/>
-    <row r="871" ht="15.75" customHeight="1"/>
-    <row r="872" ht="15.75" customHeight="1"/>
-    <row r="873" ht="15.75" customHeight="1"/>
-    <row r="874" ht="15.75" customHeight="1"/>
-    <row r="875" ht="15.75" customHeight="1"/>
-    <row r="876" ht="15.75" customHeight="1"/>
-    <row r="877" ht="15.75" customHeight="1"/>
-    <row r="878" ht="15.75" customHeight="1"/>
-    <row r="879" ht="15.75" customHeight="1"/>
-    <row r="880" ht="15.75" customHeight="1"/>
-    <row r="881" ht="15.75" customHeight="1"/>
-    <row r="882" ht="15.75" customHeight="1"/>
-    <row r="883" ht="15.75" customHeight="1"/>
-    <row r="884" ht="15.75" customHeight="1"/>
-    <row r="885" ht="15.75" customHeight="1"/>
-    <row r="886" ht="15.75" customHeight="1"/>
-    <row r="887" ht="15.75" customHeight="1"/>
-    <row r="888" ht="15.75" customHeight="1"/>
-    <row r="889" ht="15.75" customHeight="1"/>
-    <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
-    <row r="1001" ht="15.75" customHeight="1"/>
+    <row r="316" ht="17.25" customHeight="1"/>
+    <row r="317" ht="17.25" customHeight="1"/>
+    <row r="318" ht="17.25" customHeight="1"/>
+    <row r="319" ht="17.25" customHeight="1"/>
+    <row r="320" ht="17.25" customHeight="1"/>
+    <row r="321" ht="17.25" customHeight="1"/>
+    <row r="322" ht="17.25" customHeight="1"/>
+    <row r="323" ht="17.25" customHeight="1"/>
+    <row r="324" ht="17.25" customHeight="1"/>
+    <row r="325" ht="17.25" customHeight="1"/>
+    <row r="326" ht="17.25" customHeight="1"/>
+    <row r="327" ht="17.25" customHeight="1"/>
+    <row r="328" ht="17.25" customHeight="1"/>
+    <row r="329" ht="17.25" customHeight="1"/>
+    <row r="330" ht="17.25" customHeight="1"/>
+    <row r="331" ht="17.25" customHeight="1"/>
+    <row r="332" ht="17.25" customHeight="1"/>
+    <row r="333" ht="17.25" customHeight="1"/>
+    <row r="334" ht="17.25" customHeight="1"/>
+    <row r="335" ht="17.25" customHeight="1"/>
+    <row r="336" ht="17.25" customHeight="1"/>
+    <row r="337" ht="17.25" customHeight="1"/>
+    <row r="338" ht="17.25" customHeight="1"/>
+    <row r="339" ht="17.25" customHeight="1"/>
+    <row r="340" ht="17.25" customHeight="1"/>
+    <row r="341" ht="17.25" customHeight="1"/>
+    <row r="342" ht="17.25" customHeight="1"/>
+    <row r="343" ht="17.25" customHeight="1"/>
+    <row r="344" ht="17.25" customHeight="1"/>
+    <row r="345" ht="17.25" customHeight="1"/>
+    <row r="346" ht="17.25" customHeight="1"/>
+    <row r="347" ht="17.25" customHeight="1"/>
+    <row r="348" ht="17.25" customHeight="1"/>
+    <row r="349" ht="17.25" customHeight="1"/>
+    <row r="350" ht="17.25" customHeight="1"/>
+    <row r="351" ht="17.25" customHeight="1"/>
+    <row r="352" ht="17.25" customHeight="1"/>
+    <row r="353" ht="17.25" customHeight="1"/>
+    <row r="354" ht="17.25" customHeight="1"/>
+    <row r="355" ht="17.25" customHeight="1"/>
+    <row r="356" ht="17.25" customHeight="1"/>
+    <row r="357" ht="17.25" customHeight="1"/>
+    <row r="358" ht="17.25" customHeight="1"/>
+    <row r="359" ht="17.25" customHeight="1"/>
+    <row r="360" ht="17.25" customHeight="1"/>
+    <row r="361" ht="17.25" customHeight="1"/>
+    <row r="362" ht="17.25" customHeight="1"/>
+    <row r="363" ht="17.25" customHeight="1"/>
+    <row r="364" ht="17.25" customHeight="1"/>
+    <row r="365" ht="17.25" customHeight="1"/>
+    <row r="366" ht="17.25" customHeight="1"/>
+    <row r="367" ht="17.25" customHeight="1"/>
+    <row r="368" ht="17.25" customHeight="1"/>
+    <row r="369" ht="17.25" customHeight="1"/>
+    <row r="370" ht="17.25" customHeight="1"/>
+    <row r="371" ht="17.25" customHeight="1"/>
+    <row r="372" ht="17.25" customHeight="1"/>
+    <row r="373" ht="17.25" customHeight="1"/>
+    <row r="374" ht="17.25" customHeight="1"/>
+    <row r="375" ht="17.25" customHeight="1"/>
+    <row r="376" ht="17.25" customHeight="1"/>
+    <row r="377" ht="17.25" customHeight="1"/>
+    <row r="378" ht="17.25" customHeight="1"/>
+    <row r="379" ht="17.25" customHeight="1"/>
+    <row r="380" ht="17.25" customHeight="1"/>
+    <row r="381" ht="17.25" customHeight="1"/>
+    <row r="382" ht="17.25" customHeight="1"/>
+    <row r="383" ht="17.25" customHeight="1"/>
+    <row r="384" ht="17.25" customHeight="1"/>
+    <row r="385" ht="17.25" customHeight="1"/>
+    <row r="386" ht="17.25" customHeight="1"/>
+    <row r="387" ht="17.25" customHeight="1"/>
+    <row r="388" ht="17.25" customHeight="1"/>
+    <row r="389" ht="17.25" customHeight="1"/>
+    <row r="390" ht="17.25" customHeight="1"/>
+    <row r="391" ht="17.25" customHeight="1"/>
+    <row r="392" ht="17.25" customHeight="1"/>
+    <row r="393" ht="17.25" customHeight="1"/>
+    <row r="394" ht="17.25" customHeight="1"/>
+    <row r="395" ht="17.25" customHeight="1"/>
+    <row r="396" ht="17.25" customHeight="1"/>
+    <row r="397" ht="17.25" customHeight="1"/>
+    <row r="398" ht="17.25" customHeight="1"/>
+    <row r="399" ht="17.25" customHeight="1"/>
+    <row r="400" ht="17.25" customHeight="1"/>
+    <row r="401" ht="17.25" customHeight="1"/>
+    <row r="402" ht="17.25" customHeight="1"/>
+    <row r="403" ht="17.25" customHeight="1"/>
+    <row r="404" ht="17.25" customHeight="1"/>
+    <row r="405" ht="17.25" customHeight="1"/>
+    <row r="406" ht="17.25" customHeight="1"/>
+    <row r="407" ht="17.25" customHeight="1"/>
+    <row r="408" ht="17.25" customHeight="1"/>
+    <row r="409" ht="17.25" customHeight="1"/>
+    <row r="410" ht="17.25" customHeight="1"/>
+    <row r="411" ht="17.25" customHeight="1"/>
+    <row r="412" ht="17.25" customHeight="1"/>
+    <row r="413" ht="17.25" customHeight="1"/>
+    <row r="414" ht="17.25" customHeight="1"/>
+    <row r="415" ht="17.25" customHeight="1"/>
+    <row r="416" ht="17.25" customHeight="1"/>
+    <row r="417" ht="17.25" customHeight="1"/>
+    <row r="418" ht="17.25" customHeight="1"/>
+    <row r="419" ht="17.25" customHeight="1"/>
+    <row r="420" ht="17.25" customHeight="1"/>
+    <row r="421" ht="17.25" customHeight="1"/>
+    <row r="422" ht="17.25" customHeight="1"/>
+    <row r="423" ht="17.25" customHeight="1"/>
+    <row r="424" ht="17.25" customHeight="1"/>
+    <row r="425" ht="17.25" customHeight="1"/>
+    <row r="426" ht="17.25" customHeight="1"/>
+    <row r="427" ht="17.25" customHeight="1"/>
+    <row r="428" ht="17.25" customHeight="1"/>
+    <row r="429" ht="17.25" customHeight="1"/>
+    <row r="430" ht="17.25" customHeight="1"/>
+    <row r="431" ht="17.25" customHeight="1"/>
+    <row r="432" ht="17.25" customHeight="1"/>
+    <row r="433" ht="17.25" customHeight="1"/>
+    <row r="434" ht="17.25" customHeight="1"/>
+    <row r="435" ht="17.25" customHeight="1"/>
+    <row r="436" ht="17.25" customHeight="1"/>
+    <row r="437" ht="17.25" customHeight="1"/>
+    <row r="438" ht="17.25" customHeight="1"/>
+    <row r="439" ht="17.25" customHeight="1"/>
+    <row r="440" ht="17.25" customHeight="1"/>
+    <row r="441" ht="17.25" customHeight="1"/>
+    <row r="442" ht="17.25" customHeight="1"/>
+    <row r="443" ht="17.25" customHeight="1"/>
+    <row r="444" ht="17.25" customHeight="1"/>
+    <row r="445" ht="17.25" customHeight="1"/>
+    <row r="446" ht="17.25" customHeight="1"/>
+    <row r="447" ht="17.25" customHeight="1"/>
+    <row r="448" ht="17.25" customHeight="1"/>
+    <row r="449" ht="17.25" customHeight="1"/>
+    <row r="450" ht="17.25" customHeight="1"/>
+    <row r="451" ht="17.25" customHeight="1"/>
+    <row r="452" ht="17.25" customHeight="1"/>
+    <row r="453" ht="17.25" customHeight="1"/>
+    <row r="454" ht="17.25" customHeight="1"/>
+    <row r="455" ht="17.25" customHeight="1"/>
+    <row r="456" ht="17.25" customHeight="1"/>
+    <row r="457" ht="17.25" customHeight="1"/>
+    <row r="458" ht="17.25" customHeight="1"/>
+    <row r="459" ht="17.25" customHeight="1"/>
+    <row r="460" ht="17.25" customHeight="1"/>
+    <row r="461" ht="17.25" customHeight="1"/>
+    <row r="462" ht="17.25" customHeight="1"/>
+    <row r="463" ht="17.25" customHeight="1"/>
+    <row r="464" ht="17.25" customHeight="1"/>
+    <row r="465" ht="17.25" customHeight="1"/>
+    <row r="466" ht="17.25" customHeight="1"/>
+    <row r="467" ht="17.25" customHeight="1"/>
+    <row r="468" ht="17.25" customHeight="1"/>
+    <row r="469" ht="17.25" customHeight="1"/>
+    <row r="470" ht="17.25" customHeight="1"/>
+    <row r="471" ht="17.25" customHeight="1"/>
+    <row r="472" ht="17.25" customHeight="1"/>
+    <row r="473" ht="17.25" customHeight="1"/>
+    <row r="474" ht="17.25" customHeight="1"/>
+    <row r="475" ht="17.25" customHeight="1"/>
+    <row r="476" ht="17.25" customHeight="1"/>
+    <row r="477" ht="17.25" customHeight="1"/>
+    <row r="478" ht="17.25" customHeight="1"/>
+    <row r="479" ht="17.25" customHeight="1"/>
+    <row r="480" ht="17.25" customHeight="1"/>
+    <row r="481" ht="17.25" customHeight="1"/>
+    <row r="482" ht="17.25" customHeight="1"/>
+    <row r="483" ht="17.25" customHeight="1"/>
+    <row r="484" ht="17.25" customHeight="1"/>
+    <row r="485" ht="17.25" customHeight="1"/>
+    <row r="486" ht="17.25" customHeight="1"/>
+    <row r="487" ht="17.25" customHeight="1"/>
+    <row r="488" ht="17.25" customHeight="1"/>
+    <row r="489" ht="17.25" customHeight="1"/>
+    <row r="490" ht="17.25" customHeight="1"/>
+    <row r="491" ht="17.25" customHeight="1"/>
+    <row r="492" ht="17.25" customHeight="1"/>
+    <row r="493" ht="17.25" customHeight="1"/>
+    <row r="494" ht="17.25" customHeight="1"/>
+    <row r="495" ht="17.25" customHeight="1"/>
+    <row r="496" ht="17.25" customHeight="1"/>
+    <row r="497" ht="17.25" customHeight="1"/>
+    <row r="498" ht="17.25" customHeight="1"/>
+    <row r="499" ht="17.25" customHeight="1"/>
+    <row r="500" ht="17.25" customHeight="1"/>
+    <row r="501" ht="17.25" customHeight="1"/>
+    <row r="502" ht="17.25" customHeight="1"/>
+    <row r="503" ht="17.25" customHeight="1"/>
+    <row r="504" ht="17.25" customHeight="1"/>
+    <row r="505" ht="17.25" customHeight="1"/>
+    <row r="506" ht="17.25" customHeight="1"/>
+    <row r="507" ht="17.25" customHeight="1"/>
+    <row r="508" ht="17.25" customHeight="1"/>
+    <row r="509" ht="17.25" customHeight="1"/>
+    <row r="510" ht="17.25" customHeight="1"/>
+    <row r="511" ht="17.25" customHeight="1"/>
+    <row r="512" ht="17.25" customHeight="1"/>
+    <row r="513" ht="17.25" customHeight="1"/>
+    <row r="514" ht="17.25" customHeight="1"/>
+    <row r="515" ht="17.25" customHeight="1"/>
+    <row r="516" ht="17.25" customHeight="1"/>
+    <row r="517" ht="17.25" customHeight="1"/>
+    <row r="518" ht="17.25" customHeight="1"/>
+    <row r="519" ht="17.25" customHeight="1"/>
+    <row r="520" ht="17.25" customHeight="1"/>
+    <row r="521" ht="17.25" customHeight="1"/>
+    <row r="522" ht="17.25" customHeight="1"/>
+    <row r="523" ht="17.25" customHeight="1"/>
+    <row r="524" ht="17.25" customHeight="1"/>
+    <row r="525" ht="17.25" customHeight="1"/>
+    <row r="526" ht="17.25" customHeight="1"/>
+    <row r="527" ht="17.25" customHeight="1"/>
+    <row r="528" ht="17.25" customHeight="1"/>
+    <row r="529" ht="17.25" customHeight="1"/>
+    <row r="530" ht="17.25" customHeight="1"/>
+    <row r="531" ht="17.25" customHeight="1"/>
+    <row r="532" ht="17.25" customHeight="1"/>
+    <row r="533" ht="17.25" customHeight="1"/>
+    <row r="534" ht="17.25" customHeight="1"/>
+    <row r="535" ht="17.25" customHeight="1"/>
+    <row r="536" ht="17.25" customHeight="1"/>
+    <row r="537" ht="17.25" customHeight="1"/>
+    <row r="538" ht="17.25" customHeight="1"/>
+    <row r="539" ht="17.25" customHeight="1"/>
+    <row r="540" ht="17.25" customHeight="1"/>
+    <row r="541" ht="17.25" customHeight="1"/>
+    <row r="542" ht="17.25" customHeight="1"/>
+    <row r="543" ht="17.25" customHeight="1"/>
+    <row r="544" ht="17.25" customHeight="1"/>
+    <row r="545" ht="17.25" customHeight="1"/>
+    <row r="546" ht="17.25" customHeight="1"/>
+    <row r="547" ht="17.25" customHeight="1"/>
+    <row r="548" ht="17.25" customHeight="1"/>
+    <row r="549" ht="17.25" customHeight="1"/>
+    <row r="550" ht="17.25" customHeight="1"/>
+    <row r="551" ht="17.25" customHeight="1"/>
+    <row r="552" ht="17.25" customHeight="1"/>
+    <row r="553" ht="17.25" customHeight="1"/>
+    <row r="554" ht="17.25" customHeight="1"/>
+    <row r="555" ht="17.25" customHeight="1"/>
+    <row r="556" ht="17.25" customHeight="1"/>
+    <row r="557" ht="17.25" customHeight="1"/>
+    <row r="558" ht="17.25" customHeight="1"/>
+    <row r="559" ht="17.25" customHeight="1"/>
+    <row r="560" ht="17.25" customHeight="1"/>
+    <row r="561" ht="17.25" customHeight="1"/>
+    <row r="562" ht="17.25" customHeight="1"/>
+    <row r="563" ht="17.25" customHeight="1"/>
+    <row r="564" ht="17.25" customHeight="1"/>
+    <row r="565" ht="17.25" customHeight="1"/>
+    <row r="566" ht="17.25" customHeight="1"/>
+    <row r="567" ht="17.25" customHeight="1"/>
+    <row r="568" ht="17.25" customHeight="1"/>
+    <row r="569" ht="17.25" customHeight="1"/>
+    <row r="570" ht="17.25" customHeight="1"/>
+    <row r="571" ht="17.25" customHeight="1"/>
+    <row r="572" ht="17.25" customHeight="1"/>
+    <row r="573" ht="17.25" customHeight="1"/>
+    <row r="574" ht="17.25" customHeight="1"/>
+    <row r="575" ht="17.25" customHeight="1"/>
+    <row r="576" ht="17.25" customHeight="1"/>
+    <row r="577" ht="17.25" customHeight="1"/>
+    <row r="578" ht="17.25" customHeight="1"/>
+    <row r="579" ht="17.25" customHeight="1"/>
+    <row r="580" ht="17.25" customHeight="1"/>
+    <row r="581" ht="17.25" customHeight="1"/>
+    <row r="582" ht="17.25" customHeight="1"/>
+    <row r="583" ht="17.25" customHeight="1"/>
+    <row r="584" ht="17.25" customHeight="1"/>
+    <row r="585" ht="17.25" customHeight="1"/>
+    <row r="586" ht="17.25" customHeight="1"/>
+    <row r="587" ht="17.25" customHeight="1"/>
+    <row r="588" ht="17.25" customHeight="1"/>
+    <row r="589" ht="17.25" customHeight="1"/>
+    <row r="590" ht="17.25" customHeight="1"/>
+    <row r="591" ht="17.25" customHeight="1"/>
+    <row r="592" ht="17.25" customHeight="1"/>
+    <row r="593" ht="17.25" customHeight="1"/>
+    <row r="594" ht="17.25" customHeight="1"/>
+    <row r="595" ht="17.25" customHeight="1"/>
+    <row r="596" ht="17.25" customHeight="1"/>
+    <row r="597" ht="17.25" customHeight="1"/>
+    <row r="598" ht="17.25" customHeight="1"/>
+    <row r="599" ht="17.25" customHeight="1"/>
+    <row r="600" ht="17.25" customHeight="1"/>
+    <row r="601" ht="17.25" customHeight="1"/>
+    <row r="602" ht="17.25" customHeight="1"/>
+    <row r="603" ht="17.25" customHeight="1"/>
+    <row r="604" ht="17.25" customHeight="1"/>
+    <row r="605" ht="17.25" customHeight="1"/>
+    <row r="606" ht="17.25" customHeight="1"/>
+    <row r="607" ht="17.25" customHeight="1"/>
+    <row r="608" ht="17.25" customHeight="1"/>
+    <row r="609" ht="17.25" customHeight="1"/>
+    <row r="610" ht="17.25" customHeight="1"/>
+    <row r="611" ht="17.25" customHeight="1"/>
+    <row r="612" ht="17.25" customHeight="1"/>
+    <row r="613" ht="17.25" customHeight="1"/>
+    <row r="614" ht="17.25" customHeight="1"/>
+    <row r="615" ht="17.25" customHeight="1"/>
+    <row r="616" ht="17.25" customHeight="1"/>
+    <row r="617" ht="17.25" customHeight="1"/>
+    <row r="618" ht="17.25" customHeight="1"/>
+    <row r="619" ht="17.25" customHeight="1"/>
+    <row r="620" ht="17.25" customHeight="1"/>
+    <row r="621" ht="17.25" customHeight="1"/>
+    <row r="622" ht="17.25" customHeight="1"/>
+    <row r="623" ht="17.25" customHeight="1"/>
+    <row r="624" ht="17.25" customHeight="1"/>
+    <row r="625" ht="17.25" customHeight="1"/>
+    <row r="626" ht="17.25" customHeight="1"/>
+    <row r="627" ht="17.25" customHeight="1"/>
+    <row r="628" ht="17.25" customHeight="1"/>
+    <row r="629" ht="17.25" customHeight="1"/>
+    <row r="630" ht="17.25" customHeight="1"/>
+    <row r="631" ht="17.25" customHeight="1"/>
+    <row r="632" ht="17.25" customHeight="1"/>
+    <row r="633" ht="17.25" customHeight="1"/>
+    <row r="634" ht="17.25" customHeight="1"/>
+    <row r="635" ht="17.25" customHeight="1"/>
+    <row r="636" ht="17.25" customHeight="1"/>
+    <row r="637" ht="17.25" customHeight="1"/>
+    <row r="638" ht="17.25" customHeight="1"/>
+    <row r="639" ht="17.25" customHeight="1"/>
+    <row r="640" ht="17.25" customHeight="1"/>
+    <row r="641" ht="17.25" customHeight="1"/>
+    <row r="642" ht="17.25" customHeight="1"/>
+    <row r="643" ht="17.25" customHeight="1"/>
+    <row r="644" ht="17.25" customHeight="1"/>
+    <row r="645" ht="17.25" customHeight="1"/>
+    <row r="646" ht="17.25" customHeight="1"/>
+    <row r="647" ht="17.25" customHeight="1"/>
+    <row r="648" ht="17.25" customHeight="1"/>
+    <row r="649" ht="17.25" customHeight="1"/>
+    <row r="650" ht="17.25" customHeight="1"/>
+    <row r="651" ht="17.25" customHeight="1"/>
+    <row r="652" ht="17.25" customHeight="1"/>
+    <row r="653" ht="17.25" customHeight="1"/>
+    <row r="654" ht="17.25" customHeight="1"/>
+    <row r="655" ht="17.25" customHeight="1"/>
+    <row r="656" ht="17.25" customHeight="1"/>
+    <row r="657" ht="17.25" customHeight="1"/>
+    <row r="658" ht="17.25" customHeight="1"/>
+    <row r="659" ht="17.25" customHeight="1"/>
+    <row r="660" ht="17.25" customHeight="1"/>
+    <row r="661" ht="17.25" customHeight="1"/>
+    <row r="662" ht="17.25" customHeight="1"/>
+    <row r="663" ht="17.25" customHeight="1"/>
+    <row r="664" ht="17.25" customHeight="1"/>
+    <row r="665" ht="17.25" customHeight="1"/>
+    <row r="666" ht="17.25" customHeight="1"/>
+    <row r="667" ht="17.25" customHeight="1"/>
+    <row r="668" ht="17.25" customHeight="1"/>
+    <row r="669" ht="17.25" customHeight="1"/>
+    <row r="670" ht="17.25" customHeight="1"/>
+    <row r="671" ht="17.25" customHeight="1"/>
+    <row r="672" ht="17.25" customHeight="1"/>
+    <row r="673" ht="17.25" customHeight="1"/>
+    <row r="674" ht="17.25" customHeight="1"/>
+    <row r="675" ht="17.25" customHeight="1"/>
+    <row r="676" ht="17.25" customHeight="1"/>
+    <row r="677" ht="17.25" customHeight="1"/>
+    <row r="678" ht="17.25" customHeight="1"/>
+    <row r="679" ht="17.25" customHeight="1"/>
+    <row r="680" ht="17.25" customHeight="1"/>
+    <row r="681" ht="17.25" customHeight="1"/>
+    <row r="682" ht="17.25" customHeight="1"/>
+    <row r="683" ht="17.25" customHeight="1"/>
+    <row r="684" ht="17.25" customHeight="1"/>
+    <row r="685" ht="17.25" customHeight="1"/>
+    <row r="686" ht="17.25" customHeight="1"/>
+    <row r="687" ht="17.25" customHeight="1"/>
+    <row r="688" ht="17.25" customHeight="1"/>
+    <row r="689" ht="17.25" customHeight="1"/>
+    <row r="690" ht="17.25" customHeight="1"/>
+    <row r="691" ht="17.25" customHeight="1"/>
+    <row r="692" ht="17.25" customHeight="1"/>
+    <row r="693" ht="17.25" customHeight="1"/>
+    <row r="694" ht="17.25" customHeight="1"/>
+    <row r="695" ht="17.25" customHeight="1"/>
+    <row r="696" ht="17.25" customHeight="1"/>
+    <row r="697" ht="17.25" customHeight="1"/>
+    <row r="698" ht="17.25" customHeight="1"/>
+    <row r="699" ht="17.25" customHeight="1"/>
+    <row r="700" ht="17.25" customHeight="1"/>
+    <row r="701" ht="17.25" customHeight="1"/>
+    <row r="702" ht="17.25" customHeight="1"/>
+    <row r="703" ht="17.25" customHeight="1"/>
+    <row r="704" ht="17.25" customHeight="1"/>
+    <row r="705" ht="17.25" customHeight="1"/>
+    <row r="706" ht="17.25" customHeight="1"/>
+    <row r="707" ht="17.25" customHeight="1"/>
+    <row r="708" ht="17.25" customHeight="1"/>
+    <row r="709" ht="17.25" customHeight="1"/>
+    <row r="710" ht="17.25" customHeight="1"/>
+    <row r="711" ht="17.25" customHeight="1"/>
+    <row r="712" ht="17.25" customHeight="1"/>
+    <row r="713" ht="17.25" customHeight="1"/>
+    <row r="714" ht="17.25" customHeight="1"/>
+    <row r="715" ht="17.25" customHeight="1"/>
+    <row r="716" ht="17.25" customHeight="1"/>
+    <row r="717" ht="17.25" customHeight="1"/>
+    <row r="718" ht="17.25" customHeight="1"/>
+    <row r="719" ht="17.25" customHeight="1"/>
+    <row r="720" ht="17.25" customHeight="1"/>
+    <row r="721" ht="17.25" customHeight="1"/>
+    <row r="722" ht="17.25" customHeight="1"/>
+    <row r="723" ht="17.25" customHeight="1"/>
+    <row r="724" ht="17.25" customHeight="1"/>
+    <row r="725" ht="17.25" customHeight="1"/>
+    <row r="726" ht="17.25" customHeight="1"/>
+    <row r="727" ht="17.25" customHeight="1"/>
+    <row r="728" ht="17.25" customHeight="1"/>
+    <row r="729" ht="17.25" customHeight="1"/>
+    <row r="730" ht="17.25" customHeight="1"/>
+    <row r="731" ht="17.25" customHeight="1"/>
+    <row r="732" ht="17.25" customHeight="1"/>
+    <row r="733" ht="17.25" customHeight="1"/>
+    <row r="734" ht="17.25" customHeight="1"/>
+    <row r="735" ht="17.25" customHeight="1"/>
+    <row r="736" ht="17.25" customHeight="1"/>
+    <row r="737" ht="17.25" customHeight="1"/>
+    <row r="738" ht="17.25" customHeight="1"/>
+    <row r="739" ht="17.25" customHeight="1"/>
+    <row r="740" ht="17.25" customHeight="1"/>
+    <row r="741" ht="17.25" customHeight="1"/>
+    <row r="742" ht="17.25" customHeight="1"/>
+    <row r="743" ht="17.25" customHeight="1"/>
+    <row r="744" ht="17.25" customHeight="1"/>
+    <row r="745" ht="17.25" customHeight="1"/>
+    <row r="746" ht="17.25" customHeight="1"/>
+    <row r="747" ht="17.25" customHeight="1"/>
+    <row r="748" ht="17.25" customHeight="1"/>
+    <row r="749" ht="17.25" customHeight="1"/>
+    <row r="750" ht="17.25" customHeight="1"/>
+    <row r="751" ht="17.25" customHeight="1"/>
+    <row r="752" ht="17.25" customHeight="1"/>
+    <row r="753" ht="17.25" customHeight="1"/>
+    <row r="754" ht="17.25" customHeight="1"/>
+    <row r="755" ht="17.25" customHeight="1"/>
+    <row r="756" ht="17.25" customHeight="1"/>
+    <row r="757" ht="17.25" customHeight="1"/>
+    <row r="758" ht="17.25" customHeight="1"/>
+    <row r="759" ht="17.25" customHeight="1"/>
+    <row r="760" ht="17.25" customHeight="1"/>
+    <row r="761" ht="17.25" customHeight="1"/>
+    <row r="762" ht="17.25" customHeight="1"/>
+    <row r="763" ht="17.25" customHeight="1"/>
+    <row r="764" ht="17.25" customHeight="1"/>
+    <row r="765" ht="17.25" customHeight="1"/>
+    <row r="766" ht="17.25" customHeight="1"/>
+    <row r="767" ht="17.25" customHeight="1"/>
+    <row r="768" ht="17.25" customHeight="1"/>
+    <row r="769" ht="17.25" customHeight="1"/>
+    <row r="770" ht="17.25" customHeight="1"/>
+    <row r="771" ht="17.25" customHeight="1"/>
+    <row r="772" ht="17.25" customHeight="1"/>
+    <row r="773" ht="17.25" customHeight="1"/>
+    <row r="774" ht="17.25" customHeight="1"/>
+    <row r="775" ht="17.25" customHeight="1"/>
+    <row r="776" ht="17.25" customHeight="1"/>
+    <row r="777" ht="17.25" customHeight="1"/>
+    <row r="778" ht="17.25" customHeight="1"/>
+    <row r="779" ht="17.25" customHeight="1"/>
+    <row r="780" ht="17.25" customHeight="1"/>
+    <row r="781" ht="17.25" customHeight="1"/>
+    <row r="782" ht="17.25" customHeight="1"/>
+    <row r="783" ht="17.25" customHeight="1"/>
+    <row r="784" ht="17.25" customHeight="1"/>
+    <row r="785" ht="17.25" customHeight="1"/>
+    <row r="786" ht="17.25" customHeight="1"/>
+    <row r="787" ht="17.25" customHeight="1"/>
+    <row r="788" ht="17.25" customHeight="1"/>
+    <row r="789" ht="17.25" customHeight="1"/>
+    <row r="790" ht="17.25" customHeight="1"/>
+    <row r="791" ht="17.25" customHeight="1"/>
+    <row r="792" ht="17.25" customHeight="1"/>
+    <row r="793" ht="17.25" customHeight="1"/>
+    <row r="794" ht="17.25" customHeight="1"/>
+    <row r="795" ht="17.25" customHeight="1"/>
+    <row r="796" ht="17.25" customHeight="1"/>
+    <row r="797" ht="17.25" customHeight="1"/>
+    <row r="798" ht="17.25" customHeight="1"/>
+    <row r="799" ht="17.25" customHeight="1"/>
+    <row r="800" ht="17.25" customHeight="1"/>
+    <row r="801" ht="17.25" customHeight="1"/>
+    <row r="802" ht="17.25" customHeight="1"/>
+    <row r="803" ht="17.25" customHeight="1"/>
+    <row r="804" ht="17.25" customHeight="1"/>
+    <row r="805" ht="17.25" customHeight="1"/>
+    <row r="806" ht="17.25" customHeight="1"/>
+    <row r="807" ht="17.25" customHeight="1"/>
+    <row r="808" ht="17.25" customHeight="1"/>
+    <row r="809" ht="17.25" customHeight="1"/>
+    <row r="810" ht="17.25" customHeight="1"/>
+    <row r="811" ht="17.25" customHeight="1"/>
+    <row r="812" ht="17.25" customHeight="1"/>
+    <row r="813" ht="17.25" customHeight="1"/>
+    <row r="814" ht="17.25" customHeight="1"/>
+    <row r="815" ht="17.25" customHeight="1"/>
+    <row r="816" ht="17.25" customHeight="1"/>
+    <row r="817" ht="17.25" customHeight="1"/>
+    <row r="818" ht="17.25" customHeight="1"/>
+    <row r="819" ht="17.25" customHeight="1"/>
+    <row r="820" ht="17.25" customHeight="1"/>
+    <row r="821" ht="17.25" customHeight="1"/>
+    <row r="822" ht="17.25" customHeight="1"/>
+    <row r="823" ht="17.25" customHeight="1"/>
+    <row r="824" ht="17.25" customHeight="1"/>
+    <row r="825" ht="17.25" customHeight="1"/>
+    <row r="826" ht="17.25" customHeight="1"/>
+    <row r="827" ht="17.25" customHeight="1"/>
+    <row r="828" ht="17.25" customHeight="1"/>
+    <row r="829" ht="17.25" customHeight="1"/>
+    <row r="830" ht="17.25" customHeight="1"/>
+    <row r="831" ht="17.25" customHeight="1"/>
+    <row r="832" ht="17.25" customHeight="1"/>
+    <row r="833" ht="17.25" customHeight="1"/>
+    <row r="834" ht="17.25" customHeight="1"/>
+    <row r="835" ht="17.25" customHeight="1"/>
+    <row r="836" ht="17.25" customHeight="1"/>
+    <row r="837" ht="17.25" customHeight="1"/>
+    <row r="838" ht="17.25" customHeight="1"/>
+    <row r="839" ht="17.25" customHeight="1"/>
+    <row r="840" ht="17.25" customHeight="1"/>
+    <row r="841" ht="17.25" customHeight="1"/>
+    <row r="842" ht="17.25" customHeight="1"/>
+    <row r="843" ht="17.25" customHeight="1"/>
+    <row r="844" ht="17.25" customHeight="1"/>
+    <row r="845" ht="17.25" customHeight="1"/>
+    <row r="846" ht="17.25" customHeight="1"/>
+    <row r="847" ht="17.25" customHeight="1"/>
+    <row r="848" ht="17.25" customHeight="1"/>
+    <row r="849" ht="17.25" customHeight="1"/>
+    <row r="850" ht="17.25" customHeight="1"/>
+    <row r="851" ht="17.25" customHeight="1"/>
+    <row r="852" ht="17.25" customHeight="1"/>
+    <row r="853" ht="17.25" customHeight="1"/>
+    <row r="854" ht="17.25" customHeight="1"/>
+    <row r="855" ht="17.25" customHeight="1"/>
+    <row r="856" ht="17.25" customHeight="1"/>
+    <row r="857" ht="17.25" customHeight="1"/>
+    <row r="858" ht="17.25" customHeight="1"/>
+    <row r="859" ht="17.25" customHeight="1"/>
+    <row r="860" ht="17.25" customHeight="1"/>
+    <row r="861" ht="17.25" customHeight="1"/>
+    <row r="862" ht="17.25" customHeight="1"/>
+    <row r="863" ht="17.25" customHeight="1"/>
+    <row r="864" ht="17.25" customHeight="1"/>
+    <row r="865" ht="17.25" customHeight="1"/>
+    <row r="866" ht="17.25" customHeight="1"/>
+    <row r="867" ht="17.25" customHeight="1"/>
+    <row r="868" ht="17.25" customHeight="1"/>
+    <row r="869" ht="17.25" customHeight="1"/>
+    <row r="870" ht="17.25" customHeight="1"/>
+    <row r="871" ht="17.25" customHeight="1"/>
+    <row r="872" ht="17.25" customHeight="1"/>
+    <row r="873" ht="17.25" customHeight="1"/>
+    <row r="874" ht="17.25" customHeight="1"/>
+    <row r="875" ht="17.25" customHeight="1"/>
+    <row r="876" ht="17.25" customHeight="1"/>
+    <row r="877" ht="17.25" customHeight="1"/>
+    <row r="878" ht="17.25" customHeight="1"/>
+    <row r="879" ht="17.25" customHeight="1"/>
+    <row r="880" ht="17.25" customHeight="1"/>
+    <row r="881" ht="17.25" customHeight="1"/>
+    <row r="882" ht="17.25" customHeight="1"/>
+    <row r="883" ht="17.25" customHeight="1"/>
+    <row r="884" ht="17.25" customHeight="1"/>
+    <row r="885" ht="17.25" customHeight="1"/>
+    <row r="886" ht="17.25" customHeight="1"/>
+    <row r="887" ht="17.25" customHeight="1"/>
+    <row r="888" ht="17.25" customHeight="1"/>
+    <row r="889" ht="17.25" customHeight="1"/>
+    <row r="890" ht="17.25" customHeight="1"/>
+    <row r="891" ht="17.25" customHeight="1"/>
+    <row r="892" ht="17.25" customHeight="1"/>
+    <row r="893" ht="17.25" customHeight="1"/>
+    <row r="894" ht="17.25" customHeight="1"/>
+    <row r="895" ht="17.25" customHeight="1"/>
+    <row r="896" ht="17.25" customHeight="1"/>
+    <row r="897" ht="17.25" customHeight="1"/>
+    <row r="898" ht="17.25" customHeight="1"/>
+    <row r="899" ht="17.25" customHeight="1"/>
+    <row r="900" ht="17.25" customHeight="1"/>
+    <row r="901" ht="17.25" customHeight="1"/>
+    <row r="902" ht="17.25" customHeight="1"/>
+    <row r="903" ht="17.25" customHeight="1"/>
+    <row r="904" ht="17.25" customHeight="1"/>
+    <row r="905" ht="17.25" customHeight="1"/>
+    <row r="906" ht="17.25" customHeight="1"/>
+    <row r="907" ht="17.25" customHeight="1"/>
+    <row r="908" ht="17.25" customHeight="1"/>
+    <row r="909" ht="17.25" customHeight="1"/>
+    <row r="910" ht="17.25" customHeight="1"/>
+    <row r="911" ht="17.25" customHeight="1"/>
+    <row r="912" ht="17.25" customHeight="1"/>
+    <row r="913" ht="17.25" customHeight="1"/>
+    <row r="914" ht="17.25" customHeight="1"/>
+    <row r="915" ht="17.25" customHeight="1"/>
+    <row r="916" ht="17.25" customHeight="1"/>
+    <row r="917" ht="17.25" customHeight="1"/>
+    <row r="918" ht="17.25" customHeight="1"/>
+    <row r="919" ht="17.25" customHeight="1"/>
+    <row r="920" ht="17.25" customHeight="1"/>
+    <row r="921" ht="17.25" customHeight="1"/>
+    <row r="922" ht="17.25" customHeight="1"/>
+    <row r="923" ht="17.25" customHeight="1"/>
+    <row r="924" ht="17.25" customHeight="1"/>
+    <row r="925" ht="17.25" customHeight="1"/>
+    <row r="926" ht="17.25" customHeight="1"/>
+    <row r="927" ht="17.25" customHeight="1"/>
+    <row r="928" ht="17.25" customHeight="1"/>
+    <row r="929" ht="17.25" customHeight="1"/>
+    <row r="930" ht="17.25" customHeight="1"/>
+    <row r="931" ht="17.25" customHeight="1"/>
+    <row r="932" ht="17.25" customHeight="1"/>
+    <row r="933" ht="17.25" customHeight="1"/>
+    <row r="934" ht="17.25" customHeight="1"/>
+    <row r="935" ht="17.25" customHeight="1"/>
+    <row r="936" ht="17.25" customHeight="1"/>
+    <row r="937" ht="17.25" customHeight="1"/>
+    <row r="938" ht="17.25" customHeight="1"/>
+    <row r="939" ht="17.25" customHeight="1"/>
+    <row r="940" ht="17.25" customHeight="1"/>
+    <row r="941" ht="17.25" customHeight="1"/>
+    <row r="942" ht="17.25" customHeight="1"/>
+    <row r="943" ht="17.25" customHeight="1"/>
+    <row r="944" ht="17.25" customHeight="1"/>
+    <row r="945" ht="17.25" customHeight="1"/>
+    <row r="946" ht="17.25" customHeight="1"/>
+    <row r="947" ht="17.25" customHeight="1"/>
+    <row r="948" ht="17.25" customHeight="1"/>
+    <row r="949" ht="17.25" customHeight="1"/>
+    <row r="950" ht="17.25" customHeight="1"/>
+    <row r="951" ht="17.25" customHeight="1"/>
+    <row r="952" ht="17.25" customHeight="1"/>
+    <row r="953" ht="17.25" customHeight="1"/>
+    <row r="954" ht="17.25" customHeight="1"/>
+    <row r="955" ht="17.25" customHeight="1"/>
+    <row r="956" ht="17.25" customHeight="1"/>
+    <row r="957" ht="17.25" customHeight="1"/>
+    <row r="958" ht="17.25" customHeight="1"/>
+    <row r="959" ht="17.25" customHeight="1"/>
+    <row r="960" ht="17.25" customHeight="1"/>
+    <row r="961" ht="17.25" customHeight="1"/>
+    <row r="962" ht="17.25" customHeight="1"/>
+    <row r="963" ht="17.25" customHeight="1"/>
+    <row r="964" ht="17.25" customHeight="1"/>
+    <row r="965" ht="17.25" customHeight="1"/>
+    <row r="966" ht="17.25" customHeight="1"/>
+    <row r="967" ht="17.25" customHeight="1"/>
+    <row r="968" ht="17.25" customHeight="1"/>
+    <row r="969" ht="17.25" customHeight="1"/>
+    <row r="970" ht="17.25" customHeight="1"/>
+    <row r="971" ht="17.25" customHeight="1"/>
+    <row r="972" ht="17.25" customHeight="1"/>
+    <row r="973" ht="17.25" customHeight="1"/>
+    <row r="974" ht="17.25" customHeight="1"/>
+    <row r="975" ht="17.25" customHeight="1"/>
+    <row r="976" ht="17.25" customHeight="1"/>
+    <row r="977" ht="17.25" customHeight="1"/>
+    <row r="978" ht="17.25" customHeight="1"/>
+    <row r="979" ht="17.25" customHeight="1"/>
+    <row r="980" ht="17.25" customHeight="1"/>
+    <row r="981" ht="17.25" customHeight="1"/>
+    <row r="982" ht="17.25" customHeight="1"/>
+    <row r="983" ht="17.25" customHeight="1"/>
+    <row r="984" ht="17.25" customHeight="1"/>
+    <row r="985" ht="17.25" customHeight="1"/>
+    <row r="986" ht="17.25" customHeight="1"/>
+    <row r="987" ht="17.25" customHeight="1"/>
+    <row r="988" ht="17.25" customHeight="1"/>
+    <row r="989" ht="17.25" customHeight="1"/>
+    <row r="990" ht="17.25" customHeight="1"/>
+    <row r="991" ht="17.25" customHeight="1"/>
+    <row r="992" ht="17.25" customHeight="1"/>
+    <row r="993" ht="17.25" customHeight="1"/>
+    <row r="994" ht="17.25" customHeight="1"/>
+    <row r="995" ht="17.25" customHeight="1"/>
+    <row r="996" ht="17.25" customHeight="1"/>
+    <row r="997" ht="17.25" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>

--- a/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="PjQ/ZH5dNfpZSLhuzuhQKuy/nAO/JzfJl7JGthYVMbo="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="enqOkH1Z/tfQ3WIfr7wm+HPEzSLVVhkZawHcM088EJg="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="240">
   <si>
     <t>미리 로드할 어드레서블 테이블</t>
   </si>
@@ -384,12 +384,6 @@
     <t>Jewel_Cone[Cone]</t>
   </si>
   <si>
-    <t>PreLoadAsset_Mesh_Jewel_Stone[Cube.058]</t>
-  </si>
-  <si>
-    <t>Jewel_Stone[Cube.058]</t>
-  </si>
-  <si>
     <t>PreLoadAsset_Material_Lit</t>
   </si>
   <si>
@@ -426,6 +420,18 @@
     <t>Mesh_IronBox_Prefab</t>
   </si>
   <si>
+    <t>PreLoadAsset_GameObject_MeshBrokenIronBoxPrefab</t>
+  </si>
+  <si>
+    <t>Mesh_BrokenIronBox_Prefab</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_GameObject_MeshSafePrefab</t>
+  </si>
+  <si>
+    <t>Mesh_Safe_Prefab</t>
+  </si>
+  <si>
     <t>PreLoadAsset_GameObject_MeshWoodBoxPrefab</t>
   </si>
   <si>
@@ -570,6 +576,12 @@
     <t>Police_Throw</t>
   </si>
   <si>
+    <t>PreLoadAsset_Police_Dog</t>
+  </si>
+  <si>
+    <t>Police_Dog</t>
+  </si>
+  <si>
     <t>PreLoadAsset_GameObject_StatueObject</t>
   </si>
   <si>
@@ -712,6 +724,12 @@
   </si>
   <si>
     <t>MeshCollider_Junk_Bottle_Pink_Large</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_MeshCollier_Junk_Glasses</t>
+  </si>
+  <si>
+    <t>MeshCollider_Junk_Glasses</t>
   </si>
   <si>
     <t>PreLoadAsset_GameObject_ItemObject</t>
@@ -1565,21 +1583,18 @@
       </c>
     </row>
     <row r="61" ht="17.25" customHeight="1">
-      <c r="A61" s="9" t="s">
+      <c r="A61" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B61" s="10" t="s">
+      <c r="B61" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C61" s="10" t="s">
-        <v>103</v>
-      </c>
     </row>
     <row r="62" ht="17.25" customHeight="1">
-      <c r="A62" s="2" t="s">
+      <c r="A62" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B62" s="10" t="s">
         <v>125</v>
       </c>
     </row>
@@ -1656,7 +1671,7 @@
       </c>
     </row>
     <row r="72" ht="17.25" customHeight="1">
-      <c r="A72" s="10" t="s">
+      <c r="A72" s="9" t="s">
         <v>144</v>
       </c>
       <c r="B72" s="10" t="s">
@@ -1672,14 +1687,11 @@
       </c>
     </row>
     <row r="74" ht="17.25" customHeight="1">
-      <c r="A74" s="11" t="s">
+      <c r="A74" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="B74" s="11" t="s">
+      <c r="B74" s="10" t="s">
         <v>149</v>
-      </c>
-      <c r="C74" s="11" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="75" ht="17.25" customHeight="1">
@@ -1733,7 +1745,9 @@
       <c r="B79" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="C79" s="12"/>
+      <c r="C79" s="11" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="80" ht="17.25" customHeight="1">
       <c r="A80" s="11" t="s">
@@ -1808,12 +1822,13 @@
       <c r="C87" s="12"/>
     </row>
     <row r="88" ht="17.25" customHeight="1">
-      <c r="A88" s="10" t="s">
+      <c r="A88" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="B88" s="10" t="s">
+      <c r="B88" s="11" t="s">
         <v>177</v>
       </c>
+      <c r="C88" s="12"/>
     </row>
     <row r="89" ht="17.25" customHeight="1">
       <c r="A89" s="10" t="s">
@@ -1840,30 +1855,26 @@
       </c>
     </row>
     <row r="92" ht="17.25" customHeight="1">
-      <c r="A92" s="11" t="s">
+      <c r="A92" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="B92" s="11" t="s">
+      <c r="B92" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="C92" s="12"/>
     </row>
     <row r="93" ht="17.25" customHeight="1">
-      <c r="A93" s="11" t="s">
+      <c r="A93" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="B93" s="13" t="s">
+      <c r="B93" s="10" t="s">
         <v>187</v>
-      </c>
-      <c r="C93" s="11" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="94" ht="17.25" customHeight="1">
       <c r="A94" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="B94" s="13" t="s">
+      <c r="B94" s="11" t="s">
         <v>189</v>
       </c>
       <c r="C94" s="12"/>
@@ -1875,7 +1886,9 @@
       <c r="B95" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="C95" s="12"/>
+      <c r="C95" s="11" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="96" ht="17.25" customHeight="1">
       <c r="A96" s="11" t="s">
@@ -1896,20 +1909,22 @@
       <c r="C97" s="12"/>
     </row>
     <row r="98" ht="17.25" customHeight="1">
-      <c r="A98" s="10" t="s">
+      <c r="A98" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="B98" s="10" t="s">
+      <c r="B98" s="13" t="s">
         <v>197</v>
       </c>
+      <c r="C98" s="12"/>
     </row>
     <row r="99" ht="17.25" customHeight="1">
-      <c r="A99" s="10" t="s">
+      <c r="A99" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="B99" s="10" t="s">
+      <c r="B99" s="13" t="s">
         <v>199</v>
       </c>
+      <c r="C99" s="12"/>
     </row>
     <row r="100" ht="17.25" customHeight="1">
       <c r="A100" s="10" t="s">
@@ -1955,30 +1970,24 @@
       <c r="A105" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="B105" s="14" t="s">
+      <c r="B105" s="10" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="106" ht="17.25" customHeight="1">
-      <c r="A106" s="15" t="s">
+      <c r="A106" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="B106" s="16" t="s">
+      <c r="B106" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="C106" s="11" t="s">
-        <v>103</v>
-      </c>
     </row>
     <row r="107" ht="17.25" customHeight="1">
-      <c r="A107" s="15" t="s">
+      <c r="A107" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="B107" s="15" t="s">
+      <c r="B107" s="14" t="s">
         <v>215</v>
-      </c>
-      <c r="C107" s="11" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="108" ht="17.25" customHeight="1">
@@ -1996,7 +2005,7 @@
       <c r="A109" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="B109" s="16" t="s">
+      <c r="B109" s="15" t="s">
         <v>219</v>
       </c>
       <c r="C109" s="11" t="s">
@@ -2037,11 +2046,14 @@
       </c>
     </row>
     <row r="113" ht="17.25" customHeight="1">
-      <c r="A113" s="10" t="s">
+      <c r="A113" s="15" t="s">
         <v>226</v>
       </c>
-      <c r="B113" s="14" t="s">
+      <c r="B113" s="16" t="s">
         <v>227</v>
+      </c>
+      <c r="C113" s="11" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="114" ht="17.25" customHeight="1">
@@ -2056,27 +2068,54 @@
       </c>
     </row>
     <row r="115" ht="17.25" customHeight="1">
-      <c r="A115" s="15" t="s">
+      <c r="A115" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="B115" s="16" t="s">
+      <c r="B115" s="14" t="s">
         <v>231</v>
       </c>
-      <c r="C115" s="11" t="s">
+    </row>
+    <row r="116" ht="17.25" customHeight="1">
+      <c r="A116" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="B116" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="C116" s="11" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="116" ht="17.25" customHeight="1">
-      <c r="A116" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="B116" s="10" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="117" ht="17.25" customHeight="1"/>
-    <row r="118" ht="17.25" customHeight="1"/>
-    <row r="119" ht="17.25" customHeight="1"/>
+    <row r="117" ht="17.25" customHeight="1">
+      <c r="A117" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="B117" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="C117" s="11" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="118" ht="17.25" customHeight="1">
+      <c r="A118" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="B118" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="C118" s="11" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="119" ht="17.25" customHeight="1">
+      <c r="A119" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="B119" s="10" t="s">
+        <v>239</v>
+      </c>
+    </row>
     <row r="120" ht="17.25" customHeight="1"/>
     <row r="121" ht="17.25" customHeight="1"/>
     <row r="122" ht="17.25" customHeight="1"/>
@@ -2955,6 +2994,9 @@
     <row r="995" ht="17.25" customHeight="1"/>
     <row r="996" ht="17.25" customHeight="1"/>
     <row r="997" ht="17.25" customHeight="1"/>
+    <row r="998" ht="17.25" customHeight="1"/>
+    <row r="999" ht="17.25" customHeight="1"/>
+    <row r="1000" ht="17.25" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>

--- a/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="PjQ/ZH5dNfpZSLhuzuhQKuy/nAO/JzfJl7JGthYVMbo="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="v4mvBJYERGqiNruBTfijDgsGfB1L8a5WYzdi61pNbdg="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="234">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="238">
   <si>
     <t>미리 로드할 어드레서블 테이블</t>
   </si>
@@ -424,6 +424,18 @@
   </si>
   <si>
     <t>Mesh_IronBox_Prefab</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_GameObject_MeshBrokenIronBoxPrefab</t>
+  </si>
+  <si>
+    <t>Mesh_BrokenIronBox_Prefab</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_GameObject_MeshSafePrefab</t>
+  </si>
+  <si>
+    <t>Mesh_Safe_Prefab</t>
   </si>
   <si>
     <t>PreLoadAsset_GameObject_MeshWoodBoxPrefab</t>
@@ -724,7 +736,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -754,6 +766,11 @@
       <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="&quot;Malgun Gothic&quot;"/>
     </font>
     <font>
       <sz val="11.0"/>
@@ -810,7 +827,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -835,7 +852,13 @@
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -844,10 +867,10 @@
     <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -1624,18 +1647,18 @@
       </c>
     </row>
     <row r="68" ht="17.25" customHeight="1">
-      <c r="A68" s="9" t="s">
+      <c r="A68" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="B68" s="10" t="s">
+      <c r="B68" s="12" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="69" ht="17.25" customHeight="1">
-      <c r="A69" s="9" t="s">
+      <c r="A69" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="B69" s="10" t="s">
+      <c r="B69" s="12" t="s">
         <v>139</v>
       </c>
     </row>
@@ -1656,7 +1679,7 @@
       </c>
     </row>
     <row r="72" ht="17.25" customHeight="1">
-      <c r="A72" s="10" t="s">
+      <c r="A72" s="9" t="s">
         <v>144</v>
       </c>
       <c r="B72" s="10" t="s">
@@ -1664,7 +1687,7 @@
       </c>
     </row>
     <row r="73" ht="17.25" customHeight="1">
-      <c r="A73" s="10" t="s">
+      <c r="A73" s="9" t="s">
         <v>146</v>
       </c>
       <c r="B73" s="10" t="s">
@@ -1672,156 +1695,156 @@
       </c>
     </row>
     <row r="74" ht="17.25" customHeight="1">
-      <c r="A74" s="11" t="s">
+      <c r="A74" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="B74" s="11" t="s">
+      <c r="B74" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="C74" s="11" t="s">
+    </row>
+    <row r="75" ht="17.25" customHeight="1">
+      <c r="A75" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="B75" s="10" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="76" ht="17.25" customHeight="1">
+      <c r="A76" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="B76" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="C76" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="75" ht="17.25" customHeight="1">
-      <c r="A75" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="B75" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="C75" s="11" t="s">
+    <row r="77" ht="17.25" customHeight="1">
+      <c r="A77" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="B77" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="C77" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="76" ht="17.25" customHeight="1">
-      <c r="A76" s="11" t="s">
-        <v>152</v>
-      </c>
-      <c r="B76" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="C76" s="11" t="s">
+    <row r="78" ht="17.25" customHeight="1">
+      <c r="A78" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="B78" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="C78" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="77" ht="17.25" customHeight="1">
-      <c r="A77" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="B77" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="C77" s="11" t="s">
+    <row r="79" ht="17.25" customHeight="1">
+      <c r="A79" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="B79" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="C79" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="78" ht="17.25" customHeight="1">
-      <c r="A78" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="B78" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="C78" s="11" t="s">
+    <row r="80" ht="17.25" customHeight="1">
+      <c r="A80" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="B80" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="C80" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="79" ht="17.25" customHeight="1">
-      <c r="A79" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="B79" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="C79" s="12"/>
-    </row>
-    <row r="80" ht="17.25" customHeight="1">
-      <c r="A80" s="11" t="s">
-        <v>160</v>
-      </c>
-      <c r="B80" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="C80" s="12"/>
-    </row>
     <row r="81" ht="17.25" customHeight="1">
-      <c r="A81" s="11" t="s">
+      <c r="A81" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="B81" s="11" t="s">
+      <c r="B81" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="C81" s="12"/>
+      <c r="C81" s="14"/>
     </row>
     <row r="82" ht="17.25" customHeight="1">
-      <c r="A82" s="11" t="s">
+      <c r="A82" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="B82" s="11" t="s">
+      <c r="B82" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="C82" s="12"/>
+      <c r="C82" s="14"/>
     </row>
     <row r="83" ht="17.25" customHeight="1">
-      <c r="A83" s="11" t="s">
+      <c r="A83" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="B83" s="11" t="s">
+      <c r="B83" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="C83" s="12"/>
+      <c r="C83" s="14"/>
     </row>
     <row r="84" ht="17.25" customHeight="1">
-      <c r="A84" s="11" t="s">
+      <c r="A84" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="B84" s="11" t="s">
+      <c r="B84" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="C84" s="12"/>
+      <c r="C84" s="14"/>
     </row>
     <row r="85" ht="17.25" customHeight="1">
-      <c r="A85" s="11" t="s">
+      <c r="A85" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="B85" s="11" t="s">
+      <c r="B85" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="C85" s="12"/>
+      <c r="C85" s="14"/>
     </row>
     <row r="86" ht="17.25" customHeight="1">
-      <c r="A86" s="11" t="s">
+      <c r="A86" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="B86" s="11" t="s">
+      <c r="B86" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="C86" s="12"/>
+      <c r="C86" s="14"/>
     </row>
     <row r="87" ht="17.25" customHeight="1">
-      <c r="A87" s="11" t="s">
+      <c r="A87" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="B87" s="11" t="s">
+      <c r="B87" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="C87" s="12"/>
+      <c r="C87" s="14"/>
     </row>
     <row r="88" ht="17.25" customHeight="1">
-      <c r="A88" s="10" t="s">
+      <c r="A88" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="B88" s="10" t="s">
+      <c r="B88" s="13" t="s">
         <v>177</v>
       </c>
+      <c r="C88" s="14"/>
     </row>
     <row r="89" ht="17.25" customHeight="1">
-      <c r="A89" s="10" t="s">
+      <c r="A89" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="B89" s="10" t="s">
+      <c r="B89" s="13" t="s">
         <v>179</v>
       </c>
+      <c r="C89" s="14"/>
     </row>
     <row r="90" ht="17.25" customHeight="1">
       <c r="A90" s="10" t="s">
@@ -1840,76 +1863,76 @@
       </c>
     </row>
     <row r="92" ht="17.25" customHeight="1">
-      <c r="A92" s="11" t="s">
+      <c r="A92" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="B92" s="11" t="s">
+      <c r="B92" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="C92" s="12"/>
     </row>
     <row r="93" ht="17.25" customHeight="1">
-      <c r="A93" s="11" t="s">
+      <c r="A93" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="B93" s="13" t="s">
+      <c r="B93" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="C93" s="11" t="s">
-        <v>103</v>
-      </c>
     </row>
     <row r="94" ht="17.25" customHeight="1">
-      <c r="A94" s="11" t="s">
+      <c r="A94" s="13" t="s">
         <v>188</v>
       </c>
       <c r="B94" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="C94" s="12"/>
+      <c r="C94" s="14"/>
     </row>
     <row r="95" ht="17.25" customHeight="1">
-      <c r="A95" s="11" t="s">
+      <c r="A95" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="B95" s="13" t="s">
+      <c r="B95" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="C95" s="12"/>
+      <c r="C95" s="13" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="96" ht="17.25" customHeight="1">
-      <c r="A96" s="11" t="s">
+      <c r="A96" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="B96" s="13" t="s">
+      <c r="B96" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="C96" s="12"/>
+      <c r="C96" s="14"/>
     </row>
     <row r="97" ht="17.25" customHeight="1">
-      <c r="A97" s="11" t="s">
+      <c r="A97" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="B97" s="13" t="s">
+      <c r="B97" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="C97" s="12"/>
+      <c r="C97" s="14"/>
     </row>
     <row r="98" ht="17.25" customHeight="1">
-      <c r="A98" s="10" t="s">
+      <c r="A98" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="B98" s="10" t="s">
+      <c r="B98" s="15" t="s">
         <v>197</v>
       </c>
+      <c r="C98" s="14"/>
     </row>
     <row r="99" ht="17.25" customHeight="1">
-      <c r="A99" s="10" t="s">
+      <c r="A99" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="B99" s="10" t="s">
+      <c r="B99" s="15" t="s">
         <v>199</v>
       </c>
+      <c r="C99" s="14"/>
     </row>
     <row r="100" ht="17.25" customHeight="1">
       <c r="A100" s="10" t="s">
@@ -1955,127 +1978,141 @@
       <c r="A105" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="B105" s="14" t="s">
+      <c r="B105" s="10" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="106" ht="17.25" customHeight="1">
-      <c r="A106" s="15" t="s">
+      <c r="A106" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="B106" s="16" t="s">
+      <c r="B106" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="C106" s="11" t="s">
+    </row>
+    <row r="107" ht="17.25" customHeight="1">
+      <c r="A107" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="B107" s="16" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="108" ht="17.25" customHeight="1">
+      <c r="A108" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="B108" s="18" t="s">
+        <v>217</v>
+      </c>
+      <c r="C108" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="107" ht="17.25" customHeight="1">
-      <c r="A107" s="15" t="s">
-        <v>214</v>
-      </c>
-      <c r="B107" s="15" t="s">
-        <v>215</v>
-      </c>
-      <c r="C107" s="11" t="s">
+    <row r="109" ht="17.25" customHeight="1">
+      <c r="A109" s="17" t="s">
+        <v>218</v>
+      </c>
+      <c r="B109" s="17" t="s">
+        <v>219</v>
+      </c>
+      <c r="C109" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="108" ht="17.25" customHeight="1">
-      <c r="A108" s="15" t="s">
-        <v>216</v>
-      </c>
-      <c r="B108" s="16" t="s">
-        <v>217</v>
-      </c>
-      <c r="C108" s="11" t="s">
+    <row r="110" ht="17.25" customHeight="1">
+      <c r="A110" s="17" t="s">
+        <v>220</v>
+      </c>
+      <c r="B110" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="C110" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="109" ht="17.25" customHeight="1">
-      <c r="A109" s="15" t="s">
-        <v>218</v>
-      </c>
-      <c r="B109" s="16" t="s">
-        <v>219</v>
-      </c>
-      <c r="C109" s="11" t="s">
+    <row r="111" ht="17.25" customHeight="1">
+      <c r="A111" s="17" t="s">
+        <v>222</v>
+      </c>
+      <c r="B111" s="18" t="s">
+        <v>223</v>
+      </c>
+      <c r="C111" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="110" ht="17.25" customHeight="1">
-      <c r="A110" s="15" t="s">
-        <v>220</v>
-      </c>
-      <c r="B110" s="16" t="s">
-        <v>221</v>
-      </c>
-      <c r="C110" s="11" t="s">
+    <row r="112" ht="17.25" customHeight="1">
+      <c r="A112" s="17" t="s">
+        <v>224</v>
+      </c>
+      <c r="B112" s="18" t="s">
+        <v>225</v>
+      </c>
+      <c r="C112" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="111" ht="17.25" customHeight="1">
-      <c r="A111" s="15" t="s">
-        <v>222</v>
-      </c>
-      <c r="B111" s="16" t="s">
-        <v>223</v>
-      </c>
-      <c r="C111" s="11" t="s">
+    <row r="113" ht="17.25" customHeight="1">
+      <c r="A113" s="17" t="s">
+        <v>226</v>
+      </c>
+      <c r="B113" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="C113" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="112" ht="17.25" customHeight="1">
-      <c r="A112" s="15" t="s">
-        <v>224</v>
-      </c>
-      <c r="B112" s="16" t="s">
-        <v>225</v>
-      </c>
-      <c r="C112" s="11" t="s">
+    <row r="114" ht="17.25" customHeight="1">
+      <c r="A114" s="17" t="s">
+        <v>228</v>
+      </c>
+      <c r="B114" s="18" t="s">
+        <v>229</v>
+      </c>
+      <c r="C114" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="113" ht="17.25" customHeight="1">
-      <c r="A113" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="B113" s="14" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="114" ht="17.25" customHeight="1">
-      <c r="A114" s="15" t="s">
-        <v>228</v>
-      </c>
-      <c r="B114" s="16" t="s">
-        <v>229</v>
-      </c>
-      <c r="C114" s="11" t="s">
-        <v>103</v>
-      </c>
-    </row>
     <row r="115" ht="17.25" customHeight="1">
-      <c r="A115" s="15" t="s">
+      <c r="A115" s="10" t="s">
         <v>230</v>
       </c>
       <c r="B115" s="16" t="s">
         <v>231</v>
       </c>
-      <c r="C115" s="11" t="s">
+    </row>
+    <row r="116" ht="17.25" customHeight="1">
+      <c r="A116" s="17" t="s">
+        <v>232</v>
+      </c>
+      <c r="B116" s="18" t="s">
+        <v>233</v>
+      </c>
+      <c r="C116" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="116" ht="17.25" customHeight="1">
-      <c r="A116" s="10" t="s">
-        <v>232</v>
-      </c>
-      <c r="B116" s="10" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="117" ht="17.25" customHeight="1"/>
-    <row r="118" ht="17.25" customHeight="1"/>
+    <row r="117" ht="17.25" customHeight="1">
+      <c r="A117" s="17" t="s">
+        <v>234</v>
+      </c>
+      <c r="B117" s="18" t="s">
+        <v>235</v>
+      </c>
+      <c r="C117" s="13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="118" ht="17.25" customHeight="1">
+      <c r="A118" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="B118" s="10" t="s">
+        <v>237</v>
+      </c>
+    </row>
     <row r="119" ht="17.25" customHeight="1"/>
     <row r="120" ht="17.25" customHeight="1"/>
     <row r="121" ht="17.25" customHeight="1"/>
@@ -2955,6 +2992,8 @@
     <row r="995" ht="17.25" customHeight="1"/>
     <row r="996" ht="17.25" customHeight="1"/>
     <row r="997" ht="17.25" customHeight="1"/>
+    <row r="998" ht="17.25" customHeight="1"/>
+    <row r="999" ht="17.25" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>

--- a/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="v4mvBJYERGqiNruBTfijDgsGfB1L8a5WYzdi61pNbdg="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="ON79YGRFmG0PvJZg2zw1gtIfJ/OB/TVqK39qUUOl2CE="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="236">
   <si>
     <t>미리 로드할 어드레서블 테이블</t>
   </si>
@@ -688,12 +688,6 @@
   </si>
   <si>
     <t>Junk_Fish[SM_Prop_Display_Fish_02]</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_Mesh_Junk_Glasses</t>
-  </si>
-  <si>
-    <t>Junk_Glasses[SM_Prop_Glasses_01]</t>
   </si>
   <si>
     <t>PreLoadAsset_Mesh_Junk_Microphone</t>
@@ -2065,22 +2059,22 @@
       </c>
     </row>
     <row r="114" ht="17.25" customHeight="1">
-      <c r="A114" s="17" t="s">
+      <c r="A114" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="B114" s="18" t="s">
+      <c r="B114" s="16" t="s">
         <v>229</v>
       </c>
-      <c r="C114" s="13" t="s">
+    </row>
+    <row r="115" ht="17.25" customHeight="1">
+      <c r="A115" s="17" t="s">
+        <v>230</v>
+      </c>
+      <c r="B115" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="C115" s="13" t="s">
         <v>103</v>
-      </c>
-    </row>
-    <row r="115" ht="17.25" customHeight="1">
-      <c r="A115" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="B115" s="16" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="116" ht="17.25" customHeight="1">
@@ -2095,24 +2089,14 @@
       </c>
     </row>
     <row r="117" ht="17.25" customHeight="1">
-      <c r="A117" s="17" t="s">
+      <c r="A117" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="B117" s="18" t="s">
+      <c r="B117" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="C117" s="13" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="118" ht="17.25" customHeight="1">
-      <c r="A118" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="B118" s="10" t="s">
-        <v>237</v>
-      </c>
-    </row>
+    </row>
+    <row r="118" ht="17.25" customHeight="1"/>
     <row r="119" ht="17.25" customHeight="1"/>
     <row r="120" ht="17.25" customHeight="1"/>
     <row r="121" ht="17.25" customHeight="1"/>
@@ -2993,7 +2977,6 @@
     <row r="996" ht="17.25" customHeight="1"/>
     <row r="997" ht="17.25" customHeight="1"/>
     <row r="998" ht="17.25" customHeight="1"/>
-    <row r="999" ht="17.25" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>

--- a/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="ON79YGRFmG0PvJZg2zw1gtIfJ/OB/TVqK39qUUOl2CE="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="v4mvBJYERGqiNruBTfijDgsGfB1L8a5WYzdi61pNbdg="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="238">
   <si>
     <t>미리 로드할 어드레서블 테이블</t>
   </si>
@@ -688,6 +688,12 @@
   </si>
   <si>
     <t>Junk_Fish[SM_Prop_Display_Fish_02]</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_Junk_Glasses</t>
+  </si>
+  <si>
+    <t>Junk_Glasses[SM_Prop_Glasses_01]</t>
   </si>
   <si>
     <t>PreLoadAsset_Mesh_Junk_Microphone</t>
@@ -2059,22 +2065,22 @@
       </c>
     </row>
     <row r="114" ht="17.25" customHeight="1">
-      <c r="A114" s="10" t="s">
+      <c r="A114" s="17" t="s">
         <v>228</v>
       </c>
-      <c r="B114" s="16" t="s">
+      <c r="B114" s="18" t="s">
         <v>229</v>
       </c>
+      <c r="C114" s="13" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="115" ht="17.25" customHeight="1">
-      <c r="A115" s="17" t="s">
+      <c r="A115" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="B115" s="18" t="s">
+      <c r="B115" s="16" t="s">
         <v>231</v>
-      </c>
-      <c r="C115" s="13" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="116" ht="17.25" customHeight="1">
@@ -2089,14 +2095,24 @@
       </c>
     </row>
     <row r="117" ht="17.25" customHeight="1">
-      <c r="A117" s="10" t="s">
+      <c r="A117" s="17" t="s">
         <v>234</v>
       </c>
-      <c r="B117" s="10" t="s">
+      <c r="B117" s="18" t="s">
         <v>235</v>
       </c>
-    </row>
-    <row r="118" ht="17.25" customHeight="1"/>
+      <c r="C117" s="13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="118" ht="17.25" customHeight="1">
+      <c r="A118" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="B118" s="10" t="s">
+        <v>237</v>
+      </c>
+    </row>
     <row r="119" ht="17.25" customHeight="1"/>
     <row r="120" ht="17.25" customHeight="1"/>
     <row r="121" ht="17.25" customHeight="1"/>
@@ -2977,6 +2993,7 @@
     <row r="996" ht="17.25" customHeight="1"/>
     <row r="997" ht="17.25" customHeight="1"/>
     <row r="998" ht="17.25" customHeight="1"/>
+    <row r="999" ht="17.25" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>

--- a/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="248">
   <si>
     <t>미리 로드할 어드레서블 테이블</t>
   </si>
@@ -730,6 +730,36 @@
   </si>
   <si>
     <t>ItemObject</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_GameObject_Turret</t>
+  </si>
+  <si>
+    <t>TurretTrap</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_GameObject_Turret_Bullet</t>
+  </si>
+  <si>
+    <t>Turret_Bullet</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_GameObject_StonTrap</t>
+  </si>
+  <si>
+    <t>StonTrap</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_GameObject_WebTrap</t>
+  </si>
+  <si>
+    <t>WebTrap</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_GameObject_BaseTrap</t>
+  </si>
+  <si>
+    <t>BaseTrap</t>
   </si>
 </sst>
 </file>
@@ -2113,11 +2143,46 @@
         <v>237</v>
       </c>
     </row>
-    <row r="119" ht="17.25" customHeight="1"/>
-    <row r="120" ht="17.25" customHeight="1"/>
-    <row r="121" ht="17.25" customHeight="1"/>
-    <row r="122" ht="17.25" customHeight="1"/>
-    <row r="123" ht="17.25" customHeight="1"/>
+    <row r="119" ht="17.25" customHeight="1">
+      <c r="A119" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="B119" s="10" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="120" ht="17.25" customHeight="1">
+      <c r="A120" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="B120" s="10" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="121" ht="17.25" customHeight="1">
+      <c r="A121" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="B121" s="10" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="122" ht="17.25" customHeight="1">
+      <c r="A122" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="B122" s="10" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="123" ht="17.25" customHeight="1">
+      <c r="A123" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="B123" s="10" t="s">
+        <v>247</v>
+      </c>
+    </row>
     <row r="124" ht="17.25" customHeight="1"/>
     <row r="125" ht="17.25" customHeight="1"/>
     <row r="126" ht="17.25" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
@@ -1,22 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="v4mvBJYERGqiNruBTfijDgsGfB1L8a5WYzdi61pNbdg="/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="254">
   <si>
     <t>미리 로드할 어드레서블 테이블</t>
   </si>
@@ -760,64 +771,237 @@
   </si>
   <si>
     <t>BaseTrap</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_GameObject_MushroomTrap</t>
+  </si>
+  <si>
+    <t>MushroomTrap</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_Color_1</t>
+  </si>
+  <si>
+    <t>Color_1</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Material_Color_2</t>
+  </si>
+  <si>
+    <t>Color_2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="27">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Malgun Gothic"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Malgun Gothic"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="&quot;Malgun Gothic&quot;"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
-      <color theme="1"/>
-      <name val="Malgun Gothic"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.0"/>
-      <color theme="1"/>
-      <name val="Malgun Gothic"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.0"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
-      <color rgb="FF000000"/>
-      <name val="&quot;Malgun Gothic&quot;"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.0"/>
-      <color rgb="FF000000"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -825,9 +1009,201 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
-    <border/>
+  <borders count="11">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -841,6 +1217,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -852,71 +1229,550 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="2" fillId="2" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
+  <cellXfs count="15">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1106,23 +1962,23 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C999"/>
+  <sheetFormatPr defaultColWidth="14.4259259259259" defaultRowHeight="15" customHeight="1" outlineLevelCol="2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="52.14"/>
-    <col customWidth="1" min="2" max="2" width="35.14"/>
-    <col customWidth="1" min="3" max="3" width="31.43"/>
-    <col customWidth="1" min="4" max="26" width="9.0"/>
+    <col min="1" max="1" width="52.1388888888889" customWidth="1"/>
+    <col min="2" max="2" width="35.1388888888889" customWidth="1"/>
+    <col min="3" max="3" width="31.4259259259259" customWidth="1"/>
+    <col min="4" max="26" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1">
+    <row r="1" ht="17.25" customHeight="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1133,7 +1989,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="17.25" customHeight="1">
+    <row r="2" ht="17.25" customHeight="1" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1144,7 +2000,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" ht="17.25" customHeight="1">
+    <row r="3" ht="17.25" customHeight="1" spans="1:3">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1155,7 +2011,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" ht="17.25" customHeight="1">
+    <row r="4" ht="17.25" customHeight="1" spans="1:3">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1163,7 +2019,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" ht="17.25" customHeight="1">
+    <row r="5" ht="17.25" customHeight="1" spans="1:3">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -1171,7 +2027,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" ht="17.25" customHeight="1">
+    <row r="6" ht="17.25" customHeight="1" spans="1:3">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -1179,7 +2035,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" ht="17.25" customHeight="1">
+    <row r="7" ht="17.25" customHeight="1" spans="1:3">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -1187,7 +2043,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" ht="17.25" customHeight="1">
+    <row r="8" ht="17.25" customHeight="1" spans="1:3">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -1195,7 +2051,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" ht="17.25" customHeight="1">
+    <row r="9" ht="17.25" customHeight="1" spans="1:3">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -1203,7 +2059,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" ht="17.25" customHeight="1">
+    <row r="10" ht="17.25" customHeight="1" spans="1:3">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -1211,7 +2067,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" ht="17.25" customHeight="1">
+    <row r="11" ht="17.25" customHeight="1" spans="1:3">
       <c r="A11" s="1" t="s">
         <v>21</v>
       </c>
@@ -1219,7 +2075,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" ht="17.25" customHeight="1">
+    <row r="12" ht="17.25" customHeight="1" spans="1:3">
       <c r="A12" s="1" t="s">
         <v>23</v>
       </c>
@@ -1227,7 +2083,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" ht="17.25" customHeight="1">
+    <row r="13" ht="17.25" customHeight="1" spans="1:3">
       <c r="A13" s="1" t="s">
         <v>25</v>
       </c>
@@ -1235,7 +2091,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" ht="17.25" customHeight="1">
+    <row r="14" ht="17.25" customHeight="1" spans="1:3">
       <c r="A14" s="1" t="s">
         <v>27</v>
       </c>
@@ -1243,7 +2099,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" ht="17.25" customHeight="1">
+    <row r="15" ht="17.25" customHeight="1" spans="1:3">
       <c r="A15" s="1" t="s">
         <v>29</v>
       </c>
@@ -1251,7 +2107,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" ht="17.25" customHeight="1">
+    <row r="16" ht="17.25" customHeight="1" spans="1:3">
       <c r="A16" s="1" t="s">
         <v>31</v>
       </c>
@@ -1259,7 +2115,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" ht="17.25" customHeight="1">
+    <row r="17" ht="17.25" customHeight="1" spans="1:2">
       <c r="A17" s="1" t="s">
         <v>33</v>
       </c>
@@ -1267,7 +2123,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" ht="17.25" customHeight="1">
+    <row r="18" ht="17.25" customHeight="1" spans="1:2">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -1275,7 +2131,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" ht="17.25" customHeight="1">
+    <row r="19" ht="17.25" customHeight="1" spans="1:2">
       <c r="A19" s="1" t="s">
         <v>37</v>
       </c>
@@ -1283,7 +2139,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" ht="17.25" customHeight="1">
+    <row r="20" ht="17.25" customHeight="1" spans="1:2">
       <c r="A20" s="1" t="s">
         <v>39</v>
       </c>
@@ -1291,7 +2147,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" ht="17.25" customHeight="1">
+    <row r="21" ht="17.25" customHeight="1" spans="1:2">
       <c r="A21" s="1" t="s">
         <v>41</v>
       </c>
@@ -1299,7 +2155,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" ht="17.25" customHeight="1">
+    <row r="22" ht="17.25" customHeight="1" spans="1:2">
       <c r="A22" s="1" t="s">
         <v>43</v>
       </c>
@@ -1307,7 +2163,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" ht="17.25" customHeight="1">
+    <row r="23" ht="17.25" customHeight="1" spans="1:2">
       <c r="A23" s="1" t="s">
         <v>45</v>
       </c>
@@ -1315,7 +2171,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" ht="17.25" customHeight="1">
+    <row r="24" ht="17.25" customHeight="1" spans="1:2">
       <c r="A24" s="1" t="s">
         <v>47</v>
       </c>
@@ -1323,7 +2179,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" ht="17.25" customHeight="1">
+    <row r="25" ht="17.25" customHeight="1" spans="1:2">
       <c r="A25" s="1" t="s">
         <v>49</v>
       </c>
@@ -1331,7 +2187,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" ht="17.25" customHeight="1">
+    <row r="26" ht="17.25" customHeight="1" spans="1:2">
       <c r="A26" s="1" t="s">
         <v>51</v>
       </c>
@@ -1339,7 +2195,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" ht="17.25" customHeight="1">
+    <row r="27" ht="17.25" customHeight="1" spans="1:2">
       <c r="A27" s="1" t="s">
         <v>53</v>
       </c>
@@ -1347,7 +2203,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" ht="17.25" customHeight="1">
+    <row r="28" ht="17.25" customHeight="1" spans="1:2">
       <c r="A28" s="1" t="s">
         <v>55</v>
       </c>
@@ -1355,7 +2211,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" ht="17.25" customHeight="1">
+    <row r="29" ht="17.25" customHeight="1" spans="1:2">
       <c r="A29" s="1" t="s">
         <v>57</v>
       </c>
@@ -1363,7 +2219,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" ht="17.25" customHeight="1">
+    <row r="30" ht="17.25" customHeight="1" spans="1:2">
       <c r="A30" s="1" t="s">
         <v>59</v>
       </c>
@@ -1371,7 +2227,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" ht="17.25" customHeight="1">
+    <row r="31" ht="17.25" customHeight="1" spans="1:2">
       <c r="A31" s="1" t="s">
         <v>61</v>
       </c>
@@ -1379,7 +2235,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="32" ht="17.25" customHeight="1">
+    <row r="32" ht="17.25" customHeight="1" spans="1:2">
       <c r="A32" s="1" t="s">
         <v>63</v>
       </c>
@@ -1387,7 +2243,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" ht="17.25" customHeight="1">
+    <row r="33" ht="17.25" customHeight="1" spans="1:2">
       <c r="A33" s="1" t="s">
         <v>65</v>
       </c>
@@ -1395,7 +2251,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="34" ht="17.25" customHeight="1">
+    <row r="34" ht="17.25" customHeight="1" spans="1:2">
       <c r="A34" s="1" t="s">
         <v>67</v>
       </c>
@@ -1403,7 +2259,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="35" ht="17.25" customHeight="1">
+    <row r="35" ht="17.25" customHeight="1" spans="1:2">
       <c r="A35" s="1" t="s">
         <v>69</v>
       </c>
@@ -1411,7 +2267,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" ht="17.25" customHeight="1">
+    <row r="36" ht="17.25" customHeight="1" spans="1:2">
       <c r="A36" s="1" t="s">
         <v>71</v>
       </c>
@@ -1419,7 +2275,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="37" ht="17.25" customHeight="1">
+    <row r="37" ht="17.25" customHeight="1" spans="1:2">
       <c r="A37" s="1" t="s">
         <v>73</v>
       </c>
@@ -1427,7 +2283,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" ht="17.25" customHeight="1">
+    <row r="38" ht="17.25" customHeight="1" spans="1:2">
       <c r="A38" s="1" t="s">
         <v>75</v>
       </c>
@@ -1435,7 +2291,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" ht="17.25" customHeight="1">
+    <row r="39" ht="17.25" customHeight="1" spans="1:2">
       <c r="A39" s="1" t="s">
         <v>77</v>
       </c>
@@ -1443,7 +2299,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" ht="17.25" customHeight="1">
+    <row r="40" ht="17.25" customHeight="1" spans="1:2">
       <c r="A40" s="1" t="s">
         <v>79</v>
       </c>
@@ -1451,7 +2307,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41" ht="17.25" customHeight="1">
+    <row r="41" ht="17.25" customHeight="1" spans="1:2">
       <c r="A41" s="1" t="s">
         <v>81</v>
       </c>
@@ -1459,7 +2315,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" ht="17.25" customHeight="1">
+    <row r="42" ht="17.25" customHeight="1" spans="1:2">
       <c r="A42" s="1" t="s">
         <v>83</v>
       </c>
@@ -1467,7 +2323,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" ht="17.25" customHeight="1">
+    <row r="43" ht="17.25" customHeight="1" spans="1:2">
       <c r="A43" s="1" t="s">
         <v>85</v>
       </c>
@@ -1475,7 +2331,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="44" ht="17.25" customHeight="1">
+    <row r="44" ht="17.25" customHeight="1" spans="1:2">
       <c r="A44" s="1" t="s">
         <v>87</v>
       </c>
@@ -1483,7 +2339,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="45" ht="17.25" customHeight="1">
+    <row r="45" ht="17.25" customHeight="1" spans="1:2">
       <c r="A45" s="1" t="s">
         <v>89</v>
       </c>
@@ -1491,7 +2347,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="46" ht="17.25" customHeight="1">
+    <row r="46" ht="17.25" customHeight="1" spans="1:2">
       <c r="A46" s="1" t="s">
         <v>91</v>
       </c>
@@ -1499,7 +2355,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="47" ht="17.25" customHeight="1">
+    <row r="47" ht="17.25" customHeight="1" spans="1:2">
       <c r="A47" s="1" t="s">
         <v>93</v>
       </c>
@@ -1507,7 +2363,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="48" ht="17.25" customHeight="1">
+    <row r="48" ht="17.25" customHeight="1" spans="1:2">
       <c r="A48" s="2" t="s">
         <v>95</v>
       </c>
@@ -1515,7 +2371,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="49" ht="17.25" customHeight="1">
+    <row r="49" ht="17.25" customHeight="1" spans="1:3">
       <c r="A49" s="2" t="s">
         <v>97</v>
       </c>
@@ -1523,7 +2379,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="50" ht="17.25" customHeight="1">
+    <row r="50" ht="17.25" customHeight="1" spans="1:3">
       <c r="A50" s="2" t="s">
         <v>99</v>
       </c>
@@ -1531,7 +2387,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" ht="17.25" customHeight="1">
+    <row r="51" ht="17.25" customHeight="1" spans="1:3">
       <c r="A51" s="2" t="s">
         <v>101</v>
       </c>
@@ -1542,7 +2398,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="52" ht="17.25" customHeight="1">
+    <row r="52" ht="17.25" customHeight="1" spans="1:3">
       <c r="A52" s="2" t="s">
         <v>104</v>
       </c>
@@ -1550,7 +2406,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="53" ht="17.25" customHeight="1">
+    <row r="53" ht="17.25" customHeight="1" spans="1:3">
       <c r="A53" s="2" t="s">
         <v>106</v>
       </c>
@@ -1558,7 +2414,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="54" ht="17.25" customHeight="1">
+    <row r="54" ht="17.25" customHeight="1" spans="1:3">
       <c r="A54" s="2" t="s">
         <v>108</v>
       </c>
@@ -1566,7 +2422,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="55" ht="17.25" customHeight="1">
+    <row r="55" ht="17.25" customHeight="1" spans="1:3">
       <c r="A55" s="2" t="s">
         <v>110</v>
       </c>
@@ -1574,7 +2430,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="56" ht="17.25" customHeight="1">
+    <row r="56" ht="17.25" customHeight="1" spans="1:3">
       <c r="A56" s="2" t="s">
         <v>112</v>
       </c>
@@ -1582,7 +2438,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="57" ht="17.25" customHeight="1">
+    <row r="57" ht="17.25" customHeight="1" spans="1:3">
       <c r="A57" s="2" t="s">
         <v>114</v>
       </c>
@@ -1590,7 +2446,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="58" ht="17.25" customHeight="1">
+    <row r="58" ht="17.25" customHeight="1" spans="1:3">
       <c r="A58" s="2" t="s">
         <v>116</v>
       </c>
@@ -1598,7 +2454,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="59" ht="17.25" customHeight="1">
+    <row r="59" ht="17.25" customHeight="1" spans="1:3">
       <c r="A59" s="2" t="s">
         <v>118</v>
       </c>
@@ -1606,7 +2462,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="60" ht="17.25" customHeight="1">
+    <row r="60" ht="17.25" customHeight="1" spans="1:3">
       <c r="A60" s="8" t="s">
         <v>120</v>
       </c>
@@ -1617,18 +2473,18 @@
         <v>103</v>
       </c>
     </row>
-    <row r="61" ht="17.25" customHeight="1">
+    <row r="61" ht="17.25" customHeight="1" spans="1:3">
       <c r="A61" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="B61" s="10" t="s">
+      <c r="B61" t="s">
         <v>123</v>
       </c>
-      <c r="C61" s="10" t="s">
+      <c r="C61" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="62" ht="17.25" customHeight="1">
+    <row r="62" ht="17.25" customHeight="1" spans="1:3">
       <c r="A62" s="2" t="s">
         <v>124</v>
       </c>
@@ -1636,556 +2492,577 @@
         <v>125</v>
       </c>
     </row>
-    <row r="63" ht="17.25" customHeight="1">
+    <row r="63" ht="17.25" customHeight="1" spans="1:3">
       <c r="A63" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="B63" s="10" t="s">
+      <c r="B63" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="64" ht="17.25" customHeight="1">
+    <row r="64" ht="17.25" customHeight="1" spans="1:3">
       <c r="A64" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="B64" s="10" t="s">
+      <c r="B64" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="65" ht="17.25" customHeight="1">
+    <row r="65" ht="17.25" customHeight="1" spans="1:3">
       <c r="A65" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="B65" s="10" t="s">
+      <c r="B65" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="66" ht="17.25" customHeight="1">
+    <row r="66" ht="17.25" customHeight="1" spans="1:3">
       <c r="A66" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="B66" s="10" t="s">
+      <c r="B66" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="67" ht="17.25" customHeight="1">
+    <row r="67" ht="17.25" customHeight="1" spans="1:3">
       <c r="A67" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="B67" s="10" t="s">
+      <c r="B67" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="68" ht="17.25" customHeight="1">
-      <c r="A68" s="11" t="s">
+    <row r="68" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A68" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="B68" s="12" t="s">
+      <c r="B68" s="11" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="69" ht="17.25" customHeight="1">
-      <c r="A69" s="11" t="s">
+    <row r="69" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A69" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="B69" s="12" t="s">
+      <c r="B69" s="11" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="70" ht="17.25" customHeight="1">
+    <row r="70" ht="17.25" customHeight="1" spans="1:3">
       <c r="A70" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="B70" s="10" t="s">
+      <c r="B70" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="71" ht="17.25" customHeight="1">
+    <row r="71" ht="17.25" customHeight="1" spans="1:3">
       <c r="A71" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="B71" s="10" t="s">
+      <c r="B71" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="72" ht="17.25" customHeight="1">
+    <row r="72" ht="17.25" customHeight="1" spans="1:3">
       <c r="A72" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="B72" s="10" t="s">
+      <c r="B72" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="73" ht="17.25" customHeight="1">
+    <row r="73" ht="17.25" customHeight="1" spans="1:3">
       <c r="A73" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="B73" s="10" t="s">
+      <c r="B73" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="74" ht="17.25" customHeight="1">
-      <c r="A74" s="10" t="s">
+    <row r="74" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A74" t="s">
         <v>148</v>
       </c>
-      <c r="B74" s="10" t="s">
+      <c r="B74" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="75" ht="17.25" customHeight="1">
-      <c r="A75" s="10" t="s">
+    <row r="75" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A75" t="s">
         <v>150</v>
       </c>
-      <c r="B75" s="10" t="s">
+      <c r="B75" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="76" ht="17.25" customHeight="1">
-      <c r="A76" s="13" t="s">
+    <row r="76" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A76" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="B76" s="13" t="s">
+      <c r="B76" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="C76" s="13" t="s">
+      <c r="C76" s="11" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="77" ht="17.25" customHeight="1">
-      <c r="A77" s="13" t="s">
+    <row r="77" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A77" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="B77" s="13" t="s">
+      <c r="B77" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="C77" s="13" t="s">
+      <c r="C77" s="11" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="78" ht="17.25" customHeight="1">
-      <c r="A78" s="13" t="s">
+    <row r="78" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A78" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="B78" s="13" t="s">
+      <c r="B78" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="C78" s="13" t="s">
+      <c r="C78" s="11" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="79" ht="17.25" customHeight="1">
-      <c r="A79" s="13" t="s">
+    <row r="79" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A79" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="B79" s="13" t="s">
+      <c r="B79" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="C79" s="13" t="s">
+      <c r="C79" s="11" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="80" ht="17.25" customHeight="1">
-      <c r="A80" s="13" t="s">
+    <row r="80" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A80" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="B80" s="13" t="s">
+      <c r="B80" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="C80" s="13" t="s">
+      <c r="C80" s="11" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="81" ht="17.25" customHeight="1">
-      <c r="A81" s="13" t="s">
+    <row r="81" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A81" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="B81" s="13" t="s">
+      <c r="B81" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="C81" s="14"/>
-    </row>
-    <row r="82" ht="17.25" customHeight="1">
-      <c r="A82" s="13" t="s">
+      <c r="C81" s="11"/>
+    </row>
+    <row r="82" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A82" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="B82" s="13" t="s">
+      <c r="B82" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="C82" s="14"/>
-    </row>
-    <row r="83" ht="17.25" customHeight="1">
-      <c r="A83" s="13" t="s">
+      <c r="C82" s="11"/>
+    </row>
+    <row r="83" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A83" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="B83" s="13" t="s">
+      <c r="B83" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="C83" s="14"/>
-    </row>
-    <row r="84" ht="17.25" customHeight="1">
-      <c r="A84" s="13" t="s">
+      <c r="C83" s="11"/>
+    </row>
+    <row r="84" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A84" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="B84" s="13" t="s">
+      <c r="B84" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="C84" s="14"/>
-    </row>
-    <row r="85" ht="17.25" customHeight="1">
-      <c r="A85" s="13" t="s">
+      <c r="C84" s="11"/>
+    </row>
+    <row r="85" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A85" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="B85" s="13" t="s">
+      <c r="B85" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="C85" s="14"/>
-    </row>
-    <row r="86" ht="17.25" customHeight="1">
-      <c r="A86" s="13" t="s">
+      <c r="C85" s="11"/>
+    </row>
+    <row r="86" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A86" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="B86" s="13" t="s">
+      <c r="B86" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="C86" s="14"/>
-    </row>
-    <row r="87" ht="17.25" customHeight="1">
-      <c r="A87" s="13" t="s">
+      <c r="C86" s="11"/>
+    </row>
+    <row r="87" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A87" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="B87" s="13" t="s">
+      <c r="B87" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="C87" s="14"/>
-    </row>
-    <row r="88" ht="17.25" customHeight="1">
-      <c r="A88" s="13" t="s">
+      <c r="C87" s="11"/>
+    </row>
+    <row r="88" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A88" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="B88" s="13" t="s">
+      <c r="B88" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="C88" s="14"/>
-    </row>
-    <row r="89" ht="17.25" customHeight="1">
-      <c r="A89" s="13" t="s">
+      <c r="C88" s="11"/>
+    </row>
+    <row r="89" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A89" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="B89" s="13" t="s">
+      <c r="B89" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="C89" s="14"/>
-    </row>
-    <row r="90" ht="17.25" customHeight="1">
-      <c r="A90" s="10" t="s">
+      <c r="C89" s="11"/>
+    </row>
+    <row r="90" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A90" t="s">
         <v>180</v>
       </c>
-      <c r="B90" s="10" t="s">
+      <c r="B90" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="91" ht="17.25" customHeight="1">
-      <c r="A91" s="10" t="s">
+    <row r="91" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A91" t="s">
         <v>182</v>
       </c>
-      <c r="B91" s="10" t="s">
+      <c r="B91" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="92" ht="17.25" customHeight="1">
-      <c r="A92" s="10" t="s">
+    <row r="92" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A92" t="s">
         <v>184</v>
       </c>
-      <c r="B92" s="10" t="s">
+      <c r="B92" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="93" ht="17.25" customHeight="1">
-      <c r="A93" s="10" t="s">
+    <row r="93" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A93" t="s">
         <v>186</v>
       </c>
-      <c r="B93" s="10" t="s">
+      <c r="B93" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="94" ht="17.25" customHeight="1">
-      <c r="A94" s="13" t="s">
+    <row r="94" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A94" s="11" t="s">
         <v>188</v>
       </c>
-      <c r="B94" s="13" t="s">
+      <c r="B94" s="11" t="s">
         <v>189</v>
       </c>
-      <c r="C94" s="14"/>
-    </row>
-    <row r="95" ht="17.25" customHeight="1">
-      <c r="A95" s="13" t="s">
+      <c r="C94" s="11"/>
+    </row>
+    <row r="95" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A95" s="11" t="s">
         <v>190</v>
       </c>
-      <c r="B95" s="15" t="s">
+      <c r="B95" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="C95" s="13" t="s">
+      <c r="C95" s="11" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="96" ht="17.25" customHeight="1">
-      <c r="A96" s="13" t="s">
+    <row r="96" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A96" s="11" t="s">
         <v>192</v>
       </c>
-      <c r="B96" s="15" t="s">
+      <c r="B96" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="C96" s="14"/>
-    </row>
-    <row r="97" ht="17.25" customHeight="1">
-      <c r="A97" s="13" t="s">
+      <c r="C96" s="11"/>
+    </row>
+    <row r="97" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A97" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="B97" s="15" t="s">
+      <c r="B97" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="C97" s="14"/>
-    </row>
-    <row r="98" ht="17.25" customHeight="1">
-      <c r="A98" s="13" t="s">
+      <c r="C97" s="11"/>
+    </row>
+    <row r="98" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A98" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="B98" s="15" t="s">
+      <c r="B98" s="12" t="s">
         <v>197</v>
       </c>
-      <c r="C98" s="14"/>
-    </row>
-    <row r="99" ht="17.25" customHeight="1">
-      <c r="A99" s="13" t="s">
+      <c r="C98" s="11"/>
+    </row>
+    <row r="99" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A99" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="B99" s="15" t="s">
+      <c r="B99" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="C99" s="14"/>
-    </row>
-    <row r="100" ht="17.25" customHeight="1">
-      <c r="A100" s="10" t="s">
+      <c r="C99" s="11"/>
+    </row>
+    <row r="100" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A100" t="s">
         <v>200</v>
       </c>
-      <c r="B100" s="10" t="s">
+      <c r="B100" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="101" ht="17.25" customHeight="1">
-      <c r="A101" s="10" t="s">
+    <row r="101" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A101" t="s">
         <v>202</v>
       </c>
-      <c r="B101" s="10" t="s">
+      <c r="B101" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="102" ht="17.25" customHeight="1">
-      <c r="A102" s="10" t="s">
+    <row r="102" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A102" t="s">
         <v>204</v>
       </c>
-      <c r="B102" s="10" t="s">
+      <c r="B102" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="103" ht="17.25" customHeight="1">
-      <c r="A103" s="10" t="s">
+    <row r="103" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A103" t="s">
         <v>206</v>
       </c>
-      <c r="B103" s="10" t="s">
+      <c r="B103" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="104" ht="17.25" customHeight="1">
-      <c r="A104" s="10" t="s">
+    <row r="104" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A104" t="s">
         <v>208</v>
       </c>
-      <c r="B104" s="10" t="s">
+      <c r="B104" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="105" ht="17.25" customHeight="1">
-      <c r="A105" s="10" t="s">
+    <row r="105" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A105" t="s">
         <v>210</v>
       </c>
-      <c r="B105" s="10" t="s">
+      <c r="B105" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="106" ht="17.25" customHeight="1">
-      <c r="A106" s="10" t="s">
+    <row r="106" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A106" t="s">
         <v>212</v>
       </c>
-      <c r="B106" s="10" t="s">
+      <c r="B106" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="107" ht="17.25" customHeight="1">
-      <c r="A107" s="10" t="s">
+    <row r="107" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A107" t="s">
         <v>214</v>
       </c>
-      <c r="B107" s="16" t="s">
+      <c r="B107" s="13" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="108" ht="17.25" customHeight="1">
-      <c r="A108" s="17" t="s">
+    <row r="108" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A108" s="14" t="s">
         <v>216</v>
       </c>
-      <c r="B108" s="18" t="s">
+      <c r="B108" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="C108" s="13" t="s">
+      <c r="C108" s="11" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="109" ht="17.25" customHeight="1">
-      <c r="A109" s="17" t="s">
+    <row r="109" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A109" s="14" t="s">
         <v>218</v>
       </c>
-      <c r="B109" s="17" t="s">
+      <c r="B109" s="14" t="s">
         <v>219</v>
       </c>
-      <c r="C109" s="13" t="s">
+      <c r="C109" s="11" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="110" ht="17.25" customHeight="1">
-      <c r="A110" s="17" t="s">
+    <row r="110" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A110" s="14" t="s">
         <v>220</v>
       </c>
-      <c r="B110" s="18" t="s">
+      <c r="B110" s="14" t="s">
         <v>221</v>
       </c>
-      <c r="C110" s="13" t="s">
+      <c r="C110" s="11" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="111" ht="17.25" customHeight="1">
-      <c r="A111" s="17" t="s">
+    <row r="111" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A111" s="14" t="s">
         <v>222</v>
       </c>
-      <c r="B111" s="18" t="s">
+      <c r="B111" s="14" t="s">
         <v>223</v>
       </c>
-      <c r="C111" s="13" t="s">
+      <c r="C111" s="11" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="112" ht="17.25" customHeight="1">
-      <c r="A112" s="17" t="s">
+    <row r="112" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A112" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="B112" s="18" t="s">
+      <c r="B112" s="14" t="s">
         <v>225</v>
       </c>
-      <c r="C112" s="13" t="s">
+      <c r="C112" s="11" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="113" ht="17.25" customHeight="1">
-      <c r="A113" s="17" t="s">
+    <row r="113" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A113" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="B113" s="18" t="s">
+      <c r="B113" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="C113" s="13" t="s">
+      <c r="C113" s="11" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="114" ht="17.25" customHeight="1">
-      <c r="A114" s="17" t="s">
+    <row r="114" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A114" s="14" t="s">
         <v>228</v>
       </c>
-      <c r="B114" s="18" t="s">
+      <c r="B114" s="14" t="s">
         <v>229</v>
       </c>
-      <c r="C114" s="13" t="s">
+      <c r="C114" s="11" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="115" ht="17.25" customHeight="1">
-      <c r="A115" s="10" t="s">
+    <row r="115" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A115" t="s">
         <v>230</v>
       </c>
-      <c r="B115" s="16" t="s">
+      <c r="B115" s="13" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="116" ht="17.25" customHeight="1">
-      <c r="A116" s="17" t="s">
+    <row r="116" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A116" s="14" t="s">
         <v>232</v>
       </c>
-      <c r="B116" s="18" t="s">
+      <c r="B116" s="14" t="s">
         <v>233</v>
       </c>
-      <c r="C116" s="13" t="s">
+      <c r="C116" s="11" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="117" ht="17.25" customHeight="1">
-      <c r="A117" s="17" t="s">
+    <row r="117" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A117" s="14" t="s">
         <v>234</v>
       </c>
-      <c r="B117" s="18" t="s">
+      <c r="B117" s="14" t="s">
         <v>235</v>
       </c>
-      <c r="C117" s="13" t="s">
+      <c r="C117" s="11" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="118" ht="17.25" customHeight="1">
-      <c r="A118" s="10" t="s">
+    <row r="118" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A118" t="s">
         <v>236</v>
       </c>
-      <c r="B118" s="10" t="s">
+      <c r="B118" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="119" ht="17.25" customHeight="1">
-      <c r="A119" s="10" t="s">
+    <row r="119" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A119" t="s">
         <v>238</v>
       </c>
-      <c r="B119" s="10" t="s">
+      <c r="B119" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="120" ht="17.25" customHeight="1">
-      <c r="A120" s="10" t="s">
+    <row r="120" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A120" t="s">
         <v>240</v>
       </c>
-      <c r="B120" s="10" t="s">
+      <c r="B120" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="121" ht="17.25" customHeight="1">
-      <c r="A121" s="10" t="s">
+    <row r="121" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A121" t="s">
         <v>242</v>
       </c>
-      <c r="B121" s="10" t="s">
+      <c r="B121" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="122" ht="17.25" customHeight="1">
-      <c r="A122" s="10" t="s">
+    <row r="122" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A122" t="s">
         <v>244</v>
       </c>
-      <c r="B122" s="10" t="s">
+      <c r="B122" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="123" ht="17.25" customHeight="1">
-      <c r="A123" s="10" t="s">
+    <row r="123" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A123" t="s">
         <v>246</v>
       </c>
-      <c r="B123" s="10" t="s">
+      <c r="B123" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="124" ht="17.25" customHeight="1"/>
-    <row r="125" ht="17.25" customHeight="1"/>
-    <row r="126" ht="17.25" customHeight="1"/>
+    <row r="124" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A124" t="s">
+        <v>248</v>
+      </c>
+      <c r="B124" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="125" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A125" t="s">
+        <v>250</v>
+      </c>
+      <c r="B125" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="126" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A126" t="s">
+        <v>252</v>
+      </c>
+      <c r="B126" t="s">
+        <v>253</v>
+      </c>
+    </row>
     <row r="127" ht="17.25" customHeight="1"/>
     <row r="128" ht="17.25" customHeight="1"/>
     <row r="129" ht="17.25" customHeight="1"/>
@@ -3060,9 +3937,8 @@
     <row r="998" ht="17.25" customHeight="1"/>
     <row r="999" ht="17.25" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup paperSize="1" orientation="landscape"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="256">
   <si>
     <t>미리 로드할 어드레서블 테이블</t>
   </si>
@@ -777,6 +777,12 @@
   </si>
   <si>
     <t>MushroomTrap</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_MushroomTrap</t>
+  </si>
+  <si>
+    <t>Mashroom_1</t>
   </si>
   <si>
     <t>PreLoadAsset_Material_Color_1</t>
@@ -1969,7 +1975,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C999"/>
+  <dimension ref="A1:C1000"/>
   <sheetFormatPr defaultColWidth="14.4259259259259" defaultRowHeight="15" customHeight="1" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="52.1388888888889" customWidth="1"/>
@@ -3054,6 +3060,9 @@
       <c r="B125" t="s">
         <v>251</v>
       </c>
+      <c r="C125" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="126" ht="17.25" customHeight="1" spans="1:3">
       <c r="A126" t="s">
@@ -3063,7 +3072,14 @@
         <v>253</v>
       </c>
     </row>
-    <row r="127" ht="17.25" customHeight="1"/>
+    <row r="127" ht="17.25" customHeight="1" spans="1:3">
+      <c r="A127" t="s">
+        <v>254</v>
+      </c>
+      <c r="B127" t="s">
+        <v>255</v>
+      </c>
+    </row>
     <row r="128" ht="17.25" customHeight="1"/>
     <row r="129" ht="17.25" customHeight="1"/>
     <row r="130" ht="17.25" customHeight="1"/>
@@ -3936,6 +3952,7 @@
     <row r="997" ht="17.25" customHeight="1"/>
     <row r="998" ht="17.25" customHeight="1"/>
     <row r="999" ht="17.25" customHeight="1"/>
+    <row r="1000" ht="17.25" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="1" orientation="landscape"/>

--- a/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
@@ -1,33 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\바탕화면\Project\JewelThief\JewelThief\JsonConverter\ExcelFiles\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{405A4575-A771-46B8-905B-5967242A2E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView xWindow="1812" yWindow="1812" windowWidth="28080" windowHeight="14628" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext uri="GoogleSheetsCustomDataVersion2">
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="v4mvBJYERGqiNruBTfijDgsGfB1L8a5WYzdi61pNbdg="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="260">
   <si>
     <t>미리 로드할 어드레서블 테이블</t>
   </si>
@@ -789,214 +787,106 @@
   </si>
   <si>
     <t>Color_2</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_GameObject_Escape</t>
+  </si>
+  <si>
+    <t>Escape</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_MeshCollider_Escape</t>
+  </si>
+  <si>
+    <t>MeshCollider_Escape</t>
+  </si>
+  <si>
+    <t>PreLoadAsset_Mesh_Escape</t>
+  </si>
+  <si>
+    <t>Mesh_Escape[SM_Prop_Vent_01]</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="27">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Malgun Gothic"/>
-      <charset val="134"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Malgun Gothic"/>
-      <charset val="134"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="&quot;Malgun Gothic&quot;"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="8"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1009,194 +899,8 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1232,540 +936,39 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+  <cellXfs count="14">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="double">
-          <color theme="4"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color theme="4"/>
-        </left>
-        <right style="thin">
-          <color theme="4"/>
-        </right>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-        <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-  </dxfs>
-  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
-    </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
-    </tableStyle>
-  </tableStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1963,22 +1166,22 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:C999"/>
-  <sheetFormatPr defaultColWidth="14.4259259259259" defaultRowHeight="15" customHeight="1" outlineLevelCol="2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C998"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="52.1388888888889" customWidth="1"/>
-    <col min="2" max="2" width="35.1388888888889" customWidth="1"/>
-    <col min="3" max="3" width="31.4259259259259" customWidth="1"/>
+    <col min="1" max="1" width="52.109375" customWidth="1"/>
+    <col min="2" max="2" width="35.109375" customWidth="1"/>
+    <col min="3" max="3" width="31.44140625" customWidth="1"/>
     <col min="4" max="26" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1" spans="1:3">
+    <row r="1" spans="1:3" ht="17.25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1989,7 +1192,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="17.25" customHeight="1" spans="1:3">
+    <row r="2" spans="1:3" ht="17.25" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -2000,7 +1203,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" ht="17.25" customHeight="1" spans="1:3">
+    <row r="3" spans="1:3" ht="17.25" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -2011,7 +1214,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" ht="17.25" customHeight="1" spans="1:3">
+    <row r="4" spans="1:3" ht="17.25" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -2019,7 +1222,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" ht="17.25" customHeight="1" spans="1:3">
+    <row r="5" spans="1:3" ht="17.25" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -2027,7 +1230,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" ht="17.25" customHeight="1" spans="1:3">
+    <row r="6" spans="1:3" ht="17.25" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -2035,7 +1238,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" ht="17.25" customHeight="1" spans="1:3">
+    <row r="7" spans="1:3" ht="17.25" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -2043,7 +1246,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" ht="17.25" customHeight="1" spans="1:3">
+    <row r="8" spans="1:3" ht="17.25" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -2051,7 +1254,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" ht="17.25" customHeight="1" spans="1:3">
+    <row r="9" spans="1:3" ht="17.25" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -2059,7 +1262,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" ht="17.25" customHeight="1" spans="1:3">
+    <row r="10" spans="1:3" ht="17.25" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -2067,7 +1270,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" ht="17.25" customHeight="1" spans="1:3">
+    <row r="11" spans="1:3" ht="17.25" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>21</v>
       </c>
@@ -2075,7 +1278,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" ht="17.25" customHeight="1" spans="1:3">
+    <row r="12" spans="1:3" ht="17.25" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>23</v>
       </c>
@@ -2083,7 +1286,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" ht="17.25" customHeight="1" spans="1:3">
+    <row r="13" spans="1:3" ht="17.25" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>25</v>
       </c>
@@ -2091,7 +1294,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" ht="17.25" customHeight="1" spans="1:3">
+    <row r="14" spans="1:3" ht="17.25" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>27</v>
       </c>
@@ -2099,7 +1302,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" ht="17.25" customHeight="1" spans="1:3">
+    <row r="15" spans="1:3" ht="17.25" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>29</v>
       </c>
@@ -2107,7 +1310,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" ht="17.25" customHeight="1" spans="1:3">
+    <row r="16" spans="1:3" ht="17.25" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>31</v>
       </c>
@@ -2115,7 +1318,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" ht="17.25" customHeight="1" spans="1:2">
+    <row r="17" spans="1:2" ht="17.25" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>33</v>
       </c>
@@ -2123,7 +1326,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" ht="17.25" customHeight="1" spans="1:2">
+    <row r="18" spans="1:2" ht="17.25" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -2131,7 +1334,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" ht="17.25" customHeight="1" spans="1:2">
+    <row r="19" spans="1:2" ht="17.25" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>37</v>
       </c>
@@ -2139,7 +1342,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" ht="17.25" customHeight="1" spans="1:2">
+    <row r="20" spans="1:2" ht="17.25" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>39</v>
       </c>
@@ -2147,7 +1350,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" ht="17.25" customHeight="1" spans="1:2">
+    <row r="21" spans="1:2" ht="17.25" customHeight="1">
       <c r="A21" s="1" t="s">
         <v>41</v>
       </c>
@@ -2155,7 +1358,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" ht="17.25" customHeight="1" spans="1:2">
+    <row r="22" spans="1:2" ht="17.25" customHeight="1">
       <c r="A22" s="1" t="s">
         <v>43</v>
       </c>
@@ -2163,7 +1366,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" ht="17.25" customHeight="1" spans="1:2">
+    <row r="23" spans="1:2" ht="17.25" customHeight="1">
       <c r="A23" s="1" t="s">
         <v>45</v>
       </c>
@@ -2171,7 +1374,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" ht="17.25" customHeight="1" spans="1:2">
+    <row r="24" spans="1:2" ht="17.25" customHeight="1">
       <c r="A24" s="1" t="s">
         <v>47</v>
       </c>
@@ -2179,7 +1382,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" ht="17.25" customHeight="1" spans="1:2">
+    <row r="25" spans="1:2" ht="17.25" customHeight="1">
       <c r="A25" s="1" t="s">
         <v>49</v>
       </c>
@@ -2187,7 +1390,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" ht="17.25" customHeight="1" spans="1:2">
+    <row r="26" spans="1:2" ht="17.25" customHeight="1">
       <c r="A26" s="1" t="s">
         <v>51</v>
       </c>
@@ -2195,7 +1398,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" ht="17.25" customHeight="1" spans="1:2">
+    <row r="27" spans="1:2" ht="17.25" customHeight="1">
       <c r="A27" s="1" t="s">
         <v>53</v>
       </c>
@@ -2203,7 +1406,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" ht="17.25" customHeight="1" spans="1:2">
+    <row r="28" spans="1:2" ht="17.25" customHeight="1">
       <c r="A28" s="1" t="s">
         <v>55</v>
       </c>
@@ -2211,7 +1414,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" ht="17.25" customHeight="1" spans="1:2">
+    <row r="29" spans="1:2" ht="17.25" customHeight="1">
       <c r="A29" s="1" t="s">
         <v>57</v>
       </c>
@@ -2219,7 +1422,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" ht="17.25" customHeight="1" spans="1:2">
+    <row r="30" spans="1:2" ht="17.25" customHeight="1">
       <c r="A30" s="1" t="s">
         <v>59</v>
       </c>
@@ -2227,7 +1430,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" ht="17.25" customHeight="1" spans="1:2">
+    <row r="31" spans="1:2" ht="17.25" customHeight="1">
       <c r="A31" s="1" t="s">
         <v>61</v>
       </c>
@@ -2235,7 +1438,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="32" ht="17.25" customHeight="1" spans="1:2">
+    <row r="32" spans="1:2" ht="17.25" customHeight="1">
       <c r="A32" s="1" t="s">
         <v>63</v>
       </c>
@@ -2243,7 +1446,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" ht="17.25" customHeight="1" spans="1:2">
+    <row r="33" spans="1:2" ht="17.25" customHeight="1">
       <c r="A33" s="1" t="s">
         <v>65</v>
       </c>
@@ -2251,7 +1454,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="34" ht="17.25" customHeight="1" spans="1:2">
+    <row r="34" spans="1:2" ht="17.25" customHeight="1">
       <c r="A34" s="1" t="s">
         <v>67</v>
       </c>
@@ -2259,7 +1462,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="35" ht="17.25" customHeight="1" spans="1:2">
+    <row r="35" spans="1:2" ht="17.25" customHeight="1">
       <c r="A35" s="1" t="s">
         <v>69</v>
       </c>
@@ -2267,7 +1470,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" ht="17.25" customHeight="1" spans="1:2">
+    <row r="36" spans="1:2" ht="17.25" customHeight="1">
       <c r="A36" s="1" t="s">
         <v>71</v>
       </c>
@@ -2275,7 +1478,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="37" ht="17.25" customHeight="1" spans="1:2">
+    <row r="37" spans="1:2" ht="17.25" customHeight="1">
       <c r="A37" s="1" t="s">
         <v>73</v>
       </c>
@@ -2283,7 +1486,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" ht="17.25" customHeight="1" spans="1:2">
+    <row r="38" spans="1:2" ht="17.25" customHeight="1">
       <c r="A38" s="1" t="s">
         <v>75</v>
       </c>
@@ -2291,7 +1494,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" ht="17.25" customHeight="1" spans="1:2">
+    <row r="39" spans="1:2" ht="17.25" customHeight="1">
       <c r="A39" s="1" t="s">
         <v>77</v>
       </c>
@@ -2299,7 +1502,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" ht="17.25" customHeight="1" spans="1:2">
+    <row r="40" spans="1:2" ht="17.25" customHeight="1">
       <c r="A40" s="1" t="s">
         <v>79</v>
       </c>
@@ -2307,7 +1510,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41" ht="17.25" customHeight="1" spans="1:2">
+    <row r="41" spans="1:2" ht="17.25" customHeight="1">
       <c r="A41" s="1" t="s">
         <v>81</v>
       </c>
@@ -2315,7 +1518,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" ht="17.25" customHeight="1" spans="1:2">
+    <row r="42" spans="1:2" ht="17.25" customHeight="1">
       <c r="A42" s="1" t="s">
         <v>83</v>
       </c>
@@ -2323,7 +1526,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" ht="17.25" customHeight="1" spans="1:2">
+    <row r="43" spans="1:2" ht="17.25" customHeight="1">
       <c r="A43" s="1" t="s">
         <v>85</v>
       </c>
@@ -2331,7 +1534,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="44" ht="17.25" customHeight="1" spans="1:2">
+    <row r="44" spans="1:2" ht="17.25" customHeight="1">
       <c r="A44" s="1" t="s">
         <v>87</v>
       </c>
@@ -2339,7 +1542,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="45" ht="17.25" customHeight="1" spans="1:2">
+    <row r="45" spans="1:2" ht="17.25" customHeight="1">
       <c r="A45" s="1" t="s">
         <v>89</v>
       </c>
@@ -2347,7 +1550,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="46" ht="17.25" customHeight="1" spans="1:2">
+    <row r="46" spans="1:2" ht="17.25" customHeight="1">
       <c r="A46" s="1" t="s">
         <v>91</v>
       </c>
@@ -2355,7 +1558,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="47" ht="17.25" customHeight="1" spans="1:2">
+    <row r="47" spans="1:2" ht="17.25" customHeight="1">
       <c r="A47" s="1" t="s">
         <v>93</v>
       </c>
@@ -2363,7 +1566,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="48" ht="17.25" customHeight="1" spans="1:2">
+    <row r="48" spans="1:2" ht="17.25" customHeight="1">
       <c r="A48" s="2" t="s">
         <v>95</v>
       </c>
@@ -2371,7 +1574,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="49" ht="17.25" customHeight="1" spans="1:3">
+    <row r="49" spans="1:3" ht="17.25" customHeight="1">
       <c r="A49" s="2" t="s">
         <v>97</v>
       </c>
@@ -2379,7 +1582,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="50" ht="17.25" customHeight="1" spans="1:3">
+    <row r="50" spans="1:3" ht="17.25" customHeight="1">
       <c r="A50" s="2" t="s">
         <v>99</v>
       </c>
@@ -2387,7 +1590,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" ht="17.25" customHeight="1" spans="1:3">
+    <row r="51" spans="1:3" ht="17.25" customHeight="1">
       <c r="A51" s="2" t="s">
         <v>101</v>
       </c>
@@ -2398,7 +1601,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="52" ht="17.25" customHeight="1" spans="1:3">
+    <row r="52" spans="1:3" ht="17.25" customHeight="1">
       <c r="A52" s="2" t="s">
         <v>104</v>
       </c>
@@ -2406,7 +1609,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="53" ht="17.25" customHeight="1" spans="1:3">
+    <row r="53" spans="1:3" ht="17.25" customHeight="1">
       <c r="A53" s="2" t="s">
         <v>106</v>
       </c>
@@ -2414,7 +1617,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="54" ht="17.25" customHeight="1" spans="1:3">
+    <row r="54" spans="1:3" ht="17.25" customHeight="1">
       <c r="A54" s="2" t="s">
         <v>108</v>
       </c>
@@ -2422,7 +1625,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="55" ht="17.25" customHeight="1" spans="1:3">
+    <row r="55" spans="1:3" ht="17.25" customHeight="1">
       <c r="A55" s="2" t="s">
         <v>110</v>
       </c>
@@ -2430,7 +1633,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="56" ht="17.25" customHeight="1" spans="1:3">
+    <row r="56" spans="1:3" ht="17.25" customHeight="1">
       <c r="A56" s="2" t="s">
         <v>112</v>
       </c>
@@ -2438,7 +1641,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="57" ht="17.25" customHeight="1" spans="1:3">
+    <row r="57" spans="1:3" ht="17.25" customHeight="1">
       <c r="A57" s="2" t="s">
         <v>114</v>
       </c>
@@ -2446,7 +1649,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="58" ht="17.25" customHeight="1" spans="1:3">
+    <row r="58" spans="1:3" ht="17.25" customHeight="1">
       <c r="A58" s="2" t="s">
         <v>116</v>
       </c>
@@ -2454,7 +1657,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="59" ht="17.25" customHeight="1" spans="1:3">
+    <row r="59" spans="1:3" ht="17.25" customHeight="1">
       <c r="A59" s="2" t="s">
         <v>118</v>
       </c>
@@ -2462,29 +1665,29 @@
         <v>119</v>
       </c>
     </row>
-    <row r="60" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A60" s="8" t="s">
+    <row r="60" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A60" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="B60" s="8" t="s">
+      <c r="B60" s="7" t="s">
         <v>121</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="61" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A61" s="9" t="s">
+    <row r="61" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A61" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B61" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="1" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="62" ht="17.25" customHeight="1" spans="1:3">
+    <row r="62" spans="1:3" ht="17.25" customHeight="1">
       <c r="A62" s="2" t="s">
         <v>124</v>
       </c>
@@ -2492,595 +1695,624 @@
         <v>125</v>
       </c>
     </row>
-    <row r="63" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A63" s="9" t="s">
+    <row r="63" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A63" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B63" s="1" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="64" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A64" s="9" t="s">
+    <row r="64" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A64" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B64" s="1" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="65" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A65" s="9" t="s">
+    <row r="65" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A65" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B65" s="1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="66" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A66" s="9" t="s">
+    <row r="66" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A66" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B66" s="1" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="67" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A67" s="9" t="s">
+    <row r="67" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A67" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B67" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="68" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A68" s="10" t="s">
+    <row r="68" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A68" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="B68" s="11" t="s">
+      <c r="B68" s="9" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="69" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A69" s="10" t="s">
+    <row r="69" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A69" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="B69" s="11" t="s">
+      <c r="B69" s="9" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="70" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A70" s="9" t="s">
+    <row r="70" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A70" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B70" s="1" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="71" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A71" s="9" t="s">
+    <row r="71" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A71" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B71" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="72" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A72" s="9" t="s">
+    <row r="72" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A72" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="B72" t="s">
+      <c r="B72" s="1" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="73" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A73" s="9" t="s">
+    <row r="73" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A73" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B73" s="1" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="74" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A74" t="s">
+    <row r="74" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A74" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="75" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A75" t="s">
+    <row r="75" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A75" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="76" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A76" s="11" t="s">
+    <row r="76" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A76" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="B76" s="11" t="s">
+      <c r="B76" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="C76" s="11" t="s">
+      <c r="C76" s="9" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="77" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A77" s="11" t="s">
+    <row r="77" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A77" s="9" t="s">
         <v>154</v>
       </c>
-      <c r="B77" s="11" t="s">
+      <c r="B77" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="C77" s="11" t="s">
+      <c r="C77" s="9" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="78" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A78" s="11" t="s">
+    <row r="78" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A78" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="B78" s="11" t="s">
+      <c r="B78" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="C78" s="11" t="s">
+      <c r="C78" s="9" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="79" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A79" s="11" t="s">
+    <row r="79" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A79" s="9" t="s">
         <v>158</v>
       </c>
-      <c r="B79" s="11" t="s">
+      <c r="B79" s="9" t="s">
         <v>159</v>
       </c>
-      <c r="C79" s="11" t="s">
+      <c r="C79" s="9" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="80" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A80" s="11" t="s">
+    <row r="80" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A80" s="9" t="s">
         <v>160</v>
       </c>
-      <c r="B80" s="11" t="s">
+      <c r="B80" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="C80" s="11" t="s">
+      <c r="C80" s="9" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="81" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A81" s="11" t="s">
+    <row r="81" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A81" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="B81" s="11" t="s">
+      <c r="B81" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="C81" s="11"/>
-    </row>
-    <row r="82" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A82" s="11" t="s">
+      <c r="C81" s="9"/>
+    </row>
+    <row r="82" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A82" s="9" t="s">
         <v>164</v>
       </c>
-      <c r="B82" s="11" t="s">
+      <c r="B82" s="9" t="s">
         <v>165</v>
       </c>
-      <c r="C82" s="11"/>
-    </row>
-    <row r="83" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A83" s="11" t="s">
+      <c r="C82" s="9"/>
+    </row>
+    <row r="83" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A83" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="B83" s="11" t="s">
+      <c r="B83" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="C83" s="11"/>
-    </row>
-    <row r="84" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A84" s="11" t="s">
+      <c r="C83" s="9"/>
+    </row>
+    <row r="84" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A84" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="B84" s="11" t="s">
+      <c r="B84" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="C84" s="11"/>
-    </row>
-    <row r="85" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A85" s="11" t="s">
+      <c r="C84" s="9"/>
+    </row>
+    <row r="85" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A85" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="B85" s="11" t="s">
+      <c r="B85" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="C85" s="11"/>
-    </row>
-    <row r="86" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A86" s="11" t="s">
+      <c r="C85" s="9"/>
+    </row>
+    <row r="86" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A86" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="B86" s="11" t="s">
+      <c r="B86" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="C86" s="11"/>
-    </row>
-    <row r="87" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A87" s="11" t="s">
+      <c r="C86" s="9"/>
+    </row>
+    <row r="87" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A87" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="B87" s="11" t="s">
+      <c r="B87" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="C87" s="11"/>
-    </row>
-    <row r="88" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A88" s="11" t="s">
+      <c r="C87" s="9"/>
+    </row>
+    <row r="88" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A88" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="B88" s="11" t="s">
+      <c r="B88" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="C88" s="11"/>
-    </row>
-    <row r="89" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A89" s="11" t="s">
+      <c r="C88" s="9"/>
+    </row>
+    <row r="89" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A89" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="B89" s="11" t="s">
+      <c r="B89" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="C89" s="11"/>
-    </row>
-    <row r="90" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A90" t="s">
+      <c r="C89" s="9"/>
+    </row>
+    <row r="90" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A90" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B90" s="1" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="91" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A91" t="s">
+    <row r="91" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A91" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B91" s="1" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="92" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A92" t="s">
+    <row r="92" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A92" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B92" s="1" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="93" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A93" t="s">
+    <row r="93" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A93" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B93" s="1" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="94" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A94" s="11" t="s">
+    <row r="94" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A94" s="9" t="s">
         <v>188</v>
       </c>
-      <c r="B94" s="11" t="s">
+      <c r="B94" s="9" t="s">
         <v>189</v>
       </c>
-      <c r="C94" s="11"/>
-    </row>
-    <row r="95" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A95" s="11" t="s">
+      <c r="C94" s="9"/>
+    </row>
+    <row r="95" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A95" s="9" t="s">
         <v>190</v>
       </c>
-      <c r="B95" s="12" t="s">
+      <c r="B95" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="C95" s="11" t="s">
+      <c r="C95" s="9" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="96" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A96" s="11" t="s">
+    <row r="96" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A96" s="9" t="s">
         <v>192</v>
       </c>
-      <c r="B96" s="12" t="s">
+      <c r="B96" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="C96" s="11"/>
-    </row>
-    <row r="97" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A97" s="11" t="s">
+      <c r="C96" s="9"/>
+    </row>
+    <row r="97" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A97" s="9" t="s">
         <v>194</v>
       </c>
-      <c r="B97" s="12" t="s">
+      <c r="B97" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="C97" s="11"/>
-    </row>
-    <row r="98" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A98" s="11" t="s">
+      <c r="C97" s="9"/>
+    </row>
+    <row r="98" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A98" s="9" t="s">
         <v>196</v>
       </c>
-      <c r="B98" s="12" t="s">
+      <c r="B98" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="C98" s="11"/>
-    </row>
-    <row r="99" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A99" s="11" t="s">
+      <c r="C98" s="9"/>
+    </row>
+    <row r="99" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A99" s="9" t="s">
         <v>198</v>
       </c>
-      <c r="B99" s="12" t="s">
+      <c r="B99" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="C99" s="11"/>
-    </row>
-    <row r="100" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A100" t="s">
+      <c r="C99" s="9"/>
+    </row>
+    <row r="100" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A100" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B100" t="s">
+      <c r="B100" s="1" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="101" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A101" t="s">
+    <row r="101" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A101" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B101" s="1" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="102" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A102" t="s">
+    <row r="102" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A102" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B102" s="1" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="103" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A103" t="s">
+    <row r="103" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A103" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B103" s="1" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="104" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A104" t="s">
+    <row r="104" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A104" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B104" s="1" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="105" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A105" t="s">
+    <row r="105" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A105" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B105" s="1" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="106" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A106" t="s">
+    <row r="106" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A106" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B106" s="1" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="107" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A107" t="s">
+    <row r="107" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A107" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="B107" s="13" t="s">
+      <c r="B107" s="5" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="108" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A108" s="14" t="s">
+    <row r="108" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A108" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="B108" s="14" t="s">
+      <c r="B108" s="11" t="s">
         <v>217</v>
       </c>
-      <c r="C108" s="11" t="s">
+      <c r="C108" s="9" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="109" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A109" s="14" t="s">
+    <row r="109" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A109" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="B109" s="14" t="s">
+      <c r="B109" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="C109" s="11" t="s">
+      <c r="C109" s="9" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="110" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A110" s="14" t="s">
+    <row r="110" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A110" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="B110" s="14" t="s">
+      <c r="B110" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="C110" s="11" t="s">
+      <c r="C110" s="9" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="111" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A111" s="14" t="s">
+    <row r="111" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A111" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="B111" s="14" t="s">
+      <c r="B111" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="C111" s="11" t="s">
+      <c r="C111" s="9" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="112" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A112" s="14" t="s">
+    <row r="112" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A112" s="11" t="s">
         <v>224</v>
       </c>
-      <c r="B112" s="14" t="s">
+      <c r="B112" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="C112" s="11" t="s">
+      <c r="C112" s="9" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="113" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A113" s="14" t="s">
+    <row r="113" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A113" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="B113" s="14" t="s">
+      <c r="B113" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="C113" s="11" t="s">
+      <c r="C113" s="9" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="114" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A114" s="14" t="s">
+    <row r="114" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A114" s="11" t="s">
         <v>228</v>
       </c>
-      <c r="B114" s="14" t="s">
+      <c r="B114" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="C114" s="11" t="s">
+      <c r="C114" s="9" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="115" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A115" t="s">
+    <row r="115" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A115" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="B115" s="13" t="s">
+      <c r="B115" s="5" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="116" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A116" s="14" t="s">
+    <row r="116" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A116" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="B116" s="14" t="s">
+      <c r="B116" s="11" t="s">
         <v>233</v>
       </c>
-      <c r="C116" s="11" t="s">
+      <c r="C116" s="9" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="117" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A117" s="14" t="s">
+    <row r="117" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A117" s="11" t="s">
         <v>234</v>
       </c>
-      <c r="B117" s="14" t="s">
+      <c r="B117" s="11" t="s">
         <v>235</v>
       </c>
-      <c r="C117" s="11" t="s">
+      <c r="C117" s="9" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="118" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A118" t="s">
+    <row r="118" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A118" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" s="1" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="119" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A119" t="s">
+    <row r="119" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A119" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" s="1" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="120" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A120" t="s">
+    <row r="120" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A120" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" s="1" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="121" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A121" t="s">
+    <row r="121" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A121" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B121" t="s">
+      <c r="B121" s="1" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="122" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A122" t="s">
+    <row r="122" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A122" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" s="1" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="123" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A123" t="s">
+    <row r="123" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A123" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" s="1" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="124" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A124" t="s">
+    <row r="124" spans="1:3" ht="16.2" customHeight="1">
+      <c r="A124" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" s="1" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="125" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A125" t="s">
+    <row r="125" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A125" s="9" t="s">
         <v>250</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" s="9" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="126" ht="17.25" customHeight="1" spans="1:3">
-      <c r="A126" t="s">
+      <c r="C125" s="9"/>
+    </row>
+    <row r="126" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A126" s="9" t="s">
         <v>252</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" s="9" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="127" ht="17.25" customHeight="1"/>
-    <row r="128" ht="17.25" customHeight="1"/>
-    <row r="129" ht="17.25" customHeight="1"/>
-    <row r="130" ht="17.25" customHeight="1"/>
-    <row r="131" ht="17.25" customHeight="1"/>
-    <row r="132" ht="17.25" customHeight="1"/>
-    <row r="133" ht="17.25" customHeight="1"/>
-    <row r="134" ht="17.25" customHeight="1"/>
-    <row r="135" ht="17.25" customHeight="1"/>
-    <row r="136" ht="17.25" customHeight="1"/>
-    <row r="137" ht="17.25" customHeight="1"/>
-    <row r="138" ht="17.25" customHeight="1"/>
-    <row r="139" ht="17.25" customHeight="1"/>
-    <row r="140" ht="17.25" customHeight="1"/>
-    <row r="141" ht="17.25" customHeight="1"/>
-    <row r="142" ht="17.25" customHeight="1"/>
-    <row r="143" ht="17.25" customHeight="1"/>
-    <row r="144" ht="17.25" customHeight="1"/>
+      <c r="C126" s="9"/>
+    </row>
+    <row r="127" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A127" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A128" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" ht="17.25" customHeight="1">
+      <c r="A129" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B129" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C129" s="13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" ht="17.25" customHeight="1"/>
+    <row r="131" spans="1:3" ht="17.25" customHeight="1"/>
+    <row r="132" spans="1:3" ht="17.25" customHeight="1"/>
+    <row r="133" spans="1:3" ht="17.25" customHeight="1"/>
+    <row r="134" spans="1:3" ht="17.25" customHeight="1"/>
+    <row r="135" spans="1:3" ht="17.25" customHeight="1"/>
+    <row r="136" spans="1:3" ht="17.25" customHeight="1"/>
+    <row r="137" spans="1:3" ht="17.25" customHeight="1"/>
+    <row r="138" spans="1:3" ht="17.25" customHeight="1"/>
+    <row r="139" spans="1:3" ht="17.25" customHeight="1"/>
+    <row r="140" spans="1:3" ht="17.25" customHeight="1"/>
+    <row r="141" spans="1:3" ht="17.25" customHeight="1"/>
+    <row r="142" spans="1:3" ht="17.25" customHeight="1"/>
+    <row r="143" spans="1:3" ht="17.25" customHeight="1"/>
+    <row r="144" spans="1:3" ht="17.25" customHeight="1"/>
     <row r="145" ht="17.25" customHeight="1"/>
     <row r="146" ht="17.25" customHeight="1"/>
     <row r="147" ht="17.25" customHeight="1"/>
@@ -3935,10 +3167,9 @@
     <row r="996" ht="17.25" customHeight="1"/>
     <row r="997" ht="17.25" customHeight="1"/>
     <row r="998" ht="17.25" customHeight="1"/>
-    <row r="999" ht="17.25" customHeight="1"/>
   </sheetData>
+  <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup paperSize="1" orientation="landscape"/>
-  <headerFooter/>
+  <pageSetup orientation="landscape"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
@@ -1,24 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\바탕화면\Project\JewelThief\JewelThief\JsonConverter\ExcelFiles\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{405A4575-A771-46B8-905B-5967242A2E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="1812" yWindow="1812" windowWidth="28080" windowHeight="14628" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="v4mvBJYERGqiNruBTfijDgsGfB1L8a5WYzdi61pNbdg="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="ON79YGRFmG0PvJZg2zw1gtIfJ/OB/TVqK39qUUOl2CE="/>
     </ext>
   </extLst>
 </workbook>
@@ -471,10 +462,10 @@
     <t>Effect_Normal</t>
   </si>
   <si>
-    <t>PreLoadAsset_JewelInventory</t>
-  </si>
-  <si>
-    <t>JewelInventory</t>
+    <t>PreLoadAsset_BagInventoryView</t>
+  </si>
+  <si>
+    <t>BagInventoryView</t>
   </si>
   <si>
     <t>PreLoadAsset_PoliceThrow_Object</t>
@@ -810,80 +801,51 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <fonts count="9">
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Malgun Gothic"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color theme="1"/>
       <name val="Malgun Gothic"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="&quot;Malgun Gothic&quot;"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -891,7 +853,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -901,13 +863,7 @@
     </fill>
   </fills>
   <borders count="3">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -921,7 +877,6 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -933,49 +888,71 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="14">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+  <cellXfs count="19">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="2" fillId="2" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1165,23 +1142,23 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C998"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="52.109375" customWidth="1"/>
-    <col min="2" max="2" width="35.109375" customWidth="1"/>
-    <col min="3" max="3" width="31.44140625" customWidth="1"/>
-    <col min="4" max="26" width="9" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="52.14"/>
+    <col customWidth="1" min="2" max="2" width="35.14"/>
+    <col customWidth="1" min="3" max="3" width="31.43"/>
+    <col customWidth="1" min="4" max="26" width="9.0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="17.25" customHeight="1">
+    <row r="1" ht="17.25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1192,7 +1169,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="17.25" customHeight="1">
+    <row r="2" ht="17.25" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1203,7 +1180,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="17.25" customHeight="1">
+    <row r="3" ht="17.25" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1214,7 +1191,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="17.25" customHeight="1">
+    <row r="4" ht="17.25" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1222,7 +1199,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="17.25" customHeight="1">
+    <row r="5" ht="17.25" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -1230,7 +1207,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="17.25" customHeight="1">
+    <row r="6" ht="17.25" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -1238,7 +1215,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="17.25" customHeight="1">
+    <row r="7" ht="17.25" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -1246,7 +1223,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="17.25" customHeight="1">
+    <row r="8" ht="17.25" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -1254,7 +1231,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="17.25" customHeight="1">
+    <row r="9" ht="17.25" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -1262,7 +1239,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="17.25" customHeight="1">
+    <row r="10" ht="17.25" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -1270,7 +1247,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="17.25" customHeight="1">
+    <row r="11" ht="17.25" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>21</v>
       </c>
@@ -1278,7 +1255,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="17.25" customHeight="1">
+    <row r="12" ht="17.25" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>23</v>
       </c>
@@ -1286,7 +1263,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="17.25" customHeight="1">
+    <row r="13" ht="17.25" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>25</v>
       </c>
@@ -1294,7 +1271,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="17.25" customHeight="1">
+    <row r="14" ht="17.25" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>27</v>
       </c>
@@ -1302,7 +1279,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="17.25" customHeight="1">
+    <row r="15" ht="17.25" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>29</v>
       </c>
@@ -1310,7 +1287,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="17.25" customHeight="1">
+    <row r="16" ht="17.25" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>31</v>
       </c>
@@ -1318,7 +1295,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="17.25" customHeight="1">
+    <row r="17" ht="17.25" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>33</v>
       </c>
@@ -1326,7 +1303,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="17.25" customHeight="1">
+    <row r="18" ht="17.25" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -1334,7 +1311,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="17.25" customHeight="1">
+    <row r="19" ht="17.25" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>37</v>
       </c>
@@ -1342,7 +1319,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="17.25" customHeight="1">
+    <row r="20" ht="17.25" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>39</v>
       </c>
@@ -1350,7 +1327,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="17.25" customHeight="1">
+    <row r="21" ht="17.25" customHeight="1">
       <c r="A21" s="1" t="s">
         <v>41</v>
       </c>
@@ -1358,7 +1335,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="17.25" customHeight="1">
+    <row r="22" ht="17.25" customHeight="1">
       <c r="A22" s="1" t="s">
         <v>43</v>
       </c>
@@ -1366,7 +1343,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="17.25" customHeight="1">
+    <row r="23" ht="17.25" customHeight="1">
       <c r="A23" s="1" t="s">
         <v>45</v>
       </c>
@@ -1374,7 +1351,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="17.25" customHeight="1">
+    <row r="24" ht="17.25" customHeight="1">
       <c r="A24" s="1" t="s">
         <v>47</v>
       </c>
@@ -1382,7 +1359,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="17.25" customHeight="1">
+    <row r="25" ht="17.25" customHeight="1">
       <c r="A25" s="1" t="s">
         <v>49</v>
       </c>
@@ -1390,7 +1367,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="17.25" customHeight="1">
+    <row r="26" ht="17.25" customHeight="1">
       <c r="A26" s="1" t="s">
         <v>51</v>
       </c>
@@ -1398,7 +1375,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="17.25" customHeight="1">
+    <row r="27" ht="17.25" customHeight="1">
       <c r="A27" s="1" t="s">
         <v>53</v>
       </c>
@@ -1406,7 +1383,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="17.25" customHeight="1">
+    <row r="28" ht="17.25" customHeight="1">
       <c r="A28" s="1" t="s">
         <v>55</v>
       </c>
@@ -1414,7 +1391,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="17.25" customHeight="1">
+    <row r="29" ht="17.25" customHeight="1">
       <c r="A29" s="1" t="s">
         <v>57</v>
       </c>
@@ -1422,7 +1399,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="17.25" customHeight="1">
+    <row r="30" ht="17.25" customHeight="1">
       <c r="A30" s="1" t="s">
         <v>59</v>
       </c>
@@ -1430,7 +1407,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="17.25" customHeight="1">
+    <row r="31" ht="17.25" customHeight="1">
       <c r="A31" s="1" t="s">
         <v>61</v>
       </c>
@@ -1438,7 +1415,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="17.25" customHeight="1">
+    <row r="32" ht="17.25" customHeight="1">
       <c r="A32" s="1" t="s">
         <v>63</v>
       </c>
@@ -1446,7 +1423,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="17.25" customHeight="1">
+    <row r="33" ht="17.25" customHeight="1">
       <c r="A33" s="1" t="s">
         <v>65</v>
       </c>
@@ -1454,7 +1431,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="17.25" customHeight="1">
+    <row r="34" ht="17.25" customHeight="1">
       <c r="A34" s="1" t="s">
         <v>67</v>
       </c>
@@ -1462,7 +1439,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="17.25" customHeight="1">
+    <row r="35" ht="17.25" customHeight="1">
       <c r="A35" s="1" t="s">
         <v>69</v>
       </c>
@@ -1470,7 +1447,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="17.25" customHeight="1">
+    <row r="36" ht="17.25" customHeight="1">
       <c r="A36" s="1" t="s">
         <v>71</v>
       </c>
@@ -1478,7 +1455,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="17.25" customHeight="1">
+    <row r="37" ht="17.25" customHeight="1">
       <c r="A37" s="1" t="s">
         <v>73</v>
       </c>
@@ -1486,7 +1463,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="17.25" customHeight="1">
+    <row r="38" ht="17.25" customHeight="1">
       <c r="A38" s="1" t="s">
         <v>75</v>
       </c>
@@ -1494,7 +1471,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="17.25" customHeight="1">
+    <row r="39" ht="17.25" customHeight="1">
       <c r="A39" s="1" t="s">
         <v>77</v>
       </c>
@@ -1502,7 +1479,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="17.25" customHeight="1">
+    <row r="40" ht="17.25" customHeight="1">
       <c r="A40" s="1" t="s">
         <v>79</v>
       </c>
@@ -1510,7 +1487,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="17.25" customHeight="1">
+    <row r="41" ht="17.25" customHeight="1">
       <c r="A41" s="1" t="s">
         <v>81</v>
       </c>
@@ -1518,7 +1495,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="17.25" customHeight="1">
+    <row r="42" ht="17.25" customHeight="1">
       <c r="A42" s="1" t="s">
         <v>83</v>
       </c>
@@ -1526,7 +1503,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="17.25" customHeight="1">
+    <row r="43" ht="17.25" customHeight="1">
       <c r="A43" s="1" t="s">
         <v>85</v>
       </c>
@@ -1534,7 +1511,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="17.25" customHeight="1">
+    <row r="44" ht="17.25" customHeight="1">
       <c r="A44" s="1" t="s">
         <v>87</v>
       </c>
@@ -1542,7 +1519,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="17.25" customHeight="1">
+    <row r="45" ht="17.25" customHeight="1">
       <c r="A45" s="1" t="s">
         <v>89</v>
       </c>
@@ -1550,7 +1527,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="17.25" customHeight="1">
+    <row r="46" ht="17.25" customHeight="1">
       <c r="A46" s="1" t="s">
         <v>91</v>
       </c>
@@ -1558,7 +1535,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="17.25" customHeight="1">
+    <row r="47" ht="17.25" customHeight="1">
       <c r="A47" s="1" t="s">
         <v>93</v>
       </c>
@@ -1566,7 +1543,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="17.25" customHeight="1">
+    <row r="48" ht="17.25" customHeight="1">
       <c r="A48" s="2" t="s">
         <v>95</v>
       </c>
@@ -1574,7 +1551,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="17.25" customHeight="1">
+    <row r="49" ht="17.25" customHeight="1">
       <c r="A49" s="2" t="s">
         <v>97</v>
       </c>
@@ -1582,7 +1559,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="17.25" customHeight="1">
+    <row r="50" ht="17.25" customHeight="1">
       <c r="A50" s="2" t="s">
         <v>99</v>
       </c>
@@ -1590,7 +1567,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="17.25" customHeight="1">
+    <row r="51" ht="17.25" customHeight="1">
       <c r="A51" s="2" t="s">
         <v>101</v>
       </c>
@@ -1601,7 +1578,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="17.25" customHeight="1">
+    <row r="52" ht="17.25" customHeight="1">
       <c r="A52" s="2" t="s">
         <v>104</v>
       </c>
@@ -1609,7 +1586,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="17.25" customHeight="1">
+    <row r="53" ht="17.25" customHeight="1">
       <c r="A53" s="2" t="s">
         <v>106</v>
       </c>
@@ -1617,7 +1594,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="17.25" customHeight="1">
+    <row r="54" ht="17.25" customHeight="1">
       <c r="A54" s="2" t="s">
         <v>108</v>
       </c>
@@ -1625,7 +1602,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="17.25" customHeight="1">
+    <row r="55" ht="17.25" customHeight="1">
       <c r="A55" s="2" t="s">
         <v>110</v>
       </c>
@@ -1633,7 +1610,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="17.25" customHeight="1">
+    <row r="56" ht="17.25" customHeight="1">
       <c r="A56" s="2" t="s">
         <v>112</v>
       </c>
@@ -1641,7 +1618,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="17.25" customHeight="1">
+    <row r="57" ht="17.25" customHeight="1">
       <c r="A57" s="2" t="s">
         <v>114</v>
       </c>
@@ -1649,7 +1626,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="17.25" customHeight="1">
+    <row r="58" ht="17.25" customHeight="1">
       <c r="A58" s="2" t="s">
         <v>116</v>
       </c>
@@ -1657,7 +1634,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="17.25" customHeight="1">
+    <row r="59" ht="17.25" customHeight="1">
       <c r="A59" s="2" t="s">
         <v>118</v>
       </c>
@@ -1665,29 +1642,29 @@
         <v>119</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A60" s="7" t="s">
+    <row r="60" ht="17.25" customHeight="1">
+      <c r="A60" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="B60" s="7" t="s">
+      <c r="B60" s="8" t="s">
         <v>121</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A61" s="2" t="s">
+    <row r="61" ht="17.25" customHeight="1">
+      <c r="A61" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C61" s="10" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="17.25" customHeight="1">
+    <row r="62" ht="17.25" customHeight="1">
       <c r="A62" s="2" t="s">
         <v>124</v>
       </c>
@@ -1695,624 +1672,624 @@
         <v>125</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A63" s="2" t="s">
+    <row r="63" ht="17.25" customHeight="1">
+      <c r="A63" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B63" s="10" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A64" s="2" t="s">
+    <row r="64" ht="17.25" customHeight="1">
+      <c r="A64" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B64" s="10" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A65" s="2" t="s">
+    <row r="65" ht="17.25" customHeight="1">
+      <c r="A65" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B65" s="10" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A66" s="2" t="s">
+    <row r="66" ht="17.25" customHeight="1">
+      <c r="A66" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B66" s="10" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A67" s="2" t="s">
+    <row r="67" ht="17.25" customHeight="1">
+      <c r="A67" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" s="10" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A68" s="8" t="s">
+    <row r="68" ht="17.25" customHeight="1">
+      <c r="A68" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="B68" s="9" t="s">
+      <c r="B68" s="12" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A69" s="8" t="s">
+    <row r="69" ht="17.25" customHeight="1">
+      <c r="A69" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="B69" s="9" t="s">
+      <c r="B69" s="12" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A70" s="2" t="s">
+    <row r="70" ht="17.25" customHeight="1">
+      <c r="A70" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B70" s="10" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A71" s="2" t="s">
+    <row r="71" ht="17.25" customHeight="1">
+      <c r="A71" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B71" s="10" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A72" s="2" t="s">
+    <row r="72" ht="17.25" customHeight="1">
+      <c r="A72" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B72" s="10" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A73" s="2" t="s">
+    <row r="73" ht="17.25" customHeight="1">
+      <c r="A73" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B73" s="10" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A74" s="1" t="s">
+    <row r="74" ht="17.25" customHeight="1">
+      <c r="A74" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B74" s="10" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A75" s="1" t="s">
+    <row r="75" ht="17.25" customHeight="1">
+      <c r="A75" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B75" s="10" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A76" s="9" t="s">
+    <row r="76" ht="17.25" customHeight="1">
+      <c r="A76" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="B76" s="9" t="s">
+      <c r="B76" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="C76" s="9" t="s">
+      <c r="C76" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A77" s="9" t="s">
+    <row r="77" ht="17.25" customHeight="1">
+      <c r="A77" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="B77" s="9" t="s">
+      <c r="B77" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="C77" s="9" t="s">
+      <c r="C77" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A78" s="9" t="s">
+    <row r="78" ht="17.25" customHeight="1">
+      <c r="A78" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="B78" s="9" t="s">
+      <c r="B78" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="C78" s="9" t="s">
+      <c r="C78" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A79" s="9" t="s">
+    <row r="79" ht="17.25" customHeight="1">
+      <c r="A79" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="B79" s="9" t="s">
+      <c r="B79" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="C79" s="9" t="s">
+      <c r="C79" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A80" s="9" t="s">
+    <row r="80" ht="17.25" customHeight="1">
+      <c r="A80" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="B80" s="9" t="s">
+      <c r="B80" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="C80" s="9" t="s">
+      <c r="C80" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A81" s="9" t="s">
+    <row r="81" ht="17.25" customHeight="1">
+      <c r="A81" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="B81" s="9" t="s">
+      <c r="B81" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="C81" s="9"/>
-    </row>
-    <row r="82" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A82" s="9" t="s">
+      <c r="C81" s="14"/>
+    </row>
+    <row r="82" ht="17.25" customHeight="1">
+      <c r="A82" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="B82" s="9" t="s">
+      <c r="B82" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="C82" s="9"/>
-    </row>
-    <row r="83" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A83" s="9" t="s">
+      <c r="C82" s="14"/>
+    </row>
+    <row r="83" ht="17.25" customHeight="1">
+      <c r="A83" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="B83" s="9" t="s">
+      <c r="B83" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="C83" s="9"/>
-    </row>
-    <row r="84" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A84" s="9" t="s">
+      <c r="C83" s="14"/>
+    </row>
+    <row r="84" ht="17.25" customHeight="1">
+      <c r="A84" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="B84" s="9" t="s">
+      <c r="B84" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="C84" s="9"/>
-    </row>
-    <row r="85" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A85" s="9" t="s">
+      <c r="C84" s="14"/>
+    </row>
+    <row r="85" ht="17.25" customHeight="1">
+      <c r="A85" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="B85" s="9" t="s">
+      <c r="B85" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="C85" s="9"/>
-    </row>
-    <row r="86" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A86" s="9" t="s">
+      <c r="C85" s="14"/>
+    </row>
+    <row r="86" ht="17.25" customHeight="1">
+      <c r="A86" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="B86" s="9" t="s">
+      <c r="B86" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="C86" s="9"/>
-    </row>
-    <row r="87" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A87" s="9" t="s">
+      <c r="C86" s="14"/>
+    </row>
+    <row r="87" ht="17.25" customHeight="1">
+      <c r="A87" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="B87" s="9" t="s">
+      <c r="B87" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="C87" s="9"/>
-    </row>
-    <row r="88" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A88" s="9" t="s">
+      <c r="C87" s="14"/>
+    </row>
+    <row r="88" ht="17.25" customHeight="1">
+      <c r="A88" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="B88" s="9" t="s">
+      <c r="B88" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="C88" s="9"/>
-    </row>
-    <row r="89" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A89" s="9" t="s">
+      <c r="C88" s="14"/>
+    </row>
+    <row r="89" ht="17.25" customHeight="1">
+      <c r="A89" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="B89" s="9" t="s">
+      <c r="B89" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="C89" s="9"/>
-    </row>
-    <row r="90" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A90" s="1" t="s">
+      <c r="C89" s="14"/>
+    </row>
+    <row r="90" ht="17.25" customHeight="1">
+      <c r="A90" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="B90" s="10" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A91" s="1" t="s">
+    <row r="91" ht="17.25" customHeight="1">
+      <c r="A91" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="B91" s="10" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A92" s="1" t="s">
+    <row r="92" ht="17.25" customHeight="1">
+      <c r="A92" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="B92" s="10" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A93" s="1" t="s">
+    <row r="93" ht="17.25" customHeight="1">
+      <c r="A93" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="B93" s="10" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A94" s="9" t="s">
+    <row r="94" ht="17.25" customHeight="1">
+      <c r="A94" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="B94" s="9" t="s">
+      <c r="B94" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="C94" s="9"/>
-    </row>
-    <row r="95" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A95" s="9" t="s">
+      <c r="C94" s="14"/>
+    </row>
+    <row r="95" ht="17.25" customHeight="1">
+      <c r="A95" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="B95" s="10" t="s">
+      <c r="B95" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="C95" s="9" t="s">
+      <c r="C95" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A96" s="9" t="s">
+    <row r="96" ht="17.25" customHeight="1">
+      <c r="A96" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="B96" s="10" t="s">
+      <c r="B96" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="C96" s="9"/>
-    </row>
-    <row r="97" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A97" s="9" t="s">
+      <c r="C96" s="14"/>
+    </row>
+    <row r="97" ht="17.25" customHeight="1">
+      <c r="A97" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="B97" s="10" t="s">
+      <c r="B97" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="C97" s="9"/>
-    </row>
-    <row r="98" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A98" s="9" t="s">
+      <c r="C97" s="14"/>
+    </row>
+    <row r="98" ht="17.25" customHeight="1">
+      <c r="A98" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="B98" s="10" t="s">
+      <c r="B98" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="C98" s="9"/>
-    </row>
-    <row r="99" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A99" s="9" t="s">
+      <c r="C98" s="14"/>
+    </row>
+    <row r="99" ht="17.25" customHeight="1">
+      <c r="A99" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="B99" s="10" t="s">
+      <c r="B99" s="15" t="s">
         <v>199</v>
       </c>
-      <c r="C99" s="9"/>
-    </row>
-    <row r="100" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A100" s="1" t="s">
+      <c r="C99" s="14"/>
+    </row>
+    <row r="100" ht="17.25" customHeight="1">
+      <c r="A100" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="B100" s="10" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A101" s="1" t="s">
+    <row r="101" ht="17.25" customHeight="1">
+      <c r="A101" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="B101" s="10" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A102" s="1" t="s">
+    <row r="102" ht="17.25" customHeight="1">
+      <c r="A102" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="B102" s="10" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A103" s="1" t="s">
+    <row r="103" ht="17.25" customHeight="1">
+      <c r="A103" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="B103" s="10" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A104" s="1" t="s">
+    <row r="104" ht="17.25" customHeight="1">
+      <c r="A104" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="B104" s="1" t="s">
+      <c r="B104" s="10" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A105" s="1" t="s">
+    <row r="105" ht="17.25" customHeight="1">
+      <c r="A105" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="B105" s="1" t="s">
+      <c r="B105" s="10" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A106" s="1" t="s">
+    <row r="106" ht="17.25" customHeight="1">
+      <c r="A106" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="B106" s="1" t="s">
+      <c r="B106" s="10" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A107" s="1" t="s">
+    <row r="107" ht="17.25" customHeight="1">
+      <c r="A107" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="B107" s="5" t="s">
+      <c r="B107" s="16" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A108" s="11" t="s">
+    <row r="108" ht="17.25" customHeight="1">
+      <c r="A108" s="17" t="s">
         <v>216</v>
       </c>
-      <c r="B108" s="11" t="s">
+      <c r="B108" s="18" t="s">
         <v>217</v>
       </c>
-      <c r="C108" s="9" t="s">
+      <c r="C108" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A109" s="11" t="s">
+    <row r="109" ht="17.25" customHeight="1">
+      <c r="A109" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="B109" s="11" t="s">
+      <c r="B109" s="17" t="s">
         <v>219</v>
       </c>
-      <c r="C109" s="9" t="s">
+      <c r="C109" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A110" s="11" t="s">
+    <row r="110" ht="17.25" customHeight="1">
+      <c r="A110" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="B110" s="11" t="s">
+      <c r="B110" s="18" t="s">
         <v>221</v>
       </c>
-      <c r="C110" s="9" t="s">
+      <c r="C110" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A111" s="11" t="s">
+    <row r="111" ht="17.25" customHeight="1">
+      <c r="A111" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="B111" s="11" t="s">
+      <c r="B111" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="C111" s="9" t="s">
+      <c r="C111" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A112" s="11" t="s">
+    <row r="112" ht="17.25" customHeight="1">
+      <c r="A112" s="17" t="s">
         <v>224</v>
       </c>
-      <c r="B112" s="11" t="s">
+      <c r="B112" s="18" t="s">
         <v>225</v>
       </c>
-      <c r="C112" s="9" t="s">
+      <c r="C112" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A113" s="11" t="s">
+    <row r="113" ht="17.25" customHeight="1">
+      <c r="A113" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="B113" s="11" t="s">
+      <c r="B113" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="C113" s="9" t="s">
+      <c r="C113" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A114" s="11" t="s">
+    <row r="114" ht="17.25" customHeight="1">
+      <c r="A114" s="17" t="s">
         <v>228</v>
       </c>
-      <c r="B114" s="11" t="s">
+      <c r="B114" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="C114" s="9" t="s">
+      <c r="C114" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A115" s="1" t="s">
+    <row r="115" ht="17.25" customHeight="1">
+      <c r="A115" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="B115" s="5" t="s">
+      <c r="B115" s="16" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A116" s="11" t="s">
+    <row r="116" ht="17.25" customHeight="1">
+      <c r="A116" s="17" t="s">
         <v>232</v>
       </c>
-      <c r="B116" s="11" t="s">
+      <c r="B116" s="18" t="s">
         <v>233</v>
       </c>
-      <c r="C116" s="9" t="s">
+      <c r="C116" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A117" s="11" t="s">
+    <row r="117" ht="17.25" customHeight="1">
+      <c r="A117" s="17" t="s">
         <v>234</v>
       </c>
-      <c r="B117" s="11" t="s">
+      <c r="B117" s="18" t="s">
         <v>235</v>
       </c>
-      <c r="C117" s="9" t="s">
+      <c r="C117" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A118" s="1" t="s">
+    <row r="118" ht="17.25" customHeight="1">
+      <c r="A118" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="B118" s="1" t="s">
+      <c r="B118" s="10" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A119" s="1" t="s">
+    <row r="119" ht="17.25" customHeight="1">
+      <c r="A119" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="B119" s="1" t="s">
+      <c r="B119" s="10" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A120" s="1" t="s">
+    <row r="120" ht="17.25" customHeight="1">
+      <c r="A120" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="B120" s="1" t="s">
+      <c r="B120" s="10" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A121" s="1" t="s">
+    <row r="121" ht="17.25" customHeight="1">
+      <c r="A121" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="B121" s="10" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A122" s="1" t="s">
+    <row r="122" ht="17.25" customHeight="1">
+      <c r="A122" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="B122" s="1" t="s">
+      <c r="B122" s="10" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A123" s="1" t="s">
+    <row r="123" ht="17.25" customHeight="1">
+      <c r="A123" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="B123" s="1" t="s">
+      <c r="B123" s="10" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="16.2" customHeight="1">
-      <c r="A124" s="1" t="s">
+    <row r="124" ht="17.25" customHeight="1">
+      <c r="A124" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="B124" s="1" t="s">
+      <c r="B124" s="10" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="125" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A125" s="9" t="s">
+    <row r="125" ht="17.25" customHeight="1">
+      <c r="A125" s="13" t="s">
         <v>250</v>
       </c>
-      <c r="B125" s="9" t="s">
+      <c r="B125" s="13" t="s">
         <v>251</v>
       </c>
-      <c r="C125" s="9"/>
-    </row>
-    <row r="126" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A126" s="9" t="s">
+      <c r="C125" s="14"/>
+    </row>
+    <row r="126" ht="17.25" customHeight="1">
+      <c r="A126" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="B126" s="9" t="s">
+      <c r="B126" s="13" t="s">
         <v>253</v>
       </c>
-      <c r="C126" s="9"/>
-    </row>
-    <row r="127" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A127" s="1" t="s">
+      <c r="C126" s="14"/>
+    </row>
+    <row r="127" ht="17.25" customHeight="1">
+      <c r="A127" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="B127" s="1" t="s">
+      <c r="B127" s="10" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A128" s="1" t="s">
+    <row r="128" ht="17.25" customHeight="1">
+      <c r="A128" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="B128" s="1" t="s">
+      <c r="B128" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="C128" s="1" t="s">
+      <c r="C128" s="10" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A129" s="1" t="s">
+    <row r="129" ht="17.25" customHeight="1">
+      <c r="A129" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="B129" s="12" t="s">
+      <c r="B129" s="16" t="s">
         <v>259</v>
       </c>
-      <c r="C129" s="13" t="s">
+      <c r="C129" s="10" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="17.25" customHeight="1"/>
-    <row r="131" spans="1:3" ht="17.25" customHeight="1"/>
-    <row r="132" spans="1:3" ht="17.25" customHeight="1"/>
-    <row r="133" spans="1:3" ht="17.25" customHeight="1"/>
-    <row r="134" spans="1:3" ht="17.25" customHeight="1"/>
-    <row r="135" spans="1:3" ht="17.25" customHeight="1"/>
-    <row r="136" spans="1:3" ht="17.25" customHeight="1"/>
-    <row r="137" spans="1:3" ht="17.25" customHeight="1"/>
-    <row r="138" spans="1:3" ht="17.25" customHeight="1"/>
-    <row r="139" spans="1:3" ht="17.25" customHeight="1"/>
-    <row r="140" spans="1:3" ht="17.25" customHeight="1"/>
-    <row r="141" spans="1:3" ht="17.25" customHeight="1"/>
-    <row r="142" spans="1:3" ht="17.25" customHeight="1"/>
-    <row r="143" spans="1:3" ht="17.25" customHeight="1"/>
-    <row r="144" spans="1:3" ht="17.25" customHeight="1"/>
+    <row r="130" ht="17.25" customHeight="1"/>
+    <row r="131" ht="17.25" customHeight="1"/>
+    <row r="132" ht="17.25" customHeight="1"/>
+    <row r="133" ht="17.25" customHeight="1"/>
+    <row r="134" ht="17.25" customHeight="1"/>
+    <row r="135" ht="17.25" customHeight="1"/>
+    <row r="136" ht="17.25" customHeight="1"/>
+    <row r="137" ht="17.25" customHeight="1"/>
+    <row r="138" ht="17.25" customHeight="1"/>
+    <row r="139" ht="17.25" customHeight="1"/>
+    <row r="140" ht="17.25" customHeight="1"/>
+    <row r="141" ht="17.25" customHeight="1"/>
+    <row r="142" ht="17.25" customHeight="1"/>
+    <row r="143" ht="17.25" customHeight="1"/>
+    <row r="144" ht="17.25" customHeight="1"/>
     <row r="145" ht="17.25" customHeight="1"/>
     <row r="146" ht="17.25" customHeight="1"/>
     <row r="147" ht="17.25" customHeight="1"/>
@@ -3168,8 +3145,9 @@
     <row r="997" ht="17.25" customHeight="1"/>
     <row r="998" ht="17.25" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="262">
   <si>
     <t>미리 로드할 어드레서블 테이블</t>
   </si>
@@ -796,13 +796,19 @@
   </si>
   <si>
     <t>Mesh_Escape[SM_Prop_Vent_01]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PreLoadAsset_Materail_Mashroom_1 </t>
+  </si>
+  <si>
+    <t>Mashroom_1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -846,6 +852,11 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color theme="1"/>
+      <name val="&quot;gg sans&quot;"/>
     </font>
   </fonts>
   <fills count="3">
@@ -893,7 +904,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -938,6 +949,9 @@
     </xf>
     <xf borderId="1" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2275,7 +2289,14 @@
         <v>103</v>
       </c>
     </row>
-    <row r="130" ht="17.25" customHeight="1"/>
+    <row r="130" ht="17.25" customHeight="1">
+      <c r="A130" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="B130" s="19" t="s">
+        <v>261</v>
+      </c>
+    </row>
     <row r="131" ht="17.25" customHeight="1"/>
     <row r="132" ht="17.25" customHeight="1"/>
     <row r="133" ht="17.25" customHeight="1"/>

--- a/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="ON79YGRFmG0PvJZg2zw1gtIfJ/OB/TVqK39qUUOl2CE="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="IrwRp8ohCmUvTV/yUXNsVZJhJjJcNEiR2HtWorYcj/g="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="258">
   <si>
     <t>미리 로드할 어드레서블 테이블</t>
   </si>
@@ -712,18 +712,6 @@
   </si>
   <si>
     <t>PolygonNightclub_Mat_01_A_Metallic</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_MeshCollier_Junk_Bottle_Blue</t>
-  </si>
-  <si>
-    <t>MeshCollider_Junk_Bottle_Blue</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_MeshCollider_Junk_Bottle_Pink_Large</t>
-  </si>
-  <si>
-    <t>MeshCollider_Junk_Bottle_Pink_Large</t>
   </si>
   <si>
     <t>PreLoadAsset_GameObject_ItemObject</t>
@@ -2164,25 +2152,19 @@
       </c>
     </row>
     <row r="116" ht="17.25" customHeight="1">
-      <c r="A116" s="17" t="s">
+      <c r="A116" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="B116" s="18" t="s">
+      <c r="B116" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="C116" s="13" t="s">
-        <v>103</v>
-      </c>
     </row>
     <row r="117" ht="17.25" customHeight="1">
-      <c r="A117" s="17" t="s">
+      <c r="A117" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="B117" s="18" t="s">
+      <c r="B117" s="10" t="s">
         <v>235</v>
-      </c>
-      <c r="C117" s="13" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="118" ht="17.25" customHeight="1">
@@ -2226,77 +2208,63 @@
       </c>
     </row>
     <row r="123" ht="17.25" customHeight="1">
-      <c r="A123" s="10" t="s">
+      <c r="A123" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="B123" s="10" t="s">
+      <c r="B123" s="13" t="s">
         <v>247</v>
       </c>
+      <c r="C123" s="14"/>
     </row>
     <row r="124" ht="17.25" customHeight="1">
-      <c r="A124" s="10" t="s">
+      <c r="A124" s="13" t="s">
         <v>248</v>
       </c>
-      <c r="B124" s="10" t="s">
+      <c r="B124" s="13" t="s">
         <v>249</v>
       </c>
+      <c r="C124" s="14"/>
     </row>
     <row r="125" ht="17.25" customHeight="1">
-      <c r="A125" s="13" t="s">
+      <c r="A125" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="B125" s="13" t="s">
+      <c r="B125" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="C125" s="14"/>
     </row>
     <row r="126" ht="17.25" customHeight="1">
-      <c r="A126" s="13" t="s">
+      <c r="A126" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="B126" s="13" t="s">
+      <c r="B126" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="C126" s="14"/>
+      <c r="C126" s="10" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="127" ht="17.25" customHeight="1">
       <c r="A127" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="B127" s="10" t="s">
+      <c r="B127" s="16" t="s">
         <v>255</v>
+      </c>
+      <c r="C127" s="10" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="128" ht="17.25" customHeight="1">
       <c r="A128" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="B128" s="10" t="s">
+      <c r="B128" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="C128" s="10" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="129" ht="17.25" customHeight="1">
-      <c r="A129" s="10" t="s">
-        <v>258</v>
-      </c>
-      <c r="B129" s="16" t="s">
-        <v>259</v>
-      </c>
-      <c r="C129" s="10" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="130" ht="17.25" customHeight="1">
-      <c r="A130" s="10" t="s">
-        <v>260</v>
-      </c>
-      <c r="B130" s="19" t="s">
-        <v>261</v>
-      </c>
-    </row>
+    </row>
+    <row r="129" ht="17.25" customHeight="1"/>
+    <row r="130" ht="17.25" customHeight="1"/>
     <row r="131" ht="17.25" customHeight="1"/>
     <row r="132" ht="17.25" customHeight="1"/>
     <row r="133" ht="17.25" customHeight="1"/>
@@ -3163,8 +3131,6 @@
     <row r="994" ht="17.25" customHeight="1"/>
     <row r="995" ht="17.25" customHeight="1"/>
     <row r="996" ht="17.25" customHeight="1"/>
-    <row r="997" ht="17.25" customHeight="1"/>
-    <row r="998" ht="17.25" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>

--- a/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
+++ b/JsonConverter/ExcelFiles/PreLoadAsset.xlsx
@@ -1,31 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\바탕화면\Project\JewelThief\JewelThief\JsonConverter\ExcelFiles\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{405A4575-A771-46B8-905B-5967242A2E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="1812" yWindow="1812" windowWidth="28080" windowHeight="14628" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="v4mvBJYERGqiNruBTfijDgsGfB1L8a5WYzdi61pNbdg="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="IrwRp8ohCmUvTV/yUXNsVZJhJjJcNEiR2HtWorYcj/g="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="258">
   <si>
     <t>미리 로드할 어드레서블 테이블</t>
   </si>
@@ -471,10 +462,10 @@
     <t>Effect_Normal</t>
   </si>
   <si>
-    <t>PreLoadAsset_JewelInventory</t>
-  </si>
-  <si>
-    <t>JewelInventory</t>
+    <t>PreLoadAsset_BagInventoryView</t>
+  </si>
+  <si>
+    <t>BagInventoryView</t>
   </si>
   <si>
     <t>PreLoadAsset_PoliceThrow_Object</t>
@@ -723,18 +714,6 @@
     <t>PolygonNightclub_Mat_01_A_Metallic</t>
   </si>
   <si>
-    <t>PreLoadAsset_MeshCollier_Junk_Bottle_Blue</t>
-  </si>
-  <si>
-    <t>MeshCollider_Junk_Bottle_Blue</t>
-  </si>
-  <si>
-    <t>PreLoadAsset_MeshCollider_Junk_Bottle_Pink_Large</t>
-  </si>
-  <si>
-    <t>MeshCollider_Junk_Bottle_Pink_Large</t>
-  </si>
-  <si>
     <t>PreLoadAsset_GameObject_ItemObject</t>
   </si>
   <si>
@@ -805,85 +784,67 @@
   </si>
   <si>
     <t>Mesh_Escape[SM_Prop_Vent_01]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PreLoadAsset_Materail_Mashroom_1 </t>
+  </si>
+  <si>
+    <t>Mashroom_1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <fonts count="10">
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color theme="1"/>
       <name val="Malgun Gothic"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color theme="1"/>
       <name val="Malgun Gothic"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="&quot;Malgun Gothic&quot;"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
+      <sz val="12.0"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <name val="&quot;gg sans&quot;"/>
     </font>
   </fonts>
   <fills count="3">
@@ -891,7 +852,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -901,13 +862,7 @@
     </fill>
   </fills>
   <borders count="3">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -921,7 +876,6 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -933,49 +887,74 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
-      <bottom/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="14">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+  <cellXfs count="20">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="2" fillId="2" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1165,23 +1144,23 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C998"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <pageSetUpPr/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="52.109375" customWidth="1"/>
-    <col min="2" max="2" width="35.109375" customWidth="1"/>
-    <col min="3" max="3" width="31.44140625" customWidth="1"/>
-    <col min="4" max="26" width="9" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="52.14"/>
+    <col customWidth="1" min="2" max="2" width="35.14"/>
+    <col customWidth="1" min="3" max="3" width="31.43"/>
+    <col customWidth="1" min="4" max="26" width="9.0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="17.25" customHeight="1">
+    <row r="1" ht="17.25" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1192,7 +1171,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="17.25" customHeight="1">
+    <row r="2" ht="17.25" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1203,7 +1182,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="17.25" customHeight="1">
+    <row r="3" ht="17.25" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -1214,7 +1193,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="17.25" customHeight="1">
+    <row r="4" ht="17.25" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1222,7 +1201,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="17.25" customHeight="1">
+    <row r="5" ht="17.25" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -1230,7 +1209,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="17.25" customHeight="1">
+    <row r="6" ht="17.25" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -1238,7 +1217,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="17.25" customHeight="1">
+    <row r="7" ht="17.25" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -1246,7 +1225,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="17.25" customHeight="1">
+    <row r="8" ht="17.25" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>15</v>
       </c>
@@ -1254,7 +1233,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="17.25" customHeight="1">
+    <row r="9" ht="17.25" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -1262,7 +1241,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="17.25" customHeight="1">
+    <row r="10" ht="17.25" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>19</v>
       </c>
@@ -1270,7 +1249,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="17.25" customHeight="1">
+    <row r="11" ht="17.25" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>21</v>
       </c>
@@ -1278,7 +1257,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="17.25" customHeight="1">
+    <row r="12" ht="17.25" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>23</v>
       </c>
@@ -1286,7 +1265,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="17.25" customHeight="1">
+    <row r="13" ht="17.25" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>25</v>
       </c>
@@ -1294,7 +1273,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="17.25" customHeight="1">
+    <row r="14" ht="17.25" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>27</v>
       </c>
@@ -1302,7 +1281,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="17.25" customHeight="1">
+    <row r="15" ht="17.25" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>29</v>
       </c>
@@ -1310,7 +1289,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="17.25" customHeight="1">
+    <row r="16" ht="17.25" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>31</v>
       </c>
@@ -1318,7 +1297,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="17.25" customHeight="1">
+    <row r="17" ht="17.25" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>33</v>
       </c>
@@ -1326,7 +1305,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="17.25" customHeight="1">
+    <row r="18" ht="17.25" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -1334,7 +1313,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="17.25" customHeight="1">
+    <row r="19" ht="17.25" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>37</v>
       </c>
@@ -1342,7 +1321,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="17.25" customHeight="1">
+    <row r="20" ht="17.25" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>39</v>
       </c>
@@ -1350,7 +1329,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="17.25" customHeight="1">
+    <row r="21" ht="17.25" customHeight="1">
       <c r="A21" s="1" t="s">
         <v>41</v>
       </c>
@@ -1358,7 +1337,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="17.25" customHeight="1">
+    <row r="22" ht="17.25" customHeight="1">
       <c r="A22" s="1" t="s">
         <v>43</v>
       </c>
@@ -1366,7 +1345,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="17.25" customHeight="1">
+    <row r="23" ht="17.25" customHeight="1">
       <c r="A23" s="1" t="s">
         <v>45</v>
       </c>
@@ -1374,7 +1353,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="17.25" customHeight="1">
+    <row r="24" ht="17.25" customHeight="1">
       <c r="A24" s="1" t="s">
         <v>47</v>
       </c>
@@ -1382,7 +1361,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="17.25" customHeight="1">
+    <row r="25" ht="17.25" customHeight="1">
       <c r="A25" s="1" t="s">
         <v>49</v>
       </c>
@@ -1390,7 +1369,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="17.25" customHeight="1">
+    <row r="26" ht="17.25" customHeight="1">
       <c r="A26" s="1" t="s">
         <v>51</v>
       </c>
@@ -1398,7 +1377,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="17.25" customHeight="1">
+    <row r="27" ht="17.25" customHeight="1">
       <c r="A27" s="1" t="s">
         <v>53</v>
       </c>
@@ -1406,7 +1385,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="17.25" customHeight="1">
+    <row r="28" ht="17.25" customHeight="1">
       <c r="A28" s="1" t="s">
         <v>55</v>
       </c>
@@ -1414,7 +1393,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="17.25" customHeight="1">
+    <row r="29" ht="17.25" customHeight="1">
       <c r="A29" s="1" t="s">
         <v>57</v>
       </c>
@@ -1422,7 +1401,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="17.25" customHeight="1">
+    <row r="30" ht="17.25" customHeight="1">
       <c r="A30" s="1" t="s">
         <v>59</v>
       </c>
@@ -1430,7 +1409,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="17.25" customHeight="1">
+    <row r="31" ht="17.25" customHeight="1">
       <c r="A31" s="1" t="s">
         <v>61</v>
       </c>
@@ -1438,7 +1417,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="17.25" customHeight="1">
+    <row r="32" ht="17.25" customHeight="1">
       <c r="A32" s="1" t="s">
         <v>63</v>
       </c>
@@ -1446,7 +1425,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="17.25" customHeight="1">
+    <row r="33" ht="17.25" customHeight="1">
       <c r="A33" s="1" t="s">
         <v>65</v>
       </c>
@@ -1454,7 +1433,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="17.25" customHeight="1">
+    <row r="34" ht="17.25" customHeight="1">
       <c r="A34" s="1" t="s">
         <v>67</v>
       </c>
@@ -1462,7 +1441,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="17.25" customHeight="1">
+    <row r="35" ht="17.25" customHeight="1">
       <c r="A35" s="1" t="s">
         <v>69</v>
       </c>
@@ -1470,7 +1449,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="17.25" customHeight="1">
+    <row r="36" ht="17.25" customHeight="1">
       <c r="A36" s="1" t="s">
         <v>71</v>
       </c>
@@ -1478,7 +1457,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="17.25" customHeight="1">
+    <row r="37" ht="17.25" customHeight="1">
       <c r="A37" s="1" t="s">
         <v>73</v>
       </c>
@@ -1486,7 +1465,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="17.25" customHeight="1">
+    <row r="38" ht="17.25" customHeight="1">
       <c r="A38" s="1" t="s">
         <v>75</v>
       </c>
@@ -1494,7 +1473,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="17.25" customHeight="1">
+    <row r="39" ht="17.25" customHeight="1">
       <c r="A39" s="1" t="s">
         <v>77</v>
       </c>
@@ -1502,7 +1481,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="17.25" customHeight="1">
+    <row r="40" ht="17.25" customHeight="1">
       <c r="A40" s="1" t="s">
         <v>79</v>
       </c>
@@ -1510,7 +1489,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="17.25" customHeight="1">
+    <row r="41" ht="17.25" customHeight="1">
       <c r="A41" s="1" t="s">
         <v>81</v>
       </c>
@@ -1518,7 +1497,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="17.25" customHeight="1">
+    <row r="42" ht="17.25" customHeight="1">
       <c r="A42" s="1" t="s">
         <v>83</v>
       </c>
@@ -1526,7 +1505,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="17.25" customHeight="1">
+    <row r="43" ht="17.25" customHeight="1">
       <c r="A43" s="1" t="s">
         <v>85</v>
       </c>
@@ -1534,7 +1513,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="17.25" customHeight="1">
+    <row r="44" ht="17.25" customHeight="1">
       <c r="A44" s="1" t="s">
         <v>87</v>
       </c>
@@ -1542,7 +1521,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="17.25" customHeight="1">
+    <row r="45" ht="17.25" customHeight="1">
       <c r="A45" s="1" t="s">
         <v>89</v>
       </c>
@@ -1550,7 +1529,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="17.25" customHeight="1">
+    <row r="46" ht="17.25" customHeight="1">
       <c r="A46" s="1" t="s">
         <v>91</v>
       </c>
@@ -1558,7 +1537,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="17.25" customHeight="1">
+    <row r="47" ht="17.25" customHeight="1">
       <c r="A47" s="1" t="s">
         <v>93</v>
       </c>
@@ -1566,7 +1545,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="17.25" customHeight="1">
+    <row r="48" ht="17.25" customHeight="1">
       <c r="A48" s="2" t="s">
         <v>95</v>
       </c>
@@ -1574,7 +1553,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="17.25" customHeight="1">
+    <row r="49" ht="17.25" customHeight="1">
       <c r="A49" s="2" t="s">
         <v>97</v>
       </c>
@@ -1582,7 +1561,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="17.25" customHeight="1">
+    <row r="50" ht="17.25" customHeight="1">
       <c r="A50" s="2" t="s">
         <v>99</v>
       </c>
@@ -1590,7 +1569,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="17.25" customHeight="1">
+    <row r="51" ht="17.25" customHeight="1">
       <c r="A51" s="2" t="s">
         <v>101</v>
       </c>
@@ -1601,7 +1580,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="17.25" customHeight="1">
+    <row r="52" ht="17.25" customHeight="1">
       <c r="A52" s="2" t="s">
         <v>104</v>
       </c>
@@ -1609,7 +1588,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="17.25" customHeight="1">
+    <row r="53" ht="17.25" customHeight="1">
       <c r="A53" s="2" t="s">
         <v>106</v>
       </c>
@@ -1617,7 +1596,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="17.25" customHeight="1">
+    <row r="54" ht="17.25" customHeight="1">
       <c r="A54" s="2" t="s">
         <v>108</v>
       </c>
@@ -1625,7 +1604,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="17.25" customHeight="1">
+    <row r="55" ht="17.25" customHeight="1">
       <c r="A55" s="2" t="s">
         <v>110</v>
       </c>
@@ -1633,7 +1612,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="17.25" customHeight="1">
+    <row r="56" ht="17.25" customHeight="1">
       <c r="A56" s="2" t="s">
         <v>112</v>
       </c>
@@ -1641,7 +1620,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="17.25" customHeight="1">
+    <row r="57" ht="17.25" customHeight="1">
       <c r="A57" s="2" t="s">
         <v>114</v>
       </c>
@@ -1649,7 +1628,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="17.25" customHeight="1">
+    <row r="58" ht="17.25" customHeight="1">
       <c r="A58" s="2" t="s">
         <v>116</v>
       </c>
@@ -1657,7 +1636,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="17.25" customHeight="1">
+    <row r="59" ht="17.25" customHeight="1">
       <c r="A59" s="2" t="s">
         <v>118</v>
       </c>
@@ -1665,29 +1644,29 @@
         <v>119</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A60" s="7" t="s">
+    <row r="60" ht="17.25" customHeight="1">
+      <c r="A60" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="B60" s="7" t="s">
+      <c r="B60" s="8" t="s">
         <v>121</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A61" s="2" t="s">
+    <row r="61" ht="17.25" customHeight="1">
+      <c r="A61" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C61" s="10" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="17.25" customHeight="1">
+    <row r="62" ht="17.25" customHeight="1">
       <c r="A62" s="2" t="s">
         <v>124</v>
       </c>
@@ -1695,624 +1674,611 @@
         <v>125</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A63" s="2" t="s">
+    <row r="63" ht="17.25" customHeight="1">
+      <c r="A63" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B63" s="10" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A64" s="2" t="s">
+    <row r="64" ht="17.25" customHeight="1">
+      <c r="A64" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B64" s="10" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A65" s="2" t="s">
+    <row r="65" ht="17.25" customHeight="1">
+      <c r="A65" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B65" s="10" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A66" s="2" t="s">
+    <row r="66" ht="17.25" customHeight="1">
+      <c r="A66" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B66" s="10" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A67" s="2" t="s">
+    <row r="67" ht="17.25" customHeight="1">
+      <c r="A67" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" s="10" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A68" s="8" t="s">
+    <row r="68" ht="17.25" customHeight="1">
+      <c r="A68" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="B68" s="9" t="s">
+      <c r="B68" s="12" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A69" s="8" t="s">
+    <row r="69" ht="17.25" customHeight="1">
+      <c r="A69" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="B69" s="9" t="s">
+      <c r="B69" s="12" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A70" s="2" t="s">
+    <row r="70" ht="17.25" customHeight="1">
+      <c r="A70" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B70" s="10" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A71" s="2" t="s">
+    <row r="71" ht="17.25" customHeight="1">
+      <c r="A71" s="9" t="s">
         <v>142</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B71" s="10" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A72" s="2" t="s">
+    <row r="72" ht="17.25" customHeight="1">
+      <c r="A72" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B72" s="10" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A73" s="2" t="s">
+    <row r="73" ht="17.25" customHeight="1">
+      <c r="A73" s="9" t="s">
         <v>146</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B73" s="10" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A74" s="1" t="s">
+    <row r="74" ht="17.25" customHeight="1">
+      <c r="A74" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B74" s="10" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A75" s="1" t="s">
+    <row r="75" ht="17.25" customHeight="1">
+      <c r="A75" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B75" s="10" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A76" s="9" t="s">
+    <row r="76" ht="17.25" customHeight="1">
+      <c r="A76" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="B76" s="9" t="s">
+      <c r="B76" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="C76" s="9" t="s">
+      <c r="C76" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A77" s="9" t="s">
+    <row r="77" ht="17.25" customHeight="1">
+      <c r="A77" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="B77" s="9" t="s">
+      <c r="B77" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="C77" s="9" t="s">
+      <c r="C77" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A78" s="9" t="s">
+    <row r="78" ht="17.25" customHeight="1">
+      <c r="A78" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="B78" s="9" t="s">
+      <c r="B78" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="C78" s="9" t="s">
+      <c r="C78" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A79" s="9" t="s">
+    <row r="79" ht="17.25" customHeight="1">
+      <c r="A79" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="B79" s="9" t="s">
+      <c r="B79" s="13" t="s">
         <v>159</v>
       </c>
-      <c r="C79" s="9" t="s">
+      <c r="C79" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A80" s="9" t="s">
+    <row r="80" ht="17.25" customHeight="1">
+      <c r="A80" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="B80" s="9" t="s">
+      <c r="B80" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="C80" s="9" t="s">
+      <c r="C80" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A81" s="9" t="s">
+    <row r="81" ht="17.25" customHeight="1">
+      <c r="A81" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="B81" s="9" t="s">
+      <c r="B81" s="13" t="s">
         <v>163</v>
       </c>
-      <c r="C81" s="9"/>
-    </row>
-    <row r="82" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A82" s="9" t="s">
+      <c r="C81" s="14"/>
+    </row>
+    <row r="82" ht="17.25" customHeight="1">
+      <c r="A82" s="13" t="s">
         <v>164</v>
       </c>
-      <c r="B82" s="9" t="s">
+      <c r="B82" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="C82" s="9"/>
-    </row>
-    <row r="83" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A83" s="9" t="s">
+      <c r="C82" s="14"/>
+    </row>
+    <row r="83" ht="17.25" customHeight="1">
+      <c r="A83" s="13" t="s">
         <v>166</v>
       </c>
-      <c r="B83" s="9" t="s">
+      <c r="B83" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="C83" s="9"/>
-    </row>
-    <row r="84" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A84" s="9" t="s">
+      <c r="C83" s="14"/>
+    </row>
+    <row r="84" ht="17.25" customHeight="1">
+      <c r="A84" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="B84" s="9" t="s">
+      <c r="B84" s="13" t="s">
         <v>169</v>
       </c>
-      <c r="C84" s="9"/>
-    </row>
-    <row r="85" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A85" s="9" t="s">
+      <c r="C84" s="14"/>
+    </row>
+    <row r="85" ht="17.25" customHeight="1">
+      <c r="A85" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="B85" s="9" t="s">
+      <c r="B85" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="C85" s="9"/>
-    </row>
-    <row r="86" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A86" s="9" t="s">
+      <c r="C85" s="14"/>
+    </row>
+    <row r="86" ht="17.25" customHeight="1">
+      <c r="A86" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="B86" s="9" t="s">
+      <c r="B86" s="13" t="s">
         <v>173</v>
       </c>
-      <c r="C86" s="9"/>
-    </row>
-    <row r="87" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A87" s="9" t="s">
+      <c r="C86" s="14"/>
+    </row>
+    <row r="87" ht="17.25" customHeight="1">
+      <c r="A87" s="13" t="s">
         <v>174</v>
       </c>
-      <c r="B87" s="9" t="s">
+      <c r="B87" s="13" t="s">
         <v>175</v>
       </c>
-      <c r="C87" s="9"/>
-    </row>
-    <row r="88" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A88" s="9" t="s">
+      <c r="C87" s="14"/>
+    </row>
+    <row r="88" ht="17.25" customHeight="1">
+      <c r="A88" s="13" t="s">
         <v>176</v>
       </c>
-      <c r="B88" s="9" t="s">
+      <c r="B88" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="C88" s="9"/>
-    </row>
-    <row r="89" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A89" s="9" t="s">
+      <c r="C88" s="14"/>
+    </row>
+    <row r="89" ht="17.25" customHeight="1">
+      <c r="A89" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="B89" s="9" t="s">
+      <c r="B89" s="13" t="s">
         <v>179</v>
       </c>
-      <c r="C89" s="9"/>
-    </row>
-    <row r="90" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A90" s="1" t="s">
+      <c r="C89" s="14"/>
+    </row>
+    <row r="90" ht="17.25" customHeight="1">
+      <c r="A90" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="B90" s="10" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A91" s="1" t="s">
+    <row r="91" ht="17.25" customHeight="1">
+      <c r="A91" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="B91" s="10" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A92" s="1" t="s">
+    <row r="92" ht="17.25" customHeight="1">
+      <c r="A92" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="B92" s="10" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A93" s="1" t="s">
+    <row r="93" ht="17.25" customHeight="1">
+      <c r="A93" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="B93" s="10" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A94" s="9" t="s">
+    <row r="94" ht="17.25" customHeight="1">
+      <c r="A94" s="13" t="s">
         <v>188</v>
       </c>
-      <c r="B94" s="9" t="s">
+      <c r="B94" s="13" t="s">
         <v>189</v>
       </c>
-      <c r="C94" s="9"/>
-    </row>
-    <row r="95" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A95" s="9" t="s">
+      <c r="C94" s="14"/>
+    </row>
+    <row r="95" ht="17.25" customHeight="1">
+      <c r="A95" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="B95" s="10" t="s">
+      <c r="B95" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="C95" s="9" t="s">
+      <c r="C95" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A96" s="9" t="s">
+    <row r="96" ht="17.25" customHeight="1">
+      <c r="A96" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="B96" s="10" t="s">
+      <c r="B96" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="C96" s="9"/>
-    </row>
-    <row r="97" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A97" s="9" t="s">
+      <c r="C96" s="14"/>
+    </row>
+    <row r="97" ht="17.25" customHeight="1">
+      <c r="A97" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="B97" s="10" t="s">
+      <c r="B97" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="C97" s="9"/>
-    </row>
-    <row r="98" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A98" s="9" t="s">
+      <c r="C97" s="14"/>
+    </row>
+    <row r="98" ht="17.25" customHeight="1">
+      <c r="A98" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="B98" s="10" t="s">
+      <c r="B98" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="C98" s="9"/>
-    </row>
-    <row r="99" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A99" s="9" t="s">
+      <c r="C98" s="14"/>
+    </row>
+    <row r="99" ht="17.25" customHeight="1">
+      <c r="A99" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="B99" s="10" t="s">
+      <c r="B99" s="15" t="s">
         <v>199</v>
       </c>
-      <c r="C99" s="9"/>
-    </row>
-    <row r="100" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A100" s="1" t="s">
+      <c r="C99" s="14"/>
+    </row>
+    <row r="100" ht="17.25" customHeight="1">
+      <c r="A100" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="B100" s="1" t="s">
+      <c r="B100" s="10" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A101" s="1" t="s">
+    <row r="101" ht="17.25" customHeight="1">
+      <c r="A101" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="B101" s="1" t="s">
+      <c r="B101" s="10" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A102" s="1" t="s">
+    <row r="102" ht="17.25" customHeight="1">
+      <c r="A102" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="B102" s="10" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A103" s="1" t="s">
+    <row r="103" ht="17.25" customHeight="1">
+      <c r="A103" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="B103" s="10" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A104" s="1" t="s">
+    <row r="104" ht="17.25" customHeight="1">
+      <c r="A104" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="B104" s="1" t="s">
+      <c r="B104" s="10" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A105" s="1" t="s">
+    <row r="105" ht="17.25" customHeight="1">
+      <c r="A105" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="B105" s="1" t="s">
+      <c r="B105" s="10" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A106" s="1" t="s">
+    <row r="106" ht="17.25" customHeight="1">
+      <c r="A106" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="B106" s="1" t="s">
+      <c r="B106" s="10" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A107" s="1" t="s">
+    <row r="107" ht="17.25" customHeight="1">
+      <c r="A107" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="B107" s="5" t="s">
+      <c r="B107" s="16" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A108" s="11" t="s">
+    <row r="108" ht="17.25" customHeight="1">
+      <c r="A108" s="17" t="s">
         <v>216</v>
       </c>
-      <c r="B108" s="11" t="s">
+      <c r="B108" s="18" t="s">
         <v>217</v>
       </c>
-      <c r="C108" s="9" t="s">
+      <c r="C108" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A109" s="11" t="s">
+    <row r="109" ht="17.25" customHeight="1">
+      <c r="A109" s="17" t="s">
         <v>218</v>
       </c>
-      <c r="B109" s="11" t="s">
+      <c r="B109" s="17" t="s">
         <v>219</v>
       </c>
-      <c r="C109" s="9" t="s">
+      <c r="C109" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A110" s="11" t="s">
+    <row r="110" ht="17.25" customHeight="1">
+      <c r="A110" s="17" t="s">
         <v>220</v>
       </c>
-      <c r="B110" s="11" t="s">
+      <c r="B110" s="18" t="s">
         <v>221</v>
       </c>
-      <c r="C110" s="9" t="s">
+      <c r="C110" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A111" s="11" t="s">
+    <row r="111" ht="17.25" customHeight="1">
+      <c r="A111" s="17" t="s">
         <v>222</v>
       </c>
-      <c r="B111" s="11" t="s">
+      <c r="B111" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="C111" s="9" t="s">
+      <c r="C111" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A112" s="11" t="s">
+    <row r="112" ht="17.25" customHeight="1">
+      <c r="A112" s="17" t="s">
         <v>224</v>
       </c>
-      <c r="B112" s="11" t="s">
+      <c r="B112" s="18" t="s">
         <v>225</v>
       </c>
-      <c r="C112" s="9" t="s">
+      <c r="C112" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A113" s="11" t="s">
+    <row r="113" ht="17.25" customHeight="1">
+      <c r="A113" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="B113" s="11" t="s">
+      <c r="B113" s="18" t="s">
         <v>227</v>
       </c>
-      <c r="C113" s="9" t="s">
+      <c r="C113" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A114" s="11" t="s">
+    <row r="114" ht="17.25" customHeight="1">
+      <c r="A114" s="17" t="s">
         <v>228</v>
       </c>
-      <c r="B114" s="11" t="s">
+      <c r="B114" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="C114" s="9" t="s">
+      <c r="C114" s="13" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A115" s="1" t="s">
+    <row r="115" ht="17.25" customHeight="1">
+      <c r="A115" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="B115" s="5" t="s">
+      <c r="B115" s="16" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A116" s="11" t="s">
+    <row r="116" ht="17.25" customHeight="1">
+      <c r="A116" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="B116" s="11" t="s">
+      <c r="B116" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="C116" s="9" t="s">
+    </row>
+    <row r="117" ht="17.25" customHeight="1">
+      <c r="A117" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="B117" s="10" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="118" ht="17.25" customHeight="1">
+      <c r="A118" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="B118" s="10" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="119" ht="17.25" customHeight="1">
+      <c r="A119" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="B119" s="10" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="120" ht="17.25" customHeight="1">
+      <c r="A120" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="B120" s="10" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="121" ht="17.25" customHeight="1">
+      <c r="A121" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="B121" s="10" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="122" ht="17.25" customHeight="1">
+      <c r="A122" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="B122" s="10" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="123" ht="17.25" customHeight="1">
+      <c r="A123" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="B123" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="C123" s="14"/>
+    </row>
+    <row r="124" ht="17.25" customHeight="1">
+      <c r="A124" s="13" t="s">
+        <v>248</v>
+      </c>
+      <c r="B124" s="13" t="s">
+        <v>249</v>
+      </c>
+      <c r="C124" s="14"/>
+    </row>
+    <row r="125" ht="17.25" customHeight="1">
+      <c r="A125" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="B125" s="10" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="126" ht="17.25" customHeight="1">
+      <c r="A126" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="B126" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="C126" s="10" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A117" s="11" t="s">
-        <v>234</v>
-      </c>
-      <c r="B117" s="11" t="s">
-        <v>235</v>
-      </c>
-      <c r="C117" s="9" t="s">
+    <row r="127" ht="17.25" customHeight="1">
+      <c r="A127" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="B127" s="16" t="s">
+        <v>255</v>
+      </c>
+      <c r="C127" s="10" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A118" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A119" s="1" t="s">
-        <v>238</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A120" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="B120" s="1" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A121" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="B121" s="1" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A122" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="B122" s="1" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A123" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="B123" s="1" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" ht="16.2" customHeight="1">
-      <c r="A124" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A125" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="B125" s="9" t="s">
-        <v>251</v>
-      </c>
-      <c r="C125" s="9"/>
-    </row>
-    <row r="126" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A126" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="B126" s="9" t="s">
-        <v>253</v>
-      </c>
-      <c r="C126" s="9"/>
-    </row>
-    <row r="127" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A127" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="B127" s="1" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A128" s="1" t="s">
+    <row r="128" ht="17.25" customHeight="1">
+      <c r="A128" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="B128" s="1" t="s">
+      <c r="B128" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="C128" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="129" spans="1:3" ht="17.25" customHeight="1">
-      <c r="A129" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="B129" s="12" t="s">
-        <v>259</v>
-      </c>
-      <c r="C129" s="13" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="130" spans="1:3" ht="17.25" customHeight="1"/>
-    <row r="131" spans="1:3" ht="17.25" customHeight="1"/>
-    <row r="132" spans="1:3" ht="17.25" customHeight="1"/>
-    <row r="133" spans="1:3" ht="17.25" customHeight="1"/>
-    <row r="134" spans="1:3" ht="17.25" customHeight="1"/>
-    <row r="135" spans="1:3" ht="17.25" customHeight="1"/>
-    <row r="136" spans="1:3" ht="17.25" customHeight="1"/>
-    <row r="137" spans="1:3" ht="17.25" customHeight="1"/>
-    <row r="138" spans="1:3" ht="17.25" customHeight="1"/>
-    <row r="139" spans="1:3" ht="17.25" customHeight="1"/>
-    <row r="140" spans="1:3" ht="17.25" customHeight="1"/>
-    <row r="141" spans="1:3" ht="17.25" customHeight="1"/>
-    <row r="142" spans="1:3" ht="17.25" customHeight="1"/>
-    <row r="143" spans="1:3" ht="17.25" customHeight="1"/>
-    <row r="144" spans="1:3" ht="17.25" customHeight="1"/>
+    </row>
+    <row r="129" ht="17.25" customHeight="1"/>
+    <row r="130" ht="17.25" customHeight="1"/>
+    <row r="131" ht="17.25" customHeight="1"/>
+    <row r="132" ht="17.25" customHeight="1"/>
+    <row r="133" ht="17.25" customHeight="1"/>
+    <row r="134" ht="17.25" customHeight="1"/>
+    <row r="135" ht="17.25" customHeight="1"/>
+    <row r="136" ht="17.25" customHeight="1"/>
+    <row r="137" ht="17.25" customHeight="1"/>
+    <row r="138" ht="17.25" customHeight="1"/>
+    <row r="139" ht="17.25" customHeight="1"/>
+    <row r="140" ht="17.25" customHeight="1"/>
+    <row r="141" ht="17.25" customHeight="1"/>
+    <row r="142" ht="17.25" customHeight="1"/>
+    <row r="143" ht="17.25" customHeight="1"/>
+    <row r="144" ht="17.25" customHeight="1"/>
     <row r="145" ht="17.25" customHeight="1"/>
     <row r="146" ht="17.25" customHeight="1"/>
     <row r="147" ht="17.25" customHeight="1"/>
@@ -3165,11 +3131,10 @@
     <row r="994" ht="17.25" customHeight="1"/>
     <row r="995" ht="17.25" customHeight="1"/>
     <row r="996" ht="17.25" customHeight="1"/>
-    <row r="997" ht="17.25" customHeight="1"/>
-    <row r="998" ht="17.25" customHeight="1"/>
   </sheetData>
-  <phoneticPr fontId="9" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>